--- a/Översikt ÄNGELHOLM.xlsx
+++ b/Översikt ÄNGELHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45099</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         <v>45931</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
         <v>45931</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>46106</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>44802</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 74502-2021</t>
+          <t>A 32268-2022</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1204,10 +1204,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44560</v>
+        <v>44781</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1220,17 +1220,17 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>5.6</v>
+        <v>8.6</v>
       </c>
       <c r="J7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K7" t="n">
+        <v>5</v>
+      </c>
+      <c r="L7" t="n">
         <v>1</v>
       </c>
-      <c r="L7" t="n">
-        <v>3</v>
-      </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
@@ -1244,7 +1244,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1253,12 +1253,124 @@
         <v>8</v>
       </c>
       <c r="T7" t="n">
+        <v>14</v>
+      </c>
+      <c r="U7" t="n">
+        <v>14</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Bokvårtlav
+Blåmossa
+Dvärghäxört
+Skuggsprötmossa
+Trubbfjädermossa
+Västlig hakmossa
+Vanlig groda
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 32268-2022 artfynd.xlsx", "A 32268-2022")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 32268-2022 karta.png", "A 32268-2022")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 32268-2022 georefererad karta.tif", "A 32268-2022")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 32268-2022 FSC-klagomål.docx", "A 32268-2022")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 32268-2022 FSC-klagomål mail.docx", "A 32268-2022")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 32268-2022 tillsynsbegäran.docx", "A 32268-2022")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 32268-2022 tillsynsbegäran mail.docx", "A 32268-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 74502-2021</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>44560</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J8" t="n">
+        <v>6</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>3</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>8</v>
+      </c>
+      <c r="T8" t="n">
         <v>9</v>
       </c>
-      <c r="U7" t="n">
+      <c r="U8" t="n">
         <v>9</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Entita
 Grönsångare
@@ -1270,148 +1382,36 @@
 Skogsduva</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 74502-2021 artfynd.xlsx", "A 74502-2021")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 74502-2021 karta.png", "A 74502-2021")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 74502-2021 georefererad karta.tif", "A 74502-2021")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 74502-2021 FSC-klagomål.docx", "A 74502-2021")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 74502-2021 FSC-klagomål mail.docx", "A 74502-2021")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 74502-2021 tillsynsbegäran.docx", "A 74502-2021")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 74502-2021 tillsynsbegäran mail.docx", "A 74502-2021")</f>
         <v/>
       </c>
-      <c r="AE7">
+      <c r="AE8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 74502-2021 prioriterade fågelarter.docx", "A 74502-2021")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 32268-2022</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>44781</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="J8" t="n">
-        <v>2</v>
-      </c>
-      <c r="K8" t="n">
-        <v>5</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>8</v>
-      </c>
-      <c r="T8" t="n">
-        <v>14</v>
-      </c>
-      <c r="U8" t="n">
-        <v>14</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Bokvårtlav
-Blåmossa
-Dvärghäxört
-Skuggsprötmossa
-Trubbfjädermossa
-Västlig hakmossa
-Vanlig groda
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 32268-2022 artfynd.xlsx", "A 32268-2022")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 32268-2022 karta.png", "A 32268-2022")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 32268-2022 georefererad karta.tif", "A 32268-2022")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 32268-2022 FSC-klagomål.docx", "A 32268-2022")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 32268-2022 FSC-klagomål mail.docx", "A 32268-2022")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 32268-2022 tillsynsbegäran.docx", "A 32268-2022")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 32268-2022 tillsynsbegäran mail.docx", "A 32268-2022")</f>
         <v/>
       </c>
     </row>
@@ -1435,7 +1435,7 @@
         <v>45835</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 308-2023</t>
+          <t>A 5046-2022</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1547,10 +1547,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44929</v>
+        <v>44593</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1563,19 +1563,19 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.8</v>
+        <v>3</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K10" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1587,10 +1587,10 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" t="n">
         <v>1</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>6</v>
@@ -1599,9 +1599,123 @@
         <v>7</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Grönfink
+Gulsparv
+Kråka
+Kungsfågel
+Sävsparv
+Trädlärka</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 5046-2022 artfynd.xlsx", "A 5046-2022")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 5046-2022 karta.png", "A 5046-2022")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 5046-2022 georefererad karta.tif", "A 5046-2022")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 5046-2022 FSC-klagomål.docx", "A 5046-2022")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 5046-2022 FSC-klagomål mail.docx", "A 5046-2022")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 5046-2022 tillsynsbegäran.docx", "A 5046-2022")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 5046-2022 tillsynsbegäran mail.docx", "A 5046-2022")</f>
+        <v/>
+      </c>
+      <c r="AE10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 5046-2022 prioriterade fågelarter.docx", "A 5046-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 308-2023</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>44929</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>5</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>6</v>
+      </c>
+      <c r="T11" t="n">
+        <v>7</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Bokvårtlav
 Dvärghäxört
@@ -1611,146 +1725,32 @@
 Stor knopplav</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 308-2023 artfynd.xlsx", "A 308-2023")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 308-2023 karta.png", "A 308-2023")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 308-2023 georefererad karta.tif", "A 308-2023")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 308-2023 FSC-klagomål.docx", "A 308-2023")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 308-2023 FSC-klagomål mail.docx", "A 308-2023")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 308-2023 tillsynsbegäran.docx", "A 308-2023")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 308-2023 tillsynsbegäran mail.docx", "A 308-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 5046-2022</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>44593</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>3</v>
-      </c>
-      <c r="J11" t="n">
-        <v>6</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
-      <c r="S11" t="n">
-        <v>6</v>
-      </c>
-      <c r="T11" t="n">
-        <v>7</v>
-      </c>
-      <c r="U11" t="n">
-        <v>6</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Grönfink
-Gulsparv
-Kråka
-Kungsfågel
-Sävsparv
-Trädlärka</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 5046-2022 artfynd.xlsx", "A 5046-2022")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 5046-2022 karta.png", "A 5046-2022")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 5046-2022 georefererad karta.tif", "A 5046-2022")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 5046-2022 FSC-klagomål.docx", "A 5046-2022")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 5046-2022 FSC-klagomål mail.docx", "A 5046-2022")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 5046-2022 tillsynsbegäran.docx", "A 5046-2022")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 5046-2022 tillsynsbegäran mail.docx", "A 5046-2022")</f>
-        <v/>
-      </c>
-      <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 5046-2022 prioriterade fågelarter.docx", "A 5046-2022")</f>
         <v/>
       </c>
     </row>
@@ -1774,7 +1774,7 @@
         <v>45106</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>45245</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>46038</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>46265</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>45664</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>44864</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2427,7 +2427,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 28874-2023</t>
+          <t>A 905-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45104</v>
+        <v>45301</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2457,616 +2457,616 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>9</v>
+        <v>4.9</v>
       </c>
       <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
         <v>1</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
         <v>2</v>
       </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S18" t="n">
         <v>3</v>
       </c>
       <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Igelkott
+Desmeknopp
+Myskmadra</t>
+        </is>
+      </c>
+      <c r="W18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 905-2024 artfynd.xlsx", "A 905-2024")</f>
+        <v/>
+      </c>
+      <c r="X18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 905-2024 karta.png", "A 905-2024")</f>
+        <v/>
+      </c>
+      <c r="Y18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 905-2024 georefererad karta.tif", "A 905-2024")</f>
+        <v/>
+      </c>
+      <c r="AA18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 905-2024 FSC-klagomål.docx", "A 905-2024")</f>
+        <v/>
+      </c>
+      <c r="AB18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 905-2024 FSC-klagomål mail.docx", "A 905-2024")</f>
+        <v/>
+      </c>
+      <c r="AC18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 905-2024 tillsynsbegäran.docx", "A 905-2024")</f>
+        <v/>
+      </c>
+      <c r="AD18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 905-2024 tillsynsbegäran mail.docx", "A 905-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 28874-2023</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>45104</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>9</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3</v>
+      </c>
+      <c r="T19" t="n">
         <v>5</v>
       </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Blåmossa
 Stubbspretmossa
 Revlummer</t>
         </is>
       </c>
-      <c r="W18">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 28874-2023 artfynd.xlsx", "A 28874-2023")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 28874-2023 karta.png", "A 28874-2023")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 28874-2023 georefererad karta.tif", "A 28874-2023")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 28874-2023 FSC-klagomål.docx", "A 28874-2023")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 28874-2023 FSC-klagomål mail.docx", "A 28874-2023")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 28874-2023 tillsynsbegäran.docx", "A 28874-2023")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 28874-2023 tillsynsbegäran mail.docx", "A 28874-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 8065-2025</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>45707</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>3</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Småvänderot
+Gullpudra
+Svinrot</t>
+        </is>
+      </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 8065-2025 artfynd.xlsx", "A 8065-2025")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 8065-2025 karta.png", "A 8065-2025")</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 8065-2025 georefererad karta.tif", "A 8065-2025")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 8065-2025 FSC-klagomål.docx", "A 8065-2025")</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 8065-2025 FSC-klagomål mail.docx", "A 8065-2025")</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 8065-2025 tillsynsbegäran.docx", "A 8065-2025")</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 8065-2025 tillsynsbegäran mail.docx", "A 8065-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 3317-2026</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>46041</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3</v>
+      </c>
+      <c r="T21" t="n">
+        <v>6</v>
+      </c>
+      <c r="U21" t="n">
+        <v>6</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Entita
+Mindre hackspett
+Gröngöling</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 3317-2026 artfynd.xlsx", "A 3317-2026")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 3317-2026 karta.png", "A 3317-2026")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 3317-2026 georefererad karta.tif", "A 3317-2026")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 3317-2026 FSC-klagomål.docx", "A 3317-2026")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 3317-2026 FSC-klagomål mail.docx", "A 3317-2026")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 3317-2026 tillsynsbegäran.docx", "A 3317-2026")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 3317-2026 tillsynsbegäran mail.docx", "A 3317-2026")</f>
+        <v/>
+      </c>
+      <c r="AE21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 3317-2026 prioriterade fågelarter.docx", "A 3317-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 50684-2023</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>45210</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>1</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>Skogsalm
+Kopparödla
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 50684-2023 artfynd.xlsx", "A 50684-2023")</f>
+        <v/>
+      </c>
+      <c r="X22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 50684-2023 karta.png", "A 50684-2023")</f>
+        <v/>
+      </c>
+      <c r="Y22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 50684-2023 georefererad karta.tif", "A 50684-2023")</f>
+        <v/>
+      </c>
+      <c r="AA22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 50684-2023 FSC-klagomål.docx", "A 50684-2023")</f>
+        <v/>
+      </c>
+      <c r="AB22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 50684-2023 FSC-klagomål mail.docx", "A 50684-2023")</f>
+        <v/>
+      </c>
+      <c r="AC22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 50684-2023 tillsynsbegäran.docx", "A 50684-2023")</f>
+        <v/>
+      </c>
+      <c r="AD22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 50684-2023 tillsynsbegäran mail.docx", "A 50684-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
         <is>
           <t>A 31907-2023</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
         <v>45118</v>
       </c>
-      <c r="E19" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
+      <c r="E23" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
         <v>5.3</v>
       </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
         <v>2</v>
       </c>
-      <c r="L19" t="n">
+      <c r="L23" t="n">
         <v>1</v>
       </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
         <v>1</v>
       </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
         <v>3</v>
       </c>
-      <c r="T19" t="n">
+      <c r="T23" t="n">
         <v>3</v>
       </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>Bokvårtlav
 Platt fjädermossa
 Stubbspretmossa</t>
         </is>
       </c>
-      <c r="W19">
+      <c r="W23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 31907-2023 artfynd.xlsx", "A 31907-2023")</f>
         <v/>
       </c>
-      <c r="X19">
+      <c r="X23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 31907-2023 karta.png", "A 31907-2023")</f>
         <v/>
       </c>
-      <c r="Y19">
+      <c r="Y23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 31907-2023 georefererad karta.tif", "A 31907-2023")</f>
         <v/>
       </c>
-      <c r="AA19">
+      <c r="AA23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 31907-2023 FSC-klagomål.docx", "A 31907-2023")</f>
         <v/>
       </c>
-      <c r="AB19">
+      <c r="AB23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 31907-2023 FSC-klagomål mail.docx", "A 31907-2023")</f>
         <v/>
       </c>
-      <c r="AC19">
+      <c r="AC23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 31907-2023 tillsynsbegäran.docx", "A 31907-2023")</f>
         <v/>
       </c>
-      <c r="AD19">
+      <c r="AD23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 31907-2023 tillsynsbegäran mail.docx", "A 31907-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 50684-2023</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>45210</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J20" t="n">
-        <v>2</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>1</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Skogsalm
-Kopparödla
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 50684-2023 artfynd.xlsx", "A 50684-2023")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 50684-2023 karta.png", "A 50684-2023")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 50684-2023 georefererad karta.tif", "A 50684-2023")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 50684-2023 FSC-klagomål.docx", "A 50684-2023")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 50684-2023 FSC-klagomål mail.docx", "A 50684-2023")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 50684-2023 tillsynsbegäran.docx", "A 50684-2023")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 50684-2023 tillsynsbegäran mail.docx", "A 50684-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 8065-2025</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>45707</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>2</v>
-      </c>
-      <c r="M21" t="n">
-        <v>1</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>3</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3</v>
-      </c>
-      <c r="T21" t="n">
-        <v>3</v>
-      </c>
-      <c r="U21" t="n">
-        <v>2</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Småvänderot
-Gullpudra
-Svinrot</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 8065-2025 artfynd.xlsx", "A 8065-2025")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 8065-2025 karta.png", "A 8065-2025")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 8065-2025 georefererad karta.tif", "A 8065-2025")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 8065-2025 FSC-klagomål.docx", "A 8065-2025")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 8065-2025 FSC-klagomål mail.docx", "A 8065-2025")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 8065-2025 tillsynsbegäran.docx", "A 8065-2025")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 8065-2025 tillsynsbegäran mail.docx", "A 8065-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 905-2024</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>45301</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>1</v>
-      </c>
-      <c r="L22" t="n">
-        <v>1</v>
-      </c>
-      <c r="M22" t="n">
-        <v>1</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>2</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3</v>
-      </c>
-      <c r="T22" t="n">
-        <v>3</v>
-      </c>
-      <c r="U22" t="n">
-        <v>2</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Igelkott
-Desmeknopp
-Myskmadra</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 905-2024 artfynd.xlsx", "A 905-2024")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 905-2024 karta.png", "A 905-2024")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 905-2024 georefererad karta.tif", "A 905-2024")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 905-2024 FSC-klagomål.docx", "A 905-2024")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 905-2024 FSC-klagomål mail.docx", "A 905-2024")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 905-2024 tillsynsbegäran.docx", "A 905-2024")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 905-2024 tillsynsbegäran mail.docx", "A 905-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>A 3317-2026</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>46041</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J23" t="n">
-        <v>3</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>2</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>2</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3</v>
-      </c>
-      <c r="T23" t="n">
-        <v>6</v>
-      </c>
-      <c r="U23" t="n">
-        <v>6</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>Entita
-Mindre hackspett
-Gröngöling</t>
-        </is>
-      </c>
-      <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 3317-2026 artfynd.xlsx", "A 3317-2026")</f>
-        <v/>
-      </c>
-      <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 3317-2026 karta.png", "A 3317-2026")</f>
-        <v/>
-      </c>
-      <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 3317-2026 georefererad karta.tif", "A 3317-2026")</f>
-        <v/>
-      </c>
-      <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 3317-2026 FSC-klagomål.docx", "A 3317-2026")</f>
-        <v/>
-      </c>
-      <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 3317-2026 FSC-klagomål mail.docx", "A 3317-2026")</f>
-        <v/>
-      </c>
-      <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 3317-2026 tillsynsbegäran.docx", "A 3317-2026")</f>
-        <v/>
-      </c>
-      <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 3317-2026 tillsynsbegäran mail.docx", "A 3317-2026")</f>
-        <v/>
-      </c>
-      <c r="AE23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 3317-2026 prioriterade fågelarter.docx", "A 3317-2026")</f>
         <v/>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
         <v>45763</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3201,7 +3201,7 @@
         <v>45474</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>45841</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         <v>45105</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3531,7 +3531,7 @@
         <v>44553</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3641,7 +3641,7 @@
         <v>45359</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         <v>45582</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         <v>44839</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>44742</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         <v>44746</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 12150-2024</t>
+          <t>A 44062-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4173,10 +4173,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45377</v>
+        <v>44839</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4189,19 +4189,19 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
@@ -4213,10 +4213,10 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4229,42 +4229,42 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 12150-2024 artfynd.xlsx", "A 12150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 44062-2022 artfynd.xlsx", "A 44062-2022")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 12150-2024 karta.png", "A 12150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 44062-2022 karta.png", "A 44062-2022")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 12150-2024 georefererad karta.tif", "A 12150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 44062-2022 georefererad karta.tif", "A 44062-2022")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 12150-2024 FSC-klagomål.docx", "A 12150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 44062-2022 FSC-klagomål.docx", "A 44062-2022")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 12150-2024 FSC-klagomål mail.docx", "A 12150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 44062-2022 FSC-klagomål mail.docx", "A 44062-2022")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 12150-2024 tillsynsbegäran.docx", "A 12150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 44062-2022 tillsynsbegäran.docx", "A 44062-2022")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 12150-2024 tillsynsbegäran mail.docx", "A 12150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 44062-2022 tillsynsbegäran mail.docx", "A 44062-2022")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 4088-2024</t>
+          <t>A 46487-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4278,10 +4278,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45323</v>
+        <v>45582</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4294,16 +4294,16 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3.8</v>
+        <v>5.8</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
@@ -4318,7 +4318,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -4330,46 +4330,46 @@
         <v>1</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Flikbålmossa</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 4088-2024 artfynd.xlsx", "A 4088-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 46487-2024 artfynd.xlsx", "A 46487-2024")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 4088-2024 karta.png", "A 4088-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 46487-2024 karta.png", "A 46487-2024")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 4088-2024 georefererad karta.tif", "A 4088-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 46487-2024 georefererad karta.tif", "A 46487-2024")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 4088-2024 FSC-klagomål.docx", "A 4088-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 46487-2024 FSC-klagomål.docx", "A 46487-2024")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 4088-2024 FSC-klagomål mail.docx", "A 4088-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 46487-2024 FSC-klagomål mail.docx", "A 46487-2024")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 4088-2024 tillsynsbegäran.docx", "A 4088-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 46487-2024 tillsynsbegäran.docx", "A 46487-2024")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 4088-2024 tillsynsbegäran mail.docx", "A 4088-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 46487-2024 tillsynsbegäran mail.docx", "A 46487-2024")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 50642-2023</t>
+          <t>A 4088-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4383,10 +4383,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45210</v>
+        <v>45323</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4399,17 +4399,17 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.8</v>
+        <v>3.8</v>
       </c>
       <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
         <v>1</v>
       </c>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
       <c r="M36" t="n">
         <v>0</v>
       </c>
@@ -4423,7 +4423,7 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -4439,35 +4439,35 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Flikbålmossa</t>
         </is>
       </c>
       <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 50642-2023 artfynd.xlsx", "A 50642-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 4088-2024 artfynd.xlsx", "A 4088-2024")</f>
         <v/>
       </c>
       <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 50642-2023 karta.png", "A 50642-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 4088-2024 karta.png", "A 4088-2024")</f>
         <v/>
       </c>
       <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 50642-2023 georefererad karta.tif", "A 50642-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 4088-2024 georefererad karta.tif", "A 4088-2024")</f>
         <v/>
       </c>
       <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 50642-2023 FSC-klagomål.docx", "A 50642-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 4088-2024 FSC-klagomål.docx", "A 4088-2024")</f>
         <v/>
       </c>
       <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 50642-2023 FSC-klagomål mail.docx", "A 50642-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 4088-2024 FSC-klagomål mail.docx", "A 4088-2024")</f>
         <v/>
       </c>
       <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 50642-2023 tillsynsbegäran.docx", "A 50642-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 4088-2024 tillsynsbegäran.docx", "A 4088-2024")</f>
         <v/>
       </c>
       <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 50642-2023 tillsynsbegäran mail.docx", "A 50642-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 4088-2024 tillsynsbegäran mail.docx", "A 4088-2024")</f>
         <v/>
       </c>
     </row>
@@ -4491,7 +4491,7 @@
         <v>45462</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4579,7 +4579,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 61094-2021</t>
+          <t>A 27094-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4593,10 +4593,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44498</v>
+        <v>46188</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4609,7 +4609,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4645,46 +4645,46 @@
         <v>1</v>
       </c>
       <c r="U38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 61094-2021 artfynd.xlsx", "A 61094-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 27094-2026 artfynd.xlsx", "A 27094-2026")</f>
         <v/>
       </c>
       <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 61094-2021 karta.png", "A 61094-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 27094-2026 karta.png", "A 27094-2026")</f>
         <v/>
       </c>
       <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 61094-2021 georefererad karta.tif", "A 61094-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 27094-2026 georefererad karta.tif", "A 27094-2026")</f>
         <v/>
       </c>
       <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 61094-2021 FSC-klagomål.docx", "A 61094-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 27094-2026 FSC-klagomål.docx", "A 27094-2026")</f>
         <v/>
       </c>
       <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 61094-2021 FSC-klagomål mail.docx", "A 61094-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 27094-2026 FSC-klagomål mail.docx", "A 27094-2026")</f>
         <v/>
       </c>
       <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 61094-2021 tillsynsbegäran.docx", "A 61094-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 27094-2026 tillsynsbegäran.docx", "A 27094-2026")</f>
         <v/>
       </c>
       <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 61094-2021 tillsynsbegäran mail.docx", "A 61094-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 27094-2026 tillsynsbegäran mail.docx", "A 27094-2026")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 44062-2022</t>
+          <t>A 12150-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4698,10 +4698,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44839</v>
+        <v>45377</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4714,20 +4714,20 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
         <v>1</v>
       </c>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" t="n">
-        <v>0</v>
-      </c>
       <c r="N39" t="n">
         <v>0</v>
       </c>
@@ -4738,10 +4738,10 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -4754,42 +4754,42 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 44062-2022 artfynd.xlsx", "A 44062-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 12150-2024 artfynd.xlsx", "A 12150-2024")</f>
         <v/>
       </c>
       <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 44062-2022 karta.png", "A 44062-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 12150-2024 karta.png", "A 12150-2024")</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 44062-2022 georefererad karta.tif", "A 44062-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 12150-2024 georefererad karta.tif", "A 12150-2024")</f>
         <v/>
       </c>
       <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 44062-2022 FSC-klagomål.docx", "A 44062-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 12150-2024 FSC-klagomål.docx", "A 12150-2024")</f>
         <v/>
       </c>
       <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 44062-2022 FSC-klagomål mail.docx", "A 44062-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 12150-2024 FSC-klagomål mail.docx", "A 12150-2024")</f>
         <v/>
       </c>
       <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 44062-2022 tillsynsbegäran.docx", "A 44062-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 12150-2024 tillsynsbegäran.docx", "A 12150-2024")</f>
         <v/>
       </c>
       <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 44062-2022 tillsynsbegäran mail.docx", "A 44062-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 12150-2024 tillsynsbegäran mail.docx", "A 12150-2024")</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 27094-2026</t>
+          <t>A 31599-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4803,10 +4803,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46188</v>
+        <v>46224</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4819,10 +4819,10 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>6.2</v>
+        <v>1.7</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K40" t="n">
         <v>1</v>
@@ -4852,49 +4852,49 @@
         <v>1</v>
       </c>
       <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
         <v>1</v>
       </c>
-      <c r="U40" t="n">
-        <v>0</v>
-      </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="W40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 27094-2026 artfynd.xlsx", "A 27094-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 31599-2026 artfynd.xlsx", "A 31599-2026")</f>
         <v/>
       </c>
       <c r="X40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 27094-2026 karta.png", "A 27094-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 31599-2026 karta.png", "A 31599-2026")</f>
         <v/>
       </c>
       <c r="Y40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 27094-2026 georefererad karta.tif", "A 27094-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 31599-2026 georefererad karta.tif", "A 31599-2026")</f>
         <v/>
       </c>
       <c r="AA40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 27094-2026 FSC-klagomål.docx", "A 27094-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 31599-2026 FSC-klagomål.docx", "A 31599-2026")</f>
         <v/>
       </c>
       <c r="AB40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 27094-2026 FSC-klagomål mail.docx", "A 27094-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 31599-2026 FSC-klagomål mail.docx", "A 31599-2026")</f>
         <v/>
       </c>
       <c r="AC40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 27094-2026 tillsynsbegäran.docx", "A 27094-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 31599-2026 tillsynsbegäran.docx", "A 31599-2026")</f>
         <v/>
       </c>
       <c r="AD40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 27094-2026 tillsynsbegäran mail.docx", "A 27094-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 31599-2026 tillsynsbegäran mail.docx", "A 31599-2026")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 31599-2026</t>
+          <t>A 61094-2021</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4908,10 +4908,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46224</v>
+        <v>44498</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4924,10 +4924,10 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.7</v>
+        <v>6.4</v>
       </c>
       <c r="J41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
         <v>1</v>
@@ -4957,49 +4957,49 @@
         <v>1</v>
       </c>
       <c r="T41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U41" t="n">
         <v>1</v>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>Ekoxe</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 31599-2026 artfynd.xlsx", "A 31599-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 61094-2021 artfynd.xlsx", "A 61094-2021")</f>
         <v/>
       </c>
       <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 31599-2026 karta.png", "A 31599-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 61094-2021 karta.png", "A 61094-2021")</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 31599-2026 georefererad karta.tif", "A 31599-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 61094-2021 georefererad karta.tif", "A 61094-2021")</f>
         <v/>
       </c>
       <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 31599-2026 FSC-klagomål.docx", "A 31599-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 61094-2021 FSC-klagomål.docx", "A 61094-2021")</f>
         <v/>
       </c>
       <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 31599-2026 FSC-klagomål mail.docx", "A 31599-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 61094-2021 FSC-klagomål mail.docx", "A 61094-2021")</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 31599-2026 tillsynsbegäran.docx", "A 31599-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 61094-2021 tillsynsbegäran.docx", "A 61094-2021")</f>
         <v/>
       </c>
       <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 31599-2026 tillsynsbegäran mail.docx", "A 31599-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 61094-2021 tillsynsbegäran mail.docx", "A 61094-2021")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 46487-2024</t>
+          <t>A 50642-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5013,10 +5013,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45582</v>
+        <v>45210</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5029,7 +5029,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>5.8</v>
+        <v>0.8</v>
       </c>
       <c r="J42" t="n">
         <v>1</v>
@@ -5065,39 +5065,39 @@
         <v>1</v>
       </c>
       <c r="U42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 46487-2024 artfynd.xlsx", "A 46487-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 50642-2023 artfynd.xlsx", "A 50642-2023")</f>
         <v/>
       </c>
       <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 46487-2024 karta.png", "A 46487-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 50642-2023 karta.png", "A 50642-2023")</f>
         <v/>
       </c>
       <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 46487-2024 georefererad karta.tif", "A 46487-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 50642-2023 georefererad karta.tif", "A 50642-2023")</f>
         <v/>
       </c>
       <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 46487-2024 FSC-klagomål.docx", "A 46487-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 50642-2023 FSC-klagomål.docx", "A 50642-2023")</f>
         <v/>
       </c>
       <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 46487-2024 FSC-klagomål mail.docx", "A 46487-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 50642-2023 FSC-klagomål mail.docx", "A 50642-2023")</f>
         <v/>
       </c>
       <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 46487-2024 tillsynsbegäran.docx", "A 46487-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 50642-2023 tillsynsbegäran.docx", "A 50642-2023")</f>
         <v/>
       </c>
       <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 46487-2024 tillsynsbegäran mail.docx", "A 46487-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 50642-2023 tillsynsbegäran mail.docx", "A 50642-2023")</f>
         <v/>
       </c>
     </row>
@@ -5121,7 +5121,7 @@
         <v>45084</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5226,7 +5226,7 @@
         <v>44862</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         <v>44880</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5404,7 +5404,7 @@
         <v>44839</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5477,7 +5477,7 @@
         <v>44725</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5550,7 +5550,7 @@
         <v>44840</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5623,7 +5623,7 @@
         <v>44498</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5696,7 +5696,7 @@
         <v>44477</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5769,7 +5769,7 @@
         <v>44657</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5842,7 +5842,7 @@
         <v>44634</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5915,7 +5915,7 @@
         <v>44802</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5988,7 +5988,7 @@
         <v>44802</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6061,7 +6061,7 @@
         <v>44827</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>44480</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6207,7 +6207,7 @@
         <v>44634</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6263,7 +6263,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 29436-2024</t>
+          <t>A 40275-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6277,10 +6277,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45483</v>
+        <v>45169</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6293,7 +6293,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>4.2</v>
+        <v>0.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6336,7 +6336,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 8882-2025</t>
+          <t>A 6667-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6350,10 +6350,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45713</v>
+        <v>45700</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6366,7 +6366,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6409,7 +6409,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 12148-2024</t>
+          <t>A 46702-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6423,10 +6423,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45377</v>
+        <v>45583</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6439,7 +6439,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6482,7 +6482,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 53501-2022</t>
+          <t>A 31789-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6496,10 +6496,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44879</v>
+        <v>45118</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>7.2</v>
+        <v>1.1</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6555,7 +6555,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 27551-2023</t>
+          <t>A 1644-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6569,10 +6569,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45097</v>
+        <v>45670</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6585,7 +6585,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6628,7 +6628,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 9578-2025</t>
+          <t>A 40287-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6642,10 +6642,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45715</v>
+        <v>45895</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6701,7 +6701,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 64728-2023</t>
+          <t>A 55545-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6715,10 +6715,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45281</v>
+        <v>44887</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.8</v>
+        <v>4.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6774,7 +6774,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 31143-2024</t>
+          <t>A 55529-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6784,14 +6784,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45502</v>
+        <v>45622</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6804,7 +6804,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6847,7 +6847,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 607-2024</t>
+          <t>A 42826-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6861,10 +6861,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45299</v>
+        <v>45908</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6877,7 +6877,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6920,7 +6920,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 54709-2023</t>
+          <t>A 32020-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6934,10 +6934,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45236</v>
+        <v>45835</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6950,7 +6950,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3.6</v>
+        <v>0.7</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6993,7 +6993,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 31720-2023</t>
+          <t>A 13662-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7007,10 +7007,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45117</v>
+        <v>45736</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7023,7 +7023,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.5</v>
+        <v>6.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -7066,7 +7066,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 55544-2022</t>
+          <t>A 64728-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7080,10 +7080,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44887</v>
+        <v>45281</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7156,7 +7156,7 @@
         <v>45463</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7212,7 +7212,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 23976-2024</t>
+          <t>A 23676-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7226,10 +7226,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45456</v>
+        <v>45454</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7242,7 +7242,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7285,7 +7285,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 27553-2023</t>
+          <t>A 9055-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7299,10 +7299,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45097</v>
+        <v>46069</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7315,7 +7315,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7358,7 +7358,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 28253-2023</t>
+          <t>A 8139-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7372,10 +7372,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45099</v>
+        <v>45708</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7431,7 +7431,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 16419-2023</t>
+          <t>A 44448-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7445,10 +7445,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45022</v>
+        <v>45189</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7461,7 +7461,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>4.2</v>
+        <v>0.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7504,7 +7504,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 19503-2022</t>
+          <t>A 31143-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7514,14 +7514,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44693</v>
+        <v>45502</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7534,7 +7534,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>5.1</v>
+        <v>0.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7577,7 +7577,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 9055-2026</t>
+          <t>A 23328-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7591,10 +7591,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46069</v>
+        <v>44720</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7607,7 +7607,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7650,7 +7650,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 32020-2025</t>
+          <t>A 15154-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7664,10 +7664,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45835</v>
+        <v>45016</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7680,7 +7680,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.7</v>
+        <v>3.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7723,7 +7723,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 46702-2024</t>
+          <t>A 46286-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7737,10 +7737,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45583</v>
+        <v>45581</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7753,7 +7753,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7796,7 +7796,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 40287-2025</t>
+          <t>A 55544-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7810,10 +7810,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45895</v>
+        <v>44887</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7826,7 +7826,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7869,7 +7869,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 13662-2025</t>
+          <t>A 52519-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7883,10 +7883,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45736</v>
+        <v>45954</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7899,7 +7899,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>6.4</v>
+        <v>0.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7942,7 +7942,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 42826-2025</t>
+          <t>A 9803-2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7956,10 +7956,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45908</v>
+        <v>46072</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7972,7 +7972,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.1</v>
+        <v>5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -8015,7 +8015,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 49206-2024</t>
+          <t>A 7337-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -8029,10 +8029,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45595</v>
+        <v>45345</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8045,7 +8045,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8088,7 +8088,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 31503-2023</t>
+          <t>A 55728-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8102,10 +8102,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45115</v>
+        <v>45972</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8118,7 +8118,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8161,7 +8161,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 23328-2022</t>
+          <t>A 49610-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8175,10 +8175,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44720</v>
+        <v>45596</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8191,7 +8191,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.1</v>
+        <v>6.4</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8234,7 +8234,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 32364-2023</t>
+          <t>A 7707-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8248,10 +8248,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45120</v>
+        <v>45705</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8264,7 +8264,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8307,7 +8307,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 8139-2025</t>
+          <t>A 19650-2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8321,10 +8321,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45708</v>
+        <v>46134</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8337,7 +8337,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>3.5</v>
+        <v>8</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8380,7 +8380,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 52519-2025</t>
+          <t>A 13243-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8394,10 +8394,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45954</v>
+        <v>45735</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8410,7 +8410,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8453,7 +8453,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 40275-2023</t>
+          <t>A 57725-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8467,10 +8467,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45169</v>
+        <v>45981</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8483,7 +8483,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8526,7 +8526,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 1644-2025</t>
+          <t>A 58134-2022</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8540,10 +8540,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45670</v>
+        <v>44900</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8556,7 +8556,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8599,7 +8599,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 55728-2025</t>
+          <t>A 74214-2021</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8613,10 +8613,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45972</v>
+        <v>44553</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1</v>
+        <v>19.8</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8672,7 +8672,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 9803-2026</t>
+          <t>A 7811-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8686,10 +8686,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46072</v>
+        <v>44973</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8702,7 +8702,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>5</v>
+        <v>0.9</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8745,7 +8745,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 24855-2024</t>
+          <t>A 58137-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8759,10 +8759,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45461</v>
+        <v>44900</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8818,7 +8818,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 57725-2025</t>
+          <t>A 42105-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8832,10 +8832,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45981</v>
+        <v>44830</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8848,7 +8848,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8891,7 +8891,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 7871-2025</t>
+          <t>A 50652-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8905,10 +8905,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45706</v>
+        <v>45210</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8921,7 +8921,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8964,7 +8964,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 13243-2025</t>
+          <t>A 24855-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8978,10 +8978,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45735</v>
+        <v>45461</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8994,7 +8994,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -9037,7 +9037,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 6667-2025</t>
+          <t>A 4755-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -9051,10 +9051,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45700</v>
+        <v>45328</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9067,7 +9067,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9110,7 +9110,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 19650-2026</t>
+          <t>A 14400-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9124,10 +9124,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46134</v>
+        <v>45012</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9140,7 +9140,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>8</v>
+        <v>1.7</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -9183,7 +9183,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 58137-2022</t>
+          <t>A 23227-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9197,10 +9197,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44900</v>
+        <v>45075</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9213,7 +9213,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9256,7 +9256,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 2575-2024</t>
+          <t>A 9578-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9270,10 +9270,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45313</v>
+        <v>45715</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9286,7 +9286,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9329,7 +9329,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 7707-2025</t>
+          <t>A 8882-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9343,10 +9343,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45705</v>
+        <v>45713</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9359,7 +9359,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9402,7 +9402,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 31502-2023</t>
+          <t>A 43857-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9416,10 +9416,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45115</v>
+        <v>45912</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9432,7 +9432,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9475,7 +9475,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 58134-2022</t>
+          <t>A 60227-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9489,10 +9489,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44900</v>
+        <v>45994</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9505,7 +9505,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9548,7 +9548,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 46286-2024</t>
+          <t>A 13278-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9562,10 +9562,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45581</v>
+        <v>46093</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9578,7 +9578,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9621,7 +9621,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 74214-2021</t>
+          <t>A 27097-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9635,10 +9635,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44553</v>
+        <v>46188</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9651,7 +9651,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>19.8</v>
+        <v>4</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9694,7 +9694,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 7994-2023</t>
+          <t>A 29369-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9708,10 +9708,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44973</v>
+        <v>46203</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9724,7 +9724,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9767,7 +9767,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 8665-2022</t>
+          <t>A 18571-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9781,10 +9781,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44613</v>
+        <v>45763</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9797,7 +9797,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9840,7 +9840,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 18571-2025</t>
+          <t>A 16419-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9854,10 +9854,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45763</v>
+        <v>45022</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9870,7 +9870,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0.9</v>
+        <v>4.2</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9913,7 +9913,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 31709-2023</t>
+          <t>A 27551-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9927,10 +9927,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45117</v>
+        <v>45097</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9986,7 +9986,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 23227-2023</t>
+          <t>A 26986-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10000,10 +10000,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45075</v>
+        <v>46185</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10016,7 +10016,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.1</v>
+        <v>3.5</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -10059,7 +10059,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 50652-2023</t>
+          <t>A 26978-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10073,10 +10073,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45210</v>
+        <v>46185</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10089,7 +10089,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>2.4</v>
+        <v>7.7</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -10132,7 +10132,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 40278-2023</t>
+          <t>A 2575-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10146,10 +10146,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45169</v>
+        <v>45313</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10162,7 +10162,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -10205,7 +10205,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 31789-2023</t>
+          <t>A 31576-2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10219,10 +10219,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45118</v>
+        <v>46224</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10235,7 +10235,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10278,7 +10278,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 60227-2025</t>
+          <t>A 36001-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10292,10 +10292,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45994</v>
+        <v>46266</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10308,7 +10308,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10351,7 +10351,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 43857-2025</t>
+          <t>A 35912-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10365,10 +10365,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45912</v>
+        <v>46266</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10381,7 +10381,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10424,7 +10424,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 39014-2023</t>
+          <t>A 35677-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10438,10 +10438,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45163</v>
+        <v>46265</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10454,7 +10454,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.9</v>
+        <v>3.1</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10497,7 +10497,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 19500-2022</t>
+          <t>A 35680-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10511,10 +10511,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>44693</v>
+        <v>46265</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10527,7 +10527,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10570,7 +10570,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 13278-2026</t>
+          <t>A 35684-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10584,10 +10584,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46093</v>
+        <v>46265</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10600,7 +10600,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.7</v>
+        <v>3.9</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10643,7 +10643,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 44448-2023</t>
+          <t>A 4089-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10657,10 +10657,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45189</v>
+        <v>45323</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10673,7 +10673,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10716,7 +10716,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 57923-2024</t>
+          <t>A 28496-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10730,10 +10730,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45631</v>
+        <v>45103</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10746,7 +10746,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>4.5</v>
+        <v>1.8</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10789,7 +10789,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 28264-2022</t>
+          <t>A 1299-2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10803,10 +10803,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>44746</v>
+        <v>45303</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10819,7 +10819,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10862,7 +10862,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 55545-2022</t>
+          <t>A 19255-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10876,10 +10876,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44887</v>
+        <v>46132</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10892,7 +10892,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>4.4</v>
+        <v>1</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10935,7 +10935,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 27097-2026</t>
+          <t>A 19256-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10949,10 +10949,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46188</v>
+        <v>46132</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10965,7 +10965,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>4</v>
+        <v>0.7</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -11008,7 +11008,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 34514-2023</t>
+          <t>A 37628-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -11022,10 +11022,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45140</v>
+        <v>46276</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11037,8 +11037,13 @@
           <t>ÄNGELHOLM</t>
         </is>
       </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I123" t="n">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -11081,7 +11086,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 1299-2024</t>
+          <t>A 32364-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -11095,10 +11100,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45303</v>
+        <v>45120</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11111,7 +11116,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -11154,7 +11159,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 42105-2022</t>
+          <t>A 31503-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11168,10 +11173,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>44830</v>
+        <v>45115</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11184,7 +11189,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -11227,7 +11232,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 29369-2026</t>
+          <t>A 39014-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11241,10 +11246,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46203</v>
+        <v>45163</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11257,7 +11262,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11300,7 +11305,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 15154-2023</t>
+          <t>A 31908-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11314,10 +11319,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45016</v>
+        <v>45118</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11330,7 +11335,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11373,7 +11378,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 7337-2024</t>
+          <t>A 31502-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11387,10 +11392,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45345</v>
+        <v>45115</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11403,7 +11408,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>2.6</v>
+        <v>0.7</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11446,7 +11451,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 49610-2024</t>
+          <t>A 28253-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11460,10 +11465,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45596</v>
+        <v>45099</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11476,7 +11481,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>6.4</v>
+        <v>2.7</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11519,7 +11524,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 14400-2023</t>
+          <t>A 21488-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11533,10 +11538,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45012</v>
+        <v>45061</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11549,7 +11554,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11592,7 +11597,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 4089-2024</t>
+          <t>A 7994-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11606,10 +11611,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45323</v>
+        <v>44973</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11622,7 +11627,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11665,7 +11670,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 23676-2024</t>
+          <t>A 27553-2023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11679,10 +11684,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45454</v>
+        <v>45097</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11695,7 +11700,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11738,7 +11743,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 26986-2026</t>
+          <t>A 53501-2022</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11752,10 +11757,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46185</v>
+        <v>44879</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11768,7 +11773,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>3.5</v>
+        <v>7.2</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11811,7 +11816,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 26978-2026</t>
+          <t>A 54709-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11825,10 +11830,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46185</v>
+        <v>45236</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11841,7 +11846,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>7.7</v>
+        <v>3.6</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11884,7 +11889,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 60-2024</t>
+          <t>A 12148-2024</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11898,10 +11903,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45293</v>
+        <v>45377</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11914,7 +11919,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11957,7 +11962,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 58150-2024</t>
+          <t>A 19500-2022</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11971,10 +11976,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45632</v>
+        <v>44693</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11987,7 +11992,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -12030,7 +12035,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 4755-2024</t>
+          <t>A 4605-2025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -12044,10 +12049,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45328</v>
+        <v>45687</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12060,7 +12065,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -12103,7 +12108,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 31576-2026</t>
+          <t>A 31720-2023</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -12117,10 +12122,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46224</v>
+        <v>45117</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12133,7 +12138,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -12176,7 +12181,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 32430-2023</t>
+          <t>A 16314-2024</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12190,10 +12195,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45120</v>
+        <v>45407</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12206,7 +12211,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -12249,7 +12254,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 28496-2023</t>
+          <t>A 34514-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12263,10 +12268,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45103</v>
+        <v>45140</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12279,7 +12284,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -12322,7 +12327,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 35677-2026</t>
+          <t>A 46613-2024</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12336,10 +12341,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46265</v>
+        <v>45583</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12352,7 +12357,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>3.1</v>
+        <v>6.2</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12395,7 +12400,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 35680-2026</t>
+          <t>A 23976-2024</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12409,10 +12414,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46265</v>
+        <v>45456</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12425,7 +12430,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>2.9</v>
+        <v>0.6</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12468,7 +12473,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 35684-2026</t>
+          <t>A 40278-2023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12482,10 +12487,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46265</v>
+        <v>45169</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12498,7 +12503,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>3.9</v>
+        <v>1.1</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12541,7 +12546,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 36001-2026</t>
+          <t>A 7871-2025</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12555,10 +12560,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46266</v>
+        <v>45706</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12571,7 +12576,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12614,7 +12619,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 4605-2025</t>
+          <t>A 32430-2023</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12628,10 +12633,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45687</v>
+        <v>45120</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12644,7 +12649,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12687,7 +12692,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 21488-2023</t>
+          <t>A 29436-2024</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12701,10 +12706,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45061</v>
+        <v>45483</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12717,7 +12722,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1.1</v>
+        <v>4.2</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12760,7 +12765,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 31908-2023</t>
+          <t>A 58150-2024</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12774,10 +12779,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45118</v>
+        <v>45632</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12790,7 +12795,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12833,7 +12838,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 35912-2026</t>
+          <t>A 28264-2022</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12847,10 +12852,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46266</v>
+        <v>44746</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12863,7 +12868,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12906,7 +12911,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 7811-2023</t>
+          <t>A 31709-2023</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12920,10 +12925,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>44973</v>
+        <v>45117</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12936,7 +12941,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12979,7 +12984,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 16314-2024</t>
+          <t>A 8665-2022</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12993,10 +12998,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45407</v>
+        <v>44613</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13009,7 +13014,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -13052,7 +13057,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 19255-2026</t>
+          <t>A 60-2024</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -13066,10 +13071,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46132</v>
+        <v>45293</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13082,7 +13087,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -13125,7 +13130,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 19256-2026</t>
+          <t>A 607-2024</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -13139,10 +13144,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46132</v>
+        <v>45299</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13155,7 +13160,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -13198,7 +13203,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 37628-2026</t>
+          <t>A 49206-2024</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -13212,10 +13217,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46276</v>
+        <v>45595</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13227,13 +13232,8 @@
           <t>ÄNGELHOLM</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I153" t="n">
-        <v>4.5</v>
+        <v>1.7</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -13276,7 +13276,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 46613-2024</t>
+          <t>A 19503-2022</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -13290,10 +13290,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45583</v>
+        <v>44693</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13306,7 +13306,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>6.2</v>
+        <v>5.1</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -13349,7 +13349,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 20635-2024</t>
+          <t>A 57923-2024</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13363,10 +13363,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45436</v>
+        <v>45631</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13379,7 +13379,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13422,7 +13422,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 23980-2024</t>
+          <t>A 20635-2024</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13436,10 +13436,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45456</v>
+        <v>45436</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13452,7 +13452,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>1.3</v>
+        <v>4.8</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13495,7 +13495,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 55748-2024</t>
+          <t>A 23980-2024</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13509,10 +13509,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45623</v>
+        <v>45456</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13525,7 +13525,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13568,7 +13568,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 48197-2024</t>
+          <t>A 55748-2024</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45590</v>
+        <v>45623</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13598,7 +13598,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>3.1</v>
+        <v>0.9</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13641,7 +13641,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 55529-2024</t>
+          <t>A 48197-2024</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13655,10 +13655,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45622</v>
+        <v>45590</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13671,7 +13671,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13731,7 +13731,7 @@
         <v>45582</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13804,7 +13804,7 @@
         <v>45582</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13877,7 +13877,7 @@
         <v>45582</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13950,7 +13950,7 @@
         <v>45582</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14023,7 +14023,7 @@
         <v>44519</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14096,7 +14096,7 @@
         <v>45239</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14169,7 +14169,7 @@
         <v>45168</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14242,7 +14242,7 @@
         <v>44861</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14315,7 +14315,7 @@
         <v>45582</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>

--- a/Översikt ÄNGELHOLM.xlsx
+++ b/Översikt ÄNGELHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45099</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         <v>45931</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
         <v>45931</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>46106</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>44802</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 32268-2022</t>
+          <t>A 74502-2021</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1204,10 +1204,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44781</v>
+        <v>44560</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1220,16 +1220,16 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>8.6</v>
+        <v>5.6</v>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1244,7 +1244,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1253,12 +1253,128 @@
         <v>8</v>
       </c>
       <c r="T7" t="n">
+        <v>9</v>
+      </c>
+      <c r="U7" t="n">
+        <v>9</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Entita
+Grönsångare
+Sydlig sotticka
+Västlig hakmossa
+Spillkråka
+Gröngöling
+Kungsfågel
+Skogsduva</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 74502-2021 artfynd.xlsx", "A 74502-2021")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 74502-2021 karta.png", "A 74502-2021")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 74502-2021 georefererad karta.tif", "A 74502-2021")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 74502-2021 FSC-klagomål.docx", "A 74502-2021")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 74502-2021 FSC-klagomål mail.docx", "A 74502-2021")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 74502-2021 tillsynsbegäran.docx", "A 74502-2021")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 74502-2021 tillsynsbegäran mail.docx", "A 74502-2021")</f>
+        <v/>
+      </c>
+      <c r="AE7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 74502-2021 prioriterade fågelarter.docx", "A 74502-2021")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 32268-2022</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>44781</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>5</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>8</v>
+      </c>
+      <c r="T8" t="n">
         <v>14</v>
       </c>
-      <c r="U7" t="n">
+      <c r="U8" t="n">
         <v>14</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Bokvårtlav
 Blåmossa
@@ -1270,148 +1386,32 @@
 Vanlig padda</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 32268-2022 artfynd.xlsx", "A 32268-2022")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 32268-2022 karta.png", "A 32268-2022")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 32268-2022 georefererad karta.tif", "A 32268-2022")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 32268-2022 FSC-klagomål.docx", "A 32268-2022")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 32268-2022 FSC-klagomål mail.docx", "A 32268-2022")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 32268-2022 tillsynsbegäran.docx", "A 32268-2022")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 32268-2022 tillsynsbegäran mail.docx", "A 32268-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 74502-2021</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>44560</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="J8" t="n">
-        <v>6</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" t="n">
-        <v>3</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>3</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>8</v>
-      </c>
-      <c r="T8" t="n">
-        <v>9</v>
-      </c>
-      <c r="U8" t="n">
-        <v>9</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Entita
-Grönsångare
-Sydlig sotticka
-Västlig hakmossa
-Spillkråka
-Gröngöling
-Kungsfågel
-Skogsduva</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 74502-2021 artfynd.xlsx", "A 74502-2021")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 74502-2021 karta.png", "A 74502-2021")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 74502-2021 georefererad karta.tif", "A 74502-2021")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 74502-2021 FSC-klagomål.docx", "A 74502-2021")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 74502-2021 FSC-klagomål mail.docx", "A 74502-2021")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 74502-2021 tillsynsbegäran.docx", "A 74502-2021")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 74502-2021 tillsynsbegäran mail.docx", "A 74502-2021")</f>
-        <v/>
-      </c>
-      <c r="AE8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 74502-2021 prioriterade fågelarter.docx", "A 74502-2021")</f>
         <v/>
       </c>
     </row>
@@ -1435,7 +1435,7 @@
         <v>45835</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 5046-2022</t>
+          <t>A 308-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1547,10 +1547,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44593</v>
+        <v>44929</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1563,34 +1563,34 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>3</v>
+        <v>0.8</v>
       </c>
       <c r="J10" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L10" t="n">
         <v>1</v>
       </c>
       <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
         <v>1</v>
       </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2</v>
-      </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>6</v>
@@ -1599,9 +1599,119 @@
         <v>7</v>
       </c>
       <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Bokvårtlav
+Dvärghäxört
+Havstulpanlav
+Klippfrullania
+Platt fjädermossa
+Stor knopplav</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 308-2023 artfynd.xlsx", "A 308-2023")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 308-2023 karta.png", "A 308-2023")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 308-2023 georefererad karta.tif", "A 308-2023")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 308-2023 FSC-klagomål.docx", "A 308-2023")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 308-2023 FSC-klagomål mail.docx", "A 308-2023")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 308-2023 tillsynsbegäran.docx", "A 308-2023")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 308-2023 tillsynsbegäran mail.docx", "A 308-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 5046-2022</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>44593</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>3</v>
+      </c>
+      <c r="J11" t="n">
         <v>6</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>6</v>
+      </c>
+      <c r="T11" t="n">
+        <v>7</v>
+      </c>
+      <c r="U11" t="n">
+        <v>6</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Grönfink
 Gulsparv
@@ -1611,111 +1721,225 @@
 Trädlärka</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 5046-2022 artfynd.xlsx", "A 5046-2022")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 5046-2022 karta.png", "A 5046-2022")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 5046-2022 georefererad karta.tif", "A 5046-2022")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 5046-2022 FSC-klagomål.docx", "A 5046-2022")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 5046-2022 FSC-klagomål mail.docx", "A 5046-2022")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 5046-2022 tillsynsbegäran.docx", "A 5046-2022")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 5046-2022 tillsynsbegäran mail.docx", "A 5046-2022")</f>
         <v/>
       </c>
-      <c r="AE10">
+      <c r="AE11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 5046-2022 prioriterade fågelarter.docx", "A 5046-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 308-2023</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>44929</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>S 2334-2023</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Askåterföring</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>45106</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>6</v>
+      </c>
+      <c r="T12" t="n">
+        <v>6</v>
+      </c>
+      <c r="U12" t="n">
+        <v>6</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Småvänderot
+Vitfläckig guldvinge
+Kambräken
+Spillkråka
+Törnskata
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/S 2334-2023 artfynd.xlsx", "S 2334-2023")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/S 2334-2023 karta.png", "S 2334-2023")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/S 2334-2023 georefererad karta.tif", "S 2334-2023")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/S 2334-2023 FSC-klagomål.docx", "S 2334-2023")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/S 2334-2023 FSC-klagomål mail.docx", "S 2334-2023")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/S 2334-2023 tillsynsbegäran.docx", "S 2334-2023")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/S 2334-2023 tillsynsbegäran mail.docx", "S 2334-2023")</f>
+        <v/>
+      </c>
+      <c r="AE12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/S 2334-2023 prioriterade fågelarter.docx", "S 2334-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>S 4107-2023</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45245</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
         <v>5</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L13" t="n">
         <v>1</v>
       </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
         <v>1</v>
       </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
         <v>6</v>
       </c>
-      <c r="T11" t="n">
+      <c r="T13" t="n">
         <v>7</v>
       </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Bokvårtlav
 Dvärghäxört
@@ -1725,230 +1949,6 @@
 Stor knopplav</t>
         </is>
       </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 308-2023 artfynd.xlsx", "A 308-2023")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 308-2023 karta.png", "A 308-2023")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 308-2023 georefererad karta.tif", "A 308-2023")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 308-2023 FSC-klagomål.docx", "A 308-2023")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 308-2023 FSC-klagomål mail.docx", "A 308-2023")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 308-2023 tillsynsbegäran.docx", "A 308-2023")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 308-2023 tillsynsbegäran mail.docx", "A 308-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>S 2334-2023</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Askåterföring</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>45106</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>47.6</v>
-      </c>
-      <c r="J12" t="n">
-        <v>3</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1</v>
-      </c>
-      <c r="S12" t="n">
-        <v>6</v>
-      </c>
-      <c r="T12" t="n">
-        <v>6</v>
-      </c>
-      <c r="U12" t="n">
-        <v>6</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Småvänderot
-Vitfläckig guldvinge
-Kambräken
-Spillkråka
-Törnskata
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/S 2334-2023 artfynd.xlsx", "S 2334-2023")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/S 2334-2023 karta.png", "S 2334-2023")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/S 2334-2023 georefererad karta.tif", "S 2334-2023")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/S 2334-2023 FSC-klagomål.docx", "S 2334-2023")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/S 2334-2023 FSC-klagomål mail.docx", "S 2334-2023")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/S 2334-2023 tillsynsbegäran.docx", "S 2334-2023")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/S 2334-2023 tillsynsbegäran mail.docx", "S 2334-2023")</f>
-        <v/>
-      </c>
-      <c r="AE12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/S 2334-2023 prioriterade fågelarter.docx", "S 2334-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>S 4107-2023</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45245</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>5</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>6</v>
-      </c>
-      <c r="T13" t="n">
-        <v>7</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Bokvårtlav
-Dvärghäxört
-Havstulpanlav
-Klippfrullania
-Platt fjädermossa
-Stor knopplav</t>
-        </is>
-      </c>
       <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/S 4107-2023 artfynd.xlsx", "S 4107-2023")</f>
         <v/>
@@ -1998,7 +1998,7 @@
         <v>46038</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>46265</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2157,10 +2157,10 @@
         <v>5</v>
       </c>
       <c r="T15" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U15" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>45664</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>44864</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>45301</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 28874-2023</t>
+          <t>A 8065-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2548,10 +2548,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45104</v>
+        <v>45707</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2564,20 +2564,20 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>9</v>
+        <v>3.3</v>
       </c>
       <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>2</v>
+      </c>
+      <c r="M19" t="n">
         <v>1</v>
       </c>
-      <c r="K19" t="n">
-        <v>2</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
       <c r="N19" t="n">
         <v>0</v>
       </c>
@@ -2588,167 +2588,167 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S19" t="n">
         <v>3</v>
       </c>
       <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Småvänderot
+Gullpudra
+Svinrot</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 8065-2025 artfynd.xlsx", "A 8065-2025")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 8065-2025 karta.png", "A 8065-2025")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 8065-2025 georefererad karta.tif", "A 8065-2025")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 8065-2025 FSC-klagomål.docx", "A 8065-2025")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 8065-2025 FSC-klagomål mail.docx", "A 8065-2025")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 8065-2025 tillsynsbegäran.docx", "A 8065-2025")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 8065-2025 tillsynsbegäran mail.docx", "A 8065-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 28874-2023</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>45104</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>9</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3</v>
+      </c>
+      <c r="T20" t="n">
         <v>5</v>
       </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>Blåmossa
 Stubbspretmossa
 Revlummer</t>
         </is>
       </c>
-      <c r="W19">
+      <c r="W20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 28874-2023 artfynd.xlsx", "A 28874-2023")</f>
         <v/>
       </c>
-      <c r="X19">
+      <c r="X20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 28874-2023 karta.png", "A 28874-2023")</f>
         <v/>
       </c>
-      <c r="Y19">
+      <c r="Y20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 28874-2023 georefererad karta.tif", "A 28874-2023")</f>
         <v/>
       </c>
-      <c r="AA19">
+      <c r="AA20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 28874-2023 FSC-klagomål.docx", "A 28874-2023")</f>
         <v/>
       </c>
-      <c r="AB19">
+      <c r="AB20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 28874-2023 FSC-klagomål mail.docx", "A 28874-2023")</f>
         <v/>
       </c>
-      <c r="AC19">
+      <c r="AC20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 28874-2023 tillsynsbegäran.docx", "A 28874-2023")</f>
         <v/>
       </c>
-      <c r="AD19">
+      <c r="AD20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 28874-2023 tillsynsbegäran mail.docx", "A 28874-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 8065-2025</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>45707</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>2</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>3</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3</v>
-      </c>
-      <c r="U20" t="n">
-        <v>2</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Småvänderot
-Gullpudra
-Svinrot</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 8065-2025 artfynd.xlsx", "A 8065-2025")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 8065-2025 karta.png", "A 8065-2025")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 8065-2025 georefererad karta.tif", "A 8065-2025")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 8065-2025 FSC-klagomål.docx", "A 8065-2025")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 8065-2025 FSC-klagomål mail.docx", "A 8065-2025")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 8065-2025 tillsynsbegäran.docx", "A 8065-2025")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 8065-2025 tillsynsbegäran mail.docx", "A 8065-2025")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 3317-2026</t>
+          <t>A 31907-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2762,10 +2762,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46041</v>
+        <v>45118</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2778,16 +2778,16 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.9</v>
+        <v>5.3</v>
       </c>
       <c r="J21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -2802,7 +2802,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -2811,262 +2811,262 @@
         <v>3</v>
       </c>
       <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Bokvårtlav
+Platt fjädermossa
+Stubbspretmossa</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 31907-2023 artfynd.xlsx", "A 31907-2023")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 31907-2023 karta.png", "A 31907-2023")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 31907-2023 georefererad karta.tif", "A 31907-2023")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 31907-2023 FSC-klagomål.docx", "A 31907-2023")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 31907-2023 FSC-klagomål mail.docx", "A 31907-2023")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 31907-2023 tillsynsbegäran.docx", "A 31907-2023")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 31907-2023 tillsynsbegäran mail.docx", "A 31907-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 3317-2026</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>46041</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>2</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3</v>
+      </c>
+      <c r="T22" t="n">
         <v>6</v>
       </c>
-      <c r="U21" t="n">
+      <c r="U22" t="n">
         <v>6</v>
       </c>
-      <c r="V21" s="2" t="inlineStr">
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>Entita
 Mindre hackspett
 Gröngöling</t>
         </is>
       </c>
-      <c r="W21">
+      <c r="W22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 3317-2026 artfynd.xlsx", "A 3317-2026")</f>
         <v/>
       </c>
-      <c r="X21">
+      <c r="X22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 3317-2026 karta.png", "A 3317-2026")</f>
         <v/>
       </c>
-      <c r="Y21">
+      <c r="Y22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 3317-2026 georefererad karta.tif", "A 3317-2026")</f>
         <v/>
       </c>
-      <c r="AA21">
+      <c r="AA22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 3317-2026 FSC-klagomål.docx", "A 3317-2026")</f>
         <v/>
       </c>
-      <c r="AB21">
+      <c r="AB22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 3317-2026 FSC-klagomål mail.docx", "A 3317-2026")</f>
         <v/>
       </c>
-      <c r="AC21">
+      <c r="AC22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 3317-2026 tillsynsbegäran.docx", "A 3317-2026")</f>
         <v/>
       </c>
-      <c r="AD21">
+      <c r="AD22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 3317-2026 tillsynsbegäran mail.docx", "A 3317-2026")</f>
         <v/>
       </c>
-      <c r="AE21">
+      <c r="AE22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 3317-2026 prioriterade fågelarter.docx", "A 3317-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
         <is>
           <t>A 50684-2023</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
         <v>45210</v>
       </c>
-      <c r="E22" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
+      <c r="E23" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
         <v>1.6</v>
       </c>
-      <c r="J22" t="n">
+      <c r="J23" t="n">
         <v>2</v>
       </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
         <v>1</v>
       </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
         <v>1</v>
       </c>
-      <c r="R22" t="n">
+      <c r="R23" t="n">
         <v>1</v>
       </c>
-      <c r="S22" t="n">
+      <c r="S23" t="n">
         <v>3</v>
       </c>
-      <c r="T22" t="n">
+      <c r="T23" t="n">
         <v>3</v>
       </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>Skogsalm
 Kopparödla
 Vanlig padda</t>
         </is>
       </c>
-      <c r="W22">
+      <c r="W23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 50684-2023 artfynd.xlsx", "A 50684-2023")</f>
         <v/>
       </c>
-      <c r="X22">
+      <c r="X23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 50684-2023 karta.png", "A 50684-2023")</f>
         <v/>
       </c>
-      <c r="Y22">
+      <c r="Y23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 50684-2023 georefererad karta.tif", "A 50684-2023")</f>
         <v/>
       </c>
-      <c r="AA22">
+      <c r="AA23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 50684-2023 FSC-klagomål.docx", "A 50684-2023")</f>
         <v/>
       </c>
-      <c r="AB22">
+      <c r="AB23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 50684-2023 FSC-klagomål mail.docx", "A 50684-2023")</f>
         <v/>
       </c>
-      <c r="AC22">
+      <c r="AC23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 50684-2023 tillsynsbegäran.docx", "A 50684-2023")</f>
         <v/>
       </c>
-      <c r="AD22">
+      <c r="AD23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 50684-2023 tillsynsbegäran mail.docx", "A 50684-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>A 31907-2023</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>45118</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>2</v>
-      </c>
-      <c r="L23" t="n">
-        <v>1</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3</v>
-      </c>
-      <c r="T23" t="n">
-        <v>3</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>Bokvårtlav
-Platt fjädermossa
-Stubbspretmossa</t>
-        </is>
-      </c>
-      <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 31907-2023 artfynd.xlsx", "A 31907-2023")</f>
-        <v/>
-      </c>
-      <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 31907-2023 karta.png", "A 31907-2023")</f>
-        <v/>
-      </c>
-      <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 31907-2023 georefererad karta.tif", "A 31907-2023")</f>
-        <v/>
-      </c>
-      <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 31907-2023 FSC-klagomål.docx", "A 31907-2023")</f>
-        <v/>
-      </c>
-      <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 31907-2023 FSC-klagomål mail.docx", "A 31907-2023")</f>
-        <v/>
-      </c>
-      <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 31907-2023 tillsynsbegäran.docx", "A 31907-2023")</f>
-        <v/>
-      </c>
-      <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 31907-2023 tillsynsbegäran mail.docx", "A 31907-2023")</f>
         <v/>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
         <v>45763</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3201,7 +3201,7 @@
         <v>45474</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>45841</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         <v>45105</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3531,7 +3531,7 @@
         <v>44553</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3641,7 +3641,7 @@
         <v>45359</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         <v>45582</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         <v>44839</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>44742</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         <v>44746</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 44062-2022</t>
+          <t>A 12150-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4173,10 +4173,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44839</v>
+        <v>45377</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4189,20 +4189,20 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
         <v>1</v>
       </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
       <c r="N34" t="n">
         <v>0</v>
       </c>
@@ -4213,10 +4213,10 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4229,42 +4229,42 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 44062-2022 artfynd.xlsx", "A 44062-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 12150-2024 artfynd.xlsx", "A 12150-2024")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 44062-2022 karta.png", "A 44062-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 12150-2024 karta.png", "A 12150-2024")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 44062-2022 georefererad karta.tif", "A 44062-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 12150-2024 georefererad karta.tif", "A 12150-2024")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 44062-2022 FSC-klagomål.docx", "A 44062-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 12150-2024 FSC-klagomål.docx", "A 12150-2024")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 44062-2022 FSC-klagomål mail.docx", "A 44062-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 12150-2024 FSC-klagomål mail.docx", "A 12150-2024")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 44062-2022 tillsynsbegäran.docx", "A 44062-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 12150-2024 tillsynsbegäran.docx", "A 12150-2024")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 44062-2022 tillsynsbegäran mail.docx", "A 44062-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 12150-2024 tillsynsbegäran mail.docx", "A 12150-2024")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 46487-2024</t>
+          <t>A 4088-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4278,10 +4278,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45582</v>
+        <v>45323</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4294,17 +4294,17 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>5.8</v>
+        <v>3.8</v>
       </c>
       <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
         <v>1</v>
       </c>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
       <c r="M35" t="n">
         <v>0</v>
       </c>
@@ -4318,7 +4318,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -4330,46 +4330,46 @@
         <v>1</v>
       </c>
       <c r="U35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Flikbålmossa</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 46487-2024 artfynd.xlsx", "A 46487-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 4088-2024 artfynd.xlsx", "A 4088-2024")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 46487-2024 karta.png", "A 46487-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 4088-2024 karta.png", "A 4088-2024")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 46487-2024 georefererad karta.tif", "A 46487-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 4088-2024 georefererad karta.tif", "A 4088-2024")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 46487-2024 FSC-klagomål.docx", "A 46487-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 4088-2024 FSC-klagomål.docx", "A 4088-2024")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 46487-2024 FSC-klagomål mail.docx", "A 46487-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 4088-2024 FSC-klagomål mail.docx", "A 4088-2024")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 46487-2024 tillsynsbegäran.docx", "A 46487-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 4088-2024 tillsynsbegäran.docx", "A 4088-2024")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 46487-2024 tillsynsbegäran mail.docx", "A 46487-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 4088-2024 tillsynsbegäran mail.docx", "A 4088-2024")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 4088-2024</t>
+          <t>A 50642-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4383,10 +4383,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45323</v>
+        <v>45210</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4399,16 +4399,16 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>3.8</v>
+        <v>0.8</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -4423,7 +4423,7 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -4439,35 +4439,35 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>Flikbålmossa</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 4088-2024 artfynd.xlsx", "A 4088-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 50642-2023 artfynd.xlsx", "A 50642-2023")</f>
         <v/>
       </c>
       <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 4088-2024 karta.png", "A 4088-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 50642-2023 karta.png", "A 50642-2023")</f>
         <v/>
       </c>
       <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 4088-2024 georefererad karta.tif", "A 4088-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 50642-2023 georefererad karta.tif", "A 50642-2023")</f>
         <v/>
       </c>
       <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 4088-2024 FSC-klagomål.docx", "A 4088-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 50642-2023 FSC-klagomål.docx", "A 50642-2023")</f>
         <v/>
       </c>
       <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 4088-2024 FSC-klagomål mail.docx", "A 4088-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 50642-2023 FSC-klagomål mail.docx", "A 50642-2023")</f>
         <v/>
       </c>
       <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 4088-2024 tillsynsbegäran.docx", "A 4088-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 50642-2023 tillsynsbegäran.docx", "A 50642-2023")</f>
         <v/>
       </c>
       <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 4088-2024 tillsynsbegäran mail.docx", "A 4088-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 50642-2023 tillsynsbegäran mail.docx", "A 50642-2023")</f>
         <v/>
       </c>
     </row>
@@ -4491,7 +4491,7 @@
         <v>45462</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4579,7 +4579,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 27094-2026</t>
+          <t>A 61094-2021</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4593,10 +4593,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46188</v>
+        <v>44498</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4609,7 +4609,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4645,46 +4645,46 @@
         <v>1</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 27094-2026 artfynd.xlsx", "A 27094-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 61094-2021 artfynd.xlsx", "A 61094-2021")</f>
         <v/>
       </c>
       <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 27094-2026 karta.png", "A 27094-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 61094-2021 karta.png", "A 61094-2021")</f>
         <v/>
       </c>
       <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 27094-2026 georefererad karta.tif", "A 27094-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 61094-2021 georefererad karta.tif", "A 61094-2021")</f>
         <v/>
       </c>
       <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 27094-2026 FSC-klagomål.docx", "A 27094-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 61094-2021 FSC-klagomål.docx", "A 61094-2021")</f>
         <v/>
       </c>
       <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 27094-2026 FSC-klagomål mail.docx", "A 27094-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 61094-2021 FSC-klagomål mail.docx", "A 61094-2021")</f>
         <v/>
       </c>
       <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 27094-2026 tillsynsbegäran.docx", "A 27094-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 61094-2021 tillsynsbegäran.docx", "A 61094-2021")</f>
         <v/>
       </c>
       <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 27094-2026 tillsynsbegäran mail.docx", "A 27094-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 61094-2021 tillsynsbegäran mail.docx", "A 61094-2021")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 12150-2024</t>
+          <t>A 27094-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4698,10 +4698,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45377</v>
+        <v>46188</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4714,19 +4714,19 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.4</v>
+        <v>6.2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
         <v>0</v>
@@ -4738,10 +4738,10 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -4750,46 +4750,46 @@
         <v>1</v>
       </c>
       <c r="U39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 12150-2024 artfynd.xlsx", "A 12150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 27094-2026 artfynd.xlsx", "A 27094-2026")</f>
         <v/>
       </c>
       <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 12150-2024 karta.png", "A 12150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 27094-2026 karta.png", "A 27094-2026")</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 12150-2024 georefererad karta.tif", "A 12150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 27094-2026 georefererad karta.tif", "A 27094-2026")</f>
         <v/>
       </c>
       <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 12150-2024 FSC-klagomål.docx", "A 12150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 27094-2026 FSC-klagomål.docx", "A 27094-2026")</f>
         <v/>
       </c>
       <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 12150-2024 FSC-klagomål mail.docx", "A 12150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 27094-2026 FSC-klagomål mail.docx", "A 27094-2026")</f>
         <v/>
       </c>
       <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 12150-2024 tillsynsbegäran.docx", "A 12150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 27094-2026 tillsynsbegäran.docx", "A 27094-2026")</f>
         <v/>
       </c>
       <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 12150-2024 tillsynsbegäran mail.docx", "A 12150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 27094-2026 tillsynsbegäran mail.docx", "A 27094-2026")</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 31599-2026</t>
+          <t>A 44062-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4803,10 +4803,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46224</v>
+        <v>44839</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4819,10 +4819,10 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
         <v>1</v>
@@ -4852,49 +4852,49 @@
         <v>1</v>
       </c>
       <c r="T40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U40" t="n">
         <v>1</v>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>Ekoxe</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="W40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 31599-2026 artfynd.xlsx", "A 31599-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 44062-2022 artfynd.xlsx", "A 44062-2022")</f>
         <v/>
       </c>
       <c r="X40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 31599-2026 karta.png", "A 31599-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 44062-2022 karta.png", "A 44062-2022")</f>
         <v/>
       </c>
       <c r="Y40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 31599-2026 georefererad karta.tif", "A 31599-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 44062-2022 georefererad karta.tif", "A 44062-2022")</f>
         <v/>
       </c>
       <c r="AA40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 31599-2026 FSC-klagomål.docx", "A 31599-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 44062-2022 FSC-klagomål.docx", "A 44062-2022")</f>
         <v/>
       </c>
       <c r="AB40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 31599-2026 FSC-klagomål mail.docx", "A 31599-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 44062-2022 FSC-klagomål mail.docx", "A 44062-2022")</f>
         <v/>
       </c>
       <c r="AC40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 31599-2026 tillsynsbegäran.docx", "A 31599-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 44062-2022 tillsynsbegäran.docx", "A 44062-2022")</f>
         <v/>
       </c>
       <c r="AD40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 31599-2026 tillsynsbegäran mail.docx", "A 31599-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 44062-2022 tillsynsbegäran mail.docx", "A 44062-2022")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 61094-2021</t>
+          <t>A 35684-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4908,10 +4908,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44498</v>
+        <v>46265</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4924,17 +4924,17 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>6.4</v>
+        <v>3.9</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
         <v>1</v>
       </c>
-      <c r="L41" t="n">
-        <v>0</v>
-      </c>
       <c r="M41" t="n">
         <v>0</v>
       </c>
@@ -4948,7 +4948,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -4964,42 +4964,46 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 61094-2021 artfynd.xlsx", "A 61094-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 35684-2026 artfynd.xlsx", "A 35684-2026")</f>
         <v/>
       </c>
       <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 61094-2021 karta.png", "A 61094-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 35684-2026 karta.png", "A 35684-2026")</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 61094-2021 georefererad karta.tif", "A 61094-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 35684-2026 georefererad karta.tif", "A 35684-2026")</f>
         <v/>
       </c>
       <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 61094-2021 FSC-klagomål.docx", "A 61094-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 35684-2026 FSC-klagomål.docx", "A 35684-2026")</f>
         <v/>
       </c>
       <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 61094-2021 FSC-klagomål mail.docx", "A 61094-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 35684-2026 FSC-klagomål mail.docx", "A 35684-2026")</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 61094-2021 tillsynsbegäran.docx", "A 61094-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 35684-2026 tillsynsbegäran.docx", "A 35684-2026")</f>
         <v/>
       </c>
       <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 61094-2021 tillsynsbegäran mail.docx", "A 61094-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 35684-2026 tillsynsbegäran mail.docx", "A 35684-2026")</f>
+        <v/>
+      </c>
+      <c r="AE41">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 35684-2026 prioriterade fågelarter.docx", "A 35684-2026")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 50642-2023</t>
+          <t>A 31599-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5013,10 +5017,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45210</v>
+        <v>46224</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5029,13 +5033,13 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J42" t="n">
         <v>1</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
@@ -5062,66 +5066,66 @@
         <v>1</v>
       </c>
       <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
         <v>1</v>
       </c>
-      <c r="U42" t="n">
-        <v>0</v>
-      </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 50642-2023 artfynd.xlsx", "A 50642-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 31599-2026 artfynd.xlsx", "A 31599-2026")</f>
         <v/>
       </c>
       <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 50642-2023 karta.png", "A 50642-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 31599-2026 karta.png", "A 31599-2026")</f>
         <v/>
       </c>
       <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 50642-2023 georefererad karta.tif", "A 50642-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 31599-2026 georefererad karta.tif", "A 31599-2026")</f>
         <v/>
       </c>
       <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 50642-2023 FSC-klagomål.docx", "A 50642-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 31599-2026 FSC-klagomål.docx", "A 31599-2026")</f>
         <v/>
       </c>
       <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 50642-2023 FSC-klagomål mail.docx", "A 50642-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 31599-2026 FSC-klagomål mail.docx", "A 31599-2026")</f>
         <v/>
       </c>
       <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 50642-2023 tillsynsbegäran.docx", "A 50642-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 31599-2026 tillsynsbegäran.docx", "A 31599-2026")</f>
         <v/>
       </c>
       <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 50642-2023 tillsynsbegäran mail.docx", "A 50642-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 31599-2026 tillsynsbegäran mail.docx", "A 31599-2026")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>S 1961-2023</t>
+          <t>A 46487-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45084</v>
+        <v>45582</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5134,7 +5138,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>27</v>
+        <v>5.8</v>
       </c>
       <c r="J43" t="n">
         <v>1</v>
@@ -5170,46 +5174,46 @@
         <v>1</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>Huggorm</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="W43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/S 1961-2023 artfynd.xlsx", "S 1961-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 46487-2024 artfynd.xlsx", "A 46487-2024")</f>
         <v/>
       </c>
       <c r="X43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/S 1961-2023 karta.png", "S 1961-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 46487-2024 karta.png", "A 46487-2024")</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/S 1961-2023 georefererad karta.tif", "S 1961-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 46487-2024 georefererad karta.tif", "A 46487-2024")</f>
         <v/>
       </c>
       <c r="AA43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/S 1961-2023 FSC-klagomål.docx", "S 1961-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 46487-2024 FSC-klagomål.docx", "A 46487-2024")</f>
         <v/>
       </c>
       <c r="AB43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/S 1961-2023 FSC-klagomål mail.docx", "S 1961-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 46487-2024 FSC-klagomål mail.docx", "A 46487-2024")</f>
         <v/>
       </c>
       <c r="AC43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/S 1961-2023 tillsynsbegäran.docx", "S 1961-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 46487-2024 tillsynsbegäran.docx", "A 46487-2024")</f>
         <v/>
       </c>
       <c r="AD43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/S 1961-2023 tillsynsbegäran mail.docx", "S 1961-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 46487-2024 tillsynsbegäran mail.docx", "A 46487-2024")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>S 6121-2022</t>
+          <t>S 1961-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5219,14 +5223,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44862</v>
+        <v>45084</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5239,10 +5243,10 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.1</v>
+        <v>27</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -5251,7 +5255,7 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
         <v>0</v>
@@ -5263,10 +5267,10 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>1</v>
@@ -5275,63 +5279,63 @@
         <v>1</v>
       </c>
       <c r="U44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>Småvänderot</t>
+          <t>Huggorm</t>
         </is>
       </c>
       <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/S 6121-2022 artfynd.xlsx", "S 6121-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/S 1961-2023 artfynd.xlsx", "S 1961-2023")</f>
         <v/>
       </c>
       <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/S 6121-2022 karta.png", "S 6121-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/S 1961-2023 karta.png", "S 1961-2023")</f>
         <v/>
       </c>
       <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/S 6121-2022 georefererad karta.tif", "S 6121-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/S 1961-2023 georefererad karta.tif", "S 1961-2023")</f>
         <v/>
       </c>
       <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/S 6121-2022 FSC-klagomål.docx", "S 6121-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/S 1961-2023 FSC-klagomål.docx", "S 1961-2023")</f>
         <v/>
       </c>
       <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/S 6121-2022 FSC-klagomål mail.docx", "S 6121-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/S 1961-2023 FSC-klagomål mail.docx", "S 1961-2023")</f>
         <v/>
       </c>
       <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/S 6121-2022 tillsynsbegäran.docx", "S 6121-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/S 1961-2023 tillsynsbegäran.docx", "S 1961-2023")</f>
         <v/>
       </c>
       <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/S 6121-2022 tillsynsbegäran mail.docx", "S 6121-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/S 1961-2023 tillsynsbegäran mail.docx", "S 1961-2023")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 53742-2022</t>
+          <t>S 6121-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44880</v>
+        <v>44862</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5344,7 +5348,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5356,7 +5360,7 @@
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N45" t="n">
         <v>0</v>
@@ -5368,26 +5372,58 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
-      </c>
-      <c r="V45" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>Småvänderot</t>
+        </is>
+      </c>
+      <c r="W45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/S 6121-2022 artfynd.xlsx", "S 6121-2022")</f>
+        <v/>
+      </c>
+      <c r="X45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/S 6121-2022 karta.png", "S 6121-2022")</f>
+        <v/>
+      </c>
+      <c r="Y45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/S 6121-2022 georefererad karta.tif", "S 6121-2022")</f>
+        <v/>
+      </c>
+      <c r="AA45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/S 6121-2022 FSC-klagomål.docx", "S 6121-2022")</f>
+        <v/>
+      </c>
+      <c r="AB45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/S 6121-2022 FSC-klagomål mail.docx", "S 6121-2022")</f>
+        <v/>
+      </c>
+      <c r="AC45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/S 6121-2022 tillsynsbegäran.docx", "S 6121-2022")</f>
+        <v/>
+      </c>
+      <c r="AD45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/S 6121-2022 tillsynsbegäran mail.docx", "S 6121-2022")</f>
+        <v/>
+      </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 44247-2022</t>
+          <t>A 53742-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5401,10 +5437,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44839</v>
+        <v>44880</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5460,7 +5496,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 24233-2022</t>
+          <t>A 44247-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5474,10 +5510,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44725</v>
+        <v>44839</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5490,7 +5526,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5533,7 +5569,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 44473-2022</t>
+          <t>A 24233-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5547,10 +5583,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44840</v>
+        <v>44725</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5563,7 +5599,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5606,7 +5642,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 61263-2021</t>
+          <t>A 44473-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5620,10 +5656,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44498</v>
+        <v>44840</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5636,7 +5672,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5679,7 +5715,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 56094-2021</t>
+          <t>A 61263-2021</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5693,10 +5729,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44477</v>
+        <v>44498</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5709,7 +5745,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5752,7 +5788,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 15046-2022</t>
+          <t>A 56094-2021</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5766,10 +5802,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44657</v>
+        <v>44477</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5782,7 +5818,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5825,7 +5861,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 11775-2022</t>
+          <t>A 15046-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5839,10 +5875,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44634</v>
+        <v>44657</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5855,7 +5891,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5898,7 +5934,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 36036-2022</t>
+          <t>A 11775-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5912,10 +5948,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44802</v>
+        <v>44634</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5971,7 +6007,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 36041-2022</t>
+          <t>A 36036-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5988,7 +6024,7 @@
         <v>44802</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6001,7 +6037,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -6044,7 +6080,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 41725-2022</t>
+          <t>A 36041-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6058,10 +6094,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44827</v>
+        <v>44802</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6074,7 +6110,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -6117,7 +6153,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 56569-2021</t>
+          <t>A 9578-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6131,10 +6167,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44480</v>
+        <v>45715</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6147,7 +6183,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -6190,7 +6226,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 11773-2022</t>
+          <t>A 41725-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6204,10 +6240,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44634</v>
+        <v>44827</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6220,7 +6256,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.1</v>
+        <v>0.2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6263,7 +6299,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 40275-2023</t>
+          <t>A 53501-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6277,10 +6313,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45169</v>
+        <v>44879</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6293,7 +6329,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.6</v>
+        <v>7.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6336,7 +6372,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 6667-2025</t>
+          <t>A 27551-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6350,10 +6386,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45700</v>
+        <v>45097</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6366,7 +6402,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6409,7 +6445,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 46702-2024</t>
+          <t>A 11773-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6423,10 +6459,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45583</v>
+        <v>44634</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6439,7 +6475,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6482,7 +6518,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 31789-2023</t>
+          <t>A 39014-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6496,10 +6532,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45118</v>
+        <v>45163</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6512,7 +6548,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6555,7 +6591,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 1644-2025</t>
+          <t>A 19500-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6569,10 +6605,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45670</v>
+        <v>44693</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6585,7 +6621,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6628,7 +6664,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 40287-2025</t>
+          <t>A 56569-2021</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6642,10 +6678,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45895</v>
+        <v>44480</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6658,7 +6694,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6701,7 +6737,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 55545-2022</t>
+          <t>A 29436-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6715,10 +6751,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44887</v>
+        <v>45483</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6731,7 +6767,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6774,7 +6810,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 55529-2024</t>
+          <t>A 12148-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6788,10 +6824,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45622</v>
+        <v>45377</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6804,7 +6840,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6847,7 +6883,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 42826-2025</t>
+          <t>A 8882-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6861,10 +6897,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45908</v>
+        <v>45713</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6877,7 +6913,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6920,7 +6956,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 32020-2025</t>
+          <t>A 44448-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6934,10 +6970,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45835</v>
+        <v>45189</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6950,7 +6986,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6993,7 +7029,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 13662-2025</t>
+          <t>A 57923-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7007,10 +7043,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45736</v>
+        <v>45631</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7023,7 +7059,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>6.4</v>
+        <v>4.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -7066,7 +7102,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 64728-2023</t>
+          <t>A 28264-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7080,10 +7116,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45281</v>
+        <v>44746</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7096,7 +7132,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7139,7 +7175,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 25669-2024</t>
+          <t>A 64728-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7153,10 +7189,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45463</v>
+        <v>45281</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7169,7 +7205,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>17.9</v>
+        <v>1.8</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7212,7 +7248,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 23676-2024</t>
+          <t>A 55545-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7226,10 +7262,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45454</v>
+        <v>44887</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7242,7 +7278,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.9</v>
+        <v>4.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7285,7 +7321,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 9055-2026</t>
+          <t>A 31720-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7299,10 +7335,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46069</v>
+        <v>45117</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7315,7 +7351,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7358,7 +7394,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 8139-2025</t>
+          <t>A 25669-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7372,10 +7408,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45708</v>
+        <v>45463</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7388,7 +7424,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>3.5</v>
+        <v>17.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7431,7 +7467,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 44448-2023</t>
+          <t>A 31143-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7441,14 +7477,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45189</v>
+        <v>45502</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7504,7 +7540,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 31143-2024</t>
+          <t>A 607-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7514,14 +7550,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45502</v>
+        <v>45299</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7577,7 +7613,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 23328-2022</t>
+          <t>A 54709-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7591,10 +7627,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44720</v>
+        <v>45236</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7607,7 +7643,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.1</v>
+        <v>3.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7650,7 +7686,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 15154-2023</t>
+          <t>A 40287-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7664,10 +7700,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45016</v>
+        <v>45895</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7680,7 +7716,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>3.5</v>
+        <v>0.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7723,7 +7759,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 46286-2024</t>
+          <t>A 55544-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7737,10 +7773,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45581</v>
+        <v>44887</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7753,7 +7789,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7796,7 +7832,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 55544-2022</t>
+          <t>A 34514-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7810,10 +7846,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44887</v>
+        <v>45140</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7826,7 +7862,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.1</v>
+        <v>3.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7869,7 +7905,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 52519-2025</t>
+          <t>A 42826-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7883,10 +7919,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45954</v>
+        <v>45908</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7899,7 +7935,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7942,7 +7978,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 9803-2026</t>
+          <t>A 23976-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7956,10 +7992,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46072</v>
+        <v>45456</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7972,7 +8008,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>5</v>
+        <v>0.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -8015,7 +8051,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 7337-2024</t>
+          <t>A 27553-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -8029,10 +8065,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45345</v>
+        <v>45097</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8045,7 +8081,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.6</v>
+        <v>0.8</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8088,7 +8124,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 55728-2025</t>
+          <t>A 9803-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8102,10 +8138,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45972</v>
+        <v>46072</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8118,7 +8154,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8161,7 +8197,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 49610-2024</t>
+          <t>A 28253-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8175,10 +8211,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45596</v>
+        <v>45099</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8191,7 +8227,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>6.4</v>
+        <v>2.7</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8234,7 +8270,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 7707-2025</t>
+          <t>A 16419-2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8248,10 +8284,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45705</v>
+        <v>45022</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8264,7 +8300,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.2</v>
+        <v>4.2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8307,7 +8343,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 19650-2026</t>
+          <t>A 1299-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8321,10 +8357,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>46134</v>
+        <v>45303</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8337,7 +8373,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>8</v>
+        <v>0.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8380,7 +8416,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 13243-2025</t>
+          <t>A 19503-2022</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8394,10 +8430,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45735</v>
+        <v>44693</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8410,7 +8446,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.5</v>
+        <v>5.1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8453,7 +8489,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 57725-2025</t>
+          <t>A 19650-2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8467,10 +8503,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45981</v>
+        <v>46134</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8483,7 +8519,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.1</v>
+        <v>8</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8526,7 +8562,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 58134-2022</t>
+          <t>A 46702-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8540,10 +8576,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44900</v>
+        <v>45583</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8599,7 +8635,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 74214-2021</t>
+          <t>A 7707-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8613,10 +8649,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44553</v>
+        <v>45705</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8629,7 +8665,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>19.8</v>
+        <v>1.2</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8672,7 +8708,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 7811-2023</t>
+          <t>A 52519-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8686,10 +8722,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44973</v>
+        <v>45954</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8702,7 +8738,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8745,7 +8781,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 58137-2022</t>
+          <t>A 58134-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8762,7 +8798,7 @@
         <v>44900</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8775,7 +8811,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8818,7 +8854,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 42105-2022</t>
+          <t>A 49206-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8832,10 +8868,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44830</v>
+        <v>45595</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8848,7 +8884,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8891,7 +8927,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 50652-2023</t>
+          <t>A 31503-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8905,10 +8941,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45210</v>
+        <v>45115</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8921,7 +8957,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8964,7 +9000,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 24855-2024</t>
+          <t>A 74214-2021</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8978,10 +9014,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45461</v>
+        <v>44553</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8994,7 +9030,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2.4</v>
+        <v>19.8</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -9037,7 +9073,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 4755-2024</t>
+          <t>A 55728-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -9051,10 +9087,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45328</v>
+        <v>45972</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9067,7 +9103,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9110,7 +9146,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 14400-2023</t>
+          <t>A 57725-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9124,10 +9160,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45012</v>
+        <v>45981</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9140,7 +9176,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -9183,7 +9219,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 23227-2023</t>
+          <t>A 23328-2022</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9197,10 +9233,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45075</v>
+        <v>44720</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9256,7 +9292,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 9578-2025</t>
+          <t>A 42105-2022</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9270,10 +9306,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45715</v>
+        <v>44830</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9286,7 +9322,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9329,7 +9365,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 8882-2025</t>
+          <t>A 32364-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9343,10 +9379,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45713</v>
+        <v>45120</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9359,7 +9395,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9402,7 +9438,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 43857-2025</t>
+          <t>A 15154-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9416,10 +9452,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45912</v>
+        <v>45016</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9432,7 +9468,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.1</v>
+        <v>3.5</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9475,7 +9511,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 60227-2025</t>
+          <t>A 8139-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9489,10 +9525,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45994</v>
+        <v>45708</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9505,7 +9541,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9548,7 +9584,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 13278-2026</t>
+          <t>A 40275-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9562,10 +9598,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46093</v>
+        <v>45169</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9578,7 +9614,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9621,7 +9657,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 27097-2026</t>
+          <t>A 1644-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9635,10 +9671,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46188</v>
+        <v>45670</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9651,7 +9687,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9694,7 +9730,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 29369-2026</t>
+          <t>A 24855-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9708,10 +9744,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46203</v>
+        <v>45461</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9724,7 +9760,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9767,7 +9803,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 18571-2025</t>
+          <t>A 7871-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9781,10 +9817,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45763</v>
+        <v>45706</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9797,7 +9833,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9840,7 +9876,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 16419-2023</t>
+          <t>A 13243-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9854,10 +9890,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45022</v>
+        <v>45735</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9870,7 +9906,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>4.2</v>
+        <v>0.5</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9913,7 +9949,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 27551-2023</t>
+          <t>A 6667-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9927,10 +9963,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45097</v>
+        <v>45700</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9943,7 +9979,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9986,7 +10022,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 26986-2026</t>
+          <t>A 60227-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10000,10 +10036,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46185</v>
+        <v>45994</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10016,7 +10052,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -10059,7 +10095,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 26978-2026</t>
+          <t>A 43857-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10073,10 +10109,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46185</v>
+        <v>45912</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10089,7 +10125,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>7.7</v>
+        <v>1.1</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -10132,7 +10168,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 2575-2024</t>
+          <t>A 7337-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10146,10 +10182,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45313</v>
+        <v>45345</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10162,7 +10198,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -10205,7 +10241,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 31576-2026</t>
+          <t>A 49610-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10219,10 +10255,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46224</v>
+        <v>45596</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10235,7 +10271,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.6</v>
+        <v>6.4</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10278,7 +10314,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 36001-2026</t>
+          <t>A 58137-2022</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10292,10 +10328,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46266</v>
+        <v>44900</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10308,7 +10344,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10351,7 +10387,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 35912-2026</t>
+          <t>A 13278-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10365,10 +10401,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46266</v>
+        <v>46093</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10381,7 +10417,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10424,7 +10460,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 35677-2026</t>
+          <t>A 2575-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10438,10 +10474,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46265</v>
+        <v>45313</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10454,7 +10490,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>3.1</v>
+        <v>1</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10497,7 +10533,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 35680-2026</t>
+          <t>A 31502-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10511,10 +10547,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46265</v>
+        <v>45115</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10527,7 +10563,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>2.9</v>
+        <v>0.7</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10570,7 +10606,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 35684-2026</t>
+          <t>A 9055-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10584,10 +10620,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46265</v>
+        <v>46069</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10600,7 +10636,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>3.9</v>
+        <v>0.7</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10643,7 +10679,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 4089-2024</t>
+          <t>A 46286-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10657,10 +10693,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45323</v>
+        <v>45581</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10673,7 +10709,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10716,7 +10752,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 28496-2023</t>
+          <t>A 27097-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10730,10 +10766,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45103</v>
+        <v>46188</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10746,7 +10782,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.8</v>
+        <v>4</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10789,7 +10825,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 1299-2024</t>
+          <t>A 7994-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10803,10 +10839,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45303</v>
+        <v>44973</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10819,7 +10855,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10862,7 +10898,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 19255-2026</t>
+          <t>A 14400-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10876,10 +10912,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46132</v>
+        <v>45012</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10892,7 +10928,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10935,7 +10971,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 19256-2026</t>
+          <t>A 4089-2024</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10949,10 +10985,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46132</v>
+        <v>45323</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11008,7 +11044,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 37628-2026</t>
+          <t>A 23676-2024</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -11022,10 +11058,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46276</v>
+        <v>45454</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11037,13 +11073,8 @@
           <t>ÄNGELHOLM</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I123" t="n">
-        <v>4.5</v>
+        <v>0.9</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -11086,7 +11117,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 32364-2023</t>
+          <t>A 29369-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -11100,10 +11131,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45120</v>
+        <v>46203</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11116,7 +11147,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -11159,7 +11190,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 31503-2023</t>
+          <t>A 8665-2022</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11173,10 +11204,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45115</v>
+        <v>44613</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11189,7 +11220,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -11232,7 +11263,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 39014-2023</t>
+          <t>A 18571-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11246,10 +11277,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45163</v>
+        <v>45763</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11262,7 +11293,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11305,7 +11336,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 31908-2023</t>
+          <t>A 31709-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11319,10 +11350,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45118</v>
+        <v>45117</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11335,7 +11366,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11378,7 +11409,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 31502-2023</t>
+          <t>A 23227-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11392,10 +11423,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45115</v>
+        <v>45075</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11408,7 +11439,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11451,7 +11482,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 28253-2023</t>
+          <t>A 50652-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11465,10 +11496,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45099</v>
+        <v>45210</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11481,7 +11512,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11524,7 +11555,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 21488-2023</t>
+          <t>A 60-2024</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11538,10 +11569,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45061</v>
+        <v>45293</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11554,7 +11585,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11597,7 +11628,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 7994-2023</t>
+          <t>A 40278-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11611,10 +11642,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>44973</v>
+        <v>45169</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11627,7 +11658,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11670,7 +11701,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 27553-2023</t>
+          <t>A 58150-2024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11684,10 +11715,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45097</v>
+        <v>45632</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11700,7 +11731,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11743,7 +11774,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 53501-2022</t>
+          <t>A 4755-2024</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11757,10 +11788,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>44879</v>
+        <v>45328</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11773,7 +11804,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>7.2</v>
+        <v>0.9</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11816,7 +11847,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 54709-2023</t>
+          <t>A 31789-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11830,10 +11861,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45236</v>
+        <v>45118</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11846,7 +11877,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>3.6</v>
+        <v>1.1</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11889,7 +11920,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 12148-2024</t>
+          <t>A 32430-2023</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11903,10 +11934,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45377</v>
+        <v>45120</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11919,7 +11950,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11962,7 +11993,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 19500-2022</t>
+          <t>A 28496-2023</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11976,10 +12007,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>44693</v>
+        <v>45103</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11992,7 +12023,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -12052,7 +12083,7 @@
         <v>45687</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12108,7 +12139,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 31720-2023</t>
+          <t>A 21488-2023</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -12122,10 +12153,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45117</v>
+        <v>45061</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12138,7 +12169,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -12181,7 +12212,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 16314-2024</t>
+          <t>A 31908-2023</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12195,10 +12226,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45407</v>
+        <v>45118</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12211,7 +12242,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -12254,7 +12285,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 34514-2023</t>
+          <t>A 31576-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12268,10 +12299,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45140</v>
+        <v>46224</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12284,7 +12315,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>3.1</v>
+        <v>0.6</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -12327,7 +12358,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 46613-2024</t>
+          <t>A 35677-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12341,10 +12372,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45583</v>
+        <v>46265</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12357,7 +12388,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>6.2</v>
+        <v>3.1</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12400,7 +12431,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 23976-2024</t>
+          <t>A 35680-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12414,10 +12445,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45456</v>
+        <v>46265</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12430,7 +12461,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>0.6</v>
+        <v>2.9</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12473,7 +12504,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 40278-2023</t>
+          <t>A 7811-2023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12487,10 +12518,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45169</v>
+        <v>44973</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12503,7 +12534,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12546,7 +12577,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 7871-2025</t>
+          <t>A 36001-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12560,10 +12591,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45706</v>
+        <v>46266</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12576,7 +12607,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12619,7 +12650,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 32430-2023</t>
+          <t>A 35912-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12633,10 +12664,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45120</v>
+        <v>46266</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12649,7 +12680,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12692,7 +12723,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 29436-2024</t>
+          <t>A 16314-2024</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12706,10 +12737,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45483</v>
+        <v>45407</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12722,7 +12753,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>4.2</v>
+        <v>1.1</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12765,7 +12796,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 58150-2024</t>
+          <t>A 19255-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12779,10 +12810,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45632</v>
+        <v>46132</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12795,7 +12826,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12838,7 +12869,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 28264-2022</t>
+          <t>A 19256-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12852,10 +12883,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>44746</v>
+        <v>46132</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12868,7 +12899,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12911,7 +12942,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 31709-2023</t>
+          <t>A 37628-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12925,10 +12956,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45117</v>
+        <v>46276</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12940,8 +12971,13 @@
           <t>ÄNGELHOLM</t>
         </is>
       </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I149" t="n">
-        <v>0.6</v>
+        <v>4.5</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12984,7 +13020,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 8665-2022</t>
+          <t>A 46613-2024</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12998,10 +13034,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>44613</v>
+        <v>45583</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13014,7 +13050,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>0.6</v>
+        <v>6.2</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -13057,7 +13093,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 60-2024</t>
+          <t>A 26978-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -13071,10 +13107,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45293</v>
+        <v>46185</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13087,7 +13123,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.2</v>
+        <v>7.7</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -13130,7 +13166,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 607-2024</t>
+          <t>A 26986-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -13144,10 +13180,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45299</v>
+        <v>46185</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13160,7 +13196,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>0.6</v>
+        <v>3.5</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -13203,7 +13239,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 49206-2024</t>
+          <t>A 20635-2024</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -13217,10 +13253,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45595</v>
+        <v>45436</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13233,7 +13269,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>1.7</v>
+        <v>4.8</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -13276,7 +13312,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 19503-2022</t>
+          <t>A 23980-2024</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -13290,10 +13326,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>44693</v>
+        <v>45456</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13306,7 +13342,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>5.1</v>
+        <v>1.3</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -13349,7 +13385,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 57923-2024</t>
+          <t>A 55748-2024</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13363,10 +13399,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45631</v>
+        <v>45623</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13379,7 +13415,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>4.5</v>
+        <v>0.9</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13422,7 +13458,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 20635-2024</t>
+          <t>A 48197-2024</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13436,10 +13472,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45436</v>
+        <v>45590</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13452,7 +13488,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>4.8</v>
+        <v>3.1</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13495,7 +13531,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 23980-2024</t>
+          <t>A 55529-2024</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13509,10 +13545,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45456</v>
+        <v>45622</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13525,7 +13561,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13568,7 +13604,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 55748-2024</t>
+          <t>A 32020-2025</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13582,10 +13618,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45623</v>
+        <v>45835</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13598,7 +13634,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13641,7 +13677,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 48197-2024</t>
+          <t>A 13662-2025</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13655,10 +13691,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45590</v>
+        <v>45736</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13671,7 +13707,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>3.1</v>
+        <v>6.4</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13731,7 +13767,7 @@
         <v>45582</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13804,7 +13840,7 @@
         <v>45582</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13877,7 +13913,7 @@
         <v>45582</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13950,7 +13986,7 @@
         <v>45582</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14023,7 +14059,7 @@
         <v>44519</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14096,7 +14132,7 @@
         <v>45239</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14169,7 +14205,7 @@
         <v>45168</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14242,7 +14278,7 @@
         <v>44861</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14315,7 +14351,7 @@
         <v>45582</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>

--- a/Översikt ÄNGELHOLM.xlsx
+++ b/Översikt ÄNGELHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45099</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         <v>45931</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
         <v>45931</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>46106</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>44802</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 74502-2021</t>
+          <t>A 32268-2022</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1204,10 +1204,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44560</v>
+        <v>44781</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1220,17 +1220,17 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>5.6</v>
+        <v>8.6</v>
       </c>
       <c r="J7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K7" t="n">
+        <v>5</v>
+      </c>
+      <c r="L7" t="n">
         <v>1</v>
       </c>
-      <c r="L7" t="n">
-        <v>3</v>
-      </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
@@ -1244,7 +1244,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1253,12 +1253,124 @@
         <v>8</v>
       </c>
       <c r="T7" t="n">
+        <v>14</v>
+      </c>
+      <c r="U7" t="n">
+        <v>14</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Bokvårtlav
+Blåmossa
+Dvärghäxört
+Skuggsprötmossa
+Trubbfjädermossa
+Västlig hakmossa
+Vanlig groda
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 32268-2022 artfynd.xlsx", "A 32268-2022")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 32268-2022 karta.png", "A 32268-2022")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 32268-2022 georefererad karta.tif", "A 32268-2022")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 32268-2022 FSC-klagomål.docx", "A 32268-2022")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 32268-2022 FSC-klagomål mail.docx", "A 32268-2022")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 32268-2022 tillsynsbegäran.docx", "A 32268-2022")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 32268-2022 tillsynsbegäran mail.docx", "A 32268-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 74502-2021</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>44560</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J8" t="n">
+        <v>6</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>3</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>8</v>
+      </c>
+      <c r="T8" t="n">
         <v>9</v>
       </c>
-      <c r="U7" t="n">
+      <c r="U8" t="n">
         <v>9</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Entita
 Grönsångare
@@ -1270,148 +1382,36 @@
 Skogsduva</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 74502-2021 artfynd.xlsx", "A 74502-2021")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 74502-2021 karta.png", "A 74502-2021")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 74502-2021 georefererad karta.tif", "A 74502-2021")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 74502-2021 FSC-klagomål.docx", "A 74502-2021")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 74502-2021 FSC-klagomål mail.docx", "A 74502-2021")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 74502-2021 tillsynsbegäran.docx", "A 74502-2021")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 74502-2021 tillsynsbegäran mail.docx", "A 74502-2021")</f>
         <v/>
       </c>
-      <c r="AE7">
+      <c r="AE8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 74502-2021 prioriterade fågelarter.docx", "A 74502-2021")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 32268-2022</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>44781</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="J8" t="n">
-        <v>2</v>
-      </c>
-      <c r="K8" t="n">
-        <v>5</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>8</v>
-      </c>
-      <c r="T8" t="n">
-        <v>14</v>
-      </c>
-      <c r="U8" t="n">
-        <v>14</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Bokvårtlav
-Blåmossa
-Dvärghäxört
-Skuggsprötmossa
-Trubbfjädermossa
-Västlig hakmossa
-Vanlig groda
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 32268-2022 artfynd.xlsx", "A 32268-2022")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 32268-2022 karta.png", "A 32268-2022")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 32268-2022 georefererad karta.tif", "A 32268-2022")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 32268-2022 FSC-klagomål.docx", "A 32268-2022")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 32268-2022 FSC-klagomål mail.docx", "A 32268-2022")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 32268-2022 tillsynsbegäran.docx", "A 32268-2022")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 32268-2022 tillsynsbegäran mail.docx", "A 32268-2022")</f>
         <v/>
       </c>
     </row>
@@ -1435,7 +1435,7 @@
         <v>45835</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 308-2023</t>
+          <t>A 5046-2022</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1547,10 +1547,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44929</v>
+        <v>44593</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1563,19 +1563,19 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.8</v>
+        <v>3</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K10" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1587,10 +1587,10 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" t="n">
         <v>1</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>6</v>
@@ -1599,9 +1599,123 @@
         <v>7</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Grönfink
+Gulsparv
+Kråka
+Kungsfågel
+Sävsparv
+Trädlärka</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 5046-2022 artfynd.xlsx", "A 5046-2022")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 5046-2022 karta.png", "A 5046-2022")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 5046-2022 georefererad karta.tif", "A 5046-2022")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 5046-2022 FSC-klagomål.docx", "A 5046-2022")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 5046-2022 FSC-klagomål mail.docx", "A 5046-2022")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 5046-2022 tillsynsbegäran.docx", "A 5046-2022")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 5046-2022 tillsynsbegäran mail.docx", "A 5046-2022")</f>
+        <v/>
+      </c>
+      <c r="AE10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 5046-2022 prioriterade fågelarter.docx", "A 5046-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 308-2023</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>44929</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>5</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>6</v>
+      </c>
+      <c r="T11" t="n">
+        <v>7</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Bokvårtlav
 Dvärghäxört
@@ -1611,146 +1725,32 @@
 Stor knopplav</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 308-2023 artfynd.xlsx", "A 308-2023")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 308-2023 karta.png", "A 308-2023")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 308-2023 georefererad karta.tif", "A 308-2023")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 308-2023 FSC-klagomål.docx", "A 308-2023")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 308-2023 FSC-klagomål mail.docx", "A 308-2023")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 308-2023 tillsynsbegäran.docx", "A 308-2023")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 308-2023 tillsynsbegäran mail.docx", "A 308-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 5046-2022</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>44593</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>3</v>
-      </c>
-      <c r="J11" t="n">
-        <v>6</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
-      <c r="S11" t="n">
-        <v>6</v>
-      </c>
-      <c r="T11" t="n">
-        <v>7</v>
-      </c>
-      <c r="U11" t="n">
-        <v>6</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Grönfink
-Gulsparv
-Kråka
-Kungsfågel
-Sävsparv
-Trädlärka</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 5046-2022 artfynd.xlsx", "A 5046-2022")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 5046-2022 karta.png", "A 5046-2022")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 5046-2022 georefererad karta.tif", "A 5046-2022")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 5046-2022 FSC-klagomål.docx", "A 5046-2022")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 5046-2022 FSC-klagomål mail.docx", "A 5046-2022")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 5046-2022 tillsynsbegäran.docx", "A 5046-2022")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 5046-2022 tillsynsbegäran mail.docx", "A 5046-2022")</f>
-        <v/>
-      </c>
-      <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 5046-2022 prioriterade fågelarter.docx", "A 5046-2022")</f>
         <v/>
       </c>
     </row>
@@ -1774,7 +1774,7 @@
         <v>45106</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>45245</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>46038</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>46265</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>45664</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         <v>44864</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2444,7 +2444,7 @@
         <v>45301</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 8065-2025</t>
+          <t>A 28874-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2548,10 +2548,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45707</v>
+        <v>45104</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2564,19 +2564,19 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3.3</v>
+        <v>9</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -2588,167 +2588,167 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>3</v>
       </c>
       <c r="T19" t="n">
+        <v>5</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Blåmossa
+Stubbspretmossa
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 28874-2023 artfynd.xlsx", "A 28874-2023")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 28874-2023 karta.png", "A 28874-2023")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 28874-2023 georefererad karta.tif", "A 28874-2023")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 28874-2023 FSC-klagomål.docx", "A 28874-2023")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 28874-2023 FSC-klagomål mail.docx", "A 28874-2023")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 28874-2023 tillsynsbegäran.docx", "A 28874-2023")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 28874-2023 tillsynsbegäran mail.docx", "A 28874-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 8065-2025</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>45707</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
         <v>3</v>
       </c>
-      <c r="U19" t="n">
+      <c r="R20" t="n">
+        <v>1</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
         <v>2</v>
       </c>
-      <c r="V19" s="2" t="inlineStr">
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>Småvänderot
 Gullpudra
 Svinrot</t>
         </is>
       </c>
-      <c r="W19">
+      <c r="W20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 8065-2025 artfynd.xlsx", "A 8065-2025")</f>
         <v/>
       </c>
-      <c r="X19">
+      <c r="X20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 8065-2025 karta.png", "A 8065-2025")</f>
         <v/>
       </c>
-      <c r="Y19">
+      <c r="Y20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 8065-2025 georefererad karta.tif", "A 8065-2025")</f>
         <v/>
       </c>
-      <c r="AA19">
+      <c r="AA20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 8065-2025 FSC-klagomål.docx", "A 8065-2025")</f>
         <v/>
       </c>
-      <c r="AB19">
+      <c r="AB20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 8065-2025 FSC-klagomål mail.docx", "A 8065-2025")</f>
         <v/>
       </c>
-      <c r="AC19">
+      <c r="AC20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 8065-2025 tillsynsbegäran.docx", "A 8065-2025")</f>
         <v/>
       </c>
-      <c r="AD19">
+      <c r="AD20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 8065-2025 tillsynsbegäran mail.docx", "A 8065-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 28874-2023</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>45104</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>9</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1</v>
-      </c>
-      <c r="K20" t="n">
-        <v>2</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3</v>
-      </c>
-      <c r="T20" t="n">
-        <v>5</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Blåmossa
-Stubbspretmossa
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 28874-2023 artfynd.xlsx", "A 28874-2023")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 28874-2023 karta.png", "A 28874-2023")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 28874-2023 georefererad karta.tif", "A 28874-2023")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 28874-2023 FSC-klagomål.docx", "A 28874-2023")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 28874-2023 FSC-klagomål mail.docx", "A 28874-2023")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 28874-2023 tillsynsbegäran.docx", "A 28874-2023")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 28874-2023 tillsynsbegäran mail.docx", "A 28874-2023")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 31907-2023</t>
+          <t>A 50684-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2762,10 +2762,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45118</v>
+        <v>45210</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2778,22 +2778,22 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>5.3</v>
+        <v>1.6</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
         <v>1</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2805,7 +2805,7 @@
         <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S21" t="n">
         <v>3</v>
@@ -2817,256 +2817,256 @@
         <v>0</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Skogsalm
+Kopparödla
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 50684-2023 artfynd.xlsx", "A 50684-2023")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 50684-2023 karta.png", "A 50684-2023")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 50684-2023 georefererad karta.tif", "A 50684-2023")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 50684-2023 FSC-klagomål.docx", "A 50684-2023")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 50684-2023 FSC-klagomål mail.docx", "A 50684-2023")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 50684-2023 tillsynsbegäran.docx", "A 50684-2023")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 50684-2023 tillsynsbegäran mail.docx", "A 50684-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 31907-2023</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>45118</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>Bokvårtlav
 Platt fjädermossa
 Stubbspretmossa</t>
         </is>
       </c>
-      <c r="W21">
+      <c r="W22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 31907-2023 artfynd.xlsx", "A 31907-2023")</f>
         <v/>
       </c>
-      <c r="X21">
+      <c r="X22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 31907-2023 karta.png", "A 31907-2023")</f>
         <v/>
       </c>
-      <c r="Y21">
+      <c r="Y22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 31907-2023 georefererad karta.tif", "A 31907-2023")</f>
         <v/>
       </c>
-      <c r="AA21">
+      <c r="AA22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 31907-2023 FSC-klagomål.docx", "A 31907-2023")</f>
         <v/>
       </c>
-      <c r="AB21">
+      <c r="AB22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 31907-2023 FSC-klagomål mail.docx", "A 31907-2023")</f>
         <v/>
       </c>
-      <c r="AC21">
+      <c r="AC22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 31907-2023 tillsynsbegäran.docx", "A 31907-2023")</f>
         <v/>
       </c>
-      <c r="AD21">
+      <c r="AD22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 31907-2023 tillsynsbegäran mail.docx", "A 31907-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
         <is>
           <t>A 3317-2026</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
         <v>46041</v>
       </c>
-      <c r="E22" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
+      <c r="E23" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
         <v>2.9</v>
       </c>
-      <c r="J22" t="n">
+      <c r="J23" t="n">
         <v>3</v>
       </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
         <v>2</v>
       </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
         <v>2</v>
       </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
         <v>3</v>
       </c>
-      <c r="T22" t="n">
+      <c r="T23" t="n">
         <v>6</v>
       </c>
-      <c r="U22" t="n">
+      <c r="U23" t="n">
         <v>6</v>
       </c>
-      <c r="V22" s="2" t="inlineStr">
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>Entita
 Mindre hackspett
 Gröngöling</t>
         </is>
       </c>
-      <c r="W22">
+      <c r="W23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 3317-2026 artfynd.xlsx", "A 3317-2026")</f>
         <v/>
       </c>
-      <c r="X22">
+      <c r="X23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 3317-2026 karta.png", "A 3317-2026")</f>
         <v/>
       </c>
-      <c r="Y22">
+      <c r="Y23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 3317-2026 georefererad karta.tif", "A 3317-2026")</f>
         <v/>
       </c>
-      <c r="AA22">
+      <c r="AA23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 3317-2026 FSC-klagomål.docx", "A 3317-2026")</f>
         <v/>
       </c>
-      <c r="AB22">
+      <c r="AB23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 3317-2026 FSC-klagomål mail.docx", "A 3317-2026")</f>
         <v/>
       </c>
-      <c r="AC22">
+      <c r="AC23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 3317-2026 tillsynsbegäran.docx", "A 3317-2026")</f>
         <v/>
       </c>
-      <c r="AD22">
+      <c r="AD23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 3317-2026 tillsynsbegäran mail.docx", "A 3317-2026")</f>
         <v/>
       </c>
-      <c r="AE22">
+      <c r="AE23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 3317-2026 prioriterade fågelarter.docx", "A 3317-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>A 50684-2023</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>45210</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J23" t="n">
-        <v>2</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>1</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3</v>
-      </c>
-      <c r="T23" t="n">
-        <v>3</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>Skogsalm
-Kopparödla
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 50684-2023 artfynd.xlsx", "A 50684-2023")</f>
-        <v/>
-      </c>
-      <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 50684-2023 karta.png", "A 50684-2023")</f>
-        <v/>
-      </c>
-      <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 50684-2023 georefererad karta.tif", "A 50684-2023")</f>
-        <v/>
-      </c>
-      <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 50684-2023 FSC-klagomål.docx", "A 50684-2023")</f>
-        <v/>
-      </c>
-      <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 50684-2023 FSC-klagomål mail.docx", "A 50684-2023")</f>
-        <v/>
-      </c>
-      <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 50684-2023 tillsynsbegäran.docx", "A 50684-2023")</f>
-        <v/>
-      </c>
-      <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 50684-2023 tillsynsbegäran mail.docx", "A 50684-2023")</f>
         <v/>
       </c>
     </row>
@@ -3090,7 +3090,7 @@
         <v>45763</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3201,7 +3201,7 @@
         <v>45474</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>45841</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         <v>45105</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3531,7 +3531,7 @@
         <v>44553</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3641,7 +3641,7 @@
         <v>45359</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         <v>45582</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         <v>44839</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>44742</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         <v>44746</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 12150-2024</t>
+          <t>A 44062-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4173,10 +4173,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45377</v>
+        <v>44839</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4189,19 +4189,19 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
@@ -4213,10 +4213,10 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4229,42 +4229,42 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 12150-2024 artfynd.xlsx", "A 12150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 44062-2022 artfynd.xlsx", "A 44062-2022")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 12150-2024 karta.png", "A 12150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 44062-2022 karta.png", "A 44062-2022")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 12150-2024 georefererad karta.tif", "A 12150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 44062-2022 georefererad karta.tif", "A 44062-2022")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 12150-2024 FSC-klagomål.docx", "A 12150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 44062-2022 FSC-klagomål.docx", "A 44062-2022")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 12150-2024 FSC-klagomål mail.docx", "A 12150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 44062-2022 FSC-klagomål mail.docx", "A 44062-2022")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 12150-2024 tillsynsbegäran.docx", "A 12150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 44062-2022 tillsynsbegäran.docx", "A 44062-2022")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 12150-2024 tillsynsbegäran mail.docx", "A 12150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 44062-2022 tillsynsbegäran mail.docx", "A 44062-2022")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 4088-2024</t>
+          <t>A 46487-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4278,10 +4278,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45323</v>
+        <v>45582</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4294,16 +4294,16 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3.8</v>
+        <v>5.8</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
@@ -4318,7 +4318,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -4330,46 +4330,46 @@
         <v>1</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Flikbålmossa</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 4088-2024 artfynd.xlsx", "A 4088-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 46487-2024 artfynd.xlsx", "A 46487-2024")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 4088-2024 karta.png", "A 4088-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 46487-2024 karta.png", "A 46487-2024")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 4088-2024 georefererad karta.tif", "A 4088-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 46487-2024 georefererad karta.tif", "A 46487-2024")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 4088-2024 FSC-klagomål.docx", "A 4088-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 46487-2024 FSC-klagomål.docx", "A 46487-2024")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 4088-2024 FSC-klagomål mail.docx", "A 4088-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 46487-2024 FSC-klagomål mail.docx", "A 46487-2024")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 4088-2024 tillsynsbegäran.docx", "A 4088-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 46487-2024 tillsynsbegäran.docx", "A 46487-2024")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 4088-2024 tillsynsbegäran mail.docx", "A 4088-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 46487-2024 tillsynsbegäran mail.docx", "A 46487-2024")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 50642-2023</t>
+          <t>A 4088-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4383,10 +4383,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45210</v>
+        <v>45323</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4399,17 +4399,17 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.8</v>
+        <v>3.8</v>
       </c>
       <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
         <v>1</v>
       </c>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
       <c r="M36" t="n">
         <v>0</v>
       </c>
@@ -4423,7 +4423,7 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -4439,35 +4439,35 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Flikbålmossa</t>
         </is>
       </c>
       <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 50642-2023 artfynd.xlsx", "A 50642-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 4088-2024 artfynd.xlsx", "A 4088-2024")</f>
         <v/>
       </c>
       <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 50642-2023 karta.png", "A 50642-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 4088-2024 karta.png", "A 4088-2024")</f>
         <v/>
       </c>
       <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 50642-2023 georefererad karta.tif", "A 50642-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 4088-2024 georefererad karta.tif", "A 4088-2024")</f>
         <v/>
       </c>
       <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 50642-2023 FSC-klagomål.docx", "A 50642-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 4088-2024 FSC-klagomål.docx", "A 4088-2024")</f>
         <v/>
       </c>
       <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 50642-2023 FSC-klagomål mail.docx", "A 50642-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 4088-2024 FSC-klagomål mail.docx", "A 4088-2024")</f>
         <v/>
       </c>
       <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 50642-2023 tillsynsbegäran.docx", "A 50642-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 4088-2024 tillsynsbegäran.docx", "A 4088-2024")</f>
         <v/>
       </c>
       <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 50642-2023 tillsynsbegäran mail.docx", "A 50642-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 4088-2024 tillsynsbegäran mail.docx", "A 4088-2024")</f>
         <v/>
       </c>
     </row>
@@ -4491,7 +4491,7 @@
         <v>45462</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4579,7 +4579,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 61094-2021</t>
+          <t>A 12150-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4593,10 +4593,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44498</v>
+        <v>45377</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4609,20 +4609,20 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>6.4</v>
+        <v>1.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
         <v>1</v>
       </c>
-      <c r="L38" t="n">
-        <v>0</v>
-      </c>
-      <c r="M38" t="n">
-        <v>0</v>
-      </c>
       <c r="N38" t="n">
         <v>0</v>
       </c>
@@ -4633,10 +4633,10 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4649,42 +4649,42 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 61094-2021 artfynd.xlsx", "A 61094-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 12150-2024 artfynd.xlsx", "A 12150-2024")</f>
         <v/>
       </c>
       <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 61094-2021 karta.png", "A 61094-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 12150-2024 karta.png", "A 12150-2024")</f>
         <v/>
       </c>
       <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 61094-2021 georefererad karta.tif", "A 61094-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 12150-2024 georefererad karta.tif", "A 12150-2024")</f>
         <v/>
       </c>
       <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 61094-2021 FSC-klagomål.docx", "A 61094-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 12150-2024 FSC-klagomål.docx", "A 12150-2024")</f>
         <v/>
       </c>
       <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 61094-2021 FSC-klagomål mail.docx", "A 61094-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 12150-2024 FSC-klagomål mail.docx", "A 12150-2024")</f>
         <v/>
       </c>
       <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 61094-2021 tillsynsbegäran.docx", "A 61094-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 12150-2024 tillsynsbegäran.docx", "A 12150-2024")</f>
         <v/>
       </c>
       <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 61094-2021 tillsynsbegäran mail.docx", "A 61094-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 12150-2024 tillsynsbegäran mail.docx", "A 12150-2024")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 27094-2026</t>
+          <t>A 61094-2021</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4698,10 +4698,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46188</v>
+        <v>44498</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4714,7 +4714,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4750,46 +4750,46 @@
         <v>1</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 27094-2026 artfynd.xlsx", "A 27094-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 61094-2021 artfynd.xlsx", "A 61094-2021")</f>
         <v/>
       </c>
       <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 27094-2026 karta.png", "A 27094-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 61094-2021 karta.png", "A 61094-2021")</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 27094-2026 georefererad karta.tif", "A 27094-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 61094-2021 georefererad karta.tif", "A 61094-2021")</f>
         <v/>
       </c>
       <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 27094-2026 FSC-klagomål.docx", "A 27094-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 61094-2021 FSC-klagomål.docx", "A 61094-2021")</f>
         <v/>
       </c>
       <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 27094-2026 FSC-klagomål mail.docx", "A 27094-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 61094-2021 FSC-klagomål mail.docx", "A 61094-2021")</f>
         <v/>
       </c>
       <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 27094-2026 tillsynsbegäran.docx", "A 27094-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 61094-2021 tillsynsbegäran.docx", "A 61094-2021")</f>
         <v/>
       </c>
       <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 27094-2026 tillsynsbegäran mail.docx", "A 27094-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 61094-2021 tillsynsbegäran mail.docx", "A 61094-2021")</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 44062-2022</t>
+          <t>A 50642-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4803,10 +4803,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44839</v>
+        <v>45210</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4819,13 +4819,13 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -4855,46 +4855,46 @@
         <v>1</v>
       </c>
       <c r="U40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="W40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 44062-2022 artfynd.xlsx", "A 44062-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 50642-2023 artfynd.xlsx", "A 50642-2023")</f>
         <v/>
       </c>
       <c r="X40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 44062-2022 karta.png", "A 44062-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 50642-2023 karta.png", "A 50642-2023")</f>
         <v/>
       </c>
       <c r="Y40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 44062-2022 georefererad karta.tif", "A 44062-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 50642-2023 georefererad karta.tif", "A 50642-2023")</f>
         <v/>
       </c>
       <c r="AA40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 44062-2022 FSC-klagomål.docx", "A 44062-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 50642-2023 FSC-klagomål.docx", "A 50642-2023")</f>
         <v/>
       </c>
       <c r="AB40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 44062-2022 FSC-klagomål mail.docx", "A 44062-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 50642-2023 FSC-klagomål mail.docx", "A 50642-2023")</f>
         <v/>
       </c>
       <c r="AC40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 44062-2022 tillsynsbegäran.docx", "A 44062-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 50642-2023 tillsynsbegäran.docx", "A 50642-2023")</f>
         <v/>
       </c>
       <c r="AD40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 44062-2022 tillsynsbegäran mail.docx", "A 44062-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 50642-2023 tillsynsbegäran mail.docx", "A 50642-2023")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 35684-2026</t>
+          <t>A 27094-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4908,10 +4908,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46265</v>
+        <v>46188</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4924,16 +4924,16 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.9</v>
+        <v>6.2</v>
       </c>
       <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
         <v>1</v>
       </c>
-      <c r="K41" t="n">
-        <v>0</v>
-      </c>
       <c r="L41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
@@ -4948,7 +4948,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -4960,43 +4960,39 @@
         <v>1</v>
       </c>
       <c r="U41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 35684-2026 artfynd.xlsx", "A 35684-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 27094-2026 artfynd.xlsx", "A 27094-2026")</f>
         <v/>
       </c>
       <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 35684-2026 karta.png", "A 35684-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 27094-2026 karta.png", "A 27094-2026")</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 35684-2026 georefererad karta.tif", "A 35684-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 27094-2026 georefererad karta.tif", "A 27094-2026")</f>
         <v/>
       </c>
       <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 35684-2026 FSC-klagomål.docx", "A 35684-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 27094-2026 FSC-klagomål.docx", "A 27094-2026")</f>
         <v/>
       </c>
       <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 35684-2026 FSC-klagomål mail.docx", "A 35684-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 27094-2026 FSC-klagomål mail.docx", "A 27094-2026")</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 35684-2026 tillsynsbegäran.docx", "A 35684-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 27094-2026 tillsynsbegäran.docx", "A 27094-2026")</f>
         <v/>
       </c>
       <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 35684-2026 tillsynsbegäran mail.docx", "A 35684-2026")</f>
-        <v/>
-      </c>
-      <c r="AE41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 35684-2026 prioriterade fågelarter.docx", "A 35684-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 27094-2026 tillsynsbegäran mail.docx", "A 27094-2026")</f>
         <v/>
       </c>
     </row>
@@ -5020,7 +5016,7 @@
         <v>46224</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5066,10 +5062,10 @@
         <v>1</v>
       </c>
       <c r="T42" t="n">
+        <v>3</v>
+      </c>
+      <c r="U42" t="n">
         <v>2</v>
-      </c>
-      <c r="U42" t="n">
-        <v>1</v>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
@@ -5108,7 +5104,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 46487-2024</t>
+          <t>A 35684-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5122,10 +5118,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45582</v>
+        <v>46265</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5138,7 +5134,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>5.8</v>
+        <v>3.9</v>
       </c>
       <c r="J43" t="n">
         <v>1</v>
@@ -5147,7 +5143,7 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
@@ -5162,7 +5158,7 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
@@ -5178,35 +5174,39 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="W43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 46487-2024 artfynd.xlsx", "A 46487-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 35684-2026 artfynd.xlsx", "A 35684-2026")</f>
         <v/>
       </c>
       <c r="X43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 46487-2024 karta.png", "A 46487-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 35684-2026 karta.png", "A 35684-2026")</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 46487-2024 georefererad karta.tif", "A 46487-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 35684-2026 georefererad karta.tif", "A 35684-2026")</f>
         <v/>
       </c>
       <c r="AA43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 46487-2024 FSC-klagomål.docx", "A 46487-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 35684-2026 FSC-klagomål.docx", "A 35684-2026")</f>
         <v/>
       </c>
       <c r="AB43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 46487-2024 FSC-klagomål mail.docx", "A 46487-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 35684-2026 FSC-klagomål mail.docx", "A 35684-2026")</f>
         <v/>
       </c>
       <c r="AC43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 46487-2024 tillsynsbegäran.docx", "A 46487-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 35684-2026 tillsynsbegäran.docx", "A 35684-2026")</f>
         <v/>
       </c>
       <c r="AD43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 46487-2024 tillsynsbegäran mail.docx", "A 46487-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 35684-2026 tillsynsbegäran mail.docx", "A 35684-2026")</f>
+        <v/>
+      </c>
+      <c r="AE43">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 35684-2026 prioriterade fågelarter.docx", "A 35684-2026")</f>
         <v/>
       </c>
     </row>
@@ -5230,7 +5230,7 @@
         <v>45084</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5335,7 +5335,7 @@
         <v>44862</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5440,7 +5440,7 @@
         <v>44880</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         <v>44839</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5586,7 +5586,7 @@
         <v>44725</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5659,7 +5659,7 @@
         <v>44840</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5732,7 +5732,7 @@
         <v>44498</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5805,7 +5805,7 @@
         <v>44477</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5878,7 +5878,7 @@
         <v>44657</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5951,7 +5951,7 @@
         <v>44634</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6024,7 +6024,7 @@
         <v>44802</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6097,7 +6097,7 @@
         <v>44802</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6153,7 +6153,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 9578-2025</t>
+          <t>A 41725-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6167,10 +6167,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45715</v>
+        <v>44827</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6183,7 +6183,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -6226,7 +6226,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 41725-2022</t>
+          <t>A 56569-2021</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6240,10 +6240,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44827</v>
+        <v>44480</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6256,7 +6256,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.2</v>
+        <v>2.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6299,7 +6299,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 53501-2022</t>
+          <t>A 11773-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6313,10 +6313,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44879</v>
+        <v>44634</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6329,7 +6329,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>7.2</v>
+        <v>1.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6372,7 +6372,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 27551-2023</t>
+          <t>A 40275-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6386,10 +6386,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45097</v>
+        <v>45169</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6445,7 +6445,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 11773-2022</t>
+          <t>A 6667-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6459,10 +6459,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44634</v>
+        <v>45700</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6475,7 +6475,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6518,7 +6518,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 39014-2023</t>
+          <t>A 46702-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6532,10 +6532,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45163</v>
+        <v>45583</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6548,7 +6548,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6591,7 +6591,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 19500-2022</t>
+          <t>A 31789-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6605,10 +6605,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44693</v>
+        <v>45118</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6621,7 +6621,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6664,7 +6664,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 56569-2021</t>
+          <t>A 1644-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44480</v>
+        <v>45670</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6694,7 +6694,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6737,7 +6737,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 29436-2024</t>
+          <t>A 55545-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6751,10 +6751,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45483</v>
+        <v>44887</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6767,7 +6767,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6810,7 +6810,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 12148-2024</t>
+          <t>A 55529-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6824,10 +6824,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45377</v>
+        <v>45622</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6840,7 +6840,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6883,7 +6883,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 8882-2025</t>
+          <t>A 40287-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6897,10 +6897,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45713</v>
+        <v>45895</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6913,7 +6913,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6956,7 +6956,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 44448-2023</t>
+          <t>A 64728-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6970,10 +6970,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45189</v>
+        <v>45281</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6986,7 +6986,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -7029,7 +7029,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 57923-2024</t>
+          <t>A 25669-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7043,10 +7043,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45631</v>
+        <v>45463</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>4.5</v>
+        <v>17.9</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -7102,7 +7102,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 28264-2022</t>
+          <t>A 23676-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7116,10 +7116,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44746</v>
+        <v>45454</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7132,7 +7132,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7175,7 +7175,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 64728-2023</t>
+          <t>A 42826-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7189,10 +7189,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45281</v>
+        <v>45908</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7205,7 +7205,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7248,7 +7248,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 55545-2022</t>
+          <t>A 32020-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7262,10 +7262,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44887</v>
+        <v>45835</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7278,7 +7278,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>4.4</v>
+        <v>0.7</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7321,7 +7321,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 31720-2023</t>
+          <t>A 13662-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7335,10 +7335,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45117</v>
+        <v>45736</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7351,7 +7351,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.5</v>
+        <v>6.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7394,7 +7394,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 25669-2024</t>
+          <t>A 8139-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7408,10 +7408,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45463</v>
+        <v>45708</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7424,7 +7424,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>17.9</v>
+        <v>3.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7467,7 +7467,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 31143-2024</t>
+          <t>A 44448-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7477,14 +7477,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45502</v>
+        <v>45189</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7540,7 +7540,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 607-2024</t>
+          <t>A 31143-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7550,14 +7550,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45299</v>
+        <v>45502</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7613,7 +7613,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 54709-2023</t>
+          <t>A 23328-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7627,10 +7627,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45236</v>
+        <v>44720</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7643,7 +7643,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>3.6</v>
+        <v>1.1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7686,7 +7686,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 40287-2025</t>
+          <t>A 15154-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7700,10 +7700,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45895</v>
+        <v>45016</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7716,7 +7716,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7759,7 +7759,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 55544-2022</t>
+          <t>A 46286-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7773,10 +7773,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44887</v>
+        <v>45581</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7789,7 +7789,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7832,7 +7832,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 34514-2023</t>
+          <t>A 55544-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7846,10 +7846,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45140</v>
+        <v>44887</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7862,7 +7862,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>3.1</v>
+        <v>1.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7905,7 +7905,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 42826-2025</t>
+          <t>A 52519-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7919,10 +7919,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45908</v>
+        <v>45954</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7935,7 +7935,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2.1</v>
+        <v>0.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7978,7 +7978,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 23976-2024</t>
+          <t>A 7337-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7992,10 +7992,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45456</v>
+        <v>45345</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8008,7 +8008,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -8051,7 +8051,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 27553-2023</t>
+          <t>A 49610-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -8065,10 +8065,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45097</v>
+        <v>45596</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8081,7 +8081,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.8</v>
+        <v>6.4</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8124,7 +8124,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 9803-2026</t>
+          <t>A 9055-2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8138,10 +8138,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46072</v>
+        <v>46069</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8154,7 +8154,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>5</v>
+        <v>0.7</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8197,7 +8197,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 28253-2023</t>
+          <t>A 55728-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8211,10 +8211,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45099</v>
+        <v>45972</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8227,7 +8227,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.7</v>
+        <v>1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8270,7 +8270,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 16419-2023</t>
+          <t>A 13243-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8284,10 +8284,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45022</v>
+        <v>45735</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8300,7 +8300,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>4.2</v>
+        <v>0.5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8343,7 +8343,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 1299-2024</t>
+          <t>A 57725-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8357,10 +8357,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45303</v>
+        <v>45981</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8373,7 +8373,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8416,7 +8416,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 19503-2022</t>
+          <t>A 7811-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8430,10 +8430,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44693</v>
+        <v>44973</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8446,7 +8446,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>5.1</v>
+        <v>0.9</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8489,7 +8489,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 19650-2026</t>
+          <t>A 58137-2022</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8503,10 +8503,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46134</v>
+        <v>44900</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8519,7 +8519,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>8</v>
+        <v>0.9</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8562,7 +8562,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 46702-2024</t>
+          <t>A 42105-2022</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8576,10 +8576,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45583</v>
+        <v>44830</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8592,7 +8592,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8635,7 +8635,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 7707-2025</t>
+          <t>A 50652-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8649,10 +8649,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45705</v>
+        <v>45210</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8665,7 +8665,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8708,7 +8708,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 52519-2025</t>
+          <t>A 24855-2024</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8722,10 +8722,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45954</v>
+        <v>45461</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8738,7 +8738,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8781,7 +8781,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 58134-2022</t>
+          <t>A 4755-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8795,10 +8795,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44900</v>
+        <v>45328</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8811,7 +8811,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8854,7 +8854,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 49206-2024</t>
+          <t>A 14400-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8868,10 +8868,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45595</v>
+        <v>45012</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8927,7 +8927,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 31503-2023</t>
+          <t>A 23227-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8941,10 +8941,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45115</v>
+        <v>45075</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -9000,7 +9000,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 74214-2021</t>
+          <t>A 9578-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -9014,10 +9014,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44553</v>
+        <v>45715</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9030,7 +9030,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>19.8</v>
+        <v>0.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -9073,7 +9073,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 55728-2025</t>
+          <t>A 8882-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -9087,10 +9087,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45972</v>
+        <v>45713</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9146,7 +9146,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 57725-2025</t>
+          <t>A 9803-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9160,10 +9160,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45981</v>
+        <v>46072</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9176,7 +9176,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2.1</v>
+        <v>5</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -9219,7 +9219,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 23328-2022</t>
+          <t>A 7707-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9233,10 +9233,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44720</v>
+        <v>45705</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9249,7 +9249,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9292,7 +9292,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 42105-2022</t>
+          <t>A 19650-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9306,10 +9306,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>44830</v>
+        <v>46134</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9322,7 +9322,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9365,7 +9365,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 32364-2023</t>
+          <t>A 58134-2022</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9379,10 +9379,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45120</v>
+        <v>44900</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9395,7 +9395,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9438,7 +9438,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 15154-2023</t>
+          <t>A 18571-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9452,10 +9452,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45016</v>
+        <v>45763</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9468,7 +9468,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>3.5</v>
+        <v>0.9</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9511,7 +9511,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 8139-2025</t>
+          <t>A 16419-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9525,10 +9525,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45708</v>
+        <v>45022</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9541,7 +9541,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9584,7 +9584,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 40275-2023</t>
+          <t>A 27551-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9598,10 +9598,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45169</v>
+        <v>45097</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9657,7 +9657,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 1644-2025</t>
+          <t>A 74214-2021</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9671,10 +9671,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45670</v>
+        <v>44553</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9687,7 +9687,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1</v>
+        <v>19.8</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9730,7 +9730,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 24855-2024</t>
+          <t>A 2575-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9744,10 +9744,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45461</v>
+        <v>45313</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9760,7 +9760,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9803,7 +9803,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 7871-2025</t>
+          <t>A 4089-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9817,10 +9817,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45706</v>
+        <v>45323</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9833,7 +9833,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9876,7 +9876,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 13243-2025</t>
+          <t>A 28496-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9890,10 +9890,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45735</v>
+        <v>45103</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9906,7 +9906,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9949,7 +9949,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 6667-2025</t>
+          <t>A 1299-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9963,10 +9963,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45700</v>
+        <v>45303</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10022,7 +10022,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 60227-2025</t>
+          <t>A 32364-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10036,10 +10036,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45994</v>
+        <v>45120</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10052,7 +10052,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -10095,7 +10095,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 43857-2025</t>
+          <t>A 31503-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10109,10 +10109,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45912</v>
+        <v>45115</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10125,7 +10125,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -10168,7 +10168,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 7337-2024</t>
+          <t>A 39014-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10182,10 +10182,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45345</v>
+        <v>45163</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10198,7 +10198,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -10241,7 +10241,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 49610-2024</t>
+          <t>A 31908-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10255,10 +10255,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45596</v>
+        <v>45118</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10271,7 +10271,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>6.4</v>
+        <v>1.5</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10314,7 +10314,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 58137-2022</t>
+          <t>A 31502-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10328,10 +10328,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>44900</v>
+        <v>45115</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10344,7 +10344,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10387,7 +10387,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 13278-2026</t>
+          <t>A 28253-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10401,10 +10401,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46093</v>
+        <v>45099</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10417,7 +10417,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.7</v>
+        <v>2.7</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10460,7 +10460,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 2575-2024</t>
+          <t>A 21488-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10474,10 +10474,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45313</v>
+        <v>45061</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10490,7 +10490,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10533,7 +10533,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 31502-2023</t>
+          <t>A 7994-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10547,10 +10547,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45115</v>
+        <v>44973</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10563,7 +10563,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10606,7 +10606,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 9055-2026</t>
+          <t>A 27553-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10620,10 +10620,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46069</v>
+        <v>45097</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10636,7 +10636,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10679,7 +10679,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 46286-2024</t>
+          <t>A 43857-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10693,10 +10693,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45581</v>
+        <v>45912</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10709,7 +10709,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10752,7 +10752,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 27097-2026</t>
+          <t>A 60227-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10766,10 +10766,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46188</v>
+        <v>45994</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10782,7 +10782,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10825,7 +10825,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 7994-2023</t>
+          <t>A 13278-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10839,10 +10839,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>44973</v>
+        <v>46093</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10855,7 +10855,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10898,7 +10898,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 14400-2023</t>
+          <t>A 53501-2022</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10912,10 +10912,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45012</v>
+        <v>44879</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10928,7 +10928,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.7</v>
+        <v>7.2</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10971,7 +10971,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 4089-2024</t>
+          <t>A 27097-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10985,10 +10985,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45323</v>
+        <v>46188</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11001,7 +11001,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>0.7</v>
+        <v>4</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -11044,7 +11044,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 23676-2024</t>
+          <t>A 54709-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -11058,10 +11058,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45454</v>
+        <v>45236</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11074,7 +11074,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>0.9</v>
+        <v>3.6</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -11117,7 +11117,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 29369-2026</t>
+          <t>A 12148-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -11131,10 +11131,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46203</v>
+        <v>45377</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11147,7 +11147,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -11190,7 +11190,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 8665-2022</t>
+          <t>A 19500-2022</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11204,10 +11204,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>44613</v>
+        <v>44693</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11220,7 +11220,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -11263,7 +11263,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 18571-2025</t>
+          <t>A 4605-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11277,10 +11277,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45763</v>
+        <v>45687</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11293,7 +11293,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11336,7 +11336,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 31709-2023</t>
+          <t>A 31720-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11353,7 +11353,7 @@
         <v>45117</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11366,7 +11366,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11409,7 +11409,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 23227-2023</t>
+          <t>A 16314-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11423,10 +11423,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45075</v>
+        <v>45407</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11482,7 +11482,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 50652-2023</t>
+          <t>A 34514-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11496,10 +11496,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45210</v>
+        <v>45140</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11512,7 +11512,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11555,7 +11555,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 60-2024</t>
+          <t>A 29369-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11569,10 +11569,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45293</v>
+        <v>46203</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11585,7 +11585,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11628,7 +11628,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 40278-2023</t>
+          <t>A 46613-2024</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11642,10 +11642,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45169</v>
+        <v>45583</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.1</v>
+        <v>6.2</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11701,7 +11701,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 58150-2024</t>
+          <t>A 23976-2024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11715,10 +11715,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45632</v>
+        <v>45456</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11731,7 +11731,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11774,7 +11774,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 4755-2024</t>
+          <t>A 40278-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11788,10 +11788,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45328</v>
+        <v>45169</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11804,7 +11804,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11847,7 +11847,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 31789-2023</t>
+          <t>A 7871-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11861,10 +11861,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45118</v>
+        <v>45706</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11937,7 +11937,7 @@
         <v>45120</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11993,7 +11993,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 28496-2023</t>
+          <t>A 29436-2024</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -12007,10 +12007,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45103</v>
+        <v>45483</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12023,7 +12023,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1.8</v>
+        <v>4.2</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -12066,7 +12066,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 4605-2025</t>
+          <t>A 31576-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -12080,10 +12080,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45687</v>
+        <v>46224</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12096,7 +12096,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -12139,7 +12139,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 21488-2023</t>
+          <t>A 36001-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -12153,10 +12153,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45061</v>
+        <v>46266</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12169,7 +12169,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -12212,7 +12212,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 31908-2023</t>
+          <t>A 35912-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12226,10 +12226,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45118</v>
+        <v>46266</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12242,7 +12242,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -12285,7 +12285,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 31576-2026</t>
+          <t>A 58150-2024</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12299,10 +12299,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46224</v>
+        <v>45632</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12315,7 +12315,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -12358,7 +12358,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 35677-2026</t>
+          <t>A 28264-2022</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12372,10 +12372,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46265</v>
+        <v>44746</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12388,7 +12388,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12431,7 +12431,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 35680-2026</t>
+          <t>A 31709-2023</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12445,10 +12445,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46265</v>
+        <v>45117</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12461,7 +12461,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>2.9</v>
+        <v>0.6</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12504,7 +12504,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 7811-2023</t>
+          <t>A 8665-2022</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12518,10 +12518,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>44973</v>
+        <v>44613</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12534,7 +12534,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12577,7 +12577,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 36001-2026</t>
+          <t>A 60-2024</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12591,10 +12591,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46266</v>
+        <v>45293</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12607,7 +12607,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12650,7 +12650,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 35912-2026</t>
+          <t>A 607-2024</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12664,10 +12664,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46266</v>
+        <v>45299</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12680,7 +12680,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12723,7 +12723,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 16314-2024</t>
+          <t>A 49206-2024</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12737,10 +12737,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45407</v>
+        <v>45595</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12753,7 +12753,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12796,7 +12796,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 19255-2026</t>
+          <t>A 19503-2022</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12810,10 +12810,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46132</v>
+        <v>44693</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12826,7 +12826,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1</v>
+        <v>5.1</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 19256-2026</t>
+          <t>A 19255-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12886,7 +12886,7 @@
         <v>46132</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12899,7 +12899,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12942,7 +12942,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 37628-2026</t>
+          <t>A 19256-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12956,10 +12956,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46276</v>
+        <v>46132</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12971,13 +12971,8 @@
           <t>ÄNGELHOLM</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I149" t="n">
-        <v>4.5</v>
+        <v>0.7</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -13020,7 +13015,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 46613-2024</t>
+          <t>A 37628-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -13034,10 +13029,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45583</v>
+        <v>46276</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13049,8 +13044,13 @@
           <t>ÄNGELHOLM</t>
         </is>
       </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I150" t="n">
-        <v>6.2</v>
+        <v>4.5</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -13093,7 +13093,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 26978-2026</t>
+          <t>A 57923-2024</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -13107,10 +13107,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46185</v>
+        <v>45631</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13123,7 +13123,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>7.7</v>
+        <v>4.5</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -13166,7 +13166,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 26986-2026</t>
+          <t>A 35677-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -13180,10 +13180,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46185</v>
+        <v>46265</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13196,7 +13196,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -13239,7 +13239,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 20635-2024</t>
+          <t>A 26986-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -13253,10 +13253,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45436</v>
+        <v>46185</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13269,7 +13269,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -13312,7 +13312,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 23980-2024</t>
+          <t>A 35680-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -13326,10 +13326,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45456</v>
+        <v>46265</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13342,7 +13342,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1.3</v>
+        <v>2.9</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -13385,7 +13385,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 55748-2024</t>
+          <t>A 20635-2024</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13399,10 +13399,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45623</v>
+        <v>45436</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13415,7 +13415,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>0.9</v>
+        <v>4.8</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13458,7 +13458,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 48197-2024</t>
+          <t>A 26978-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13472,10 +13472,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45590</v>
+        <v>46185</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13488,7 +13488,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>3.1</v>
+        <v>7.7</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13531,7 +13531,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 55529-2024</t>
+          <t>A 23980-2024</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13545,10 +13545,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45622</v>
+        <v>45456</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13561,7 +13561,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13604,7 +13604,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 32020-2025</t>
+          <t>A 55748-2024</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13618,10 +13618,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45835</v>
+        <v>45623</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13634,7 +13634,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13677,7 +13677,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 13662-2025</t>
+          <t>A 48197-2024</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13691,10 +13691,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45736</v>
+        <v>45590</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13707,7 +13707,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>6.4</v>
+        <v>3.1</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13767,7 +13767,7 @@
         <v>45582</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13840,7 +13840,7 @@
         <v>45582</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13913,7 +13913,7 @@
         <v>45582</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13986,7 +13986,7 @@
         <v>45582</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14059,7 +14059,7 @@
         <v>44519</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14132,7 +14132,7 @@
         <v>45239</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14205,7 +14205,7 @@
         <v>45168</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14278,7 +14278,7 @@
         <v>44861</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14351,7 +14351,7 @@
         <v>45582</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>

--- a/Översikt ÄNGELHOLM.xlsx
+++ b/Översikt ÄNGELHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45099</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         <v>45931</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
         <v>45931</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>46106</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>44802</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 32268-2022</t>
+          <t>A 74502-2021</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1204,10 +1204,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44781</v>
+        <v>44560</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1220,16 +1220,16 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>8.6</v>
+        <v>5.6</v>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1244,7 +1244,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1253,12 +1253,128 @@
         <v>8</v>
       </c>
       <c r="T7" t="n">
+        <v>9</v>
+      </c>
+      <c r="U7" t="n">
+        <v>9</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Entita
+Grönsångare
+Sydlig sotticka
+Västlig hakmossa
+Spillkråka
+Gröngöling
+Kungsfågel
+Skogsduva</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 74502-2021 artfynd.xlsx", "A 74502-2021")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 74502-2021 karta.png", "A 74502-2021")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 74502-2021 georefererad karta.tif", "A 74502-2021")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 74502-2021 FSC-klagomål.docx", "A 74502-2021")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 74502-2021 FSC-klagomål mail.docx", "A 74502-2021")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 74502-2021 tillsynsbegäran.docx", "A 74502-2021")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 74502-2021 tillsynsbegäran mail.docx", "A 74502-2021")</f>
+        <v/>
+      </c>
+      <c r="AE7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 74502-2021 prioriterade fågelarter.docx", "A 74502-2021")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 32268-2022</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>44781</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>5</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>8</v>
+      </c>
+      <c r="T8" t="n">
         <v>14</v>
       </c>
-      <c r="U7" t="n">
+      <c r="U8" t="n">
         <v>14</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Bokvårtlav
 Blåmossa
@@ -1270,148 +1386,32 @@
 Vanlig padda</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 32268-2022 artfynd.xlsx", "A 32268-2022")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 32268-2022 karta.png", "A 32268-2022")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 32268-2022 georefererad karta.tif", "A 32268-2022")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 32268-2022 FSC-klagomål.docx", "A 32268-2022")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 32268-2022 FSC-klagomål mail.docx", "A 32268-2022")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 32268-2022 tillsynsbegäran.docx", "A 32268-2022")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 32268-2022 tillsynsbegäran mail.docx", "A 32268-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 74502-2021</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>44560</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="J8" t="n">
-        <v>6</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" t="n">
-        <v>3</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>3</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>8</v>
-      </c>
-      <c r="T8" t="n">
-        <v>9</v>
-      </c>
-      <c r="U8" t="n">
-        <v>9</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Entita
-Grönsångare
-Sydlig sotticka
-Västlig hakmossa
-Spillkråka
-Gröngöling
-Kungsfågel
-Skogsduva</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 74502-2021 artfynd.xlsx", "A 74502-2021")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 74502-2021 karta.png", "A 74502-2021")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 74502-2021 georefererad karta.tif", "A 74502-2021")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 74502-2021 FSC-klagomål.docx", "A 74502-2021")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 74502-2021 FSC-klagomål mail.docx", "A 74502-2021")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 74502-2021 tillsynsbegäran.docx", "A 74502-2021")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 74502-2021 tillsynsbegäran mail.docx", "A 74502-2021")</f>
-        <v/>
-      </c>
-      <c r="AE8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 74502-2021 prioriterade fågelarter.docx", "A 74502-2021")</f>
         <v/>
       </c>
     </row>
@@ -1435,7 +1435,7 @@
         <v>45835</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 5046-2022</t>
+          <t>A 308-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1547,10 +1547,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44593</v>
+        <v>44929</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1563,34 +1563,34 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>3</v>
+        <v>0.8</v>
       </c>
       <c r="J10" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L10" t="n">
         <v>1</v>
       </c>
       <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
         <v>1</v>
       </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2</v>
-      </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>6</v>
@@ -1599,9 +1599,119 @@
         <v>7</v>
       </c>
       <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Bokvårtlav
+Dvärghäxört
+Havstulpanlav
+Klippfrullania
+Platt fjädermossa
+Stor knopplav</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 308-2023 artfynd.xlsx", "A 308-2023")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 308-2023 karta.png", "A 308-2023")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 308-2023 georefererad karta.tif", "A 308-2023")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 308-2023 FSC-klagomål.docx", "A 308-2023")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 308-2023 FSC-klagomål mail.docx", "A 308-2023")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 308-2023 tillsynsbegäran.docx", "A 308-2023")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 308-2023 tillsynsbegäran mail.docx", "A 308-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 5046-2022</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>44593</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>3</v>
+      </c>
+      <c r="J11" t="n">
         <v>6</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>6</v>
+      </c>
+      <c r="T11" t="n">
+        <v>7</v>
+      </c>
+      <c r="U11" t="n">
+        <v>6</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Grönfink
 Gulsparv
@@ -1611,111 +1721,225 @@
 Trädlärka</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 5046-2022 artfynd.xlsx", "A 5046-2022")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 5046-2022 karta.png", "A 5046-2022")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 5046-2022 georefererad karta.tif", "A 5046-2022")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 5046-2022 FSC-klagomål.docx", "A 5046-2022")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 5046-2022 FSC-klagomål mail.docx", "A 5046-2022")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 5046-2022 tillsynsbegäran.docx", "A 5046-2022")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 5046-2022 tillsynsbegäran mail.docx", "A 5046-2022")</f>
         <v/>
       </c>
-      <c r="AE10">
+      <c r="AE11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 5046-2022 prioriterade fågelarter.docx", "A 5046-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 308-2023</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>44929</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>S 2334-2023</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Askåterföring</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>45106</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>6</v>
+      </c>
+      <c r="T12" t="n">
+        <v>6</v>
+      </c>
+      <c r="U12" t="n">
+        <v>6</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Småvänderot
+Vitfläckig guldvinge
+Kambräken
+Spillkråka
+Törnskata
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/S 2334-2023 artfynd.xlsx", "S 2334-2023")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/S 2334-2023 karta.png", "S 2334-2023")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/S 2334-2023 georefererad karta.tif", "S 2334-2023")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/S 2334-2023 FSC-klagomål.docx", "S 2334-2023")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/S 2334-2023 FSC-klagomål mail.docx", "S 2334-2023")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/S 2334-2023 tillsynsbegäran.docx", "S 2334-2023")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/S 2334-2023 tillsynsbegäran mail.docx", "S 2334-2023")</f>
+        <v/>
+      </c>
+      <c r="AE12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/S 2334-2023 prioriterade fågelarter.docx", "S 2334-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>S 4107-2023</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45245</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
         <v>5</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L13" t="n">
         <v>1</v>
       </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
         <v>1</v>
       </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
         <v>6</v>
       </c>
-      <c r="T11" t="n">
+      <c r="T13" t="n">
         <v>7</v>
       </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Bokvårtlav
 Dvärghäxört
@@ -1725,230 +1949,6 @@
 Stor knopplav</t>
         </is>
       </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 308-2023 artfynd.xlsx", "A 308-2023")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 308-2023 karta.png", "A 308-2023")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 308-2023 georefererad karta.tif", "A 308-2023")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 308-2023 FSC-klagomål.docx", "A 308-2023")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 308-2023 FSC-klagomål mail.docx", "A 308-2023")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 308-2023 tillsynsbegäran.docx", "A 308-2023")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 308-2023 tillsynsbegäran mail.docx", "A 308-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>S 2334-2023</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Askåterföring</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>45106</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>47.6</v>
-      </c>
-      <c r="J12" t="n">
-        <v>3</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1</v>
-      </c>
-      <c r="S12" t="n">
-        <v>6</v>
-      </c>
-      <c r="T12" t="n">
-        <v>6</v>
-      </c>
-      <c r="U12" t="n">
-        <v>6</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Småvänderot
-Vitfläckig guldvinge
-Kambräken
-Spillkråka
-Törnskata
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/S 2334-2023 artfynd.xlsx", "S 2334-2023")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/S 2334-2023 karta.png", "S 2334-2023")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/S 2334-2023 georefererad karta.tif", "S 2334-2023")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/S 2334-2023 FSC-klagomål.docx", "S 2334-2023")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/S 2334-2023 FSC-klagomål mail.docx", "S 2334-2023")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/S 2334-2023 tillsynsbegäran.docx", "S 2334-2023")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/S 2334-2023 tillsynsbegäran mail.docx", "S 2334-2023")</f>
-        <v/>
-      </c>
-      <c r="AE12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/S 2334-2023 prioriterade fågelarter.docx", "S 2334-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>S 4107-2023</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45245</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>5</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>6</v>
-      </c>
-      <c r="T13" t="n">
-        <v>7</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Bokvårtlav
-Dvärghäxört
-Havstulpanlav
-Klippfrullania
-Platt fjädermossa
-Stor knopplav</t>
-        </is>
-      </c>
       <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/S 4107-2023 artfynd.xlsx", "S 4107-2023")</f>
         <v/>
@@ -1998,7 +1998,7 @@
         <v>46038</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>46265</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>45664</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 49885-2022</t>
+          <t>A 35680-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2333,10 +2333,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44864</v>
+        <v>46265</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2349,16 +2349,16 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.4</v>
+        <v>2.9</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" t="n">
         <v>1</v>
@@ -2373,7 +2373,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R17" t="n">
         <v>1</v>
@@ -2382,12 +2382,124 @@
         <v>4</v>
       </c>
       <c r="T17" t="n">
+        <v>5</v>
+      </c>
+      <c r="U17" t="n">
+        <v>5</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Vedlavklubba
+Entita
+Blåmossa
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 35680-2026 artfynd.xlsx", "A 35680-2026")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 35680-2026 karta.png", "A 35680-2026")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 35680-2026 georefererad karta.tif", "A 35680-2026")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 35680-2026 FSC-klagomål.docx", "A 35680-2026")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 35680-2026 FSC-klagomål mail.docx", "A 35680-2026")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 35680-2026 tillsynsbegäran.docx", "A 35680-2026")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 35680-2026 tillsynsbegäran mail.docx", "A 35680-2026")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 35680-2026 prioriterade fågelarter.docx", "A 35680-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 49885-2022</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>44864</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1</v>
+      </c>
+      <c r="S18" t="n">
         <v>4</v>
       </c>
-      <c r="U17" t="n">
+      <c r="T18" t="n">
+        <v>4</v>
+      </c>
+      <c r="U18" t="n">
         <v>2</v>
       </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Rosa lundlav
 Guldlockmossa
@@ -2395,1557 +2507,1452 @@
 Rostfläck</t>
         </is>
       </c>
-      <c r="W17">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 49885-2022 artfynd.xlsx", "A 49885-2022")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 49885-2022 karta.png", "A 49885-2022")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 49885-2022 georefererad karta.tif", "A 49885-2022")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 49885-2022 FSC-klagomål.docx", "A 49885-2022")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 49885-2022 FSC-klagomål mail.docx", "A 49885-2022")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 49885-2022 tillsynsbegäran.docx", "A 49885-2022")</f>
         <v/>
       </c>
-      <c r="AD17">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 49885-2022 tillsynsbegäran mail.docx", "A 49885-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A 28874-2023</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>45104</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>9</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3</v>
+      </c>
+      <c r="T19" t="n">
+        <v>5</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Blåmossa
+Stubbspretmossa
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 28874-2023 artfynd.xlsx", "A 28874-2023")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 28874-2023 karta.png", "A 28874-2023")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 28874-2023 georefererad karta.tif", "A 28874-2023")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 28874-2023 FSC-klagomål.docx", "A 28874-2023")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 28874-2023 FSC-klagomål mail.docx", "A 28874-2023")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 28874-2023 tillsynsbegäran.docx", "A 28874-2023")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 28874-2023 tillsynsbegäran mail.docx", "A 28874-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 31907-2023</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>45118</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Bokvårtlav
+Platt fjädermossa
+Stubbspretmossa</t>
+        </is>
+      </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 31907-2023 artfynd.xlsx", "A 31907-2023")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 31907-2023 karta.png", "A 31907-2023")</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 31907-2023 georefererad karta.tif", "A 31907-2023")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 31907-2023 FSC-klagomål.docx", "A 31907-2023")</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 31907-2023 FSC-klagomål mail.docx", "A 31907-2023")</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 31907-2023 tillsynsbegäran.docx", "A 31907-2023")</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 31907-2023 tillsynsbegäran mail.docx", "A 31907-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 8065-2025</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>45707</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Småvänderot
+Gullpudra
+Svinrot</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 8065-2025 artfynd.xlsx", "A 8065-2025")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 8065-2025 karta.png", "A 8065-2025")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 8065-2025 georefererad karta.tif", "A 8065-2025")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 8065-2025 FSC-klagomål.docx", "A 8065-2025")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 8065-2025 FSC-klagomål mail.docx", "A 8065-2025")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 8065-2025 tillsynsbegäran.docx", "A 8065-2025")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 8065-2025 tillsynsbegäran mail.docx", "A 8065-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 50684-2023</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>45210</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>1</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>Skogsalm
+Kopparödla
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 50684-2023 artfynd.xlsx", "A 50684-2023")</f>
+        <v/>
+      </c>
+      <c r="X22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 50684-2023 karta.png", "A 50684-2023")</f>
+        <v/>
+      </c>
+      <c r="Y22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 50684-2023 georefererad karta.tif", "A 50684-2023")</f>
+        <v/>
+      </c>
+      <c r="AA22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 50684-2023 FSC-klagomål.docx", "A 50684-2023")</f>
+        <v/>
+      </c>
+      <c r="AB22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 50684-2023 FSC-klagomål mail.docx", "A 50684-2023")</f>
+        <v/>
+      </c>
+      <c r="AC22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 50684-2023 tillsynsbegäran.docx", "A 50684-2023")</f>
+        <v/>
+      </c>
+      <c r="AD22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 50684-2023 tillsynsbegäran mail.docx", "A 50684-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>A 3317-2026</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>46041</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>2</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3</v>
+      </c>
+      <c r="T23" t="n">
+        <v>6</v>
+      </c>
+      <c r="U23" t="n">
+        <v>6</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>Entita
+Mindre hackspett
+Gröngöling</t>
+        </is>
+      </c>
+      <c r="W23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 3317-2026 artfynd.xlsx", "A 3317-2026")</f>
+        <v/>
+      </c>
+      <c r="X23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 3317-2026 karta.png", "A 3317-2026")</f>
+        <v/>
+      </c>
+      <c r="Y23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 3317-2026 georefererad karta.tif", "A 3317-2026")</f>
+        <v/>
+      </c>
+      <c r="AA23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 3317-2026 FSC-klagomål.docx", "A 3317-2026")</f>
+        <v/>
+      </c>
+      <c r="AB23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 3317-2026 FSC-klagomål mail.docx", "A 3317-2026")</f>
+        <v/>
+      </c>
+      <c r="AC23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 3317-2026 tillsynsbegäran.docx", "A 3317-2026")</f>
+        <v/>
+      </c>
+      <c r="AD23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 3317-2026 tillsynsbegäran mail.docx", "A 3317-2026")</f>
+        <v/>
+      </c>
+      <c r="AE23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 3317-2026 prioriterade fågelarter.docx", "A 3317-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" t="inlineStr">
         <is>
           <t>A 905-2024</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="n">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="n">
         <v>45301</v>
       </c>
-      <c r="E18" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
+      <c r="E24" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
         <v>4.9</v>
       </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
         <v>1</v>
       </c>
-      <c r="L18" t="n">
+      <c r="L24" t="n">
         <v>1</v>
       </c>
-      <c r="M18" t="n">
+      <c r="M24" t="n">
         <v>1</v>
       </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
         <v>2</v>
       </c>
-      <c r="R18" t="n">
+      <c r="R24" t="n">
         <v>1</v>
       </c>
-      <c r="S18" t="n">
+      <c r="S24" t="n">
         <v>3</v>
       </c>
-      <c r="T18" t="n">
+      <c r="T24" t="n">
         <v>3</v>
       </c>
-      <c r="U18" t="n">
+      <c r="U24" t="n">
         <v>2</v>
       </c>
-      <c r="V18" s="2" t="inlineStr">
+      <c r="V24" s="2" t="inlineStr">
         <is>
           <t>Igelkott
 Desmeknopp
 Myskmadra</t>
         </is>
       </c>
-      <c r="W18">
+      <c r="W24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 905-2024 artfynd.xlsx", "A 905-2024")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 905-2024 karta.png", "A 905-2024")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 905-2024 georefererad karta.tif", "A 905-2024")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 905-2024 FSC-klagomål.docx", "A 905-2024")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 905-2024 FSC-klagomål mail.docx", "A 905-2024")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AC24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 905-2024 tillsynsbegäran.docx", "A 905-2024")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AD24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 905-2024 tillsynsbegäran mail.docx", "A 905-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A 28874-2023</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>45104</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>9</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" t="n">
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>A 18559-2025</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="n">
+        <v>45763</v>
+      </c>
+      <c r="E25" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>3</v>
+      </c>
+      <c r="J25" t="n">
+        <v>3</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
         <v>2</v>
       </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
         <v>3</v>
       </c>
-      <c r="T19" t="n">
-        <v>5</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>Blåmossa
-Stubbspretmossa
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 28874-2023 artfynd.xlsx", "A 28874-2023")</f>
-        <v/>
-      </c>
-      <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 28874-2023 karta.png", "A 28874-2023")</f>
-        <v/>
-      </c>
-      <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 28874-2023 georefererad karta.tif", "A 28874-2023")</f>
-        <v/>
-      </c>
-      <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 28874-2023 FSC-klagomål.docx", "A 28874-2023")</f>
-        <v/>
-      </c>
-      <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 28874-2023 FSC-klagomål mail.docx", "A 28874-2023")</f>
-        <v/>
-      </c>
-      <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 28874-2023 tillsynsbegäran.docx", "A 28874-2023")</f>
-        <v/>
-      </c>
-      <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 28874-2023 tillsynsbegäran mail.docx", "A 28874-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 8065-2025</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>45707</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>2</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
+      <c r="T25" t="n">
         <v>3</v>
       </c>
-      <c r="R20" t="n">
-        <v>1</v>
-      </c>
-      <c r="S20" t="n">
+      <c r="U25" t="n">
         <v>3</v>
       </c>
-      <c r="T20" t="n">
-        <v>3</v>
-      </c>
-      <c r="U20" t="n">
-        <v>2</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Småvänderot
-Gullpudra
-Svinrot</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 8065-2025 artfynd.xlsx", "A 8065-2025")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 8065-2025 karta.png", "A 8065-2025")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 8065-2025 georefererad karta.tif", "A 8065-2025")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 8065-2025 FSC-klagomål.docx", "A 8065-2025")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 8065-2025 FSC-klagomål mail.docx", "A 8065-2025")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 8065-2025 tillsynsbegäran.docx", "A 8065-2025")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 8065-2025 tillsynsbegäran mail.docx", "A 8065-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 50684-2023</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>45210</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J21" t="n">
-        <v>2</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>1</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3</v>
-      </c>
-      <c r="T21" t="n">
-        <v>3</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Skogsalm
-Kopparödla
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 50684-2023 artfynd.xlsx", "A 50684-2023")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 50684-2023 karta.png", "A 50684-2023")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 50684-2023 georefererad karta.tif", "A 50684-2023")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 50684-2023 FSC-klagomål.docx", "A 50684-2023")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 50684-2023 FSC-klagomål mail.docx", "A 50684-2023")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 50684-2023 tillsynsbegäran.docx", "A 50684-2023")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 50684-2023 tillsynsbegäran mail.docx", "A 50684-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 31907-2023</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>45118</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>2</v>
-      </c>
-      <c r="L22" t="n">
-        <v>1</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3</v>
-      </c>
-      <c r="T22" t="n">
-        <v>3</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Bokvårtlav
-Platt fjädermossa
-Stubbspretmossa</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 31907-2023 artfynd.xlsx", "A 31907-2023")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 31907-2023 karta.png", "A 31907-2023")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 31907-2023 georefererad karta.tif", "A 31907-2023")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 31907-2023 FSC-klagomål.docx", "A 31907-2023")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 31907-2023 FSC-klagomål mail.docx", "A 31907-2023")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 31907-2023 tillsynsbegäran.docx", "A 31907-2023")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 31907-2023 tillsynsbegäran mail.docx", "A 31907-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>A 3317-2026</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>46041</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J23" t="n">
-        <v>3</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>2</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>2</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3</v>
-      </c>
-      <c r="T23" t="n">
-        <v>6</v>
-      </c>
-      <c r="U23" t="n">
-        <v>6</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>Entita
-Mindre hackspett
-Gröngöling</t>
-        </is>
-      </c>
-      <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 3317-2026 artfynd.xlsx", "A 3317-2026")</f>
-        <v/>
-      </c>
-      <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 3317-2026 karta.png", "A 3317-2026")</f>
-        <v/>
-      </c>
-      <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 3317-2026 georefererad karta.tif", "A 3317-2026")</f>
-        <v/>
-      </c>
-      <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 3317-2026 FSC-klagomål.docx", "A 3317-2026")</f>
-        <v/>
-      </c>
-      <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 3317-2026 FSC-klagomål mail.docx", "A 3317-2026")</f>
-        <v/>
-      </c>
-      <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 3317-2026 tillsynsbegäran.docx", "A 3317-2026")</f>
-        <v/>
-      </c>
-      <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 3317-2026 tillsynsbegäran mail.docx", "A 3317-2026")</f>
-        <v/>
-      </c>
-      <c r="AE23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 3317-2026 prioriterade fågelarter.docx", "A 3317-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>A 18559-2025</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="n">
-        <v>45763</v>
-      </c>
-      <c r="E24" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>3</v>
-      </c>
-      <c r="J24" t="n">
-        <v>3</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>2</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>2</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3</v>
-      </c>
-      <c r="T24" t="n">
-        <v>3</v>
-      </c>
-      <c r="U24" t="n">
-        <v>3</v>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>Grönsångare
 Gulsparv
 Gröngöling</t>
         </is>
       </c>
-      <c r="W24">
+      <c r="W25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 18559-2025 artfynd.xlsx", "A 18559-2025")</f>
         <v/>
       </c>
-      <c r="X24">
+      <c r="X25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 18559-2025 karta.png", "A 18559-2025")</f>
         <v/>
       </c>
-      <c r="Y24">
+      <c r="Y25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 18559-2025 georefererad karta.tif", "A 18559-2025")</f>
         <v/>
       </c>
-      <c r="AA24">
+      <c r="AA25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 18559-2025 FSC-klagomål.docx", "A 18559-2025")</f>
         <v/>
       </c>
-      <c r="AB24">
+      <c r="AB25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 18559-2025 FSC-klagomål mail.docx", "A 18559-2025")</f>
         <v/>
       </c>
-      <c r="AC24">
+      <c r="AC25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 18559-2025 tillsynsbegäran.docx", "A 18559-2025")</f>
         <v/>
       </c>
-      <c r="AD24">
+      <c r="AD25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 18559-2025 tillsynsbegäran mail.docx", "A 18559-2025")</f>
         <v/>
       </c>
-      <c r="AE24">
+      <c r="AE25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 18559-2025 prioriterade fågelarter.docx", "A 18559-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" t="inlineStr">
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" t="inlineStr">
         <is>
           <t>A 27544-2024</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="n">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D26" s="1" t="n">
         <v>45474</v>
       </c>
-      <c r="E25" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
+      <c r="E26" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
         <v>3.2</v>
       </c>
-      <c r="J25" t="n">
+      <c r="J26" t="n">
         <v>1</v>
       </c>
-      <c r="K25" t="n">
+      <c r="K26" t="n">
         <v>1</v>
       </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
         <v>2</v>
       </c>
-      <c r="T25" t="n">
+      <c r="T26" t="n">
         <v>2</v>
       </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>Västlig hakmossa
 Spillkråka</t>
         </is>
       </c>
-      <c r="W25">
+      <c r="W26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 27544-2024 artfynd.xlsx", "A 27544-2024")</f>
         <v/>
       </c>
-      <c r="X25">
+      <c r="X26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 27544-2024 karta.png", "A 27544-2024")</f>
         <v/>
       </c>
-      <c r="Y25">
+      <c r="Y26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 27544-2024 georefererad karta.tif", "A 27544-2024")</f>
         <v/>
       </c>
-      <c r="AA25">
+      <c r="AA26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 27544-2024 FSC-klagomål.docx", "A 27544-2024")</f>
         <v/>
       </c>
-      <c r="AB25">
+      <c r="AB26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 27544-2024 FSC-klagomål mail.docx", "A 27544-2024")</f>
         <v/>
       </c>
-      <c r="AC25">
+      <c r="AC26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 27544-2024 tillsynsbegäran.docx", "A 27544-2024")</f>
         <v/>
       </c>
-      <c r="AD25">
+      <c r="AD26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 27544-2024 tillsynsbegäran mail.docx", "A 27544-2024")</f>
         <v/>
       </c>
-      <c r="AE25">
+      <c r="AE26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 27544-2024 prioriterade fågelarter.docx", "A 27544-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" t="inlineStr">
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" t="inlineStr">
         <is>
           <t>A 33520-2025</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D26" s="1" t="n">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D27" s="1" t="n">
         <v>45841</v>
       </c>
-      <c r="E26" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
+      <c r="E27" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
         <v>2.4</v>
       </c>
-      <c r="J26" t="n">
+      <c r="J27" t="n">
         <v>1</v>
       </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
         <v>1</v>
       </c>
-      <c r="M26" t="n">
+      <c r="M27" t="n">
         <v>1</v>
       </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
         <v>2</v>
       </c>
-      <c r="R26" t="n">
+      <c r="R27" t="n">
         <v>1</v>
       </c>
-      <c r="S26" t="n">
+      <c r="S27" t="n">
         <v>2</v>
       </c>
-      <c r="T26" t="n">
+      <c r="T27" t="n">
         <v>2</v>
       </c>
-      <c r="U26" t="n">
+      <c r="U27" t="n">
         <v>2</v>
       </c>
-      <c r="V26" s="2" t="inlineStr">
+      <c r="V27" s="2" t="inlineStr">
         <is>
           <t>Småvänderot
 Entita</t>
         </is>
       </c>
-      <c r="W26">
+      <c r="W27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 33520-2025 artfynd.xlsx", "A 33520-2025")</f>
         <v/>
       </c>
-      <c r="X26">
+      <c r="X27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 33520-2025 karta.png", "A 33520-2025")</f>
         <v/>
       </c>
-      <c r="Y26">
+      <c r="Y27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 33520-2025 georefererad karta.tif", "A 33520-2025")</f>
         <v/>
       </c>
-      <c r="AA26">
+      <c r="AA27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 33520-2025 FSC-klagomål.docx", "A 33520-2025")</f>
         <v/>
       </c>
-      <c r="AB26">
+      <c r="AB27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 33520-2025 FSC-klagomål mail.docx", "A 33520-2025")</f>
         <v/>
       </c>
-      <c r="AC26">
+      <c r="AC27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 33520-2025 tillsynsbegäran.docx", "A 33520-2025")</f>
         <v/>
       </c>
-      <c r="AD26">
+      <c r="AD27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 33520-2025 tillsynsbegäran mail.docx", "A 33520-2025")</f>
         <v/>
       </c>
-      <c r="AE26">
+      <c r="AE27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 33520-2025 prioriterade fågelarter.docx", "A 33520-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" t="inlineStr">
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" t="inlineStr">
         <is>
           <t>A 29157-2023</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="n">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D28" s="1" t="n">
         <v>45105</v>
       </c>
-      <c r="E27" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
+      <c r="E28" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
         <v>6.9</v>
       </c>
-      <c r="J27" t="n">
+      <c r="J28" t="n">
         <v>2</v>
       </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
         <v>2</v>
       </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
         <v>2</v>
       </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
         <v>2</v>
       </c>
-      <c r="T27" t="n">
+      <c r="T28" t="n">
         <v>2</v>
       </c>
-      <c r="U27" t="n">
+      <c r="U28" t="n">
         <v>2</v>
       </c>
-      <c r="V27" s="2" t="inlineStr">
+      <c r="V28" s="2" t="inlineStr">
         <is>
           <t>Entita
 Talltita</t>
         </is>
       </c>
-      <c r="W27">
+      <c r="W28">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 29157-2023 artfynd.xlsx", "A 29157-2023")</f>
         <v/>
       </c>
-      <c r="X27">
+      <c r="X28">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 29157-2023 karta.png", "A 29157-2023")</f>
         <v/>
       </c>
-      <c r="Y27">
+      <c r="Y28">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 29157-2023 georefererad karta.tif", "A 29157-2023")</f>
         <v/>
       </c>
-      <c r="AA27">
+      <c r="AA28">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 29157-2023 FSC-klagomål.docx", "A 29157-2023")</f>
         <v/>
       </c>
-      <c r="AB27">
+      <c r="AB28">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 29157-2023 FSC-klagomål mail.docx", "A 29157-2023")</f>
         <v/>
       </c>
-      <c r="AC27">
+      <c r="AC28">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 29157-2023 tillsynsbegäran.docx", "A 29157-2023")</f>
         <v/>
       </c>
-      <c r="AD27">
+      <c r="AD28">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 29157-2023 tillsynsbegäran mail.docx", "A 29157-2023")</f>
         <v/>
       </c>
-      <c r="AE27">
+      <c r="AE28">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 29157-2023 prioriterade fågelarter.docx", "A 29157-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1">
-      <c r="A28" t="inlineStr">
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" t="inlineStr">
         <is>
           <t>A 74272-2021</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D28" s="1" t="n">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D29" s="1" t="n">
         <v>44553</v>
       </c>
-      <c r="E28" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I28" t="n">
+      <c r="E29" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
         <v>5</v>
       </c>
-      <c r="J28" t="n">
+      <c r="J29" t="n">
         <v>2</v>
       </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
         <v>1</v>
       </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
         <v>1</v>
       </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="n">
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
         <v>2</v>
       </c>
-      <c r="T28" t="n">
+      <c r="T29" t="n">
         <v>2</v>
       </c>
-      <c r="U28" t="n">
+      <c r="U29" t="n">
         <v>2</v>
       </c>
-      <c r="V28" s="2" t="inlineStr">
+      <c r="V29" s="2" t="inlineStr">
         <is>
           <t>Entita
 Grönsiska</t>
         </is>
       </c>
-      <c r="W28">
+      <c r="W29">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 74272-2021 artfynd.xlsx", "A 74272-2021")</f>
         <v/>
       </c>
-      <c r="X28">
+      <c r="X29">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 74272-2021 karta.png", "A 74272-2021")</f>
         <v/>
       </c>
-      <c r="Y28">
+      <c r="Y29">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 74272-2021 georefererad karta.tif", "A 74272-2021")</f>
         <v/>
       </c>
-      <c r="AA28">
+      <c r="AA29">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 74272-2021 FSC-klagomål.docx", "A 74272-2021")</f>
         <v/>
       </c>
-      <c r="AB28">
+      <c r="AB29">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 74272-2021 FSC-klagomål mail.docx", "A 74272-2021")</f>
         <v/>
       </c>
-      <c r="AC28">
+      <c r="AC29">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 74272-2021 tillsynsbegäran.docx", "A 74272-2021")</f>
         <v/>
       </c>
-      <c r="AD28">
+      <c r="AD29">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 74272-2021 tillsynsbegäran mail.docx", "A 74272-2021")</f>
         <v/>
       </c>
-      <c r="AE28">
+      <c r="AE29">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 74272-2021 prioriterade fågelarter.docx", "A 74272-2021")</f>
         <v/>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1">
-      <c r="A29" t="inlineStr">
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" t="inlineStr">
         <is>
           <t>S 687-2024</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>Askåterföring</t>
         </is>
       </c>
-      <c r="D29" s="1" t="n">
+      <c r="D30" s="1" t="n">
         <v>45359</v>
       </c>
-      <c r="E29" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I29" t="n">
+      <c r="E30" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
         <v>37.1</v>
       </c>
-      <c r="J29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" t="n">
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
         <v>2</v>
       </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="n">
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
         <v>2</v>
       </c>
-      <c r="T29" t="n">
+      <c r="T30" t="n">
         <v>4</v>
       </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
         <is>
           <t>Skuggmossa
 Stubbspretmossa</t>
         </is>
       </c>
-      <c r="W29">
+      <c r="W30">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/S 687-2024 artfynd.xlsx", "S 687-2024")</f>
         <v/>
       </c>
-      <c r="X29">
+      <c r="X30">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/S 687-2024 karta.png", "S 687-2024")</f>
         <v/>
       </c>
-      <c r="Y29">
+      <c r="Y30">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/S 687-2024 georefererad karta.tif", "S 687-2024")</f>
         <v/>
       </c>
-      <c r="AA29">
+      <c r="AA30">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/S 687-2024 FSC-klagomål.docx", "S 687-2024")</f>
         <v/>
       </c>
-      <c r="AB29">
+      <c r="AB30">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/S 687-2024 FSC-klagomål mail.docx", "S 687-2024")</f>
         <v/>
       </c>
-      <c r="AC29">
+      <c r="AC30">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/S 687-2024 tillsynsbegäran.docx", "S 687-2024")</f>
         <v/>
       </c>
-      <c r="AD29">
+      <c r="AD30">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/S 687-2024 tillsynsbegäran mail.docx", "S 687-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1">
-      <c r="A30" t="inlineStr">
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" t="inlineStr">
         <is>
           <t>S 4248-2024</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>Askåterföring</t>
         </is>
       </c>
-      <c r="D30" s="1" t="n">
+      <c r="D31" s="1" t="n">
         <v>45582</v>
       </c>
-      <c r="E30" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I30" t="n">
+      <c r="E31" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
         <v>15.9</v>
       </c>
-      <c r="J30" t="n">
+      <c r="J31" t="n">
         <v>2</v>
       </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
         <v>1</v>
       </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
         <v>1</v>
       </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
         <v>2</v>
       </c>
-      <c r="T30" t="n">
+      <c r="T31" t="n">
         <v>2</v>
       </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
         <is>
           <t>Entita
 Grönsiska</t>
         </is>
       </c>
-      <c r="W30">
+      <c r="W31">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/S 4248-2024 artfynd.xlsx", "S 4248-2024")</f>
         <v/>
       </c>
-      <c r="X30">
+      <c r="X31">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/S 4248-2024 karta.png", "S 4248-2024")</f>
         <v/>
       </c>
-      <c r="Y30">
+      <c r="Y31">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/S 4248-2024 georefererad karta.tif", "S 4248-2024")</f>
         <v/>
       </c>
-      <c r="AA30">
+      <c r="AA31">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/S 4248-2024 FSC-klagomål.docx", "S 4248-2024")</f>
         <v/>
       </c>
-      <c r="AB30">
+      <c r="AB31">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/S 4248-2024 FSC-klagomål mail.docx", "S 4248-2024")</f>
         <v/>
       </c>
-      <c r="AC30">
+      <c r="AC31">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/S 4248-2024 tillsynsbegäran.docx", "S 4248-2024")</f>
         <v/>
       </c>
-      <c r="AD30">
+      <c r="AD31">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/S 4248-2024 tillsynsbegäran mail.docx", "S 4248-2024")</f>
         <v/>
       </c>
-      <c r="AE30">
+      <c r="AE31">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/S 4248-2024 prioriterade fågelarter.docx", "S 4248-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" ht="15" customHeight="1">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>A 44060-2022</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D31" s="1" t="n">
-        <v>44839</v>
-      </c>
-      <c r="E31" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I31" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="n">
-        <v>1</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>1</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1</v>
-      </c>
-      <c r="S31" t="n">
-        <v>1</v>
-      </c>
-      <c r="T31" t="n">
-        <v>1</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" s="2" t="inlineStr">
-        <is>
-          <t>Ask</t>
-        </is>
-      </c>
-      <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 44060-2022 artfynd.xlsx", "A 44060-2022")</f>
-        <v/>
-      </c>
-      <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 44060-2022 karta.png", "A 44060-2022")</f>
-        <v/>
-      </c>
-      <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 44060-2022 georefererad karta.tif", "A 44060-2022")</f>
-        <v/>
-      </c>
-      <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 44060-2022 FSC-klagomål.docx", "A 44060-2022")</f>
-        <v/>
-      </c>
-      <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 44060-2022 FSC-klagomål mail.docx", "A 44060-2022")</f>
-        <v/>
-      </c>
-      <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 44060-2022 tillsynsbegäran.docx", "A 44060-2022")</f>
-        <v/>
-      </c>
-      <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 44060-2022 tillsynsbegäran mail.docx", "A 44060-2022")</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 27327-2022</t>
+          <t>A 44060-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3959,10 +3966,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44742</v>
+        <v>44839</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3975,7 +3982,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3987,10 +3994,10 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
         <v>1</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4011,46 +4018,46 @@
         <v>1</v>
       </c>
       <c r="U32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>Småvänderot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 27327-2022 artfynd.xlsx", "A 27327-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 44060-2022 artfynd.xlsx", "A 44060-2022")</f>
         <v/>
       </c>
       <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 27327-2022 karta.png", "A 27327-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 44060-2022 karta.png", "A 44060-2022")</f>
         <v/>
       </c>
       <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 27327-2022 georefererad karta.tif", "A 27327-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 44060-2022 georefererad karta.tif", "A 44060-2022")</f>
         <v/>
       </c>
       <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 27327-2022 FSC-klagomål.docx", "A 27327-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 44060-2022 FSC-klagomål.docx", "A 44060-2022")</f>
         <v/>
       </c>
       <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 27327-2022 FSC-klagomål mail.docx", "A 27327-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 44060-2022 FSC-klagomål mail.docx", "A 44060-2022")</f>
         <v/>
       </c>
       <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 27327-2022 tillsynsbegäran.docx", "A 27327-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 44060-2022 tillsynsbegäran.docx", "A 44060-2022")</f>
         <v/>
       </c>
       <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 27327-2022 tillsynsbegäran mail.docx", "A 27327-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 44060-2022 tillsynsbegäran mail.docx", "A 44060-2022")</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 28265-2022</t>
+          <t>A 27327-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4064,10 +4071,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44746</v>
+        <v>44742</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4080,20 +4087,20 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3.3</v>
+        <v>0.6</v>
       </c>
       <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
         <v>1</v>
       </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
       <c r="N33" t="n">
         <v>0</v>
       </c>
@@ -4104,10 +4111,10 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -4120,46 +4127,42 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Småvänderot</t>
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 28265-2022 artfynd.xlsx", "A 28265-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 27327-2022 artfynd.xlsx", "A 27327-2022")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 28265-2022 karta.png", "A 28265-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 27327-2022 karta.png", "A 27327-2022")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 28265-2022 georefererad karta.tif", "A 28265-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 27327-2022 georefererad karta.tif", "A 27327-2022")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 28265-2022 FSC-klagomål.docx", "A 28265-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 27327-2022 FSC-klagomål.docx", "A 27327-2022")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 28265-2022 FSC-klagomål mail.docx", "A 28265-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 27327-2022 FSC-klagomål mail.docx", "A 27327-2022")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 28265-2022 tillsynsbegäran.docx", "A 28265-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 27327-2022 tillsynsbegäran.docx", "A 27327-2022")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 28265-2022 tillsynsbegäran mail.docx", "A 28265-2022")</f>
-        <v/>
-      </c>
-      <c r="AE33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 28265-2022 prioriterade fågelarter.docx", "A 28265-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 27327-2022 tillsynsbegäran mail.docx", "A 27327-2022")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 44062-2022</t>
+          <t>A 28265-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4173,10 +4176,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44839</v>
+        <v>44746</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4189,13 +4192,13 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.2</v>
+        <v>3.3</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -4229,42 +4232,46 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 44062-2022 artfynd.xlsx", "A 44062-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 28265-2022 artfynd.xlsx", "A 28265-2022")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 44062-2022 karta.png", "A 44062-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 28265-2022 karta.png", "A 28265-2022")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 44062-2022 georefererad karta.tif", "A 44062-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 28265-2022 georefererad karta.tif", "A 28265-2022")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 44062-2022 FSC-klagomål.docx", "A 44062-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 28265-2022 FSC-klagomål.docx", "A 28265-2022")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 44062-2022 FSC-klagomål mail.docx", "A 44062-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 28265-2022 FSC-klagomål mail.docx", "A 28265-2022")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 44062-2022 tillsynsbegäran.docx", "A 44062-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 28265-2022 tillsynsbegäran.docx", "A 28265-2022")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 44062-2022 tillsynsbegäran mail.docx", "A 44062-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 28265-2022 tillsynsbegäran mail.docx", "A 28265-2022")</f>
+        <v/>
+      </c>
+      <c r="AE34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 28265-2022 prioriterade fågelarter.docx", "A 28265-2022")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 46487-2024</t>
+          <t>A 12150-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4278,10 +4285,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45582</v>
+        <v>45377</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4294,20 +4301,20 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>5.8</v>
+        <v>1.4</v>
       </c>
       <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
         <v>1</v>
       </c>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
       <c r="N35" t="n">
         <v>0</v>
       </c>
@@ -4318,10 +4325,10 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4334,35 +4341,35 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 46487-2024 artfynd.xlsx", "A 46487-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 12150-2024 artfynd.xlsx", "A 12150-2024")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 46487-2024 karta.png", "A 46487-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 12150-2024 karta.png", "A 12150-2024")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 46487-2024 georefererad karta.tif", "A 46487-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 12150-2024 georefererad karta.tif", "A 12150-2024")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 46487-2024 FSC-klagomål.docx", "A 46487-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 12150-2024 FSC-klagomål.docx", "A 12150-2024")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 46487-2024 FSC-klagomål mail.docx", "A 46487-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 12150-2024 FSC-klagomål mail.docx", "A 12150-2024")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 46487-2024 tillsynsbegäran.docx", "A 46487-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 12150-2024 tillsynsbegäran.docx", "A 12150-2024")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 46487-2024 tillsynsbegäran mail.docx", "A 46487-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 12150-2024 tillsynsbegäran mail.docx", "A 12150-2024")</f>
         <v/>
       </c>
     </row>
@@ -4386,7 +4393,7 @@
         <v>45323</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4474,7 +4481,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 25129-2024</t>
+          <t>A 50642-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4488,10 +4495,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45462</v>
+        <v>45210</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4504,16 +4511,16 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>4.6</v>
+        <v>0.8</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
@@ -4528,7 +4535,7 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
@@ -4544,42 +4551,42 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="W37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 25129-2024 artfynd.xlsx", "A 25129-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 50642-2023 artfynd.xlsx", "A 50642-2023")</f>
         <v/>
       </c>
       <c r="X37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 25129-2024 karta.png", "A 25129-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 50642-2023 karta.png", "A 50642-2023")</f>
         <v/>
       </c>
       <c r="Y37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 25129-2024 georefererad karta.tif", "A 25129-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 50642-2023 georefererad karta.tif", "A 50642-2023")</f>
         <v/>
       </c>
       <c r="AA37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 25129-2024 FSC-klagomål.docx", "A 25129-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 50642-2023 FSC-klagomål.docx", "A 50642-2023")</f>
         <v/>
       </c>
       <c r="AB37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 25129-2024 FSC-klagomål mail.docx", "A 25129-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 50642-2023 FSC-klagomål mail.docx", "A 50642-2023")</f>
         <v/>
       </c>
       <c r="AC37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 25129-2024 tillsynsbegäran.docx", "A 25129-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 50642-2023 tillsynsbegäran.docx", "A 50642-2023")</f>
         <v/>
       </c>
       <c r="AD37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 25129-2024 tillsynsbegäran mail.docx", "A 25129-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 50642-2023 tillsynsbegäran mail.docx", "A 50642-2023")</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 12150-2024</t>
+          <t>A 25129-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4593,10 +4600,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45377</v>
+        <v>45462</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4609,7 +4616,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.4</v>
+        <v>4.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4618,10 +4625,10 @@
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
         <v>0</v>
@@ -4636,7 +4643,7 @@
         <v>1</v>
       </c>
       <c r="R38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4645,39 +4652,39 @@
         <v>1</v>
       </c>
       <c r="U38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 12150-2024 artfynd.xlsx", "A 12150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 25129-2024 artfynd.xlsx", "A 25129-2024")</f>
         <v/>
       </c>
       <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 12150-2024 karta.png", "A 12150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 25129-2024 karta.png", "A 25129-2024")</f>
         <v/>
       </c>
       <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 12150-2024 georefererad karta.tif", "A 12150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 25129-2024 georefererad karta.tif", "A 25129-2024")</f>
         <v/>
       </c>
       <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 12150-2024 FSC-klagomål.docx", "A 12150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 25129-2024 FSC-klagomål.docx", "A 25129-2024")</f>
         <v/>
       </c>
       <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 12150-2024 FSC-klagomål mail.docx", "A 12150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 25129-2024 FSC-klagomål mail.docx", "A 25129-2024")</f>
         <v/>
       </c>
       <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 12150-2024 tillsynsbegäran.docx", "A 12150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 25129-2024 tillsynsbegäran.docx", "A 25129-2024")</f>
         <v/>
       </c>
       <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 12150-2024 tillsynsbegäran mail.docx", "A 12150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 25129-2024 tillsynsbegäran mail.docx", "A 25129-2024")</f>
         <v/>
       </c>
     </row>
@@ -4701,7 +4708,7 @@
         <v>44498</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4789,7 +4796,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 50642-2023</t>
+          <t>A 27094-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4803,10 +4810,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45210</v>
+        <v>46188</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4819,13 +4826,13 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.8</v>
+        <v>6.2</v>
       </c>
       <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
         <v>1</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -4859,42 +4866,42 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="W40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 50642-2023 artfynd.xlsx", "A 50642-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 27094-2026 artfynd.xlsx", "A 27094-2026")</f>
         <v/>
       </c>
       <c r="X40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 50642-2023 karta.png", "A 50642-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 27094-2026 karta.png", "A 27094-2026")</f>
         <v/>
       </c>
       <c r="Y40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 50642-2023 georefererad karta.tif", "A 50642-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 27094-2026 georefererad karta.tif", "A 27094-2026")</f>
         <v/>
       </c>
       <c r="AA40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 50642-2023 FSC-klagomål.docx", "A 50642-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 27094-2026 FSC-klagomål.docx", "A 27094-2026")</f>
         <v/>
       </c>
       <c r="AB40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 50642-2023 FSC-klagomål mail.docx", "A 50642-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 27094-2026 FSC-klagomål mail.docx", "A 27094-2026")</f>
         <v/>
       </c>
       <c r="AC40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 50642-2023 tillsynsbegäran.docx", "A 50642-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 27094-2026 tillsynsbegäran.docx", "A 27094-2026")</f>
         <v/>
       </c>
       <c r="AD40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 50642-2023 tillsynsbegäran mail.docx", "A 50642-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 27094-2026 tillsynsbegäran mail.docx", "A 27094-2026")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 27094-2026</t>
+          <t>A 44062-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4908,10 +4915,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46188</v>
+        <v>44839</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4924,7 +4931,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>6.2</v>
+        <v>1.2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4960,46 +4967,46 @@
         <v>1</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 27094-2026 artfynd.xlsx", "A 27094-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 44062-2022 artfynd.xlsx", "A 44062-2022")</f>
         <v/>
       </c>
       <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 27094-2026 karta.png", "A 27094-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 44062-2022 karta.png", "A 44062-2022")</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 27094-2026 georefererad karta.tif", "A 27094-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 44062-2022 georefererad karta.tif", "A 44062-2022")</f>
         <v/>
       </c>
       <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 27094-2026 FSC-klagomål.docx", "A 27094-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 44062-2022 FSC-klagomål.docx", "A 44062-2022")</f>
         <v/>
       </c>
       <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 27094-2026 FSC-klagomål mail.docx", "A 27094-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 44062-2022 FSC-klagomål mail.docx", "A 44062-2022")</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 27094-2026 tillsynsbegäran.docx", "A 27094-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 44062-2022 tillsynsbegäran.docx", "A 44062-2022")</f>
         <v/>
       </c>
       <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 27094-2026 tillsynsbegäran mail.docx", "A 27094-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 44062-2022 tillsynsbegäran mail.docx", "A 44062-2022")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 31599-2026</t>
+          <t>A 35684-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5013,10 +5020,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46224</v>
+        <v>46265</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5029,17 +5036,17 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.7</v>
+        <v>3.9</v>
       </c>
       <c r="J42" t="n">
         <v>1</v>
       </c>
       <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
         <v>1</v>
       </c>
-      <c r="L42" t="n">
-        <v>0</v>
-      </c>
       <c r="M42" t="n">
         <v>0</v>
       </c>
@@ -5053,7 +5060,7 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -5062,49 +5069,53 @@
         <v>1</v>
       </c>
       <c r="T42" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>Ekoxe</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 31599-2026 artfynd.xlsx", "A 31599-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 35684-2026 artfynd.xlsx", "A 35684-2026")</f>
         <v/>
       </c>
       <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 31599-2026 karta.png", "A 31599-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 35684-2026 karta.png", "A 35684-2026")</f>
         <v/>
       </c>
       <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 31599-2026 georefererad karta.tif", "A 31599-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 35684-2026 georefererad karta.tif", "A 35684-2026")</f>
         <v/>
       </c>
       <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 31599-2026 FSC-klagomål.docx", "A 31599-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 35684-2026 FSC-klagomål.docx", "A 35684-2026")</f>
         <v/>
       </c>
       <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 31599-2026 FSC-klagomål mail.docx", "A 31599-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 35684-2026 FSC-klagomål mail.docx", "A 35684-2026")</f>
         <v/>
       </c>
       <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 31599-2026 tillsynsbegäran.docx", "A 31599-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 35684-2026 tillsynsbegäran.docx", "A 35684-2026")</f>
         <v/>
       </c>
       <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 31599-2026 tillsynsbegäran mail.docx", "A 31599-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 35684-2026 tillsynsbegäran mail.docx", "A 35684-2026")</f>
+        <v/>
+      </c>
+      <c r="AE42">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 35684-2026 prioriterade fågelarter.docx", "A 35684-2026")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 35684-2026</t>
+          <t>A 31599-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5118,10 +5129,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46265</v>
+        <v>46224</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5134,16 +5145,16 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>3.9</v>
+        <v>1.7</v>
       </c>
       <c r="J43" t="n">
         <v>1</v>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
@@ -5158,7 +5169,7 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
@@ -5167,70 +5178,66 @@
         <v>1</v>
       </c>
       <c r="T43" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="W43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 35684-2026 artfynd.xlsx", "A 35684-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 31599-2026 artfynd.xlsx", "A 31599-2026")</f>
         <v/>
       </c>
       <c r="X43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 35684-2026 karta.png", "A 35684-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 31599-2026 karta.png", "A 31599-2026")</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 35684-2026 georefererad karta.tif", "A 35684-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 31599-2026 georefererad karta.tif", "A 31599-2026")</f>
         <v/>
       </c>
       <c r="AA43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 35684-2026 FSC-klagomål.docx", "A 35684-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 31599-2026 FSC-klagomål.docx", "A 31599-2026")</f>
         <v/>
       </c>
       <c r="AB43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 35684-2026 FSC-klagomål mail.docx", "A 35684-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 31599-2026 FSC-klagomål mail.docx", "A 31599-2026")</f>
         <v/>
       </c>
       <c r="AC43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 35684-2026 tillsynsbegäran.docx", "A 35684-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 31599-2026 tillsynsbegäran.docx", "A 31599-2026")</f>
         <v/>
       </c>
       <c r="AD43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 35684-2026 tillsynsbegäran mail.docx", "A 35684-2026")</f>
-        <v/>
-      </c>
-      <c r="AE43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 35684-2026 prioriterade fågelarter.docx", "A 35684-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 31599-2026 tillsynsbegäran mail.docx", "A 31599-2026")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>S 1961-2023</t>
+          <t>A 46487-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45084</v>
+        <v>45582</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5243,7 +5250,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>27</v>
+        <v>5.8</v>
       </c>
       <c r="J44" t="n">
         <v>1</v>
@@ -5279,46 +5286,46 @@
         <v>1</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>Huggorm</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/S 1961-2023 artfynd.xlsx", "S 1961-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 46487-2024 artfynd.xlsx", "A 46487-2024")</f>
         <v/>
       </c>
       <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/S 1961-2023 karta.png", "S 1961-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 46487-2024 karta.png", "A 46487-2024")</f>
         <v/>
       </c>
       <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/S 1961-2023 georefererad karta.tif", "S 1961-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 46487-2024 georefererad karta.tif", "A 46487-2024")</f>
         <v/>
       </c>
       <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/S 1961-2023 FSC-klagomål.docx", "S 1961-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 46487-2024 FSC-klagomål.docx", "A 46487-2024")</f>
         <v/>
       </c>
       <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/S 1961-2023 FSC-klagomål mail.docx", "S 1961-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 46487-2024 FSC-klagomål mail.docx", "A 46487-2024")</f>
         <v/>
       </c>
       <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/S 1961-2023 tillsynsbegäran.docx", "S 1961-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 46487-2024 tillsynsbegäran.docx", "A 46487-2024")</f>
         <v/>
       </c>
       <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/S 1961-2023 tillsynsbegäran mail.docx", "S 1961-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 46487-2024 tillsynsbegäran mail.docx", "A 46487-2024")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>S 6121-2022</t>
+          <t>S 1961-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5328,14 +5335,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44862</v>
+        <v>45084</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5348,10 +5355,10 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.1</v>
+        <v>27</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
@@ -5360,7 +5367,7 @@
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
         <v>0</v>
@@ -5372,10 +5379,10 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>1</v>
@@ -5384,63 +5391,63 @@
         <v>1</v>
       </c>
       <c r="U45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>Småvänderot</t>
+          <t>Huggorm</t>
         </is>
       </c>
       <c r="W45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/S 6121-2022 artfynd.xlsx", "S 6121-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/S 1961-2023 artfynd.xlsx", "S 1961-2023")</f>
         <v/>
       </c>
       <c r="X45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/S 6121-2022 karta.png", "S 6121-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/S 1961-2023 karta.png", "S 1961-2023")</f>
         <v/>
       </c>
       <c r="Y45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/S 6121-2022 georefererad karta.tif", "S 6121-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/S 1961-2023 georefererad karta.tif", "S 1961-2023")</f>
         <v/>
       </c>
       <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/S 6121-2022 FSC-klagomål.docx", "S 6121-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/S 1961-2023 FSC-klagomål.docx", "S 1961-2023")</f>
         <v/>
       </c>
       <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/S 6121-2022 FSC-klagomål mail.docx", "S 6121-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/S 1961-2023 FSC-klagomål mail.docx", "S 1961-2023")</f>
         <v/>
       </c>
       <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/S 6121-2022 tillsynsbegäran.docx", "S 6121-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/S 1961-2023 tillsynsbegäran.docx", "S 1961-2023")</f>
         <v/>
       </c>
       <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/S 6121-2022 tillsynsbegäran mail.docx", "S 6121-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/S 1961-2023 tillsynsbegäran mail.docx", "S 1961-2023")</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 53742-2022</t>
+          <t>S 6121-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44880</v>
+        <v>44862</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5453,7 +5460,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5465,7 +5472,7 @@
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N46" t="n">
         <v>0</v>
@@ -5477,26 +5484,58 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
-      </c>
-      <c r="V46" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>Småvänderot</t>
+        </is>
+      </c>
+      <c r="W46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/S 6121-2022 artfynd.xlsx", "S 6121-2022")</f>
+        <v/>
+      </c>
+      <c r="X46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/S 6121-2022 karta.png", "S 6121-2022")</f>
+        <v/>
+      </c>
+      <c r="Y46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/S 6121-2022 georefererad karta.tif", "S 6121-2022")</f>
+        <v/>
+      </c>
+      <c r="AA46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/S 6121-2022 FSC-klagomål.docx", "S 6121-2022")</f>
+        <v/>
+      </c>
+      <c r="AB46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/S 6121-2022 FSC-klagomål mail.docx", "S 6121-2022")</f>
+        <v/>
+      </c>
+      <c r="AC46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/S 6121-2022 tillsynsbegäran.docx", "S 6121-2022")</f>
+        <v/>
+      </c>
+      <c r="AD46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/S 6121-2022 tillsynsbegäran mail.docx", "S 6121-2022")</f>
+        <v/>
+      </c>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 44247-2022</t>
+          <t>A 53742-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5510,10 +5549,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44839</v>
+        <v>44880</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5569,7 +5608,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 24233-2022</t>
+          <t>A 44247-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5583,10 +5622,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44725</v>
+        <v>44839</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5599,7 +5638,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5642,7 +5681,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 44473-2022</t>
+          <t>A 24233-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5656,10 +5695,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44840</v>
+        <v>44725</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5672,7 +5711,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -5715,7 +5754,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 61263-2021</t>
+          <t>A 44473-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5729,10 +5768,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44498</v>
+        <v>44840</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5745,7 +5784,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -5788,7 +5827,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 56094-2021</t>
+          <t>A 61263-2021</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5802,10 +5841,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44477</v>
+        <v>44498</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5818,7 +5857,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5861,7 +5900,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 15046-2022</t>
+          <t>A 56094-2021</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5875,10 +5914,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44657</v>
+        <v>44477</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5891,7 +5930,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5934,7 +5973,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 11775-2022</t>
+          <t>A 15046-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5948,10 +5987,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44634</v>
+        <v>44657</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5964,7 +6003,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -6007,7 +6046,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 36036-2022</t>
+          <t>A 11775-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6021,10 +6060,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44802</v>
+        <v>44634</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6080,7 +6119,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 36041-2022</t>
+          <t>A 36036-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6097,7 +6136,7 @@
         <v>44802</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6110,7 +6149,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -6153,7 +6192,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 41725-2022</t>
+          <t>A 36041-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6167,10 +6206,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44827</v>
+        <v>44802</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6183,7 +6222,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -6226,7 +6265,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 56569-2021</t>
+          <t>A 41725-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6240,10 +6279,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44480</v>
+        <v>44827</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6256,7 +6295,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.4</v>
+        <v>0.2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6299,7 +6338,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 11773-2022</t>
+          <t>A 56569-2021</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6313,10 +6352,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44634</v>
+        <v>44480</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6329,7 +6368,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6372,7 +6411,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 40275-2023</t>
+          <t>A 11773-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6386,10 +6425,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45169</v>
+        <v>44634</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6402,7 +6441,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6445,7 +6484,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 6667-2025</t>
+          <t>A 29436-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6459,10 +6498,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45700</v>
+        <v>45483</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6475,7 +6514,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.5</v>
+        <v>4.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6518,7 +6557,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 46702-2024</t>
+          <t>A 8882-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6532,10 +6571,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45583</v>
+        <v>45713</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6548,7 +6587,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6591,7 +6630,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 31789-2023</t>
+          <t>A 12148-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6605,10 +6644,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45118</v>
+        <v>45377</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6621,7 +6660,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6664,7 +6703,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 1644-2025</t>
+          <t>A 9578-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6678,10 +6717,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45670</v>
+        <v>45715</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6694,7 +6733,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6737,7 +6776,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 55545-2022</t>
+          <t>A 53501-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6751,10 +6790,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44887</v>
+        <v>44879</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6767,7 +6806,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>4.4</v>
+        <v>7.2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6810,7 +6849,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 55529-2024</t>
+          <t>A 27551-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6824,10 +6863,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45622</v>
+        <v>45097</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6840,7 +6879,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6883,7 +6922,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 40287-2025</t>
+          <t>A 64728-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6897,10 +6936,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45895</v>
+        <v>45281</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6913,7 +6952,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6956,7 +6995,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 64728-2023</t>
+          <t>A 31720-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6970,10 +7009,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45281</v>
+        <v>45117</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6986,7 +7025,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -7046,7 +7085,7 @@
         <v>45463</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7102,7 +7141,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 23676-2024</t>
+          <t>A 31143-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7112,14 +7151,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45454</v>
+        <v>45502</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7132,7 +7171,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7175,7 +7214,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 42826-2025</t>
+          <t>A 607-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7189,10 +7228,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45908</v>
+        <v>45299</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7205,7 +7244,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7248,7 +7287,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 32020-2025</t>
+          <t>A 54709-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7262,10 +7301,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45835</v>
+        <v>45236</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7278,7 +7317,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.7</v>
+        <v>3.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7321,7 +7360,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 13662-2025</t>
+          <t>A 55544-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7335,10 +7374,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45736</v>
+        <v>44887</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7351,7 +7390,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>6.4</v>
+        <v>1.1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7394,7 +7433,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 8139-2025</t>
+          <t>A 27553-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7408,10 +7447,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45708</v>
+        <v>45097</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7424,7 +7463,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>3.5</v>
+        <v>0.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7467,7 +7506,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 44448-2023</t>
+          <t>A 23976-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7481,10 +7520,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45189</v>
+        <v>45456</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7540,7 +7579,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 31143-2024</t>
+          <t>A 28253-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7550,14 +7589,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45502</v>
+        <v>45099</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7570,7 +7609,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.6</v>
+        <v>2.7</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7613,7 +7652,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 23328-2022</t>
+          <t>A 16419-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7627,10 +7666,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44720</v>
+        <v>45022</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7643,7 +7682,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.1</v>
+        <v>4.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7686,7 +7725,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 15154-2023</t>
+          <t>A 9055-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7700,10 +7739,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45016</v>
+        <v>46069</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7716,7 +7755,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>3.5</v>
+        <v>0.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7759,7 +7798,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 46286-2024</t>
+          <t>A 19503-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7773,10 +7812,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45581</v>
+        <v>44693</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7789,7 +7828,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2</v>
+        <v>5.1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7832,7 +7871,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 55544-2022</t>
+          <t>A 46702-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7846,10 +7885,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44887</v>
+        <v>45583</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7862,7 +7901,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7905,7 +7944,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 52519-2025</t>
+          <t>A 32020-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7919,10 +7958,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45954</v>
+        <v>45835</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7978,7 +8017,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 7337-2024</t>
+          <t>A 13662-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7992,10 +8031,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45345</v>
+        <v>45736</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8008,7 +8047,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>2.6</v>
+        <v>6.4</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -8051,7 +8090,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 49610-2024</t>
+          <t>A 49206-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -8065,10 +8104,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45596</v>
+        <v>45595</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8081,7 +8120,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>6.4</v>
+        <v>1.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8124,7 +8163,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 9055-2026</t>
+          <t>A 31503-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8138,10 +8177,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>46069</v>
+        <v>45115</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8154,7 +8193,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8197,7 +8236,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 55728-2025</t>
+          <t>A 9803-2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8211,10 +8250,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45972</v>
+        <v>46072</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8227,7 +8266,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8270,7 +8309,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 13243-2025</t>
+          <t>A 40287-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8284,10 +8323,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45735</v>
+        <v>45895</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8343,7 +8382,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 57725-2025</t>
+          <t>A 23328-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8357,10 +8396,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45981</v>
+        <v>44720</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8373,7 +8412,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8416,7 +8455,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 7811-2023</t>
+          <t>A 19650-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8430,10 +8469,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44973</v>
+        <v>46134</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8446,7 +8485,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.9</v>
+        <v>8</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8489,7 +8528,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 58137-2022</t>
+          <t>A 32364-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8503,10 +8542,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>44900</v>
+        <v>45120</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8519,7 +8558,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8562,7 +8601,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 42105-2022</t>
+          <t>A 42826-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8576,10 +8615,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>44830</v>
+        <v>45908</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8592,7 +8631,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8635,7 +8674,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 50652-2023</t>
+          <t>A 7707-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8649,10 +8688,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45210</v>
+        <v>45705</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8665,7 +8704,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8708,7 +8747,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 24855-2024</t>
+          <t>A 8139-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8722,10 +8761,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45461</v>
+        <v>45708</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8738,7 +8777,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2.4</v>
+        <v>3.5</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8781,7 +8820,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 4755-2024</t>
+          <t>A 40275-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8795,10 +8834,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45328</v>
+        <v>45169</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8811,7 +8850,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8854,7 +8893,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 14400-2023</t>
+          <t>A 58134-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8868,10 +8907,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45012</v>
+        <v>44900</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8884,7 +8923,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8927,7 +8966,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 23227-2023</t>
+          <t>A 1644-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8941,10 +8980,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45075</v>
+        <v>45670</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8957,7 +8996,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -9000,7 +9039,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 9578-2025</t>
+          <t>A 74214-2021</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -9014,10 +9053,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45715</v>
+        <v>44553</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9030,7 +9069,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.5</v>
+        <v>19.8</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -9073,7 +9112,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 8882-2025</t>
+          <t>A 24855-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -9087,10 +9126,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45713</v>
+        <v>45461</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9103,7 +9142,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9146,7 +9185,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 9803-2026</t>
+          <t>A 7871-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9160,10 +9199,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>46072</v>
+        <v>45706</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9176,7 +9215,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>5</v>
+        <v>1.1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -9219,7 +9258,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 7707-2025</t>
+          <t>A 13243-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9233,10 +9272,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45705</v>
+        <v>45735</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9249,7 +9288,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9292,7 +9331,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 19650-2026</t>
+          <t>A 6667-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9306,10 +9345,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>46134</v>
+        <v>45700</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9322,7 +9361,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>8</v>
+        <v>0.5</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9365,7 +9404,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 58134-2022</t>
+          <t>A 58137-2022</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9382,7 +9421,7 @@
         <v>44900</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9395,7 +9434,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9438,7 +9477,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 18571-2025</t>
+          <t>A 2575-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9452,10 +9491,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45763</v>
+        <v>45313</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9468,7 +9507,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9511,7 +9550,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 16419-2023</t>
+          <t>A 31502-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9525,10 +9564,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45022</v>
+        <v>45115</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9541,7 +9580,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>4.2</v>
+        <v>0.7</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9584,7 +9623,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 27551-2023</t>
+          <t>A 46286-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9598,10 +9637,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45097</v>
+        <v>45581</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9614,7 +9653,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9657,7 +9696,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 74214-2021</t>
+          <t>A 7994-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9671,10 +9710,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44553</v>
+        <v>44973</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9687,7 +9726,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>19.8</v>
+        <v>0.6</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9730,7 +9769,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 2575-2024</t>
+          <t>A 60227-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9744,10 +9783,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45313</v>
+        <v>45994</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9760,7 +9799,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9803,7 +9842,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 4089-2024</t>
+          <t>A 43857-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9817,10 +9856,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45323</v>
+        <v>45912</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9833,7 +9872,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9876,7 +9915,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 28496-2023</t>
+          <t>A 13278-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9890,10 +9929,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45103</v>
+        <v>46093</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9906,7 +9945,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9949,7 +9988,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 1299-2024</t>
+          <t>A 8665-2022</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9963,10 +10002,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45303</v>
+        <v>44613</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9979,7 +10018,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -10022,7 +10061,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 32364-2023</t>
+          <t>A 18571-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10036,10 +10075,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45120</v>
+        <v>45763</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10052,7 +10091,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -10095,7 +10134,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 31503-2023</t>
+          <t>A 31709-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10109,10 +10148,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45115</v>
+        <v>45117</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10125,7 +10164,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -10168,7 +10207,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 39014-2023</t>
+          <t>A 23227-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10182,10 +10221,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45163</v>
+        <v>45075</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10198,7 +10237,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -10241,7 +10280,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 31908-2023</t>
+          <t>A 52519-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10255,10 +10294,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45118</v>
+        <v>45954</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10271,7 +10310,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10314,7 +10353,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 31502-2023</t>
+          <t>A 50652-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10328,10 +10367,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45115</v>
+        <v>45210</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10344,7 +10383,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10387,7 +10426,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 28253-2023</t>
+          <t>A 27097-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10401,10 +10440,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45099</v>
+        <v>46188</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10417,7 +10456,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>2.7</v>
+        <v>4</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10460,7 +10499,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 21488-2023</t>
+          <t>A 40278-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10474,10 +10513,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45061</v>
+        <v>45169</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10533,7 +10572,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 7994-2023</t>
+          <t>A 55728-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10547,10 +10586,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>44973</v>
+        <v>45972</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10563,7 +10602,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10606,7 +10645,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 27553-2023</t>
+          <t>A 29369-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10620,10 +10659,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45097</v>
+        <v>46203</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10636,7 +10675,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10679,7 +10718,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 43857-2025</t>
+          <t>A 31789-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10693,10 +10732,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45912</v>
+        <v>45118</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10752,7 +10791,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 60227-2025</t>
+          <t>A 57725-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10766,10 +10805,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45994</v>
+        <v>45981</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10782,7 +10821,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10825,7 +10864,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 13278-2026</t>
+          <t>A 39014-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10839,10 +10878,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46093</v>
+        <v>45163</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10855,7 +10894,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10898,7 +10937,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 53501-2022</t>
+          <t>A 19500-2022</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10912,10 +10951,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44879</v>
+        <v>44693</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10928,7 +10967,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>7.2</v>
+        <v>1.2</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10971,7 +11010,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 27097-2026</t>
+          <t>A 44448-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10985,10 +11024,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46188</v>
+        <v>45189</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11001,7 +11040,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>4</v>
+        <v>0.6</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -11044,7 +11083,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 54709-2023</t>
+          <t>A 57923-2024</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -11058,10 +11097,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45236</v>
+        <v>45631</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11074,7 +11113,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -11117,7 +11156,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 12148-2024</t>
+          <t>A 28264-2022</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -11131,10 +11170,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45377</v>
+        <v>44746</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11190,7 +11229,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 19500-2022</t>
+          <t>A 55545-2022</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11204,10 +11243,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>44693</v>
+        <v>44887</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11220,7 +11259,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.2</v>
+        <v>4.4</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -11263,7 +11302,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 4605-2025</t>
+          <t>A 31576-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11277,10 +11316,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45687</v>
+        <v>46224</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11293,7 +11332,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11336,7 +11375,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 31720-2023</t>
+          <t>A 36001-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11350,10 +11389,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45117</v>
+        <v>46266</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11366,7 +11405,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11409,7 +11448,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 16314-2024</t>
+          <t>A 34514-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11423,10 +11462,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45407</v>
+        <v>45140</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11439,7 +11478,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.1</v>
+        <v>3.1</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11482,7 +11521,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 34514-2023</t>
+          <t>A 35912-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11496,10 +11535,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45140</v>
+        <v>46266</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11512,7 +11551,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>3.1</v>
+        <v>1.3</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11555,7 +11594,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 29369-2026</t>
+          <t>A 1299-2024</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11569,10 +11608,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46203</v>
+        <v>45303</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11585,7 +11624,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11628,7 +11667,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 46613-2024</t>
+          <t>A 19255-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11642,10 +11681,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45583</v>
+        <v>46132</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11658,7 +11697,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>6.2</v>
+        <v>1</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11701,7 +11740,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 23976-2024</t>
+          <t>A 19256-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11715,10 +11754,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45456</v>
+        <v>46132</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11731,7 +11770,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11774,7 +11813,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 40278-2023</t>
+          <t>A 37628-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11788,10 +11827,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45169</v>
+        <v>46276</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11803,8 +11842,13 @@
           <t>ÄNGELHOLM</t>
         </is>
       </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I133" t="n">
-        <v>1.1</v>
+        <v>4.5</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11847,7 +11891,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 7871-2025</t>
+          <t>A 26978-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11861,10 +11905,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45706</v>
+        <v>46185</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11877,7 +11921,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1.1</v>
+        <v>7.7</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11920,7 +11964,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 32430-2023</t>
+          <t>A 26986-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11934,10 +11978,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45120</v>
+        <v>46185</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11950,7 +11994,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>0.9</v>
+        <v>3.5</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11993,7 +12037,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 29436-2024</t>
+          <t>A 42105-2022</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -12007,10 +12051,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45483</v>
+        <v>44830</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12023,7 +12067,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>4.2</v>
+        <v>1</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -12066,7 +12110,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 31576-2026</t>
+          <t>A 35677-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -12080,10 +12124,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46224</v>
+        <v>46265</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12096,7 +12140,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>0.6</v>
+        <v>3.1</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -12139,7 +12183,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 36001-2026</t>
+          <t>A 15154-2023</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -12153,10 +12197,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46266</v>
+        <v>45016</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12169,7 +12213,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>0.8</v>
+        <v>3.5</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -12212,7 +12256,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 35912-2026</t>
+          <t>A 7337-2024</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12226,10 +12270,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46266</v>
+        <v>45345</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12242,7 +12286,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -12285,7 +12329,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 58150-2024</t>
+          <t>A 49610-2024</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12299,10 +12343,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45632</v>
+        <v>45596</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12315,7 +12359,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>0.5</v>
+        <v>6.4</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -12358,7 +12402,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 28264-2022</t>
+          <t>A 14400-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12372,10 +12416,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>44746</v>
+        <v>45012</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12388,7 +12432,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12431,7 +12475,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 31709-2023</t>
+          <t>A 4089-2024</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12445,10 +12489,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45117</v>
+        <v>45323</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12461,7 +12505,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12504,7 +12548,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 8665-2022</t>
+          <t>A 23676-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12518,10 +12562,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>44613</v>
+        <v>45454</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12534,7 +12578,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12594,7 +12638,7 @@
         <v>45293</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12650,7 +12694,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 607-2024</t>
+          <t>A 58150-2024</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12664,10 +12708,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45299</v>
+        <v>45632</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12680,7 +12724,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12723,7 +12767,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 49206-2024</t>
+          <t>A 4755-2024</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12737,10 +12781,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45595</v>
+        <v>45328</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12753,7 +12797,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12796,7 +12840,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 19503-2022</t>
+          <t>A 32430-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12810,10 +12854,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>44693</v>
+        <v>45120</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12826,7 +12870,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>5.1</v>
+        <v>0.9</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12869,7 +12913,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 19255-2026</t>
+          <t>A 28496-2023</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12883,10 +12927,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46132</v>
+        <v>45103</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12899,7 +12943,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12942,7 +12986,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 19256-2026</t>
+          <t>A 4605-2025</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12956,10 +13000,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46132</v>
+        <v>45687</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12972,7 +13016,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -13015,7 +13059,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 37628-2026</t>
+          <t>A 21488-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -13029,10 +13073,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46276</v>
+        <v>45061</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13044,13 +13088,8 @@
           <t>ÄNGELHOLM</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I150" t="n">
-        <v>4.5</v>
+        <v>1.1</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -13093,7 +13132,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 57923-2024</t>
+          <t>A 31908-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -13107,10 +13146,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45631</v>
+        <v>45118</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13123,7 +13162,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>4.5</v>
+        <v>1.5</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -13166,7 +13205,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 35677-2026</t>
+          <t>A 7811-2023</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -13180,10 +13219,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46265</v>
+        <v>44973</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13196,7 +13235,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>3.1</v>
+        <v>0.9</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -13239,7 +13278,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 26986-2026</t>
+          <t>A 16314-2024</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -13253,10 +13292,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46185</v>
+        <v>45407</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13269,7 +13308,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>3.5</v>
+        <v>1.1</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -13312,7 +13351,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 35680-2026</t>
+          <t>A 46613-2024</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -13326,10 +13365,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46265</v>
+        <v>45583</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13342,7 +13381,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>2.9</v>
+        <v>6.2</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -13402,7 +13441,7 @@
         <v>45436</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13458,7 +13497,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 26978-2026</t>
+          <t>A 23980-2024</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13472,10 +13511,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46185</v>
+        <v>45456</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13488,7 +13527,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>7.7</v>
+        <v>1.3</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13531,7 +13570,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 23980-2024</t>
+          <t>A 55748-2024</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13545,10 +13584,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45456</v>
+        <v>45623</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13561,7 +13600,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13604,7 +13643,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 55748-2024</t>
+          <t>A 48197-2024</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13618,10 +13657,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45623</v>
+        <v>45590</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13634,7 +13673,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>0.9</v>
+        <v>3.1</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13677,7 +13716,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 48197-2024</t>
+          <t>A 55529-2024</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13691,10 +13730,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45590</v>
+        <v>45622</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13707,7 +13746,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13767,7 +13806,7 @@
         <v>45582</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13840,7 +13879,7 @@
         <v>45582</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13913,7 +13952,7 @@
         <v>45582</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13986,7 +14025,7 @@
         <v>45582</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14059,7 +14098,7 @@
         <v>44519</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14132,7 +14171,7 @@
         <v>45239</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14205,7 +14244,7 @@
         <v>45168</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14278,7 +14317,7 @@
         <v>44861</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14351,7 +14390,7 @@
         <v>45582</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>

--- a/Översikt ÄNGELHOLM.xlsx
+++ b/Översikt ÄNGELHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45099</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         <v>45931</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
         <v>45931</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>46106</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>44802</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 74502-2021</t>
+          <t>A 32268-2022</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1204,10 +1204,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44560</v>
+        <v>44781</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1220,17 +1220,17 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>5.6</v>
+        <v>8.6</v>
       </c>
       <c r="J7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K7" t="n">
+        <v>5</v>
+      </c>
+      <c r="L7" t="n">
         <v>1</v>
       </c>
-      <c r="L7" t="n">
-        <v>3</v>
-      </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
@@ -1244,7 +1244,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1253,12 +1253,124 @@
         <v>8</v>
       </c>
       <c r="T7" t="n">
+        <v>14</v>
+      </c>
+      <c r="U7" t="n">
+        <v>14</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Bokvårtlav
+Blåmossa
+Dvärghäxört
+Skuggsprötmossa
+Trubbfjädermossa
+Västlig hakmossa
+Vanlig groda
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 32268-2022 artfynd.xlsx", "A 32268-2022")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 32268-2022 karta.png", "A 32268-2022")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 32268-2022 georefererad karta.tif", "A 32268-2022")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 32268-2022 FSC-klagomål.docx", "A 32268-2022")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 32268-2022 FSC-klagomål mail.docx", "A 32268-2022")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 32268-2022 tillsynsbegäran.docx", "A 32268-2022")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 32268-2022 tillsynsbegäran mail.docx", "A 32268-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 74502-2021</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>44560</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J8" t="n">
+        <v>6</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>3</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>8</v>
+      </c>
+      <c r="T8" t="n">
         <v>9</v>
       </c>
-      <c r="U7" t="n">
+      <c r="U8" t="n">
         <v>9</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Entita
 Grönsångare
@@ -1270,148 +1382,36 @@
 Skogsduva</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 74502-2021 artfynd.xlsx", "A 74502-2021")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 74502-2021 karta.png", "A 74502-2021")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 74502-2021 georefererad karta.tif", "A 74502-2021")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 74502-2021 FSC-klagomål.docx", "A 74502-2021")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 74502-2021 FSC-klagomål mail.docx", "A 74502-2021")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 74502-2021 tillsynsbegäran.docx", "A 74502-2021")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 74502-2021 tillsynsbegäran mail.docx", "A 74502-2021")</f>
         <v/>
       </c>
-      <c r="AE7">
+      <c r="AE8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 74502-2021 prioriterade fågelarter.docx", "A 74502-2021")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 32268-2022</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>44781</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="J8" t="n">
-        <v>2</v>
-      </c>
-      <c r="K8" t="n">
-        <v>5</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>8</v>
-      </c>
-      <c r="T8" t="n">
-        <v>14</v>
-      </c>
-      <c r="U8" t="n">
-        <v>14</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Bokvårtlav
-Blåmossa
-Dvärghäxört
-Skuggsprötmossa
-Trubbfjädermossa
-Västlig hakmossa
-Vanlig groda
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 32268-2022 artfynd.xlsx", "A 32268-2022")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 32268-2022 karta.png", "A 32268-2022")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 32268-2022 georefererad karta.tif", "A 32268-2022")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 32268-2022 FSC-klagomål.docx", "A 32268-2022")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 32268-2022 FSC-klagomål mail.docx", "A 32268-2022")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 32268-2022 tillsynsbegäran.docx", "A 32268-2022")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 32268-2022 tillsynsbegäran mail.docx", "A 32268-2022")</f>
         <v/>
       </c>
     </row>
@@ -1435,7 +1435,7 @@
         <v>45835</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 308-2023</t>
+          <t>A 5046-2022</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1547,10 +1547,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44929</v>
+        <v>44593</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1563,19 +1563,19 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.8</v>
+        <v>3</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K10" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1587,10 +1587,10 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" t="n">
         <v>1</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>6</v>
@@ -1599,9 +1599,123 @@
         <v>7</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Grönfink
+Gulsparv
+Kråka
+Kungsfågel
+Sävsparv
+Trädlärka</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 5046-2022 artfynd.xlsx", "A 5046-2022")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 5046-2022 karta.png", "A 5046-2022")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 5046-2022 georefererad karta.tif", "A 5046-2022")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 5046-2022 FSC-klagomål.docx", "A 5046-2022")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 5046-2022 FSC-klagomål mail.docx", "A 5046-2022")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 5046-2022 tillsynsbegäran.docx", "A 5046-2022")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 5046-2022 tillsynsbegäran mail.docx", "A 5046-2022")</f>
+        <v/>
+      </c>
+      <c r="AE10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 5046-2022 prioriterade fågelarter.docx", "A 5046-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 308-2023</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>44929</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>5</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>6</v>
+      </c>
+      <c r="T11" t="n">
+        <v>7</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Bokvårtlav
 Dvärghäxört
@@ -1611,146 +1725,32 @@
 Stor knopplav</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 308-2023 artfynd.xlsx", "A 308-2023")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 308-2023 karta.png", "A 308-2023")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 308-2023 georefererad karta.tif", "A 308-2023")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 308-2023 FSC-klagomål.docx", "A 308-2023")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 308-2023 FSC-klagomål mail.docx", "A 308-2023")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 308-2023 tillsynsbegäran.docx", "A 308-2023")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 308-2023 tillsynsbegäran mail.docx", "A 308-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 5046-2022</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>44593</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>3</v>
-      </c>
-      <c r="J11" t="n">
-        <v>6</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
-      <c r="S11" t="n">
-        <v>6</v>
-      </c>
-      <c r="T11" t="n">
-        <v>7</v>
-      </c>
-      <c r="U11" t="n">
-        <v>6</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Grönfink
-Gulsparv
-Kråka
-Kungsfågel
-Sävsparv
-Trädlärka</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 5046-2022 artfynd.xlsx", "A 5046-2022")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 5046-2022 karta.png", "A 5046-2022")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 5046-2022 georefererad karta.tif", "A 5046-2022")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 5046-2022 FSC-klagomål.docx", "A 5046-2022")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 5046-2022 FSC-klagomål mail.docx", "A 5046-2022")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 5046-2022 tillsynsbegäran.docx", "A 5046-2022")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 5046-2022 tillsynsbegäran mail.docx", "A 5046-2022")</f>
-        <v/>
-      </c>
-      <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 5046-2022 prioriterade fågelarter.docx", "A 5046-2022")</f>
         <v/>
       </c>
     </row>
@@ -1774,7 +1774,7 @@
         <v>45106</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>45245</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>46038</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>46265</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2207,75 +2207,188 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
+          <t>A 35680-2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>2</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="n">
+        <v>7</v>
+      </c>
+      <c r="U16" t="n">
+        <v>7</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Vedlavklubba
+Entita
+Kandelabersvamp
+Blåmossa
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 35680-2026 artfynd.xlsx", "A 35680-2026")</f>
+        <v/>
+      </c>
+      <c r="X16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 35680-2026 karta.png", "A 35680-2026")</f>
+        <v/>
+      </c>
+      <c r="Y16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 35680-2026 georefererad karta.tif", "A 35680-2026")</f>
+        <v/>
+      </c>
+      <c r="AA16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 35680-2026 FSC-klagomål.docx", "A 35680-2026")</f>
+        <v/>
+      </c>
+      <c r="AB16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 35680-2026 FSC-klagomål mail.docx", "A 35680-2026")</f>
+        <v/>
+      </c>
+      <c r="AC16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 35680-2026 tillsynsbegäran.docx", "A 35680-2026")</f>
+        <v/>
+      </c>
+      <c r="AD16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 35680-2026 tillsynsbegäran mail.docx", "A 35680-2026")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 35680-2026 prioriterade fågelarter.docx", "A 35680-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>A 584-2025</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="n">
         <v>45664</v>
       </c>
-      <c r="E16" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
+      <c r="E17" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
         <v>1.2</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J17" t="n">
         <v>4</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
         <v>1</v>
       </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
         <v>1</v>
       </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
         <v>4</v>
       </c>
-      <c r="T16" t="n">
+      <c r="T17" t="n">
         <v>4</v>
       </c>
-      <c r="U16" t="n">
+      <c r="U17" t="n">
         <v>4</v>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>Entita
 Spillkråka
@@ -2283,148 +2396,36 @@
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W16">
+      <c r="W17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 584-2025 artfynd.xlsx", "A 584-2025")</f>
         <v/>
       </c>
-      <c r="X16">
+      <c r="X17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 584-2025 karta.png", "A 584-2025")</f>
         <v/>
       </c>
-      <c r="Y16">
+      <c r="Y17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 584-2025 georefererad karta.tif", "A 584-2025")</f>
         <v/>
       </c>
-      <c r="AA16">
+      <c r="AA17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 584-2025 FSC-klagomål.docx", "A 584-2025")</f>
         <v/>
       </c>
-      <c r="AB16">
+      <c r="AB17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 584-2025 FSC-klagomål mail.docx", "A 584-2025")</f>
         <v/>
       </c>
-      <c r="AC16">
+      <c r="AC17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 584-2025 tillsynsbegäran.docx", "A 584-2025")</f>
         <v/>
       </c>
-      <c r="AD16">
+      <c r="AD17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 584-2025 tillsynsbegäran mail.docx", "A 584-2025")</f>
         <v/>
       </c>
-      <c r="AE16">
+      <c r="AE17">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 584-2025 prioriterade fågelarter.docx", "A 584-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A 35680-2026</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J17" t="n">
-        <v>2</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1</v>
-      </c>
-      <c r="S17" t="n">
-        <v>4</v>
-      </c>
-      <c r="T17" t="n">
-        <v>5</v>
-      </c>
-      <c r="U17" t="n">
-        <v>5</v>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Vedlavklubba
-Entita
-Blåmossa
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 35680-2026 artfynd.xlsx", "A 35680-2026")</f>
-        <v/>
-      </c>
-      <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 35680-2026 karta.png", "A 35680-2026")</f>
-        <v/>
-      </c>
-      <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 35680-2026 georefererad karta.tif", "A 35680-2026")</f>
-        <v/>
-      </c>
-      <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 35680-2026 FSC-klagomål.docx", "A 35680-2026")</f>
-        <v/>
-      </c>
-      <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 35680-2026 FSC-klagomål mail.docx", "A 35680-2026")</f>
-        <v/>
-      </c>
-      <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 35680-2026 tillsynsbegäran.docx", "A 35680-2026")</f>
-        <v/>
-      </c>
-      <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 35680-2026 tillsynsbegäran mail.docx", "A 35680-2026")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 35680-2026 prioriterade fågelarter.docx", "A 35680-2026")</f>
         <v/>
       </c>
     </row>
@@ -2448,7 +2449,7 @@
         <v>44864</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2539,7 +2540,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 28874-2023</t>
+          <t>A 905-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2553,10 +2554,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45104</v>
+        <v>45301</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2569,616 +2570,616 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>9</v>
+        <v>4.9</v>
       </c>
       <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
         <v>1</v>
       </c>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
         <v>2</v>
       </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S19" t="n">
         <v>3</v>
       </c>
       <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Igelkott
+Desmeknopp
+Myskmadra</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 905-2024 artfynd.xlsx", "A 905-2024")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 905-2024 karta.png", "A 905-2024")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 905-2024 georefererad karta.tif", "A 905-2024")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 905-2024 FSC-klagomål.docx", "A 905-2024")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 905-2024 FSC-klagomål mail.docx", "A 905-2024")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 905-2024 tillsynsbegäran.docx", "A 905-2024")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 905-2024 tillsynsbegäran mail.docx", "A 905-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 28874-2023</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>45104</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>9</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3</v>
+      </c>
+      <c r="T20" t="n">
         <v>5</v>
       </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>Blåmossa
 Stubbspretmossa
 Revlummer</t>
         </is>
       </c>
-      <c r="W19">
+      <c r="W20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 28874-2023 artfynd.xlsx", "A 28874-2023")</f>
         <v/>
       </c>
-      <c r="X19">
+      <c r="X20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 28874-2023 karta.png", "A 28874-2023")</f>
         <v/>
       </c>
-      <c r="Y19">
+      <c r="Y20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 28874-2023 georefererad karta.tif", "A 28874-2023")</f>
         <v/>
       </c>
-      <c r="AA19">
+      <c r="AA20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 28874-2023 FSC-klagomål.docx", "A 28874-2023")</f>
         <v/>
       </c>
-      <c r="AB19">
+      <c r="AB20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 28874-2023 FSC-klagomål mail.docx", "A 28874-2023")</f>
         <v/>
       </c>
-      <c r="AC19">
+      <c r="AC20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 28874-2023 tillsynsbegäran.docx", "A 28874-2023")</f>
         <v/>
       </c>
-      <c r="AD19">
+      <c r="AD20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 28874-2023 tillsynsbegäran mail.docx", "A 28874-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 8065-2025</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>45707</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Småvänderot
+Gullpudra
+Svinrot</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 8065-2025 artfynd.xlsx", "A 8065-2025")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 8065-2025 karta.png", "A 8065-2025")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 8065-2025 georefererad karta.tif", "A 8065-2025")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 8065-2025 FSC-klagomål.docx", "A 8065-2025")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 8065-2025 FSC-klagomål mail.docx", "A 8065-2025")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 8065-2025 tillsynsbegäran.docx", "A 8065-2025")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 8065-2025 tillsynsbegäran mail.docx", "A 8065-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 50684-2023</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>45210</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>1</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>Skogsalm
+Kopparödla
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 50684-2023 artfynd.xlsx", "A 50684-2023")</f>
+        <v/>
+      </c>
+      <c r="X22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 50684-2023 karta.png", "A 50684-2023")</f>
+        <v/>
+      </c>
+      <c r="Y22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 50684-2023 georefererad karta.tif", "A 50684-2023")</f>
+        <v/>
+      </c>
+      <c r="AA22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 50684-2023 FSC-klagomål.docx", "A 50684-2023")</f>
+        <v/>
+      </c>
+      <c r="AB22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 50684-2023 FSC-klagomål mail.docx", "A 50684-2023")</f>
+        <v/>
+      </c>
+      <c r="AC22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 50684-2023 tillsynsbegäran.docx", "A 50684-2023")</f>
+        <v/>
+      </c>
+      <c r="AD22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 50684-2023 tillsynsbegäran mail.docx", "A 50684-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
         <is>
           <t>A 31907-2023</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
         <v>45118</v>
       </c>
-      <c r="E20" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
+      <c r="E23" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
         <v>5.3</v>
       </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
         <v>2</v>
       </c>
-      <c r="L20" t="n">
+      <c r="L23" t="n">
         <v>1</v>
       </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
         <v>1</v>
       </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
         <v>3</v>
       </c>
-      <c r="T20" t="n">
+      <c r="T23" t="n">
         <v>3</v>
       </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>Bokvårtlav
 Platt fjädermossa
 Stubbspretmossa</t>
         </is>
       </c>
-      <c r="W20">
+      <c r="W23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 31907-2023 artfynd.xlsx", "A 31907-2023")</f>
         <v/>
       </c>
-      <c r="X20">
+      <c r="X23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 31907-2023 karta.png", "A 31907-2023")</f>
         <v/>
       </c>
-      <c r="Y20">
+      <c r="Y23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 31907-2023 georefererad karta.tif", "A 31907-2023")</f>
         <v/>
       </c>
-      <c r="AA20">
+      <c r="AA23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 31907-2023 FSC-klagomål.docx", "A 31907-2023")</f>
         <v/>
       </c>
-      <c r="AB20">
+      <c r="AB23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 31907-2023 FSC-klagomål mail.docx", "A 31907-2023")</f>
         <v/>
       </c>
-      <c r="AC20">
+      <c r="AC23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 31907-2023 tillsynsbegäran.docx", "A 31907-2023")</f>
         <v/>
       </c>
-      <c r="AD20">
+      <c r="AD23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 31907-2023 tillsynsbegäran mail.docx", "A 31907-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 8065-2025</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>45707</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>A 3317-2026</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="n">
+        <v>46041</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
         <v>2</v>
       </c>
-      <c r="M21" t="n">
-        <v>1</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
         <v>3</v>
       </c>
-      <c r="R21" t="n">
-        <v>1</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3</v>
-      </c>
-      <c r="T21" t="n">
-        <v>3</v>
-      </c>
-      <c r="U21" t="n">
-        <v>2</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Småvänderot
-Gullpudra
-Svinrot</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 8065-2025 artfynd.xlsx", "A 8065-2025")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 8065-2025 karta.png", "A 8065-2025")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 8065-2025 georefererad karta.tif", "A 8065-2025")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 8065-2025 FSC-klagomål.docx", "A 8065-2025")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 8065-2025 FSC-klagomål mail.docx", "A 8065-2025")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 8065-2025 tillsynsbegäran.docx", "A 8065-2025")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 8065-2025 tillsynsbegäran mail.docx", "A 8065-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 50684-2023</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>45210</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J22" t="n">
-        <v>2</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>1</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3</v>
-      </c>
-      <c r="T22" t="n">
-        <v>3</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Skogsalm
-Kopparödla
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 50684-2023 artfynd.xlsx", "A 50684-2023")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 50684-2023 karta.png", "A 50684-2023")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 50684-2023 georefererad karta.tif", "A 50684-2023")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 50684-2023 FSC-klagomål.docx", "A 50684-2023")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 50684-2023 FSC-klagomål mail.docx", "A 50684-2023")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 50684-2023 tillsynsbegäran.docx", "A 50684-2023")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 50684-2023 tillsynsbegäran mail.docx", "A 50684-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>A 3317-2026</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>46041</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J23" t="n">
-        <v>3</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>2</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>2</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3</v>
-      </c>
-      <c r="T23" t="n">
+      <c r="T24" t="n">
         <v>6</v>
       </c>
-      <c r="U23" t="n">
+      <c r="U24" t="n">
         <v>6</v>
       </c>
-      <c r="V23" s="2" t="inlineStr">
+      <c r="V24" s="2" t="inlineStr">
         <is>
           <t>Entita
 Mindre hackspett
 Gröngöling</t>
         </is>
       </c>
-      <c r="W23">
+      <c r="W24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 3317-2026 artfynd.xlsx", "A 3317-2026")</f>
         <v/>
       </c>
-      <c r="X23">
+      <c r="X24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 3317-2026 karta.png", "A 3317-2026")</f>
         <v/>
       </c>
-      <c r="Y23">
+      <c r="Y24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 3317-2026 georefererad karta.tif", "A 3317-2026")</f>
         <v/>
       </c>
-      <c r="AA23">
+      <c r="AA24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 3317-2026 FSC-klagomål.docx", "A 3317-2026")</f>
         <v/>
       </c>
-      <c r="AB23">
+      <c r="AB24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 3317-2026 FSC-klagomål mail.docx", "A 3317-2026")</f>
         <v/>
       </c>
-      <c r="AC23">
+      <c r="AC24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 3317-2026 tillsynsbegäran.docx", "A 3317-2026")</f>
         <v/>
       </c>
-      <c r="AD23">
+      <c r="AD24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 3317-2026 tillsynsbegäran mail.docx", "A 3317-2026")</f>
         <v/>
       </c>
-      <c r="AE23">
+      <c r="AE24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 3317-2026 prioriterade fågelarter.docx", "A 3317-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>A 905-2024</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="n">
-        <v>45301</v>
-      </c>
-      <c r="E24" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>1</v>
-      </c>
-      <c r="L24" t="n">
-        <v>1</v>
-      </c>
-      <c r="M24" t="n">
-        <v>1</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>2</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3</v>
-      </c>
-      <c r="T24" t="n">
-        <v>3</v>
-      </c>
-      <c r="U24" t="n">
-        <v>2</v>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>Igelkott
-Desmeknopp
-Myskmadra</t>
-        </is>
-      </c>
-      <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 905-2024 artfynd.xlsx", "A 905-2024")</f>
-        <v/>
-      </c>
-      <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 905-2024 karta.png", "A 905-2024")</f>
-        <v/>
-      </c>
-      <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 905-2024 georefererad karta.tif", "A 905-2024")</f>
-        <v/>
-      </c>
-      <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 905-2024 FSC-klagomål.docx", "A 905-2024")</f>
-        <v/>
-      </c>
-      <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 905-2024 FSC-klagomål mail.docx", "A 905-2024")</f>
-        <v/>
-      </c>
-      <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 905-2024 tillsynsbegäran.docx", "A 905-2024")</f>
-        <v/>
-      </c>
-      <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 905-2024 tillsynsbegäran mail.docx", "A 905-2024")</f>
         <v/>
       </c>
     </row>
@@ -3202,7 +3203,7 @@
         <v>45763</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3313,7 +3314,7 @@
         <v>45474</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3423,7 +3424,7 @@
         <v>45841</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3533,7 +3534,7 @@
         <v>45105</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3643,7 +3644,7 @@
         <v>44553</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3753,7 +3754,7 @@
         <v>45359</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3859,7 +3860,7 @@
         <v>45582</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3969,7 +3970,7 @@
         <v>44839</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4074,7 +4075,7 @@
         <v>44742</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4179,7 +4180,7 @@
         <v>44746</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4271,7 +4272,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 12150-2024</t>
+          <t>A 44062-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4285,10 +4286,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45377</v>
+        <v>44839</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4301,19 +4302,19 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -4325,10 +4326,10 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4341,35 +4342,35 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 12150-2024 artfynd.xlsx", "A 12150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 44062-2022 artfynd.xlsx", "A 44062-2022")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 12150-2024 karta.png", "A 12150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 44062-2022 karta.png", "A 44062-2022")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 12150-2024 georefererad karta.tif", "A 12150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 44062-2022 georefererad karta.tif", "A 44062-2022")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 12150-2024 FSC-klagomål.docx", "A 12150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 44062-2022 FSC-klagomål.docx", "A 44062-2022")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 12150-2024 FSC-klagomål mail.docx", "A 12150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 44062-2022 FSC-klagomål mail.docx", "A 44062-2022")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 12150-2024 tillsynsbegäran.docx", "A 12150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 44062-2022 tillsynsbegäran.docx", "A 44062-2022")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 12150-2024 tillsynsbegäran mail.docx", "A 12150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 44062-2022 tillsynsbegäran mail.docx", "A 44062-2022")</f>
         <v/>
       </c>
     </row>
@@ -4393,7 +4394,7 @@
         <v>45323</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4481,7 +4482,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 50642-2023</t>
+          <t>A 25129-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4495,10 +4496,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45210</v>
+        <v>45462</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4511,17 +4512,17 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.8</v>
+        <v>4.6</v>
       </c>
       <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
         <v>1</v>
       </c>
-      <c r="K37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" t="n">
-        <v>0</v>
-      </c>
       <c r="M37" t="n">
         <v>0</v>
       </c>
@@ -4535,7 +4536,7 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
@@ -4551,42 +4552,42 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 50642-2023 artfynd.xlsx", "A 50642-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 25129-2024 artfynd.xlsx", "A 25129-2024")</f>
         <v/>
       </c>
       <c r="X37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 50642-2023 karta.png", "A 50642-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 25129-2024 karta.png", "A 25129-2024")</f>
         <v/>
       </c>
       <c r="Y37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 50642-2023 georefererad karta.tif", "A 50642-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 25129-2024 georefererad karta.tif", "A 25129-2024")</f>
         <v/>
       </c>
       <c r="AA37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 50642-2023 FSC-klagomål.docx", "A 50642-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 25129-2024 FSC-klagomål.docx", "A 25129-2024")</f>
         <v/>
       </c>
       <c r="AB37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 50642-2023 FSC-klagomål mail.docx", "A 50642-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 25129-2024 FSC-klagomål mail.docx", "A 25129-2024")</f>
         <v/>
       </c>
       <c r="AC37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 50642-2023 tillsynsbegäran.docx", "A 50642-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 25129-2024 tillsynsbegäran.docx", "A 25129-2024")</f>
         <v/>
       </c>
       <c r="AD37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 50642-2023 tillsynsbegäran mail.docx", "A 50642-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 25129-2024 tillsynsbegäran mail.docx", "A 25129-2024")</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 25129-2024</t>
+          <t>A 12150-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4600,10 +4601,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45462</v>
+        <v>45377</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4616,7 +4617,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>4.6</v>
+        <v>1.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4625,10 +4626,10 @@
         <v>0</v>
       </c>
       <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
         <v>1</v>
-      </c>
-      <c r="M38" t="n">
-        <v>0</v>
       </c>
       <c r="N38" t="n">
         <v>0</v>
@@ -4643,7 +4644,7 @@
         <v>1</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4652,39 +4653,39 @@
         <v>1</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 25129-2024 artfynd.xlsx", "A 25129-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 12150-2024 artfynd.xlsx", "A 12150-2024")</f>
         <v/>
       </c>
       <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 25129-2024 karta.png", "A 25129-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 12150-2024 karta.png", "A 12150-2024")</f>
         <v/>
       </c>
       <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 25129-2024 georefererad karta.tif", "A 25129-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 12150-2024 georefererad karta.tif", "A 12150-2024")</f>
         <v/>
       </c>
       <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 25129-2024 FSC-klagomål.docx", "A 25129-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 12150-2024 FSC-klagomål.docx", "A 12150-2024")</f>
         <v/>
       </c>
       <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 25129-2024 FSC-klagomål mail.docx", "A 25129-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 12150-2024 FSC-klagomål mail.docx", "A 12150-2024")</f>
         <v/>
       </c>
       <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 25129-2024 tillsynsbegäran.docx", "A 25129-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 12150-2024 tillsynsbegäran.docx", "A 12150-2024")</f>
         <v/>
       </c>
       <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 25129-2024 tillsynsbegäran mail.docx", "A 25129-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 12150-2024 tillsynsbegäran mail.docx", "A 12150-2024")</f>
         <v/>
       </c>
     </row>
@@ -4708,7 +4709,7 @@
         <v>44498</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4796,7 +4797,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 27094-2026</t>
+          <t>A 50642-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4810,10 +4811,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46188</v>
+        <v>45210</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4826,13 +4827,13 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>6.2</v>
+        <v>0.8</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -4866,42 +4867,42 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="W40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 27094-2026 artfynd.xlsx", "A 27094-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 50642-2023 artfynd.xlsx", "A 50642-2023")</f>
         <v/>
       </c>
       <c r="X40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 27094-2026 karta.png", "A 27094-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 50642-2023 karta.png", "A 50642-2023")</f>
         <v/>
       </c>
       <c r="Y40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 27094-2026 georefererad karta.tif", "A 27094-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 50642-2023 georefererad karta.tif", "A 50642-2023")</f>
         <v/>
       </c>
       <c r="AA40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 27094-2026 FSC-klagomål.docx", "A 27094-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 50642-2023 FSC-klagomål.docx", "A 50642-2023")</f>
         <v/>
       </c>
       <c r="AB40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 27094-2026 FSC-klagomål mail.docx", "A 27094-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 50642-2023 FSC-klagomål mail.docx", "A 50642-2023")</f>
         <v/>
       </c>
       <c r="AC40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 27094-2026 tillsynsbegäran.docx", "A 27094-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 50642-2023 tillsynsbegäran.docx", "A 50642-2023")</f>
         <v/>
       </c>
       <c r="AD40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 27094-2026 tillsynsbegäran mail.docx", "A 27094-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 50642-2023 tillsynsbegäran mail.docx", "A 50642-2023")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 44062-2022</t>
+          <t>A 27094-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4915,10 +4916,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44839</v>
+        <v>46188</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4931,7 +4932,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.2</v>
+        <v>6.2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4967,46 +4968,46 @@
         <v>1</v>
       </c>
       <c r="U41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 44062-2022 artfynd.xlsx", "A 44062-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 27094-2026 artfynd.xlsx", "A 27094-2026")</f>
         <v/>
       </c>
       <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 44062-2022 karta.png", "A 44062-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 27094-2026 karta.png", "A 27094-2026")</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 44062-2022 georefererad karta.tif", "A 44062-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 27094-2026 georefererad karta.tif", "A 27094-2026")</f>
         <v/>
       </c>
       <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 44062-2022 FSC-klagomål.docx", "A 44062-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 27094-2026 FSC-klagomål.docx", "A 27094-2026")</f>
         <v/>
       </c>
       <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 44062-2022 FSC-klagomål mail.docx", "A 44062-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 27094-2026 FSC-klagomål mail.docx", "A 27094-2026")</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 44062-2022 tillsynsbegäran.docx", "A 44062-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 27094-2026 tillsynsbegäran.docx", "A 27094-2026")</f>
         <v/>
       </c>
       <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 44062-2022 tillsynsbegäran mail.docx", "A 44062-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 27094-2026 tillsynsbegäran mail.docx", "A 27094-2026")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 35684-2026</t>
+          <t>A 31599-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5020,10 +5021,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46265</v>
+        <v>46224</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5036,16 +5037,16 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3.9</v>
+        <v>1.7</v>
       </c>
       <c r="J42" t="n">
         <v>1</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
@@ -5060,7 +5061,7 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -5069,53 +5070,49 @@
         <v>1</v>
       </c>
       <c r="T42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 35684-2026 artfynd.xlsx", "A 35684-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 31599-2026 artfynd.xlsx", "A 31599-2026")</f>
         <v/>
       </c>
       <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 35684-2026 karta.png", "A 35684-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 31599-2026 karta.png", "A 31599-2026")</f>
         <v/>
       </c>
       <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 35684-2026 georefererad karta.tif", "A 35684-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 31599-2026 georefererad karta.tif", "A 31599-2026")</f>
         <v/>
       </c>
       <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 35684-2026 FSC-klagomål.docx", "A 35684-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 31599-2026 FSC-klagomål.docx", "A 31599-2026")</f>
         <v/>
       </c>
       <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 35684-2026 FSC-klagomål mail.docx", "A 35684-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 31599-2026 FSC-klagomål mail.docx", "A 31599-2026")</f>
         <v/>
       </c>
       <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 35684-2026 tillsynsbegäran.docx", "A 35684-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 31599-2026 tillsynsbegäran.docx", "A 31599-2026")</f>
         <v/>
       </c>
       <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 35684-2026 tillsynsbegäran mail.docx", "A 35684-2026")</f>
-        <v/>
-      </c>
-      <c r="AE42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 35684-2026 prioriterade fågelarter.docx", "A 35684-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 31599-2026 tillsynsbegäran mail.docx", "A 31599-2026")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 31599-2026</t>
+          <t>A 35684-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5129,10 +5126,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46224</v>
+        <v>46265</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5145,17 +5142,17 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.7</v>
+        <v>3.9</v>
       </c>
       <c r="J43" t="n">
         <v>1</v>
       </c>
       <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
         <v>1</v>
       </c>
-      <c r="L43" t="n">
-        <v>0</v>
-      </c>
       <c r="M43" t="n">
         <v>0</v>
       </c>
@@ -5169,7 +5166,7 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
@@ -5178,42 +5175,46 @@
         <v>1</v>
       </c>
       <c r="T43" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>Ekoxe</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="W43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 31599-2026 artfynd.xlsx", "A 31599-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 35684-2026 artfynd.xlsx", "A 35684-2026")</f>
         <v/>
       </c>
       <c r="X43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 31599-2026 karta.png", "A 31599-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 35684-2026 karta.png", "A 35684-2026")</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 31599-2026 georefererad karta.tif", "A 31599-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 35684-2026 georefererad karta.tif", "A 35684-2026")</f>
         <v/>
       </c>
       <c r="AA43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 31599-2026 FSC-klagomål.docx", "A 31599-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 35684-2026 FSC-klagomål.docx", "A 35684-2026")</f>
         <v/>
       </c>
       <c r="AB43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 31599-2026 FSC-klagomål mail.docx", "A 31599-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 35684-2026 FSC-klagomål mail.docx", "A 35684-2026")</f>
         <v/>
       </c>
       <c r="AC43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 31599-2026 tillsynsbegäran.docx", "A 31599-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 35684-2026 tillsynsbegäran.docx", "A 35684-2026")</f>
         <v/>
       </c>
       <c r="AD43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 31599-2026 tillsynsbegäran mail.docx", "A 31599-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 35684-2026 tillsynsbegäran mail.docx", "A 35684-2026")</f>
+        <v/>
+      </c>
+      <c r="AE43">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 35684-2026 prioriterade fågelarter.docx", "A 35684-2026")</f>
         <v/>
       </c>
     </row>
@@ -5237,7 +5238,7 @@
         <v>45582</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5342,7 +5343,7 @@
         <v>45084</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5447,7 +5448,7 @@
         <v>44862</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5552,7 +5553,7 @@
         <v>44880</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5625,7 +5626,7 @@
         <v>44839</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5698,7 +5699,7 @@
         <v>44725</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5771,7 +5772,7 @@
         <v>44840</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5844,7 +5845,7 @@
         <v>44498</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5917,7 +5918,7 @@
         <v>44477</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5990,7 +5991,7 @@
         <v>44657</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6063,7 +6064,7 @@
         <v>44634</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6136,7 +6137,7 @@
         <v>44802</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6209,7 +6210,7 @@
         <v>44802</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6282,7 +6283,7 @@
         <v>44827</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6355,7 +6356,7 @@
         <v>44480</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6428,7 +6429,7 @@
         <v>44634</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6484,7 +6485,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 29436-2024</t>
+          <t>A 40275-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6498,10 +6499,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45483</v>
+        <v>45169</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6514,7 +6515,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>4.2</v>
+        <v>0.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6557,7 +6558,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 8882-2025</t>
+          <t>A 6667-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6571,10 +6572,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45713</v>
+        <v>45700</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6587,7 +6588,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6630,7 +6631,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 12148-2024</t>
+          <t>A 46702-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6644,10 +6645,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45377</v>
+        <v>45583</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6660,7 +6661,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6703,7 +6704,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 9578-2025</t>
+          <t>A 31789-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6717,10 +6718,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45715</v>
+        <v>45118</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6733,7 +6734,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6776,7 +6777,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 53501-2022</t>
+          <t>A 1644-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6790,10 +6791,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44879</v>
+        <v>45670</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6806,7 +6807,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>7.2</v>
+        <v>1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6849,7 +6850,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 27551-2023</t>
+          <t>A 55545-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6863,10 +6864,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45097</v>
+        <v>44887</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6879,7 +6880,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.6</v>
+        <v>4.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6939,7 +6940,7 @@
         <v>45281</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6995,7 +6996,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 31720-2023</t>
+          <t>A 23676-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -7009,10 +7010,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45117</v>
+        <v>45454</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7025,7 +7026,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -7085,7 +7086,7 @@
         <v>45463</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7141,7 +7142,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 31143-2024</t>
+          <t>A 8139-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7151,14 +7152,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45502</v>
+        <v>45708</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7171,7 +7172,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.6</v>
+        <v>3.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7214,7 +7215,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 607-2024</t>
+          <t>A 44448-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7228,10 +7229,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45299</v>
+        <v>45189</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7287,7 +7288,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 54709-2023</t>
+          <t>A 31143-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7297,14 +7298,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45236</v>
+        <v>45502</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7317,7 +7318,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>3.6</v>
+        <v>0.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7360,7 +7361,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 55544-2022</t>
+          <t>A 23328-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7374,10 +7375,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44887</v>
+        <v>44720</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7433,7 +7434,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 27553-2023</t>
+          <t>A 46286-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7447,10 +7448,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45097</v>
+        <v>45581</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7463,7 +7464,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7506,7 +7507,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 23976-2024</t>
+          <t>A 15154-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7520,10 +7521,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45456</v>
+        <v>45016</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7536,7 +7537,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.6</v>
+        <v>3.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7579,7 +7580,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 28253-2023</t>
+          <t>A 7337-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7593,10 +7594,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45099</v>
+        <v>45345</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7609,7 +7610,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7652,7 +7653,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 16419-2023</t>
+          <t>A 55544-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7666,10 +7667,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45022</v>
+        <v>44887</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7682,7 +7683,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>4.2</v>
+        <v>1.1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7725,7 +7726,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 9055-2026</t>
+          <t>A 49610-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7739,10 +7740,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46069</v>
+        <v>45596</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7755,7 +7756,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.7</v>
+        <v>6.4</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7798,7 +7799,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 19503-2022</t>
+          <t>A 13243-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7812,10 +7813,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44693</v>
+        <v>45735</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7828,7 +7829,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>5.1</v>
+        <v>0.5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7871,7 +7872,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 46702-2024</t>
+          <t>A 74214-2021</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7885,10 +7886,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45583</v>
+        <v>44553</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7901,7 +7902,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.2</v>
+        <v>19.8</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7944,7 +7945,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 32020-2025</t>
+          <t>A 7811-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7958,10 +7959,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45835</v>
+        <v>44973</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7974,7 +7975,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -8017,7 +8018,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 13662-2025</t>
+          <t>A 58137-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -8031,10 +8032,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45736</v>
+        <v>44900</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8047,7 +8048,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>6.4</v>
+        <v>0.9</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -8090,7 +8091,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 49206-2024</t>
+          <t>A 42105-2022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -8104,10 +8105,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45595</v>
+        <v>44830</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8120,7 +8121,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8163,7 +8164,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 31503-2023</t>
+          <t>A 40287-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8177,10 +8178,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45115</v>
+        <v>45895</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8193,7 +8194,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8236,7 +8237,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 9803-2026</t>
+          <t>A 50652-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8250,10 +8251,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46072</v>
+        <v>45210</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8266,7 +8267,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>5</v>
+        <v>2.4</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8309,7 +8310,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 40287-2025</t>
+          <t>A 24855-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8323,10 +8324,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45895</v>
+        <v>45461</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8339,7 +8340,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8382,7 +8383,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 23328-2022</t>
+          <t>A 42826-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8396,10 +8397,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44720</v>
+        <v>45908</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8412,7 +8413,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8455,7 +8456,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 19650-2026</t>
+          <t>A 4755-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8469,10 +8470,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46134</v>
+        <v>45328</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8485,7 +8486,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>8</v>
+        <v>0.9</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8528,7 +8529,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 32364-2023</t>
+          <t>A 14400-2023</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8542,10 +8543,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45120</v>
+        <v>45012</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8558,7 +8559,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8601,7 +8602,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 42826-2025</t>
+          <t>A 23227-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8615,10 +8616,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45908</v>
+        <v>45075</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8631,7 +8632,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8674,7 +8675,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 7707-2025</t>
+          <t>A 9578-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8688,10 +8689,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45705</v>
+        <v>45715</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8704,7 +8705,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8747,7 +8748,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 8139-2025</t>
+          <t>A 8882-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8761,10 +8762,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45708</v>
+        <v>45713</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8777,7 +8778,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8820,7 +8821,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 40275-2023</t>
+          <t>A 52519-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8834,10 +8835,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45169</v>
+        <v>45954</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8850,7 +8851,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8893,7 +8894,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 58134-2022</t>
+          <t>A 18571-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8907,10 +8908,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44900</v>
+        <v>45763</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8923,7 +8924,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8966,7 +8967,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 1644-2025</t>
+          <t>A 55728-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8980,10 +8981,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45670</v>
+        <v>45972</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9039,7 +9040,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 74214-2021</t>
+          <t>A 16419-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -9053,10 +9054,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44553</v>
+        <v>45022</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9069,7 +9070,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>19.8</v>
+        <v>4.2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -9112,7 +9113,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 24855-2024</t>
+          <t>A 27551-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -9126,10 +9127,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45461</v>
+        <v>45097</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9142,7 +9143,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.4</v>
+        <v>0.6</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9185,7 +9186,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 7871-2025</t>
+          <t>A 2575-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9199,10 +9200,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45706</v>
+        <v>45313</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9215,7 +9216,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -9258,7 +9259,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 13243-2025</t>
+          <t>A 57725-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9272,10 +9273,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45735</v>
+        <v>45981</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9288,7 +9289,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9331,7 +9332,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 6667-2025</t>
+          <t>A 4089-2024</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9345,10 +9346,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45700</v>
+        <v>45323</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9361,7 +9362,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9404,7 +9405,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 58137-2022</t>
+          <t>A 28496-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9418,10 +9419,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44900</v>
+        <v>45103</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9434,7 +9435,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9477,7 +9478,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 2575-2024</t>
+          <t>A 1299-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9491,10 +9492,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45313</v>
+        <v>45303</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9507,7 +9508,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9550,7 +9551,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 31502-2023</t>
+          <t>A 32364-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9564,10 +9565,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45115</v>
+        <v>45120</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9580,7 +9581,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9623,7 +9624,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 46286-2024</t>
+          <t>A 31503-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9637,10 +9638,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45581</v>
+        <v>45115</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9653,7 +9654,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9696,7 +9697,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 7994-2023</t>
+          <t>A 39014-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9710,10 +9711,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44973</v>
+        <v>45163</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9726,7 +9727,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9769,7 +9770,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 60227-2025</t>
+          <t>A 31908-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9783,10 +9784,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45994</v>
+        <v>45118</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9842,7 +9843,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 43857-2025</t>
+          <t>A 31502-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9856,10 +9857,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45912</v>
+        <v>45115</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9872,7 +9873,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9915,7 +9916,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 13278-2026</t>
+          <t>A 43857-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9929,10 +9930,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46093</v>
+        <v>45912</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9945,7 +9946,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9988,7 +9989,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 8665-2022</t>
+          <t>A 28253-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -10002,10 +10003,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44613</v>
+        <v>45099</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10018,7 +10019,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.6</v>
+        <v>2.7</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -10061,7 +10062,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 18571-2025</t>
+          <t>A 60227-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10075,10 +10076,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45763</v>
+        <v>45994</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10091,7 +10092,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -10134,7 +10135,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 31709-2023</t>
+          <t>A 21488-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10148,10 +10149,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45117</v>
+        <v>45061</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10164,7 +10165,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -10207,7 +10208,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 23227-2023</t>
+          <t>A 7994-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10221,10 +10222,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45075</v>
+        <v>44973</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10237,7 +10238,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -10280,7 +10281,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 52519-2025</t>
+          <t>A 27553-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10294,10 +10295,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45954</v>
+        <v>45097</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10310,7 +10311,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10353,7 +10354,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 50652-2023</t>
+          <t>A 13278-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10367,10 +10368,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45210</v>
+        <v>46093</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10383,7 +10384,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10426,7 +10427,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 27097-2026</t>
+          <t>A 9055-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10440,10 +10441,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46188</v>
+        <v>46069</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10456,7 +10457,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>4</v>
+        <v>0.7</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10499,7 +10500,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 40278-2023</t>
+          <t>A 53501-2022</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10513,10 +10514,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45169</v>
+        <v>44879</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10529,7 +10530,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.1</v>
+        <v>7.2</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10572,7 +10573,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 55728-2025</t>
+          <t>A 27097-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10586,10 +10587,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45972</v>
+        <v>46188</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10602,7 +10603,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10645,7 +10646,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 29369-2026</t>
+          <t>A 54709-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10659,10 +10660,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46203</v>
+        <v>45236</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10675,7 +10676,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.3</v>
+        <v>3.6</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10718,7 +10719,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 31789-2023</t>
+          <t>A 12148-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10732,10 +10733,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45118</v>
+        <v>45377</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10748,7 +10749,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10791,7 +10792,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 57725-2025</t>
+          <t>A 19500-2022</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10805,10 +10806,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45981</v>
+        <v>44693</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10821,7 +10822,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10864,7 +10865,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 39014-2023</t>
+          <t>A 4605-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10878,10 +10879,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45163</v>
+        <v>45687</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10894,7 +10895,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10937,7 +10938,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 19500-2022</t>
+          <t>A 31720-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10951,10 +10952,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44693</v>
+        <v>45117</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10967,7 +10968,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -11010,7 +11011,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 44448-2023</t>
+          <t>A 16314-2024</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -11024,10 +11025,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45189</v>
+        <v>45407</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11040,7 +11041,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -11083,7 +11084,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 57923-2024</t>
+          <t>A 9803-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -11097,10 +11098,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45631</v>
+        <v>46072</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11113,7 +11114,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -11156,7 +11157,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 28264-2022</t>
+          <t>A 34514-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -11170,10 +11171,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44746</v>
+        <v>45140</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11186,7 +11187,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.5</v>
+        <v>3.1</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -11229,7 +11230,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 55545-2022</t>
+          <t>A 7707-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11243,10 +11244,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>44887</v>
+        <v>45705</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11259,7 +11260,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>4.4</v>
+        <v>1.2</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -11302,7 +11303,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 31576-2026</t>
+          <t>A 19650-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11316,10 +11317,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46224</v>
+        <v>46134</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11332,7 +11333,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>0.6</v>
+        <v>8</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11375,7 +11376,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 36001-2026</t>
+          <t>A 46613-2024</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11389,10 +11390,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46266</v>
+        <v>45583</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11405,7 +11406,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>0.8</v>
+        <v>6.2</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11448,7 +11449,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 34514-2023</t>
+          <t>A 23976-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11462,10 +11463,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45140</v>
+        <v>45456</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11478,7 +11479,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>3.1</v>
+        <v>0.6</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11521,7 +11522,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 35912-2026</t>
+          <t>A 40278-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11535,10 +11536,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46266</v>
+        <v>45169</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11551,7 +11552,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11594,7 +11595,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 1299-2024</t>
+          <t>A 58134-2022</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11608,10 +11609,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45303</v>
+        <v>44900</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11624,7 +11625,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11667,7 +11668,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 19255-2026</t>
+          <t>A 29369-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11681,10 +11682,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46132</v>
+        <v>46203</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11697,7 +11698,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11740,7 +11741,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 19256-2026</t>
+          <t>A 7871-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11754,10 +11755,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46132</v>
+        <v>45706</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11770,7 +11771,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11813,7 +11814,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 37628-2026</t>
+          <t>A 32430-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11827,10 +11828,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46276</v>
+        <v>45120</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11842,13 +11843,8 @@
           <t>ÄNGELHOLM</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I133" t="n">
-        <v>4.5</v>
+        <v>0.9</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11891,7 +11887,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 26978-2026</t>
+          <t>A 29436-2024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11905,10 +11901,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46185</v>
+        <v>45483</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11921,7 +11917,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>7.7</v>
+        <v>4.2</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11964,7 +11960,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 26986-2026</t>
+          <t>A 58150-2024</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11978,10 +11974,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46185</v>
+        <v>45632</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11994,7 +11990,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>3.5</v>
+        <v>0.5</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -12037,7 +12033,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 42105-2022</t>
+          <t>A 28264-2022</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -12051,10 +12047,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>44830</v>
+        <v>44746</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12067,7 +12063,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -12110,7 +12106,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 35677-2026</t>
+          <t>A 31709-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -12124,10 +12120,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46265</v>
+        <v>45117</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12140,7 +12136,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>3.1</v>
+        <v>0.6</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -12183,7 +12179,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 15154-2023</t>
+          <t>A 8665-2022</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -12197,10 +12193,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45016</v>
+        <v>44613</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12213,7 +12209,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>3.5</v>
+        <v>0.6</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -12256,7 +12252,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 7337-2024</t>
+          <t>A 60-2024</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12270,10 +12266,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45345</v>
+        <v>45293</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12286,7 +12282,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -12329,7 +12325,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 49610-2024</t>
+          <t>A 607-2024</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12343,10 +12339,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45596</v>
+        <v>45299</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12359,7 +12355,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>6.4</v>
+        <v>0.6</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -12402,7 +12398,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 14400-2023</t>
+          <t>A 49206-2024</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12416,10 +12412,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45012</v>
+        <v>45595</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12475,7 +12471,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 4089-2024</t>
+          <t>A 19503-2022</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12489,10 +12485,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45323</v>
+        <v>44693</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12505,7 +12501,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>0.7</v>
+        <v>5.1</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12548,7 +12544,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 23676-2024</t>
+          <t>A 31576-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12562,10 +12558,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45454</v>
+        <v>46224</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12578,7 +12574,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12621,7 +12617,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 60-2024</t>
+          <t>A 57923-2024</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12635,10 +12631,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45293</v>
+        <v>45631</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12651,7 +12647,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.2</v>
+        <v>4.5</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12694,7 +12690,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 58150-2024</t>
+          <t>A 36001-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12708,10 +12704,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45632</v>
+        <v>46266</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12724,7 +12720,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12767,7 +12763,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 4755-2024</t>
+          <t>A 35912-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12781,10 +12777,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45328</v>
+        <v>46266</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12797,7 +12793,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12840,7 +12836,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 32430-2023</t>
+          <t>A 20635-2024</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12854,10 +12850,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45120</v>
+        <v>45436</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12870,7 +12866,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>0.9</v>
+        <v>4.8</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12913,7 +12909,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 28496-2023</t>
+          <t>A 19255-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12927,10 +12923,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45103</v>
+        <v>46132</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12943,7 +12939,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12986,7 +12982,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 4605-2025</t>
+          <t>A 19256-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -13000,10 +12996,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45687</v>
+        <v>46132</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13016,7 +13012,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -13059,7 +13055,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 21488-2023</t>
+          <t>A 37628-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -13073,10 +13069,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45061</v>
+        <v>46276</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13088,8 +13084,13 @@
           <t>ÄNGELHOLM</t>
         </is>
       </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I150" t="n">
-        <v>1.1</v>
+        <v>4.5</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -13132,7 +13133,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 31908-2023</t>
+          <t>A 23980-2024</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -13146,10 +13147,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45118</v>
+        <v>45456</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13162,7 +13163,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -13205,7 +13206,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 7811-2023</t>
+          <t>A 55748-2024</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -13219,10 +13220,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>44973</v>
+        <v>45623</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13278,7 +13279,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 16314-2024</t>
+          <t>A 26986-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -13292,10 +13293,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45407</v>
+        <v>46185</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13308,7 +13309,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>1.1</v>
+        <v>3.5</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -13351,7 +13352,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 46613-2024</t>
+          <t>A 48197-2024</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -13365,10 +13366,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45583</v>
+        <v>45590</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13381,7 +13382,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>6.2</v>
+        <v>3.1</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -13424,7 +13425,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 20635-2024</t>
+          <t>A 26978-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13438,10 +13439,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45436</v>
+        <v>46185</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13454,7 +13455,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>4.8</v>
+        <v>7.7</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13497,7 +13498,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 23980-2024</t>
+          <t>A 35677-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13511,10 +13512,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45456</v>
+        <v>46265</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13527,7 +13528,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>1.3</v>
+        <v>3.1</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13570,7 +13571,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 55748-2024</t>
+          <t>A 55529-2024</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13584,10 +13585,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45623</v>
+        <v>45622</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13600,7 +13601,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13643,7 +13644,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 48197-2024</t>
+          <t>A 32020-2025</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13657,10 +13658,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45590</v>
+        <v>45835</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13673,7 +13674,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>3.1</v>
+        <v>0.7</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13716,7 +13717,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 55529-2024</t>
+          <t>A 13662-2025</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13730,10 +13731,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45622</v>
+        <v>45736</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13746,7 +13747,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>2.2</v>
+        <v>6.4</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13806,7 +13807,7 @@
         <v>45582</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13879,7 +13880,7 @@
         <v>45582</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13952,7 +13953,7 @@
         <v>45582</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14025,7 +14026,7 @@
         <v>45582</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14098,7 +14099,7 @@
         <v>44519</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14171,7 +14172,7 @@
         <v>45239</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14244,7 +14245,7 @@
         <v>45168</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14317,7 +14318,7 @@
         <v>44861</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14390,7 +14391,7 @@
         <v>45582</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>

--- a/Översikt ÄNGELHOLM.xlsx
+++ b/Översikt ÄNGELHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45099</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         <v>45931</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
         <v>45931</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>46106</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>44802</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>44781</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>44560</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
         <v>45835</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>44593</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
         <v>44929</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>45106</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>45245</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>46038</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>46265</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>46265</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2337,7 +2337,7 @@
         <v>45664</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2449,7 +2449,7 @@
         <v>44864</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
         <v>45301</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>45104</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         <v>45707</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2878,7 +2878,7 @@
         <v>45210</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         <v>45118</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
         <v>46041</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>45763</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3314,7 +3314,7 @@
         <v>45474</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3424,7 +3424,7 @@
         <v>45841</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
         <v>45105</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
         <v>44553</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3754,7 +3754,7 @@
         <v>45359</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
         <v>45582</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>44839</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>44742</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4180,7 +4180,7 @@
         <v>44746</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4289,7 +4289,7 @@
         <v>44839</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4394,7 +4394,7 @@
         <v>45323</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4499,7 +4499,7 @@
         <v>45462</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
         <v>45377</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         <v>44498</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4814,7 +4814,7 @@
         <v>45210</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4919,7 +4919,7 @@
         <v>46188</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5024,7 +5024,7 @@
         <v>46224</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5129,7 +5129,7 @@
         <v>46265</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5238,7 +5238,7 @@
         <v>45582</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         <v>45084</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5448,7 +5448,7 @@
         <v>44862</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5553,7 +5553,7 @@
         <v>44880</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5626,7 +5626,7 @@
         <v>44839</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5699,7 +5699,7 @@
         <v>44725</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5772,7 +5772,7 @@
         <v>44840</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5845,7 +5845,7 @@
         <v>44498</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5918,7 +5918,7 @@
         <v>44477</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5991,7 +5991,7 @@
         <v>44657</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
         <v>44634</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6137,7 +6137,7 @@
         <v>44802</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6210,7 +6210,7 @@
         <v>44802</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
         <v>44827</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6356,7 +6356,7 @@
         <v>44480</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6429,7 +6429,7 @@
         <v>44634</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         <v>45169</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6575,7 +6575,7 @@
         <v>45700</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6648,7 +6648,7 @@
         <v>45583</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6721,7 +6721,7 @@
         <v>45118</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6794,7 +6794,7 @@
         <v>45670</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6867,7 +6867,7 @@
         <v>44887</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6940,7 +6940,7 @@
         <v>45281</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7013,7 +7013,7 @@
         <v>45454</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7086,7 +7086,7 @@
         <v>45463</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7159,7 +7159,7 @@
         <v>45708</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7232,7 +7232,7 @@
         <v>45189</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         <v>45502</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7378,7 +7378,7 @@
         <v>44720</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7451,7 +7451,7 @@
         <v>45581</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7524,7 +7524,7 @@
         <v>45016</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7597,7 +7597,7 @@
         <v>45345</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7670,7 +7670,7 @@
         <v>44887</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7743,7 +7743,7 @@
         <v>45596</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7816,7 +7816,7 @@
         <v>45735</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7889,7 +7889,7 @@
         <v>44553</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7962,7 +7962,7 @@
         <v>44973</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8035,7 +8035,7 @@
         <v>44900</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8108,7 +8108,7 @@
         <v>44830</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8181,7 +8181,7 @@
         <v>45895</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8254,7 +8254,7 @@
         <v>45210</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8327,7 +8327,7 @@
         <v>45461</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8400,7 +8400,7 @@
         <v>45908</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8473,7 +8473,7 @@
         <v>45328</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8546,7 +8546,7 @@
         <v>45012</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8619,7 +8619,7 @@
         <v>45075</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8692,7 +8692,7 @@
         <v>45715</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8765,7 +8765,7 @@
         <v>45713</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8838,7 +8838,7 @@
         <v>45954</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8911,7 +8911,7 @@
         <v>45763</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8984,7 +8984,7 @@
         <v>45972</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9057,7 +9057,7 @@
         <v>45022</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9130,7 +9130,7 @@
         <v>45097</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         <v>45313</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9276,7 +9276,7 @@
         <v>45981</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         <v>45323</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9422,7 +9422,7 @@
         <v>45103</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9495,7 +9495,7 @@
         <v>45303</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         <v>45120</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9641,7 +9641,7 @@
         <v>45115</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9714,7 +9714,7 @@
         <v>45163</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9787,7 +9787,7 @@
         <v>45118</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9860,7 +9860,7 @@
         <v>45115</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9933,7 +9933,7 @@
         <v>45912</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10006,7 +10006,7 @@
         <v>45099</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10079,7 +10079,7 @@
         <v>45994</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10152,7 +10152,7 @@
         <v>45061</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10225,7 +10225,7 @@
         <v>44973</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10298,7 +10298,7 @@
         <v>45097</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10371,7 +10371,7 @@
         <v>46093</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10444,7 +10444,7 @@
         <v>46069</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10517,7 +10517,7 @@
         <v>44879</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10590,7 +10590,7 @@
         <v>46188</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10663,7 +10663,7 @@
         <v>45236</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10736,7 +10736,7 @@
         <v>45377</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10809,7 +10809,7 @@
         <v>44693</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10882,7 +10882,7 @@
         <v>45687</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10955,7 +10955,7 @@
         <v>45117</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11028,7 +11028,7 @@
         <v>45407</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11101,7 +11101,7 @@
         <v>46072</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11174,7 +11174,7 @@
         <v>45140</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11247,7 +11247,7 @@
         <v>45705</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11320,7 +11320,7 @@
         <v>46134</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11393,7 +11393,7 @@
         <v>45583</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11466,7 +11466,7 @@
         <v>45456</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11539,7 +11539,7 @@
         <v>45169</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11612,7 +11612,7 @@
         <v>44900</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11685,7 +11685,7 @@
         <v>46203</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11758,7 +11758,7 @@
         <v>45706</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11831,7 +11831,7 @@
         <v>45120</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11904,7 +11904,7 @@
         <v>45483</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11977,7 +11977,7 @@
         <v>45632</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12050,7 +12050,7 @@
         <v>44746</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12123,7 +12123,7 @@
         <v>45117</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12196,7 +12196,7 @@
         <v>44613</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12269,7 +12269,7 @@
         <v>45293</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12342,7 +12342,7 @@
         <v>45299</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12415,7 +12415,7 @@
         <v>45595</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12488,7 +12488,7 @@
         <v>44693</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         <v>46224</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
         <v>45631</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12707,7 +12707,7 @@
         <v>46266</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12780,7 +12780,7 @@
         <v>46266</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12853,7 +12853,7 @@
         <v>45436</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12926,7 +12926,7 @@
         <v>46132</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12999,7 +12999,7 @@
         <v>46132</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13072,7 +13072,7 @@
         <v>46276</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13150,7 +13150,7 @@
         <v>45456</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13223,7 +13223,7 @@
         <v>45623</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13296,7 +13296,7 @@
         <v>46185</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13369,7 +13369,7 @@
         <v>45590</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13442,7 +13442,7 @@
         <v>46185</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13515,7 +13515,7 @@
         <v>46265</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13588,7 +13588,7 @@
         <v>45622</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13661,7 +13661,7 @@
         <v>45835</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13734,7 +13734,7 @@
         <v>45736</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13807,7 +13807,7 @@
         <v>45582</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13880,7 +13880,7 @@
         <v>45582</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13953,7 +13953,7 @@
         <v>45582</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14026,7 +14026,7 @@
         <v>45582</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14099,7 +14099,7 @@
         <v>44519</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14172,7 +14172,7 @@
         <v>45239</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14245,7 +14245,7 @@
         <v>45168</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14318,7 +14318,7 @@
         <v>44861</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14391,7 +14391,7 @@
         <v>45582</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>

--- a/Översikt ÄNGELHOLM.xlsx
+++ b/Översikt ÄNGELHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45099</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         <v>45931</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
         <v>45931</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>46106</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>44802</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>44781</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>44560</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
         <v>45835</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>44593</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
         <v>44929</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>45106</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>45245</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>46038</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>46265</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>46265</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2337,7 +2337,7 @@
         <v>45664</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2449,7 +2449,7 @@
         <v>44864</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
         <v>45301</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>45104</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         <v>45707</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2861,7 +2861,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 50684-2023</t>
+          <t>A 3317-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2875,10 +2875,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45210</v>
+        <v>46041</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2891,22 +2891,22 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
       <c r="J22" t="n">
+        <v>3</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
         <v>2</v>
       </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
       <c r="M22" t="n">
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -2915,271 +2915,271 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>3</v>
       </c>
       <c r="T22" t="n">
+        <v>6</v>
+      </c>
+      <c r="U22" t="n">
+        <v>6</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>Entita
+Mindre hackspett
+Gröngöling</t>
+        </is>
+      </c>
+      <c r="W22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 3317-2026 artfynd.xlsx", "A 3317-2026")</f>
+        <v/>
+      </c>
+      <c r="X22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 3317-2026 karta.png", "A 3317-2026")</f>
+        <v/>
+      </c>
+      <c r="Y22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 3317-2026 georefererad karta.tif", "A 3317-2026")</f>
+        <v/>
+      </c>
+      <c r="AA22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 3317-2026 FSC-klagomål.docx", "A 3317-2026")</f>
+        <v/>
+      </c>
+      <c r="AB22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 3317-2026 FSC-klagomål mail.docx", "A 3317-2026")</f>
+        <v/>
+      </c>
+      <c r="AC22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 3317-2026 tillsynsbegäran.docx", "A 3317-2026")</f>
+        <v/>
+      </c>
+      <c r="AD22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 3317-2026 tillsynsbegäran mail.docx", "A 3317-2026")</f>
+        <v/>
+      </c>
+      <c r="AE22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 3317-2026 prioriterade fågelarter.docx", "A 3317-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>A 50684-2023</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>45210</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>1</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1</v>
+      </c>
+      <c r="S23" t="n">
         <v>3</v>
       </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>Skogsalm
 Kopparödla
 Vanlig padda</t>
         </is>
       </c>
-      <c r="W22">
+      <c r="W23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 50684-2023 artfynd.xlsx", "A 50684-2023")</f>
         <v/>
       </c>
-      <c r="X22">
+      <c r="X23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 50684-2023 karta.png", "A 50684-2023")</f>
         <v/>
       </c>
-      <c r="Y22">
+      <c r="Y23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 50684-2023 georefererad karta.tif", "A 50684-2023")</f>
         <v/>
       </c>
-      <c r="AA22">
+      <c r="AA23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 50684-2023 FSC-klagomål.docx", "A 50684-2023")</f>
         <v/>
       </c>
-      <c r="AB22">
+      <c r="AB23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 50684-2023 FSC-klagomål mail.docx", "A 50684-2023")</f>
         <v/>
       </c>
-      <c r="AC22">
+      <c r="AC23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 50684-2023 tillsynsbegäran.docx", "A 50684-2023")</f>
         <v/>
       </c>
-      <c r="AD22">
+      <c r="AD23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 50684-2023 tillsynsbegäran mail.docx", "A 50684-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" t="inlineStr">
         <is>
           <t>A 31907-2023</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="n">
         <v>45118</v>
       </c>
-      <c r="E23" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
+      <c r="E24" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
         <v>5.3</v>
       </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
         <v>2</v>
       </c>
-      <c r="L23" t="n">
+      <c r="L24" t="n">
         <v>1</v>
       </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
         <v>1</v>
       </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
         <v>3</v>
       </c>
-      <c r="T23" t="n">
+      <c r="T24" t="n">
         <v>3</v>
       </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
         <is>
           <t>Bokvårtlav
 Platt fjädermossa
 Stubbspretmossa</t>
         </is>
       </c>
-      <c r="W23">
+      <c r="W24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 31907-2023 artfynd.xlsx", "A 31907-2023")</f>
         <v/>
       </c>
-      <c r="X23">
+      <c r="X24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 31907-2023 karta.png", "A 31907-2023")</f>
         <v/>
       </c>
-      <c r="Y23">
+      <c r="Y24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 31907-2023 georefererad karta.tif", "A 31907-2023")</f>
         <v/>
       </c>
-      <c r="AA23">
+      <c r="AA24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 31907-2023 FSC-klagomål.docx", "A 31907-2023")</f>
         <v/>
       </c>
-      <c r="AB23">
+      <c r="AB24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 31907-2023 FSC-klagomål mail.docx", "A 31907-2023")</f>
         <v/>
       </c>
-      <c r="AC23">
+      <c r="AC24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 31907-2023 tillsynsbegäran.docx", "A 31907-2023")</f>
         <v/>
       </c>
-      <c r="AD23">
+      <c r="AD24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 31907-2023 tillsynsbegäran mail.docx", "A 31907-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>A 3317-2026</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="n">
-        <v>46041</v>
-      </c>
-      <c r="E24" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J24" t="n">
-        <v>3</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>2</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>2</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3</v>
-      </c>
-      <c r="T24" t="n">
-        <v>6</v>
-      </c>
-      <c r="U24" t="n">
-        <v>6</v>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>Entita
-Mindre hackspett
-Gröngöling</t>
-        </is>
-      </c>
-      <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 3317-2026 artfynd.xlsx", "A 3317-2026")</f>
-        <v/>
-      </c>
-      <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 3317-2026 karta.png", "A 3317-2026")</f>
-        <v/>
-      </c>
-      <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 3317-2026 georefererad karta.tif", "A 3317-2026")</f>
-        <v/>
-      </c>
-      <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 3317-2026 FSC-klagomål.docx", "A 3317-2026")</f>
-        <v/>
-      </c>
-      <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 3317-2026 FSC-klagomål mail.docx", "A 3317-2026")</f>
-        <v/>
-      </c>
-      <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 3317-2026 tillsynsbegäran.docx", "A 3317-2026")</f>
-        <v/>
-      </c>
-      <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 3317-2026 tillsynsbegäran mail.docx", "A 3317-2026")</f>
-        <v/>
-      </c>
-      <c r="AE24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 3317-2026 prioriterade fågelarter.docx", "A 3317-2026")</f>
         <v/>
       </c>
     </row>
@@ -3203,7 +3203,7 @@
         <v>45763</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3314,7 +3314,7 @@
         <v>45474</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3424,7 +3424,7 @@
         <v>45841</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
         <v>45105</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
         <v>44553</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3754,7 +3754,7 @@
         <v>45359</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
         <v>45582</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>44839</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>44742</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4180,7 +4180,7 @@
         <v>44746</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4289,7 +4289,7 @@
         <v>44839</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4394,7 +4394,7 @@
         <v>45323</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4499,7 +4499,7 @@
         <v>45462</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
         <v>45377</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 61094-2021</t>
+          <t>A 27094-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4706,10 +4706,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44498</v>
+        <v>46188</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4722,7 +4722,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4758,46 +4758,46 @@
         <v>1</v>
       </c>
       <c r="U39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 61094-2021 artfynd.xlsx", "A 61094-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 27094-2026 artfynd.xlsx", "A 27094-2026")</f>
         <v/>
       </c>
       <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 61094-2021 karta.png", "A 61094-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 27094-2026 karta.png", "A 27094-2026")</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 61094-2021 georefererad karta.tif", "A 61094-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 27094-2026 georefererad karta.tif", "A 27094-2026")</f>
         <v/>
       </c>
       <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 61094-2021 FSC-klagomål.docx", "A 61094-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 27094-2026 FSC-klagomål.docx", "A 27094-2026")</f>
         <v/>
       </c>
       <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 61094-2021 FSC-klagomål mail.docx", "A 61094-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 27094-2026 FSC-klagomål mail.docx", "A 27094-2026")</f>
         <v/>
       </c>
       <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 61094-2021 tillsynsbegäran.docx", "A 61094-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 27094-2026 tillsynsbegäran.docx", "A 27094-2026")</f>
         <v/>
       </c>
       <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 61094-2021 tillsynsbegäran mail.docx", "A 61094-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 27094-2026 tillsynsbegäran mail.docx", "A 27094-2026")</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 50642-2023</t>
+          <t>A 61094-2021</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4811,10 +4811,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45210</v>
+        <v>44498</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4827,13 +4827,13 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.8</v>
+        <v>6.4</v>
       </c>
       <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
         <v>1</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -4863,46 +4863,46 @@
         <v>1</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="W40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 50642-2023 artfynd.xlsx", "A 50642-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 61094-2021 artfynd.xlsx", "A 61094-2021")</f>
         <v/>
       </c>
       <c r="X40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 50642-2023 karta.png", "A 50642-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 61094-2021 karta.png", "A 61094-2021")</f>
         <v/>
       </c>
       <c r="Y40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 50642-2023 georefererad karta.tif", "A 50642-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 61094-2021 georefererad karta.tif", "A 61094-2021")</f>
         <v/>
       </c>
       <c r="AA40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 50642-2023 FSC-klagomål.docx", "A 50642-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 61094-2021 FSC-klagomål.docx", "A 61094-2021")</f>
         <v/>
       </c>
       <c r="AB40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 50642-2023 FSC-klagomål mail.docx", "A 50642-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 61094-2021 FSC-klagomål mail.docx", "A 61094-2021")</f>
         <v/>
       </c>
       <c r="AC40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 50642-2023 tillsynsbegäran.docx", "A 50642-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 61094-2021 tillsynsbegäran.docx", "A 61094-2021")</f>
         <v/>
       </c>
       <c r="AD40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 50642-2023 tillsynsbegäran mail.docx", "A 50642-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 61094-2021 tillsynsbegäran mail.docx", "A 61094-2021")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 27094-2026</t>
+          <t>A 50642-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46188</v>
+        <v>45210</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4932,13 +4932,13 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>6.2</v>
+        <v>0.8</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -4972,42 +4972,42 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 27094-2026 artfynd.xlsx", "A 27094-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 50642-2023 artfynd.xlsx", "A 50642-2023")</f>
         <v/>
       </c>
       <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 27094-2026 karta.png", "A 27094-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 50642-2023 karta.png", "A 50642-2023")</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 27094-2026 georefererad karta.tif", "A 27094-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 50642-2023 georefererad karta.tif", "A 50642-2023")</f>
         <v/>
       </c>
       <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 27094-2026 FSC-klagomål.docx", "A 27094-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 50642-2023 FSC-klagomål.docx", "A 50642-2023")</f>
         <v/>
       </c>
       <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 27094-2026 FSC-klagomål mail.docx", "A 27094-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 50642-2023 FSC-klagomål mail.docx", "A 50642-2023")</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 27094-2026 tillsynsbegäran.docx", "A 27094-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 50642-2023 tillsynsbegäran.docx", "A 50642-2023")</f>
         <v/>
       </c>
       <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 27094-2026 tillsynsbegäran mail.docx", "A 27094-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 50642-2023 tillsynsbegäran mail.docx", "A 50642-2023")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 31599-2026</t>
+          <t>A 35684-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5021,10 +5021,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46224</v>
+        <v>46265</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5037,17 +5037,17 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.7</v>
+        <v>3.9</v>
       </c>
       <c r="J42" t="n">
         <v>1</v>
       </c>
       <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
         <v>1</v>
       </c>
-      <c r="L42" t="n">
-        <v>0</v>
-      </c>
       <c r="M42" t="n">
         <v>0</v>
       </c>
@@ -5061,7 +5061,7 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -5070,49 +5070,53 @@
         <v>1</v>
       </c>
       <c r="T42" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>Ekoxe</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 31599-2026 artfynd.xlsx", "A 31599-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 35684-2026 artfynd.xlsx", "A 35684-2026")</f>
         <v/>
       </c>
       <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 31599-2026 karta.png", "A 31599-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 35684-2026 karta.png", "A 35684-2026")</f>
         <v/>
       </c>
       <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 31599-2026 georefererad karta.tif", "A 31599-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 35684-2026 georefererad karta.tif", "A 35684-2026")</f>
         <v/>
       </c>
       <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 31599-2026 FSC-klagomål.docx", "A 31599-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 35684-2026 FSC-klagomål.docx", "A 35684-2026")</f>
         <v/>
       </c>
       <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 31599-2026 FSC-klagomål mail.docx", "A 31599-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 35684-2026 FSC-klagomål mail.docx", "A 35684-2026")</f>
         <v/>
       </c>
       <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 31599-2026 tillsynsbegäran.docx", "A 31599-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 35684-2026 tillsynsbegäran.docx", "A 35684-2026")</f>
         <v/>
       </c>
       <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 31599-2026 tillsynsbegäran mail.docx", "A 31599-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 35684-2026 tillsynsbegäran mail.docx", "A 35684-2026")</f>
+        <v/>
+      </c>
+      <c r="AE42">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 35684-2026 prioriterade fågelarter.docx", "A 35684-2026")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 35684-2026</t>
+          <t>A 31599-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5126,10 +5130,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46265</v>
+        <v>46224</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5142,16 +5146,16 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>3.9</v>
+        <v>1.7</v>
       </c>
       <c r="J43" t="n">
         <v>1</v>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
@@ -5166,7 +5170,7 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
@@ -5175,46 +5179,42 @@
         <v>1</v>
       </c>
       <c r="T43" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="W43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 35684-2026 artfynd.xlsx", "A 35684-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 31599-2026 artfynd.xlsx", "A 31599-2026")</f>
         <v/>
       </c>
       <c r="X43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 35684-2026 karta.png", "A 35684-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 31599-2026 karta.png", "A 31599-2026")</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 35684-2026 georefererad karta.tif", "A 35684-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 31599-2026 georefererad karta.tif", "A 31599-2026")</f>
         <v/>
       </c>
       <c r="AA43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 35684-2026 FSC-klagomål.docx", "A 35684-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 31599-2026 FSC-klagomål.docx", "A 31599-2026")</f>
         <v/>
       </c>
       <c r="AB43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 35684-2026 FSC-klagomål mail.docx", "A 35684-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 31599-2026 FSC-klagomål mail.docx", "A 31599-2026")</f>
         <v/>
       </c>
       <c r="AC43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 35684-2026 tillsynsbegäran.docx", "A 35684-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 31599-2026 tillsynsbegäran.docx", "A 31599-2026")</f>
         <v/>
       </c>
       <c r="AD43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 35684-2026 tillsynsbegäran mail.docx", "A 35684-2026")</f>
-        <v/>
-      </c>
-      <c r="AE43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 35684-2026 prioriterade fågelarter.docx", "A 35684-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 31599-2026 tillsynsbegäran mail.docx", "A 31599-2026")</f>
         <v/>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
         <v>45582</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         <v>45084</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5448,7 +5448,7 @@
         <v>44862</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5553,7 +5553,7 @@
         <v>44880</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5626,7 +5626,7 @@
         <v>44839</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5699,7 +5699,7 @@
         <v>44725</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5772,7 +5772,7 @@
         <v>44840</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5845,7 +5845,7 @@
         <v>44498</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5918,7 +5918,7 @@
         <v>44477</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5991,7 +5991,7 @@
         <v>44657</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
         <v>44634</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6137,7 +6137,7 @@
         <v>44802</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6210,7 +6210,7 @@
         <v>44802</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
         <v>44827</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6356,7 +6356,7 @@
         <v>44480</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6429,7 +6429,7 @@
         <v>44634</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         <v>45169</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6575,7 +6575,7 @@
         <v>45700</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6648,7 +6648,7 @@
         <v>45583</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6721,7 +6721,7 @@
         <v>45118</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6794,7 +6794,7 @@
         <v>45670</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6867,7 +6867,7 @@
         <v>44887</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6940,7 +6940,7 @@
         <v>45281</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6996,7 +6996,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 23676-2024</t>
+          <t>A 25669-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -7010,10 +7010,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45454</v>
+        <v>45463</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7026,7 +7026,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.9</v>
+        <v>17.9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -7069,7 +7069,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 25669-2024</t>
+          <t>A 23676-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7083,10 +7083,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45463</v>
+        <v>45454</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7099,7 +7099,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>17.9</v>
+        <v>0.9</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -7142,7 +7142,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 8139-2025</t>
+          <t>A 44448-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7156,10 +7156,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45708</v>
+        <v>45189</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7172,7 +7172,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>3.5</v>
+        <v>0.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7215,7 +7215,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 44448-2023</t>
+          <t>A 31143-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7225,14 +7225,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45189</v>
+        <v>45502</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7288,7 +7288,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 31143-2024</t>
+          <t>A 8139-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7298,14 +7298,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45502</v>
+        <v>45708</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7318,7 +7318,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.6</v>
+        <v>3.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7378,7 +7378,7 @@
         <v>44720</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7434,7 +7434,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 46286-2024</t>
+          <t>A 15154-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7448,10 +7448,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45581</v>
+        <v>45016</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7464,7 +7464,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7507,7 +7507,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 15154-2023</t>
+          <t>A 55544-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7521,10 +7521,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45016</v>
+        <v>44887</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7537,7 +7537,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>3.5</v>
+        <v>1.1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7580,7 +7580,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 7337-2024</t>
+          <t>A 46286-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7594,10 +7594,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45345</v>
+        <v>45581</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7610,7 +7610,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7653,7 +7653,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 55544-2022</t>
+          <t>A 58134-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7667,10 +7667,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44887</v>
+        <v>44900</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7683,7 +7683,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7726,7 +7726,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 49610-2024</t>
+          <t>A 7337-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7740,10 +7740,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45596</v>
+        <v>45345</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7756,7 +7756,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>6.4</v>
+        <v>2.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7799,7 +7799,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 13243-2025</t>
+          <t>A 40287-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7813,10 +7813,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45735</v>
+        <v>45895</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7872,7 +7872,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 74214-2021</t>
+          <t>A 49610-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7886,10 +7886,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44553</v>
+        <v>45596</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>19.8</v>
+        <v>6.4</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7945,7 +7945,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 7811-2023</t>
+          <t>A 74214-2021</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7959,10 +7959,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44973</v>
+        <v>44553</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7975,7 +7975,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.9</v>
+        <v>19.8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -8018,7 +8018,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 58137-2022</t>
+          <t>A 13243-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -8032,10 +8032,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44900</v>
+        <v>45735</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -8091,7 +8091,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 42105-2022</t>
+          <t>A 42826-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -8105,10 +8105,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44830</v>
+        <v>45908</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8121,7 +8121,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8164,7 +8164,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 40287-2025</t>
+          <t>A 7811-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8178,10 +8178,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45895</v>
+        <v>44973</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8194,7 +8194,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8237,7 +8237,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 50652-2023</t>
+          <t>A 58137-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8251,10 +8251,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45210</v>
+        <v>44900</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8267,7 +8267,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8310,7 +8310,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 24855-2024</t>
+          <t>A 42105-2022</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8324,10 +8324,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45461</v>
+        <v>44830</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8340,7 +8340,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8383,7 +8383,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 42826-2025</t>
+          <t>A 50652-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8397,10 +8397,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45908</v>
+        <v>45210</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8413,7 +8413,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8456,7 +8456,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 4755-2024</t>
+          <t>A 24855-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8470,10 +8470,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45328</v>
+        <v>45461</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8486,7 +8486,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8529,7 +8529,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 14400-2023</t>
+          <t>A 4755-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8543,10 +8543,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45012</v>
+        <v>45328</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8559,7 +8559,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8602,7 +8602,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 23227-2023</t>
+          <t>A 14400-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8616,10 +8616,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45075</v>
+        <v>45012</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8632,7 +8632,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8675,7 +8675,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 9578-2025</t>
+          <t>A 52519-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8689,10 +8689,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45715</v>
+        <v>45954</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8748,7 +8748,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 8882-2025</t>
+          <t>A 23227-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8762,10 +8762,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45713</v>
+        <v>45075</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8778,7 +8778,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8821,7 +8821,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 52519-2025</t>
+          <t>A 55728-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8835,10 +8835,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45954</v>
+        <v>45972</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 18571-2025</t>
+          <t>A 9578-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8908,10 +8908,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45763</v>
+        <v>45715</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8924,7 +8924,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8967,7 +8967,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 55728-2025</t>
+          <t>A 57725-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8981,10 +8981,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45972</v>
+        <v>45981</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8997,7 +8997,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -9040,7 +9040,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 16419-2023</t>
+          <t>A 8882-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -9054,10 +9054,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45022</v>
+        <v>45713</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9070,7 +9070,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>4.2</v>
+        <v>2.3</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -9113,7 +9113,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 27551-2023</t>
+          <t>A 43857-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -9127,10 +9127,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45097</v>
+        <v>45912</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9143,7 +9143,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9186,7 +9186,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 2575-2024</t>
+          <t>A 60227-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9200,10 +9200,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45313</v>
+        <v>45994</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9216,7 +9216,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -9259,7 +9259,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 57725-2025</t>
+          <t>A 18571-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9273,10 +9273,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45981</v>
+        <v>45763</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9289,7 +9289,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9332,7 +9332,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 4089-2024</t>
+          <t>A 16419-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9346,10 +9346,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45323</v>
+        <v>45022</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9362,7 +9362,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.7</v>
+        <v>4.2</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9405,7 +9405,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 28496-2023</t>
+          <t>A 27551-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9419,10 +9419,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45103</v>
+        <v>45097</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9435,7 +9435,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9478,7 +9478,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 1299-2024</t>
+          <t>A 13278-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9492,10 +9492,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45303</v>
+        <v>46093</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9508,7 +9508,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9551,7 +9551,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 32364-2023</t>
+          <t>A 2575-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9565,10 +9565,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45120</v>
+        <v>45313</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9581,7 +9581,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9624,7 +9624,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 31503-2023</t>
+          <t>A 27097-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9638,10 +9638,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45115</v>
+        <v>46188</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9654,7 +9654,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.9</v>
+        <v>4</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9697,7 +9697,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 39014-2023</t>
+          <t>A 4089-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9711,10 +9711,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45163</v>
+        <v>45323</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9727,7 +9727,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9770,7 +9770,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 31908-2023</t>
+          <t>A 28496-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9784,10 +9784,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45118</v>
+        <v>45103</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9800,7 +9800,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9843,7 +9843,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 31502-2023</t>
+          <t>A 1299-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9857,10 +9857,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45115</v>
+        <v>45303</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9873,7 +9873,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9916,7 +9916,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 43857-2025</t>
+          <t>A 32364-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9930,10 +9930,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45912</v>
+        <v>45120</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9946,7 +9946,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9989,7 +9989,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 28253-2023</t>
+          <t>A 9055-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -10003,10 +10003,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45099</v>
+        <v>46069</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10019,7 +10019,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>2.7</v>
+        <v>0.7</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -10062,7 +10062,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 60227-2025</t>
+          <t>A 31503-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10076,10 +10076,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45994</v>
+        <v>45115</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10092,7 +10092,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -10135,7 +10135,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 21488-2023</t>
+          <t>A 39014-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10149,10 +10149,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45061</v>
+        <v>45163</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10165,7 +10165,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -10208,7 +10208,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 7994-2023</t>
+          <t>A 31908-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10222,10 +10222,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>44973</v>
+        <v>45118</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10238,7 +10238,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -10281,7 +10281,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 27553-2023</t>
+          <t>A 31502-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10295,10 +10295,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45097</v>
+        <v>45115</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10311,7 +10311,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10354,7 +10354,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 13278-2026</t>
+          <t>A 28253-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10368,10 +10368,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46093</v>
+        <v>45099</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10384,7 +10384,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.7</v>
+        <v>2.7</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10427,7 +10427,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 9055-2026</t>
+          <t>A 21488-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10441,10 +10441,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46069</v>
+        <v>45061</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10457,7 +10457,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10500,7 +10500,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 53501-2022</t>
+          <t>A 29369-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10514,10 +10514,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>44879</v>
+        <v>46203</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10530,7 +10530,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>7.2</v>
+        <v>1.3</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10573,7 +10573,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 27097-2026</t>
+          <t>A 7994-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10587,10 +10587,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46188</v>
+        <v>44973</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10603,7 +10603,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>4</v>
+        <v>0.6</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10646,7 +10646,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 54709-2023</t>
+          <t>A 27553-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10660,10 +10660,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45236</v>
+        <v>45097</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10676,7 +10676,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>3.6</v>
+        <v>0.8</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10719,7 +10719,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 12148-2024</t>
+          <t>A 9803-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10733,10 +10733,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45377</v>
+        <v>46072</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10749,7 +10749,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.5</v>
+        <v>5</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10792,7 +10792,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 19500-2022</t>
+          <t>A 7707-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10806,10 +10806,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>44693</v>
+        <v>45705</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10865,7 +10865,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 4605-2025</t>
+          <t>A 19650-2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10879,10 +10879,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45687</v>
+        <v>46134</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10895,7 +10895,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>0.8</v>
+        <v>8</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10938,7 +10938,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 31720-2023</t>
+          <t>A 53501-2022</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10952,10 +10952,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45117</v>
+        <v>44879</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10968,7 +10968,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>0.5</v>
+        <v>7.2</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -11011,7 +11011,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 16314-2024</t>
+          <t>A 54709-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -11025,10 +11025,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45407</v>
+        <v>45236</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11041,7 +11041,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.1</v>
+        <v>3.6</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -11084,7 +11084,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 9803-2026</t>
+          <t>A 12148-2024</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -11098,10 +11098,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46072</v>
+        <v>45377</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11114,7 +11114,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>5</v>
+        <v>1.5</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -11157,7 +11157,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 34514-2023</t>
+          <t>A 19500-2022</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -11171,10 +11171,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45140</v>
+        <v>44693</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11187,7 +11187,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>3.1</v>
+        <v>1.2</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -11230,7 +11230,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 7707-2025</t>
+          <t>A 4605-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11244,10 +11244,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45705</v>
+        <v>45687</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11260,7 +11260,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -11303,7 +11303,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 19650-2026</t>
+          <t>A 31720-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11317,10 +11317,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46134</v>
+        <v>45117</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11333,7 +11333,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>8</v>
+        <v>0.5</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11376,7 +11376,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 46613-2024</t>
+          <t>A 16314-2024</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11390,10 +11390,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45583</v>
+        <v>45407</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11406,7 +11406,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>6.2</v>
+        <v>1.1</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11449,7 +11449,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 23976-2024</t>
+          <t>A 34514-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45456</v>
+        <v>45140</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11479,7 +11479,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>0.6</v>
+        <v>3.1</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11522,7 +11522,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 40278-2023</t>
+          <t>A 31576-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11536,10 +11536,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45169</v>
+        <v>46224</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11552,7 +11552,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11595,7 +11595,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 58134-2022</t>
+          <t>A 36001-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11609,10 +11609,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44900</v>
+        <v>46266</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11625,7 +11625,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11668,7 +11668,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 29369-2026</t>
+          <t>A 46613-2024</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11682,10 +11682,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46203</v>
+        <v>45583</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11698,7 +11698,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.3</v>
+        <v>6.2</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11741,7 +11741,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 7871-2025</t>
+          <t>A 35912-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11755,10 +11755,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45706</v>
+        <v>46266</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11771,7 +11771,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11814,7 +11814,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 32430-2023</t>
+          <t>A 23976-2024</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11828,10 +11828,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45120</v>
+        <v>45456</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11844,7 +11844,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11887,7 +11887,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 29436-2024</t>
+          <t>A 40278-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11901,10 +11901,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45483</v>
+        <v>45169</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11917,7 +11917,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>4.2</v>
+        <v>1.1</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11960,7 +11960,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 58150-2024</t>
+          <t>A 19255-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11974,10 +11974,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45632</v>
+        <v>46132</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11990,7 +11990,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -12033,7 +12033,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 28264-2022</t>
+          <t>A 19256-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -12047,10 +12047,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>44746</v>
+        <v>46132</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12063,7 +12063,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -12106,7 +12106,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 31709-2023</t>
+          <t>A 37628-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -12120,10 +12120,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45117</v>
+        <v>46276</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12135,8 +12135,13 @@
           <t>ÄNGELHOLM</t>
         </is>
       </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I137" t="n">
-        <v>0.6</v>
+        <v>4.5</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -12179,7 +12184,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 8665-2022</t>
+          <t>A 7871-2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -12193,10 +12198,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>44613</v>
+        <v>45706</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12209,7 +12214,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -12252,7 +12257,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 60-2024</t>
+          <t>A 32430-2023</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12266,10 +12271,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45293</v>
+        <v>45120</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12282,7 +12287,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -12325,7 +12330,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 607-2024</t>
+          <t>A 26986-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12339,10 +12344,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45299</v>
+        <v>46185</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12355,7 +12360,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>0.6</v>
+        <v>3.5</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -12398,7 +12403,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 49206-2024</t>
+          <t>A 29436-2024</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12412,10 +12417,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45595</v>
+        <v>45483</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12428,7 +12433,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1.7</v>
+        <v>4.2</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12471,7 +12476,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 19503-2022</t>
+          <t>A 26978-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12485,10 +12490,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>44693</v>
+        <v>46185</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12501,7 +12506,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>5.1</v>
+        <v>7.7</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12544,7 +12549,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 31576-2026</t>
+          <t>A 58150-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12558,10 +12563,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46224</v>
+        <v>45632</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12574,7 +12579,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12617,7 +12622,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 57923-2024</t>
+          <t>A 28264-2022</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12631,10 +12636,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45631</v>
+        <v>44746</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12647,7 +12652,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>4.5</v>
+        <v>1.5</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12690,7 +12695,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 36001-2026</t>
+          <t>A 35677-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12704,10 +12709,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46266</v>
+        <v>46265</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12720,7 +12725,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>0.8</v>
+        <v>3.1</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12763,7 +12768,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 35912-2026</t>
+          <t>A 31709-2023</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12777,10 +12782,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46266</v>
+        <v>45117</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12793,7 +12798,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12836,7 +12841,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 20635-2024</t>
+          <t>A 8665-2022</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12850,10 +12855,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45436</v>
+        <v>44613</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12866,7 +12871,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>4.8</v>
+        <v>0.6</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12909,7 +12914,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 19255-2026</t>
+          <t>A 60-2024</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12923,10 +12928,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46132</v>
+        <v>45293</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12939,7 +12944,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12982,7 +12987,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 19256-2026</t>
+          <t>A 607-2024</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12996,10 +13001,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46132</v>
+        <v>45299</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13012,7 +13017,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -13055,7 +13060,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 37628-2026</t>
+          <t>A 49206-2024</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -13069,10 +13074,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46276</v>
+        <v>45595</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13084,13 +13089,8 @@
           <t>ÄNGELHOLM</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I150" t="n">
-        <v>4.5</v>
+        <v>1.7</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -13133,7 +13133,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 23980-2024</t>
+          <t>A 19503-2022</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -13147,10 +13147,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45456</v>
+        <v>44693</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13163,7 +13163,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.3</v>
+        <v>5.1</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -13206,7 +13206,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 55748-2024</t>
+          <t>A 57923-2024</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -13220,10 +13220,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45623</v>
+        <v>45631</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13236,7 +13236,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>0.9</v>
+        <v>4.5</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -13279,7 +13279,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 26986-2026</t>
+          <t>A 20635-2024</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -13293,10 +13293,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46185</v>
+        <v>45436</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13309,7 +13309,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -13352,7 +13352,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 48197-2024</t>
+          <t>A 23980-2024</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -13366,10 +13366,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45590</v>
+        <v>45456</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13382,7 +13382,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>3.1</v>
+        <v>1.3</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -13425,7 +13425,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 26978-2026</t>
+          <t>A 55748-2024</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13439,10 +13439,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46185</v>
+        <v>45623</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13455,7 +13455,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>7.7</v>
+        <v>0.9</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13498,7 +13498,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 35677-2026</t>
+          <t>A 48197-2024</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13512,10 +13512,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46265</v>
+        <v>45590</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13588,7 +13588,7 @@
         <v>45622</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13661,7 +13661,7 @@
         <v>45835</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13734,7 +13734,7 @@
         <v>45736</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13807,7 +13807,7 @@
         <v>45582</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13880,7 +13880,7 @@
         <v>45582</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13953,7 +13953,7 @@
         <v>45582</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14026,7 +14026,7 @@
         <v>45582</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14099,7 +14099,7 @@
         <v>44519</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14172,7 +14172,7 @@
         <v>45239</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14245,7 +14245,7 @@
         <v>45168</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14318,7 +14318,7 @@
         <v>44861</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14391,7 +14391,7 @@
         <v>45582</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>

--- a/Översikt ÄNGELHOLM.xlsx
+++ b/Översikt ÄNGELHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45099</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         <v>45931</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
         <v>45931</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>46106</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>44802</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 32268-2022</t>
+          <t>A 74502-2021</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1204,10 +1204,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44781</v>
+        <v>44560</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1220,16 +1220,16 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>8.6</v>
+        <v>5.6</v>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1244,7 +1244,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1253,12 +1253,128 @@
         <v>8</v>
       </c>
       <c r="T7" t="n">
+        <v>9</v>
+      </c>
+      <c r="U7" t="n">
+        <v>9</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Entita
+Grönsångare
+Sydlig sotticka
+Västlig hakmossa
+Spillkråka
+Gröngöling
+Kungsfågel
+Skogsduva</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 74502-2021 artfynd.xlsx", "A 74502-2021")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 74502-2021 karta.png", "A 74502-2021")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 74502-2021 georefererad karta.tif", "A 74502-2021")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 74502-2021 FSC-klagomål.docx", "A 74502-2021")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 74502-2021 FSC-klagomål mail.docx", "A 74502-2021")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 74502-2021 tillsynsbegäran.docx", "A 74502-2021")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 74502-2021 tillsynsbegäran mail.docx", "A 74502-2021")</f>
+        <v/>
+      </c>
+      <c r="AE7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 74502-2021 prioriterade fågelarter.docx", "A 74502-2021")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 32268-2022</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>44781</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>5</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>8</v>
+      </c>
+      <c r="T8" t="n">
         <v>14</v>
       </c>
-      <c r="U7" t="n">
+      <c r="U8" t="n">
         <v>14</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Bokvårtlav
 Blåmossa
@@ -1270,148 +1386,32 @@
 Vanlig padda</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 32268-2022 artfynd.xlsx", "A 32268-2022")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 32268-2022 karta.png", "A 32268-2022")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 32268-2022 georefererad karta.tif", "A 32268-2022")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 32268-2022 FSC-klagomål.docx", "A 32268-2022")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 32268-2022 FSC-klagomål mail.docx", "A 32268-2022")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 32268-2022 tillsynsbegäran.docx", "A 32268-2022")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 32268-2022 tillsynsbegäran mail.docx", "A 32268-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 74502-2021</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>44560</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="J8" t="n">
-        <v>6</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" t="n">
-        <v>3</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>3</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>8</v>
-      </c>
-      <c r="T8" t="n">
-        <v>9</v>
-      </c>
-      <c r="U8" t="n">
-        <v>9</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Entita
-Grönsångare
-Sydlig sotticka
-Västlig hakmossa
-Spillkråka
-Gröngöling
-Kungsfågel
-Skogsduva</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 74502-2021 artfynd.xlsx", "A 74502-2021")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 74502-2021 karta.png", "A 74502-2021")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 74502-2021 georefererad karta.tif", "A 74502-2021")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 74502-2021 FSC-klagomål.docx", "A 74502-2021")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 74502-2021 FSC-klagomål mail.docx", "A 74502-2021")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 74502-2021 tillsynsbegäran.docx", "A 74502-2021")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 74502-2021 tillsynsbegäran mail.docx", "A 74502-2021")</f>
-        <v/>
-      </c>
-      <c r="AE8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 74502-2021 prioriterade fågelarter.docx", "A 74502-2021")</f>
         <v/>
       </c>
     </row>
@@ -1435,7 +1435,7 @@
         <v>45835</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 5046-2022</t>
+          <t>A 308-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1547,10 +1547,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44593</v>
+        <v>44929</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1563,34 +1563,34 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>3</v>
+        <v>0.8</v>
       </c>
       <c r="J10" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L10" t="n">
         <v>1</v>
       </c>
       <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
         <v>1</v>
       </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2</v>
-      </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>6</v>
@@ -1599,9 +1599,119 @@
         <v>7</v>
       </c>
       <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Bokvårtlav
+Dvärghäxört
+Havstulpanlav
+Klippfrullania
+Platt fjädermossa
+Stor knopplav</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 308-2023 artfynd.xlsx", "A 308-2023")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 308-2023 karta.png", "A 308-2023")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 308-2023 georefererad karta.tif", "A 308-2023")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 308-2023 FSC-klagomål.docx", "A 308-2023")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 308-2023 FSC-klagomål mail.docx", "A 308-2023")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 308-2023 tillsynsbegäran.docx", "A 308-2023")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 308-2023 tillsynsbegäran mail.docx", "A 308-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 5046-2022</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>44593</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>3</v>
+      </c>
+      <c r="J11" t="n">
         <v>6</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>6</v>
+      </c>
+      <c r="T11" t="n">
+        <v>7</v>
+      </c>
+      <c r="U11" t="n">
+        <v>6</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Grönfink
 Gulsparv
@@ -1611,111 +1721,225 @@
 Trädlärka</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 5046-2022 artfynd.xlsx", "A 5046-2022")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 5046-2022 karta.png", "A 5046-2022")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 5046-2022 georefererad karta.tif", "A 5046-2022")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 5046-2022 FSC-klagomål.docx", "A 5046-2022")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 5046-2022 FSC-klagomål mail.docx", "A 5046-2022")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 5046-2022 tillsynsbegäran.docx", "A 5046-2022")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 5046-2022 tillsynsbegäran mail.docx", "A 5046-2022")</f>
         <v/>
       </c>
-      <c r="AE10">
+      <c r="AE11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 5046-2022 prioriterade fågelarter.docx", "A 5046-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 308-2023</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>44929</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>S 2334-2023</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Askåterföring</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>45106</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>6</v>
+      </c>
+      <c r="T12" t="n">
+        <v>6</v>
+      </c>
+      <c r="U12" t="n">
+        <v>6</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Småvänderot
+Vitfläckig guldvinge
+Kambräken
+Spillkråka
+Törnskata
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/S 2334-2023 artfynd.xlsx", "S 2334-2023")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/S 2334-2023 karta.png", "S 2334-2023")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/S 2334-2023 georefererad karta.tif", "S 2334-2023")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/S 2334-2023 FSC-klagomål.docx", "S 2334-2023")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/S 2334-2023 FSC-klagomål mail.docx", "S 2334-2023")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/S 2334-2023 tillsynsbegäran.docx", "S 2334-2023")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/S 2334-2023 tillsynsbegäran mail.docx", "S 2334-2023")</f>
+        <v/>
+      </c>
+      <c r="AE12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/S 2334-2023 prioriterade fågelarter.docx", "S 2334-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>S 4107-2023</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45245</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
         <v>5</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L13" t="n">
         <v>1</v>
       </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
         <v>1</v>
       </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
         <v>6</v>
       </c>
-      <c r="T11" t="n">
+      <c r="T13" t="n">
         <v>7</v>
       </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Bokvårtlav
 Dvärghäxört
@@ -1725,230 +1949,6 @@
 Stor knopplav</t>
         </is>
       </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 308-2023 artfynd.xlsx", "A 308-2023")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 308-2023 karta.png", "A 308-2023")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 308-2023 georefererad karta.tif", "A 308-2023")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 308-2023 FSC-klagomål.docx", "A 308-2023")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 308-2023 FSC-klagomål mail.docx", "A 308-2023")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 308-2023 tillsynsbegäran.docx", "A 308-2023")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 308-2023 tillsynsbegäran mail.docx", "A 308-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>S 2334-2023</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Askåterföring</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>45106</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>47.6</v>
-      </c>
-      <c r="J12" t="n">
-        <v>3</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1</v>
-      </c>
-      <c r="S12" t="n">
-        <v>6</v>
-      </c>
-      <c r="T12" t="n">
-        <v>6</v>
-      </c>
-      <c r="U12" t="n">
-        <v>6</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Småvänderot
-Vitfläckig guldvinge
-Kambräken
-Spillkråka
-Törnskata
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/S 2334-2023 artfynd.xlsx", "S 2334-2023")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/S 2334-2023 karta.png", "S 2334-2023")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/S 2334-2023 georefererad karta.tif", "S 2334-2023")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/S 2334-2023 FSC-klagomål.docx", "S 2334-2023")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/S 2334-2023 FSC-klagomål mail.docx", "S 2334-2023")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/S 2334-2023 tillsynsbegäran.docx", "S 2334-2023")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/S 2334-2023 tillsynsbegäran mail.docx", "S 2334-2023")</f>
-        <v/>
-      </c>
-      <c r="AE12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/S 2334-2023 prioriterade fågelarter.docx", "S 2334-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>S 4107-2023</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45245</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>5</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>6</v>
-      </c>
-      <c r="T13" t="n">
-        <v>7</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Bokvårtlav
-Dvärghäxört
-Havstulpanlav
-Klippfrullania
-Platt fjädermossa
-Stor knopplav</t>
-        </is>
-      </c>
       <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/S 4107-2023 artfynd.xlsx", "S 4107-2023")</f>
         <v/>
@@ -1981,7 +1981,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 2931-2026</t>
+          <t>A 35675-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1995,10 +1995,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46038</v>
+        <v>46265</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2011,13 +2011,13 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>3.5</v>
+        <v>8.9</v>
       </c>
       <c r="J14" t="n">
         <v>4</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
         <v>1</v>
@@ -2044,12 +2044,238 @@
         <v>5</v>
       </c>
       <c r="T14" t="n">
+        <v>10</v>
+      </c>
+      <c r="U14" t="n">
+        <v>9</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Lappuggla
+Entita
+Blåmossa
+Skogsödla
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 35675-2026 artfynd.xlsx", "A 35675-2026")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 35675-2026 karta.png", "A 35675-2026")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 35675-2026 georefererad karta.tif", "A 35675-2026")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 35675-2026 FSC-klagomål.docx", "A 35675-2026")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 35675-2026 FSC-klagomål mail.docx", "A 35675-2026")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 35675-2026 tillsynsbegäran.docx", "A 35675-2026")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 35675-2026 tillsynsbegäran mail.docx", "A 35675-2026")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 35675-2026 prioriterade fågelarter.docx", "A 35675-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 35680-2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>2</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>3</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="n">
+        <v>7</v>
+      </c>
+      <c r="U15" t="n">
+        <v>7</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Vedlavklubba
+Entita
+Kandelabersvamp
+Blåmossa
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 35680-2026 artfynd.xlsx", "A 35680-2026")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 35680-2026 karta.png", "A 35680-2026")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 35680-2026 georefererad karta.tif", "A 35680-2026")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 35680-2026 FSC-klagomål.docx", "A 35680-2026")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 35680-2026 FSC-klagomål mail.docx", "A 35680-2026")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 35680-2026 tillsynsbegäran.docx", "A 35680-2026")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 35680-2026 tillsynsbegäran mail.docx", "A 35680-2026")</f>
+        <v/>
+      </c>
+      <c r="AE15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 35680-2026 prioriterade fågelarter.docx", "A 35680-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 2931-2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>46038</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J16" t="n">
+        <v>4</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="n">
         <v>6</v>
       </c>
-      <c r="U14" t="n">
+      <c r="U16" t="n">
         <v>5</v>
       </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Småvänderot
 Entita
@@ -2058,262 +2284,36 @@
 Grönsiska</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 2931-2026 artfynd.xlsx", "A 2931-2026")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 2931-2026 karta.png", "A 2931-2026")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 2931-2026 georefererad karta.tif", "A 2931-2026")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 2931-2026 FSC-klagomål.docx", "A 2931-2026")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 2931-2026 FSC-klagomål mail.docx", "A 2931-2026")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 2931-2026 tillsynsbegäran.docx", "A 2931-2026")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 2931-2026 tillsynsbegäran mail.docx", "A 2931-2026")</f>
         <v/>
       </c>
-      <c r="AE14">
+      <c r="AE16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 2931-2026 prioriterade fågelarter.docx", "A 2931-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 35675-2026</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="J15" t="n">
-        <v>4</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1</v>
-      </c>
-      <c r="S15" t="n">
-        <v>5</v>
-      </c>
-      <c r="T15" t="n">
-        <v>10</v>
-      </c>
-      <c r="U15" t="n">
-        <v>9</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Lappuggla
-Entita
-Blåmossa
-Skogsödla
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 35675-2026 artfynd.xlsx", "A 35675-2026")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 35675-2026 karta.png", "A 35675-2026")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 35675-2026 georefererad karta.tif", "A 35675-2026")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 35675-2026 FSC-klagomål.docx", "A 35675-2026")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 35675-2026 FSC-klagomål mail.docx", "A 35675-2026")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 35675-2026 tillsynsbegäran.docx", "A 35675-2026")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 35675-2026 tillsynsbegäran mail.docx", "A 35675-2026")</f>
-        <v/>
-      </c>
-      <c r="AE15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 35675-2026 prioriterade fågelarter.docx", "A 35675-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 35680-2026</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J16" t="n">
-        <v>2</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" t="n">
-        <v>2</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>3</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1</v>
-      </c>
-      <c r="S16" t="n">
-        <v>5</v>
-      </c>
-      <c r="T16" t="n">
-        <v>7</v>
-      </c>
-      <c r="U16" t="n">
-        <v>7</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Vedlavklubba
-Entita
-Kandelabersvamp
-Blåmossa
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 35680-2026 artfynd.xlsx", "A 35680-2026")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 35680-2026 karta.png", "A 35680-2026")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 35680-2026 georefererad karta.tif", "A 35680-2026")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 35680-2026 FSC-klagomål.docx", "A 35680-2026")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 35680-2026 FSC-klagomål mail.docx", "A 35680-2026")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 35680-2026 tillsynsbegäran.docx", "A 35680-2026")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 35680-2026 tillsynsbegäran mail.docx", "A 35680-2026")</f>
-        <v/>
-      </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 35680-2026 prioriterade fågelarter.docx", "A 35680-2026")</f>
         <v/>
       </c>
     </row>
@@ -2337,7 +2337,7 @@
         <v>45664</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2449,7 +2449,7 @@
         <v>44864</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 905-2024</t>
+          <t>A 28874-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2554,10 +2554,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45301</v>
+        <v>45104</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2570,19 +2570,19 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>4.9</v>
+        <v>9</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -2594,710 +2594,710 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>3</v>
       </c>
       <c r="T19" t="n">
+        <v>5</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Blåmossa
+Stubbspretmossa
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 28874-2023 artfynd.xlsx", "A 28874-2023")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 28874-2023 karta.png", "A 28874-2023")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 28874-2023 georefererad karta.tif", "A 28874-2023")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 28874-2023 FSC-klagomål.docx", "A 28874-2023")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 28874-2023 FSC-klagomål mail.docx", "A 28874-2023")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 28874-2023 tillsynsbegäran.docx", "A 28874-2023")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 28874-2023 tillsynsbegäran mail.docx", "A 28874-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 31907-2023</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>45118</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
         <v>3</v>
       </c>
-      <c r="U19" t="n">
+      <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Bokvårtlav
+Platt fjädermossa
+Stubbspretmossa</t>
+        </is>
+      </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 31907-2023 artfynd.xlsx", "A 31907-2023")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 31907-2023 karta.png", "A 31907-2023")</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 31907-2023 georefererad karta.tif", "A 31907-2023")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 31907-2023 FSC-klagomål.docx", "A 31907-2023")</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 31907-2023 FSC-klagomål mail.docx", "A 31907-2023")</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 31907-2023 tillsynsbegäran.docx", "A 31907-2023")</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 31907-2023 tillsynsbegäran mail.docx", "A 31907-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 50684-2023</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>45210</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J21" t="n">
         <v>2</v>
       </c>
-      <c r="V19" s="2" t="inlineStr">
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Skogsalm
+Kopparödla
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 50684-2023 artfynd.xlsx", "A 50684-2023")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 50684-2023 karta.png", "A 50684-2023")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 50684-2023 georefererad karta.tif", "A 50684-2023")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 50684-2023 FSC-klagomål.docx", "A 50684-2023")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 50684-2023 FSC-klagomål mail.docx", "A 50684-2023")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 50684-2023 tillsynsbegäran.docx", "A 50684-2023")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 50684-2023 tillsynsbegäran mail.docx", "A 50684-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 905-2024</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>45301</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>Igelkott
 Desmeknopp
 Myskmadra</t>
         </is>
       </c>
-      <c r="W19">
+      <c r="W22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 905-2024 artfynd.xlsx", "A 905-2024")</f>
         <v/>
       </c>
-      <c r="X19">
+      <c r="X22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 905-2024 karta.png", "A 905-2024")</f>
         <v/>
       </c>
-      <c r="Y19">
+      <c r="Y22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 905-2024 georefererad karta.tif", "A 905-2024")</f>
         <v/>
       </c>
-      <c r="AA19">
+      <c r="AA22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 905-2024 FSC-klagomål.docx", "A 905-2024")</f>
         <v/>
       </c>
-      <c r="AB19">
+      <c r="AB22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 905-2024 FSC-klagomål mail.docx", "A 905-2024")</f>
         <v/>
       </c>
-      <c r="AC19">
+      <c r="AC22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 905-2024 tillsynsbegäran.docx", "A 905-2024")</f>
         <v/>
       </c>
-      <c r="AD19">
+      <c r="AD22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 905-2024 tillsynsbegäran mail.docx", "A 905-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 28874-2023</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>45104</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>9</v>
-      </c>
-      <c r="J20" t="n">
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>A 18559-2025</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>45763</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>3</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>2</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>3</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>Grönsångare
+Gulsparv
+Gröngöling</t>
+        </is>
+      </c>
+      <c r="W23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 18559-2025 artfynd.xlsx", "A 18559-2025")</f>
+        <v/>
+      </c>
+      <c r="X23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 18559-2025 karta.png", "A 18559-2025")</f>
+        <v/>
+      </c>
+      <c r="Y23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 18559-2025 georefererad karta.tif", "A 18559-2025")</f>
+        <v/>
+      </c>
+      <c r="AA23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 18559-2025 FSC-klagomål.docx", "A 18559-2025")</f>
+        <v/>
+      </c>
+      <c r="AB23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 18559-2025 FSC-klagomål mail.docx", "A 18559-2025")</f>
+        <v/>
+      </c>
+      <c r="AC23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 18559-2025 tillsynsbegäran.docx", "A 18559-2025")</f>
+        <v/>
+      </c>
+      <c r="AD23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 18559-2025 tillsynsbegäran mail.docx", "A 18559-2025")</f>
+        <v/>
+      </c>
+      <c r="AE23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 18559-2025 prioriterade fågelarter.docx", "A 18559-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>A 8065-2025</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="n">
+        <v>45707</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>2</v>
+      </c>
+      <c r="M24" t="n">
         <v>1</v>
       </c>
-      <c r="K20" t="n">
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>3</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
         <v>2</v>
       </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3</v>
-      </c>
-      <c r="T20" t="n">
-        <v>5</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Blåmossa
-Stubbspretmossa
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 28874-2023 artfynd.xlsx", "A 28874-2023")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 28874-2023 karta.png", "A 28874-2023")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 28874-2023 georefererad karta.tif", "A 28874-2023")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 28874-2023 FSC-klagomål.docx", "A 28874-2023")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 28874-2023 FSC-klagomål mail.docx", "A 28874-2023")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 28874-2023 tillsynsbegäran.docx", "A 28874-2023")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 28874-2023 tillsynsbegäran mail.docx", "A 28874-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 8065-2025</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>45707</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>2</v>
-      </c>
-      <c r="M21" t="n">
-        <v>1</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>3</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3</v>
-      </c>
-      <c r="T21" t="n">
-        <v>3</v>
-      </c>
-      <c r="U21" t="n">
-        <v>2</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
+      <c r="V24" s="2" t="inlineStr">
         <is>
           <t>Småvänderot
 Gullpudra
 Svinrot</t>
         </is>
       </c>
-      <c r="W21">
+      <c r="W24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 8065-2025 artfynd.xlsx", "A 8065-2025")</f>
         <v/>
       </c>
-      <c r="X21">
+      <c r="X24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 8065-2025 karta.png", "A 8065-2025")</f>
         <v/>
       </c>
-      <c r="Y21">
+      <c r="Y24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 8065-2025 georefererad karta.tif", "A 8065-2025")</f>
         <v/>
       </c>
-      <c r="AA21">
+      <c r="AA24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 8065-2025 FSC-klagomål.docx", "A 8065-2025")</f>
         <v/>
       </c>
-      <c r="AB21">
+      <c r="AB24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 8065-2025 FSC-klagomål mail.docx", "A 8065-2025")</f>
         <v/>
       </c>
-      <c r="AC21">
+      <c r="AC24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 8065-2025 tillsynsbegäran.docx", "A 8065-2025")</f>
         <v/>
       </c>
-      <c r="AD21">
+      <c r="AD24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 8065-2025 tillsynsbegäran mail.docx", "A 8065-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" t="inlineStr">
         <is>
           <t>A 3317-2026</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="n">
         <v>46041</v>
       </c>
-      <c r="E22" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
+      <c r="E25" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
         <v>2.9</v>
       </c>
-      <c r="J22" t="n">
+      <c r="J25" t="n">
         <v>3</v>
       </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
         <v>2</v>
       </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
         <v>2</v>
       </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
         <v>3</v>
       </c>
-      <c r="T22" t="n">
+      <c r="T25" t="n">
         <v>6</v>
       </c>
-      <c r="U22" t="n">
+      <c r="U25" t="n">
         <v>6</v>
       </c>
-      <c r="V22" s="2" t="inlineStr">
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>Entita
 Mindre hackspett
 Gröngöling</t>
         </is>
       </c>
-      <c r="W22">
+      <c r="W25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 3317-2026 artfynd.xlsx", "A 3317-2026")</f>
         <v/>
       </c>
-      <c r="X22">
+      <c r="X25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 3317-2026 karta.png", "A 3317-2026")</f>
         <v/>
       </c>
-      <c r="Y22">
+      <c r="Y25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 3317-2026 georefererad karta.tif", "A 3317-2026")</f>
         <v/>
       </c>
-      <c r="AA22">
+      <c r="AA25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 3317-2026 FSC-klagomål.docx", "A 3317-2026")</f>
         <v/>
       </c>
-      <c r="AB22">
+      <c r="AB25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 3317-2026 FSC-klagomål mail.docx", "A 3317-2026")</f>
         <v/>
       </c>
-      <c r="AC22">
+      <c r="AC25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 3317-2026 tillsynsbegäran.docx", "A 3317-2026")</f>
         <v/>
       </c>
-      <c r="AD22">
+      <c r="AD25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 3317-2026 tillsynsbegäran mail.docx", "A 3317-2026")</f>
         <v/>
       </c>
-      <c r="AE22">
+      <c r="AE25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 3317-2026 prioriterade fågelarter.docx", "A 3317-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>A 50684-2023</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>45210</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J23" t="n">
-        <v>2</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>1</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3</v>
-      </c>
-      <c r="T23" t="n">
-        <v>3</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>Skogsalm
-Kopparödla
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 50684-2023 artfynd.xlsx", "A 50684-2023")</f>
-        <v/>
-      </c>
-      <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 50684-2023 karta.png", "A 50684-2023")</f>
-        <v/>
-      </c>
-      <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 50684-2023 georefererad karta.tif", "A 50684-2023")</f>
-        <v/>
-      </c>
-      <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 50684-2023 FSC-klagomål.docx", "A 50684-2023")</f>
-        <v/>
-      </c>
-      <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 50684-2023 FSC-klagomål mail.docx", "A 50684-2023")</f>
-        <v/>
-      </c>
-      <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 50684-2023 tillsynsbegäran.docx", "A 50684-2023")</f>
-        <v/>
-      </c>
-      <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 50684-2023 tillsynsbegäran mail.docx", "A 50684-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>A 31907-2023</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="n">
-        <v>45118</v>
-      </c>
-      <c r="E24" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>2</v>
-      </c>
-      <c r="L24" t="n">
-        <v>1</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3</v>
-      </c>
-      <c r="T24" t="n">
-        <v>3</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>Bokvårtlav
-Platt fjädermossa
-Stubbspretmossa</t>
-        </is>
-      </c>
-      <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 31907-2023 artfynd.xlsx", "A 31907-2023")</f>
-        <v/>
-      </c>
-      <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 31907-2023 karta.png", "A 31907-2023")</f>
-        <v/>
-      </c>
-      <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 31907-2023 georefererad karta.tif", "A 31907-2023")</f>
-        <v/>
-      </c>
-      <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 31907-2023 FSC-klagomål.docx", "A 31907-2023")</f>
-        <v/>
-      </c>
-      <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 31907-2023 FSC-klagomål mail.docx", "A 31907-2023")</f>
-        <v/>
-      </c>
-      <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 31907-2023 tillsynsbegäran.docx", "A 31907-2023")</f>
-        <v/>
-      </c>
-      <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 31907-2023 tillsynsbegäran mail.docx", "A 31907-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>A 18559-2025</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="n">
-        <v>45763</v>
-      </c>
-      <c r="E25" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>3</v>
-      </c>
-      <c r="J25" t="n">
-        <v>3</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>2</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>2</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>3</v>
-      </c>
-      <c r="T25" t="n">
-        <v>3</v>
-      </c>
-      <c r="U25" t="n">
-        <v>3</v>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>Grönsångare
-Gulsparv
-Gröngöling</t>
-        </is>
-      </c>
-      <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 18559-2025 artfynd.xlsx", "A 18559-2025")</f>
-        <v/>
-      </c>
-      <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 18559-2025 karta.png", "A 18559-2025")</f>
-        <v/>
-      </c>
-      <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 18559-2025 georefererad karta.tif", "A 18559-2025")</f>
-        <v/>
-      </c>
-      <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 18559-2025 FSC-klagomål.docx", "A 18559-2025")</f>
-        <v/>
-      </c>
-      <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 18559-2025 FSC-klagomål mail.docx", "A 18559-2025")</f>
-        <v/>
-      </c>
-      <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 18559-2025 tillsynsbegäran.docx", "A 18559-2025")</f>
-        <v/>
-      </c>
-      <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 18559-2025 tillsynsbegäran mail.docx", "A 18559-2025")</f>
-        <v/>
-      </c>
-      <c r="AE25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 18559-2025 prioriterade fågelarter.docx", "A 18559-2025")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 27544-2024</t>
+          <t>A 29157-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3311,10 +3311,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45474</v>
+        <v>45105</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3327,16 +3327,16 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3.2</v>
+        <v>6.9</v>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -3351,7 +3351,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -3363,264 +3363,264 @@
         <v>2</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>Entita
+Talltita</t>
+        </is>
+      </c>
+      <c r="W26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 29157-2023 artfynd.xlsx", "A 29157-2023")</f>
+        <v/>
+      </c>
+      <c r="X26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 29157-2023 karta.png", "A 29157-2023")</f>
+        <v/>
+      </c>
+      <c r="Y26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 29157-2023 georefererad karta.tif", "A 29157-2023")</f>
+        <v/>
+      </c>
+      <c r="AA26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 29157-2023 FSC-klagomål.docx", "A 29157-2023")</f>
+        <v/>
+      </c>
+      <c r="AB26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 29157-2023 FSC-klagomål mail.docx", "A 29157-2023")</f>
+        <v/>
+      </c>
+      <c r="AC26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 29157-2023 tillsynsbegäran.docx", "A 29157-2023")</f>
+        <v/>
+      </c>
+      <c r="AD26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 29157-2023 tillsynsbegäran mail.docx", "A 29157-2023")</f>
+        <v/>
+      </c>
+      <c r="AE26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 29157-2023 prioriterade fågelarter.docx", "A 29157-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>A 33520-2025</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D27" s="1" t="n">
+        <v>45841</v>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2</v>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>Småvänderot
+Entita</t>
+        </is>
+      </c>
+      <c r="W27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 33520-2025 artfynd.xlsx", "A 33520-2025")</f>
+        <v/>
+      </c>
+      <c r="X27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 33520-2025 karta.png", "A 33520-2025")</f>
+        <v/>
+      </c>
+      <c r="Y27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 33520-2025 georefererad karta.tif", "A 33520-2025")</f>
+        <v/>
+      </c>
+      <c r="AA27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 33520-2025 FSC-klagomål.docx", "A 33520-2025")</f>
+        <v/>
+      </c>
+      <c r="AB27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 33520-2025 FSC-klagomål mail.docx", "A 33520-2025")</f>
+        <v/>
+      </c>
+      <c r="AC27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 33520-2025 tillsynsbegäran.docx", "A 33520-2025")</f>
+        <v/>
+      </c>
+      <c r="AD27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 33520-2025 tillsynsbegäran mail.docx", "A 33520-2025")</f>
+        <v/>
+      </c>
+      <c r="AE27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 33520-2025 prioriterade fågelarter.docx", "A 33520-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>A 27544-2024</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D28" s="1" t="n">
+        <v>45474</v>
+      </c>
+      <c r="E28" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
         <is>
           <t>Västlig hakmossa
 Spillkråka</t>
         </is>
       </c>
-      <c r="W26">
+      <c r="W28">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 27544-2024 artfynd.xlsx", "A 27544-2024")</f>
         <v/>
       </c>
-      <c r="X26">
+      <c r="X28">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 27544-2024 karta.png", "A 27544-2024")</f>
         <v/>
       </c>
-      <c r="Y26">
+      <c r="Y28">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 27544-2024 georefererad karta.tif", "A 27544-2024")</f>
         <v/>
       </c>
-      <c r="AA26">
+      <c r="AA28">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 27544-2024 FSC-klagomål.docx", "A 27544-2024")</f>
         <v/>
       </c>
-      <c r="AB26">
+      <c r="AB28">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 27544-2024 FSC-klagomål mail.docx", "A 27544-2024")</f>
         <v/>
       </c>
-      <c r="AC26">
+      <c r="AC28">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 27544-2024 tillsynsbegäran.docx", "A 27544-2024")</f>
         <v/>
       </c>
-      <c r="AD26">
+      <c r="AD28">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 27544-2024 tillsynsbegäran mail.docx", "A 27544-2024")</f>
         <v/>
       </c>
-      <c r="AE26">
+      <c r="AE28">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 27544-2024 prioriterade fågelarter.docx", "A 27544-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>A 33520-2025</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="n">
-        <v>45841</v>
-      </c>
-      <c r="E27" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J27" t="n">
-        <v>1</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>1</v>
-      </c>
-      <c r="M27" t="n">
-        <v>1</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>2</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2</v>
-      </c>
-      <c r="U27" t="n">
-        <v>2</v>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>Småvänderot
-Entita</t>
-        </is>
-      </c>
-      <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 33520-2025 artfynd.xlsx", "A 33520-2025")</f>
-        <v/>
-      </c>
-      <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 33520-2025 karta.png", "A 33520-2025")</f>
-        <v/>
-      </c>
-      <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 33520-2025 georefererad karta.tif", "A 33520-2025")</f>
-        <v/>
-      </c>
-      <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 33520-2025 FSC-klagomål.docx", "A 33520-2025")</f>
-        <v/>
-      </c>
-      <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 33520-2025 FSC-klagomål mail.docx", "A 33520-2025")</f>
-        <v/>
-      </c>
-      <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 33520-2025 tillsynsbegäran.docx", "A 33520-2025")</f>
-        <v/>
-      </c>
-      <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 33520-2025 tillsynsbegäran mail.docx", "A 33520-2025")</f>
-        <v/>
-      </c>
-      <c r="AE27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 33520-2025 prioriterade fågelarter.docx", "A 33520-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="15" customHeight="1">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>A 29157-2023</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D28" s="1" t="n">
-        <v>45105</v>
-      </c>
-      <c r="E28" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I28" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="J28" t="n">
-        <v>2</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>2</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>2</v>
-      </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2</v>
-      </c>
-      <c r="U28" t="n">
-        <v>2</v>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>Entita
-Talltita</t>
-        </is>
-      </c>
-      <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 29157-2023 artfynd.xlsx", "A 29157-2023")</f>
-        <v/>
-      </c>
-      <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 29157-2023 karta.png", "A 29157-2023")</f>
-        <v/>
-      </c>
-      <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 29157-2023 georefererad karta.tif", "A 29157-2023")</f>
-        <v/>
-      </c>
-      <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 29157-2023 FSC-klagomål.docx", "A 29157-2023")</f>
-        <v/>
-      </c>
-      <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 29157-2023 FSC-klagomål mail.docx", "A 29157-2023")</f>
-        <v/>
-      </c>
-      <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 29157-2023 tillsynsbegäran.docx", "A 29157-2023")</f>
-        <v/>
-      </c>
-      <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 29157-2023 tillsynsbegäran mail.docx", "A 29157-2023")</f>
-        <v/>
-      </c>
-      <c r="AE28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 29157-2023 prioriterade fågelarter.docx", "A 29157-2023")</f>
         <v/>
       </c>
     </row>
@@ -3644,7 +3644,7 @@
         <v>44553</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3754,7 +3754,7 @@
         <v>45359</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
         <v>45582</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>44839</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>44742</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4180,7 +4180,7 @@
         <v>44746</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 44062-2022</t>
+          <t>A 12150-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4286,10 +4286,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44839</v>
+        <v>45377</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4302,20 +4302,20 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
         <v>1</v>
       </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
       <c r="N35" t="n">
         <v>0</v>
       </c>
@@ -4326,10 +4326,10 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4342,42 +4342,42 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 44062-2022 artfynd.xlsx", "A 44062-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 12150-2024 artfynd.xlsx", "A 12150-2024")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 44062-2022 karta.png", "A 44062-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 12150-2024 karta.png", "A 12150-2024")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 44062-2022 georefererad karta.tif", "A 44062-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 12150-2024 georefererad karta.tif", "A 12150-2024")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 44062-2022 FSC-klagomål.docx", "A 44062-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 12150-2024 FSC-klagomål.docx", "A 12150-2024")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 44062-2022 FSC-klagomål mail.docx", "A 44062-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 12150-2024 FSC-klagomål mail.docx", "A 12150-2024")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 44062-2022 tillsynsbegäran.docx", "A 44062-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 12150-2024 tillsynsbegäran.docx", "A 12150-2024")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 44062-2022 tillsynsbegäran mail.docx", "A 44062-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 12150-2024 tillsynsbegäran mail.docx", "A 12150-2024")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 4088-2024</t>
+          <t>A 25129-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4391,10 +4391,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45323</v>
+        <v>45462</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4407,7 +4407,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4447,42 +4447,42 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>Flikbålmossa</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 4088-2024 artfynd.xlsx", "A 4088-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 25129-2024 artfynd.xlsx", "A 25129-2024")</f>
         <v/>
       </c>
       <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 4088-2024 karta.png", "A 4088-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 25129-2024 karta.png", "A 25129-2024")</f>
         <v/>
       </c>
       <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 4088-2024 georefererad karta.tif", "A 4088-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 25129-2024 georefererad karta.tif", "A 25129-2024")</f>
         <v/>
       </c>
       <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 4088-2024 FSC-klagomål.docx", "A 4088-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 25129-2024 FSC-klagomål.docx", "A 25129-2024")</f>
         <v/>
       </c>
       <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 4088-2024 FSC-klagomål mail.docx", "A 4088-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 25129-2024 FSC-klagomål mail.docx", "A 25129-2024")</f>
         <v/>
       </c>
       <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 4088-2024 tillsynsbegäran.docx", "A 4088-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 25129-2024 tillsynsbegäran.docx", "A 25129-2024")</f>
         <v/>
       </c>
       <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 4088-2024 tillsynsbegäran mail.docx", "A 4088-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 25129-2024 tillsynsbegäran mail.docx", "A 25129-2024")</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 25129-2024</t>
+          <t>A 61094-2021</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4496,10 +4496,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45462</v>
+        <v>44498</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4512,16 +4512,16 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>4.6</v>
+        <v>6.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
@@ -4536,7 +4536,7 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
@@ -4548,46 +4548,46 @@
         <v>1</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="W37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 25129-2024 artfynd.xlsx", "A 25129-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 61094-2021 artfynd.xlsx", "A 61094-2021")</f>
         <v/>
       </c>
       <c r="X37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 25129-2024 karta.png", "A 25129-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 61094-2021 karta.png", "A 61094-2021")</f>
         <v/>
       </c>
       <c r="Y37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 25129-2024 georefererad karta.tif", "A 25129-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 61094-2021 georefererad karta.tif", "A 61094-2021")</f>
         <v/>
       </c>
       <c r="AA37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 25129-2024 FSC-klagomål.docx", "A 25129-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 61094-2021 FSC-klagomål.docx", "A 61094-2021")</f>
         <v/>
       </c>
       <c r="AB37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 25129-2024 FSC-klagomål mail.docx", "A 25129-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 61094-2021 FSC-klagomål mail.docx", "A 61094-2021")</f>
         <v/>
       </c>
       <c r="AC37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 25129-2024 tillsynsbegäran.docx", "A 25129-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 61094-2021 tillsynsbegäran.docx", "A 61094-2021")</f>
         <v/>
       </c>
       <c r="AD37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 25129-2024 tillsynsbegäran mail.docx", "A 25129-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 61094-2021 tillsynsbegäran mail.docx", "A 61094-2021")</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 12150-2024</t>
+          <t>A 4088-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4601,10 +4601,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45377</v>
+        <v>45323</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4617,7 +4617,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.4</v>
+        <v>3.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4626,10 +4626,10 @@
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
         <v>0</v>
@@ -4644,7 +4644,7 @@
         <v>1</v>
       </c>
       <c r="R38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4653,46 +4653,46 @@
         <v>1</v>
       </c>
       <c r="U38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Flikbålmossa</t>
         </is>
       </c>
       <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 12150-2024 artfynd.xlsx", "A 12150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 4088-2024 artfynd.xlsx", "A 4088-2024")</f>
         <v/>
       </c>
       <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 12150-2024 karta.png", "A 12150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 4088-2024 karta.png", "A 4088-2024")</f>
         <v/>
       </c>
       <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 12150-2024 georefererad karta.tif", "A 12150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 4088-2024 georefererad karta.tif", "A 4088-2024")</f>
         <v/>
       </c>
       <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 12150-2024 FSC-klagomål.docx", "A 12150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 4088-2024 FSC-klagomål.docx", "A 4088-2024")</f>
         <v/>
       </c>
       <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 12150-2024 FSC-klagomål mail.docx", "A 12150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 4088-2024 FSC-klagomål mail.docx", "A 4088-2024")</f>
         <v/>
       </c>
       <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 12150-2024 tillsynsbegäran.docx", "A 12150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 4088-2024 tillsynsbegäran.docx", "A 4088-2024")</f>
         <v/>
       </c>
       <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 12150-2024 tillsynsbegäran mail.docx", "A 12150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 4088-2024 tillsynsbegäran mail.docx", "A 4088-2024")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 27094-2026</t>
+          <t>A 50642-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4706,10 +4706,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46188</v>
+        <v>45210</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4722,13 +4722,13 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>6.2</v>
+        <v>0.8</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
@@ -4762,42 +4762,42 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 27094-2026 artfynd.xlsx", "A 27094-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 50642-2023 artfynd.xlsx", "A 50642-2023")</f>
         <v/>
       </c>
       <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 27094-2026 karta.png", "A 27094-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 50642-2023 karta.png", "A 50642-2023")</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 27094-2026 georefererad karta.tif", "A 27094-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 50642-2023 georefererad karta.tif", "A 50642-2023")</f>
         <v/>
       </c>
       <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 27094-2026 FSC-klagomål.docx", "A 27094-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 50642-2023 FSC-klagomål.docx", "A 50642-2023")</f>
         <v/>
       </c>
       <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 27094-2026 FSC-klagomål mail.docx", "A 27094-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 50642-2023 FSC-klagomål mail.docx", "A 50642-2023")</f>
         <v/>
       </c>
       <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 27094-2026 tillsynsbegäran.docx", "A 27094-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 50642-2023 tillsynsbegäran.docx", "A 50642-2023")</f>
         <v/>
       </c>
       <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 27094-2026 tillsynsbegäran mail.docx", "A 27094-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 50642-2023 tillsynsbegäran mail.docx", "A 50642-2023")</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 61094-2021</t>
+          <t>A 46487-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4811,10 +4811,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44498</v>
+        <v>45582</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4827,13 +4827,13 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -4867,42 +4867,42 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="W40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 61094-2021 artfynd.xlsx", "A 61094-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 46487-2024 artfynd.xlsx", "A 46487-2024")</f>
         <v/>
       </c>
       <c r="X40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 61094-2021 karta.png", "A 61094-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 46487-2024 karta.png", "A 46487-2024")</f>
         <v/>
       </c>
       <c r="Y40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 61094-2021 georefererad karta.tif", "A 61094-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 46487-2024 georefererad karta.tif", "A 46487-2024")</f>
         <v/>
       </c>
       <c r="AA40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 61094-2021 FSC-klagomål.docx", "A 61094-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 46487-2024 FSC-klagomål.docx", "A 46487-2024")</f>
         <v/>
       </c>
       <c r="AB40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 61094-2021 FSC-klagomål mail.docx", "A 61094-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 46487-2024 FSC-klagomål mail.docx", "A 46487-2024")</f>
         <v/>
       </c>
       <c r="AC40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 61094-2021 tillsynsbegäran.docx", "A 61094-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 46487-2024 tillsynsbegäran.docx", "A 46487-2024")</f>
         <v/>
       </c>
       <c r="AD40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 61094-2021 tillsynsbegäran mail.docx", "A 61094-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 46487-2024 tillsynsbegäran mail.docx", "A 46487-2024")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 50642-2023</t>
+          <t>A 44062-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45210</v>
+        <v>44839</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4932,13 +4932,13 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
         <v>1</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -4968,39 +4968,39 @@
         <v>1</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 50642-2023 artfynd.xlsx", "A 50642-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 44062-2022 artfynd.xlsx", "A 44062-2022")</f>
         <v/>
       </c>
       <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 50642-2023 karta.png", "A 50642-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 44062-2022 karta.png", "A 44062-2022")</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 50642-2023 georefererad karta.tif", "A 50642-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 44062-2022 georefererad karta.tif", "A 44062-2022")</f>
         <v/>
       </c>
       <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 50642-2023 FSC-klagomål.docx", "A 50642-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 44062-2022 FSC-klagomål.docx", "A 44062-2022")</f>
         <v/>
       </c>
       <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 50642-2023 FSC-klagomål mail.docx", "A 50642-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 44062-2022 FSC-klagomål mail.docx", "A 44062-2022")</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 50642-2023 tillsynsbegäran.docx", "A 50642-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 44062-2022 tillsynsbegäran.docx", "A 44062-2022")</f>
         <v/>
       </c>
       <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 50642-2023 tillsynsbegäran mail.docx", "A 50642-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 44062-2022 tillsynsbegäran mail.docx", "A 44062-2022")</f>
         <v/>
       </c>
     </row>
@@ -5024,7 +5024,7 @@
         <v>46265</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5133,7 +5133,7 @@
         <v>46224</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5221,7 +5221,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 46487-2024</t>
+          <t>A 27094-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5235,10 +5235,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45582</v>
+        <v>46188</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5251,13 +5251,13 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
         <v>1</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
@@ -5287,39 +5287,39 @@
         <v>1</v>
       </c>
       <c r="U44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 46487-2024 artfynd.xlsx", "A 46487-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 27094-2026 artfynd.xlsx", "A 27094-2026")</f>
         <v/>
       </c>
       <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 46487-2024 karta.png", "A 46487-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 27094-2026 karta.png", "A 27094-2026")</f>
         <v/>
       </c>
       <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 46487-2024 georefererad karta.tif", "A 46487-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 27094-2026 georefererad karta.tif", "A 27094-2026")</f>
         <v/>
       </c>
       <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 46487-2024 FSC-klagomål.docx", "A 46487-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 27094-2026 FSC-klagomål.docx", "A 27094-2026")</f>
         <v/>
       </c>
       <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 46487-2024 FSC-klagomål mail.docx", "A 46487-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 27094-2026 FSC-klagomål mail.docx", "A 27094-2026")</f>
         <v/>
       </c>
       <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 46487-2024 tillsynsbegäran.docx", "A 46487-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 27094-2026 tillsynsbegäran.docx", "A 27094-2026")</f>
         <v/>
       </c>
       <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 46487-2024 tillsynsbegäran mail.docx", "A 46487-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 27094-2026 tillsynsbegäran mail.docx", "A 27094-2026")</f>
         <v/>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
         <v>45084</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5448,7 +5448,7 @@
         <v>44862</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5553,7 +5553,7 @@
         <v>44880</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5626,7 +5626,7 @@
         <v>44839</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5699,7 +5699,7 @@
         <v>44725</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5772,7 +5772,7 @@
         <v>44840</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5845,7 +5845,7 @@
         <v>44498</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5918,7 +5918,7 @@
         <v>44477</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5991,7 +5991,7 @@
         <v>44657</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
         <v>44634</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6137,7 +6137,7 @@
         <v>44802</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6210,7 +6210,7 @@
         <v>44802</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
         <v>44827</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 56569-2021</t>
+          <t>A 23328-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6353,10 +6353,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44480</v>
+        <v>44720</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6369,7 +6369,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6429,7 +6429,7 @@
         <v>44634</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 40275-2023</t>
+          <t>A 32364-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6499,10 +6499,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45169</v>
+        <v>45120</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6558,7 +6558,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 6667-2025</t>
+          <t>A 56569-2021</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6572,10 +6572,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45700</v>
+        <v>44480</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6588,7 +6588,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6631,7 +6631,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 46702-2024</t>
+          <t>A 8139-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6645,10 +6645,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45583</v>
+        <v>45708</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.2</v>
+        <v>3.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6704,7 +6704,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 31789-2023</t>
+          <t>A 23980-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6718,10 +6718,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45118</v>
+        <v>45456</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6777,7 +6777,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 1644-2025</t>
+          <t>A 55748-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6791,10 +6791,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45670</v>
+        <v>45623</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6850,7 +6850,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 55545-2022</t>
+          <t>A 29436-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6864,10 +6864,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44887</v>
+        <v>45483</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6923,7 +6923,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 64728-2023</t>
+          <t>A 40275-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6937,10 +6937,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45281</v>
+        <v>45169</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6953,7 +6953,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6996,7 +6996,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 25669-2024</t>
+          <t>A 12148-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -7010,10 +7010,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45463</v>
+        <v>45377</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7026,7 +7026,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>17.9</v>
+        <v>1.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -7069,7 +7069,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 23676-2024</t>
+          <t>A 8882-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7083,10 +7083,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45454</v>
+        <v>45713</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7099,7 +7099,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -7142,7 +7142,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 44448-2023</t>
+          <t>A 1644-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7156,10 +7156,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45189</v>
+        <v>45670</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7172,7 +7172,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7215,7 +7215,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 31143-2024</t>
+          <t>A 9578-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7225,14 +7225,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45502</v>
+        <v>45715</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7245,7 +7245,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7288,7 +7288,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 8139-2025</t>
+          <t>A 53501-2022</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7302,10 +7302,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45708</v>
+        <v>44879</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7318,7 +7318,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>3.5</v>
+        <v>7.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 23328-2022</t>
+          <t>A 24855-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7375,10 +7375,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44720</v>
+        <v>45461</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7391,7 +7391,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7434,7 +7434,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 15154-2023</t>
+          <t>A 27551-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7448,10 +7448,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45016</v>
+        <v>45097</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7464,7 +7464,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>3.5</v>
+        <v>0.6</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7507,7 +7507,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 55544-2022</t>
+          <t>A 48197-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7521,10 +7521,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44887</v>
+        <v>45590</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7537,7 +7537,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.1</v>
+        <v>3.1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7580,7 +7580,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 46286-2024</t>
+          <t>A 7871-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7594,10 +7594,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45581</v>
+        <v>45706</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7610,7 +7610,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7653,7 +7653,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 58134-2022</t>
+          <t>A 13243-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7667,10 +7667,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44900</v>
+        <v>45735</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7683,7 +7683,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7726,7 +7726,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 7337-2024</t>
+          <t>A 6667-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7740,10 +7740,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45345</v>
+        <v>45700</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7756,7 +7756,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7799,7 +7799,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 40287-2025</t>
+          <t>A 58137-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7813,10 +7813,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45895</v>
+        <v>44900</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7829,7 +7829,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7872,7 +7872,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 49610-2024</t>
+          <t>A 2575-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7886,10 +7886,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45596</v>
+        <v>45313</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>6.4</v>
+        <v>1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7945,7 +7945,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 74214-2021</t>
+          <t>A 64728-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7959,10 +7959,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44553</v>
+        <v>45281</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7975,7 +7975,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>19.8</v>
+        <v>1.8</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -8018,7 +8018,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 13243-2025</t>
+          <t>A 31502-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -8032,10 +8032,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45735</v>
+        <v>45115</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -8091,7 +8091,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 42826-2025</t>
+          <t>A 40287-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -8105,10 +8105,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45908</v>
+        <v>45895</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8121,7 +8121,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8164,7 +8164,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 7811-2023</t>
+          <t>A 31720-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8178,10 +8178,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44973</v>
+        <v>45117</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8194,7 +8194,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8237,7 +8237,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 58137-2022</t>
+          <t>A 46286-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8251,10 +8251,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44900</v>
+        <v>45581</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8267,7 +8267,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8310,7 +8310,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 42105-2022</t>
+          <t>A 25669-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8324,10 +8324,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44830</v>
+        <v>45463</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8340,7 +8340,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1</v>
+        <v>17.9</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8383,7 +8383,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 50652-2023</t>
+          <t>A 31143-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8393,14 +8393,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45210</v>
+        <v>45502</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8413,7 +8413,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2.4</v>
+        <v>0.6</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8456,7 +8456,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 24855-2024</t>
+          <t>A 607-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8470,10 +8470,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45461</v>
+        <v>45299</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8486,7 +8486,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2.4</v>
+        <v>0.6</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8529,7 +8529,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 4755-2024</t>
+          <t>A 42826-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8543,10 +8543,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45328</v>
+        <v>45908</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8559,7 +8559,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8602,7 +8602,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 14400-2023</t>
+          <t>A 54709-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8616,10 +8616,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45012</v>
+        <v>45236</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8632,7 +8632,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.7</v>
+        <v>3.6</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8675,7 +8675,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 52519-2025</t>
+          <t>A 7994-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8689,10 +8689,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45954</v>
+        <v>44973</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8748,7 +8748,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 23227-2023</t>
+          <t>A 55544-2022</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8762,10 +8762,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45075</v>
+        <v>44887</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8821,7 +8821,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 55728-2025</t>
+          <t>A 23976-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8835,10 +8835,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45972</v>
+        <v>45456</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 9578-2025</t>
+          <t>A 27553-2023</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8908,10 +8908,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45715</v>
+        <v>45097</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8924,7 +8924,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8967,7 +8967,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 57725-2025</t>
+          <t>A 8665-2022</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8981,10 +8981,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45981</v>
+        <v>44613</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8997,7 +8997,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -9040,7 +9040,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 8882-2025</t>
+          <t>A 18571-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -9054,10 +9054,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45713</v>
+        <v>45763</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9070,7 +9070,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -9113,7 +9113,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 43857-2025</t>
+          <t>A 31709-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -9127,10 +9127,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45912</v>
+        <v>45117</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9143,7 +9143,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9186,7 +9186,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 60227-2025</t>
+          <t>A 28253-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9200,10 +9200,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45994</v>
+        <v>45099</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9216,7 +9216,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -9259,7 +9259,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 18571-2025</t>
+          <t>A 23227-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9273,10 +9273,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45763</v>
+        <v>45075</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9289,7 +9289,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9332,7 +9332,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 16419-2023</t>
+          <t>A 50652-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9346,10 +9346,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45022</v>
+        <v>45210</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9362,7 +9362,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>4.2</v>
+        <v>2.4</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9405,7 +9405,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 27551-2023</t>
+          <t>A 16419-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9419,10 +9419,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45097</v>
+        <v>45022</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9435,7 +9435,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.6</v>
+        <v>4.2</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9478,7 +9478,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 13278-2026</t>
+          <t>A 40278-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9492,10 +9492,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>46093</v>
+        <v>45169</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9508,7 +9508,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9551,7 +9551,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 2575-2024</t>
+          <t>A 19503-2022</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9565,10 +9565,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45313</v>
+        <v>44693</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9581,7 +9581,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1</v>
+        <v>5.1</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9624,7 +9624,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 27097-2026</t>
+          <t>A 55529-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9638,10 +9638,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46188</v>
+        <v>45622</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9654,7 +9654,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>4</v>
+        <v>2.2</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9697,7 +9697,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 4089-2024</t>
+          <t>A 46702-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9711,10 +9711,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45323</v>
+        <v>45583</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9727,7 +9727,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9770,7 +9770,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 28496-2023</t>
+          <t>A 52519-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9784,10 +9784,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45103</v>
+        <v>45954</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9800,7 +9800,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9843,7 +9843,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 1299-2024</t>
+          <t>A 49206-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9857,10 +9857,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45303</v>
+        <v>45595</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9873,7 +9873,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9916,7 +9916,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 32364-2023</t>
+          <t>A 31789-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9930,10 +9930,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45120</v>
+        <v>45118</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9946,7 +9946,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9989,7 +9989,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 9055-2026</t>
+          <t>A 55728-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -10003,10 +10003,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46069</v>
+        <v>45972</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10019,7 +10019,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -10079,7 +10079,7 @@
         <v>45115</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10135,7 +10135,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 39014-2023</t>
+          <t>A 57725-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10149,10 +10149,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45163</v>
+        <v>45981</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10165,7 +10165,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -10208,7 +10208,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 31908-2023</t>
+          <t>A 39014-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10222,10 +10222,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45118</v>
+        <v>45163</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10238,7 +10238,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -10281,7 +10281,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 31502-2023</t>
+          <t>A 19500-2022</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10295,10 +10295,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45115</v>
+        <v>44693</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10311,7 +10311,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10354,7 +10354,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 28253-2023</t>
+          <t>A 44448-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10368,10 +10368,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45099</v>
+        <v>45189</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10384,7 +10384,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>2.7</v>
+        <v>0.6</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10427,7 +10427,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 21488-2023</t>
+          <t>A 32020-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10441,10 +10441,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45061</v>
+        <v>45835</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10457,7 +10457,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10500,7 +10500,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 29369-2026</t>
+          <t>A 57923-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10514,10 +10514,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46203</v>
+        <v>45631</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10530,7 +10530,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.3</v>
+        <v>4.5</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10573,7 +10573,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 7994-2023</t>
+          <t>A 28264-2022</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10587,10 +10587,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>44973</v>
+        <v>44746</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10603,7 +10603,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10646,7 +10646,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 27553-2023</t>
+          <t>A 55545-2022</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10660,10 +10660,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45097</v>
+        <v>44887</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10676,7 +10676,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.8</v>
+        <v>4.4</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10719,7 +10719,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 9803-2026</t>
+          <t>A 34514-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10733,10 +10733,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46072</v>
+        <v>45140</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10749,7 +10749,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>5</v>
+        <v>3.1</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10792,7 +10792,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 7707-2025</t>
+          <t>A 35677-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10806,10 +10806,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45705</v>
+        <v>46265</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10822,7 +10822,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.2</v>
+        <v>3.1</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10865,7 +10865,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 19650-2026</t>
+          <t>A 1299-2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10879,10 +10879,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>46134</v>
+        <v>45303</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10895,7 +10895,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>8</v>
+        <v>0.5</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10938,7 +10938,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 53501-2022</t>
+          <t>A 9055-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10952,10 +10952,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44879</v>
+        <v>46069</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10968,7 +10968,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>7.2</v>
+        <v>0.7</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -11011,7 +11011,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 54709-2023</t>
+          <t>A 19255-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -11025,10 +11025,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45236</v>
+        <v>46132</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11041,7 +11041,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>3.6</v>
+        <v>1</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -11084,7 +11084,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 12148-2024</t>
+          <t>A 13662-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -11098,10 +11098,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45377</v>
+        <v>45736</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11114,7 +11114,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.5</v>
+        <v>6.4</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -11157,7 +11157,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 19500-2022</t>
+          <t>A 42105-2022</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -11171,10 +11171,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44693</v>
+        <v>44830</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11187,7 +11187,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -11230,7 +11230,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 4605-2025</t>
+          <t>A 15154-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11244,10 +11244,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45687</v>
+        <v>45016</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11260,7 +11260,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.8</v>
+        <v>3.5</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -11303,7 +11303,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 31720-2023</t>
+          <t>A 7337-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11317,10 +11317,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45117</v>
+        <v>45345</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11333,7 +11333,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>0.5</v>
+        <v>2.6</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11376,7 +11376,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 16314-2024</t>
+          <t>A 49610-2024</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11390,10 +11390,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45407</v>
+        <v>45596</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11406,7 +11406,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.1</v>
+        <v>6.4</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11449,7 +11449,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 34514-2023</t>
+          <t>A 9803-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45140</v>
+        <v>46072</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11479,7 +11479,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>3.1</v>
+        <v>5</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11522,7 +11522,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 31576-2026</t>
+          <t>A 14400-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11536,10 +11536,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>46224</v>
+        <v>45012</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11552,7 +11552,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11595,7 +11595,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 36001-2026</t>
+          <t>A 4089-2024</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11609,10 +11609,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46266</v>
+        <v>45323</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11625,7 +11625,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11668,7 +11668,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 46613-2024</t>
+          <t>A 19650-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11682,10 +11682,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45583</v>
+        <v>46134</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11698,7 +11698,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11741,7 +11741,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 35912-2026</t>
+          <t>A 23676-2024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11755,10 +11755,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46266</v>
+        <v>45454</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11771,7 +11771,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11814,7 +11814,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 23976-2024</t>
+          <t>A 60-2024</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11828,10 +11828,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45456</v>
+        <v>45293</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11844,7 +11844,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11887,7 +11887,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 40278-2023</t>
+          <t>A 7707-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11901,10 +11901,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45169</v>
+        <v>45705</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11917,7 +11917,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11960,7 +11960,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 19255-2026</t>
+          <t>A 58150-2024</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11974,10 +11974,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46132</v>
+        <v>45632</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11990,7 +11990,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -12033,7 +12033,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 19256-2026</t>
+          <t>A 4755-2024</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -12047,10 +12047,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46132</v>
+        <v>45328</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12063,7 +12063,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -12106,7 +12106,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 37628-2026</t>
+          <t>A 58134-2022</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -12120,10 +12120,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46276</v>
+        <v>44900</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12135,13 +12135,8 @@
           <t>ÄNGELHOLM</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I137" t="n">
-        <v>4.5</v>
+        <v>1.2</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -12184,7 +12179,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 7871-2025</t>
+          <t>A 32430-2023</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -12198,10 +12193,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45706</v>
+        <v>45120</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12214,7 +12209,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -12257,7 +12252,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 32430-2023</t>
+          <t>A 28496-2023</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12271,10 +12266,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45120</v>
+        <v>45103</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12287,7 +12282,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -12330,7 +12325,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 26986-2026</t>
+          <t>A 4605-2025</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12344,10 +12339,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46185</v>
+        <v>45687</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12360,7 +12355,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>3.5</v>
+        <v>0.8</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -12403,7 +12398,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 29436-2024</t>
+          <t>A 21488-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12417,10 +12412,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45483</v>
+        <v>45061</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12433,7 +12428,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>4.2</v>
+        <v>1.1</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12476,7 +12471,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 26978-2026</t>
+          <t>A 74214-2021</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12490,10 +12485,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46185</v>
+        <v>44553</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12506,7 +12501,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>7.7</v>
+        <v>19.8</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12549,7 +12544,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 58150-2024</t>
+          <t>A 31908-2023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12563,10 +12558,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45632</v>
+        <v>45118</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12579,7 +12574,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12622,7 +12617,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 28264-2022</t>
+          <t>A 7811-2023</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12636,10 +12631,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>44746</v>
+        <v>44973</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12652,7 +12647,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12695,7 +12690,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 35677-2026</t>
+          <t>A 16314-2024</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12709,10 +12704,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46265</v>
+        <v>45407</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12725,7 +12720,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>3.1</v>
+        <v>1.1</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12768,7 +12763,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 31709-2023</t>
+          <t>A 46613-2024</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12782,10 +12777,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45117</v>
+        <v>45583</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12798,7 +12793,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>0.6</v>
+        <v>6.2</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12841,7 +12836,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 8665-2022</t>
+          <t>A 20635-2024</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12855,10 +12850,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>44613</v>
+        <v>45436</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12871,7 +12866,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>0.6</v>
+        <v>4.8</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12914,7 +12909,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 60-2024</t>
+          <t>A 60227-2025</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12928,10 +12923,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45293</v>
+        <v>45994</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12944,7 +12939,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12987,7 +12982,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 607-2024</t>
+          <t>A 43857-2025</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -13001,10 +12996,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45299</v>
+        <v>45912</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13017,7 +13012,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -13060,7 +13055,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 49206-2024</t>
+          <t>A 13278-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -13074,10 +13069,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45595</v>
+        <v>46093</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13133,7 +13128,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 19503-2022</t>
+          <t>A 27097-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -13147,10 +13142,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>44693</v>
+        <v>46188</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13163,7 +13158,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>5.1</v>
+        <v>4</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -13206,7 +13201,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 57923-2024</t>
+          <t>A 29369-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -13220,10 +13215,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45631</v>
+        <v>46203</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13236,7 +13231,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>4.5</v>
+        <v>1.3</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -13279,7 +13274,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 20635-2024</t>
+          <t>A 31576-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -13293,10 +13288,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45436</v>
+        <v>46224</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13309,7 +13304,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>4.8</v>
+        <v>0.6</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -13352,7 +13347,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 23980-2024</t>
+          <t>A 36001-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -13366,10 +13361,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45456</v>
+        <v>46266</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13382,7 +13377,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -13425,7 +13420,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 55748-2024</t>
+          <t>A 35912-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13439,10 +13434,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45623</v>
+        <v>46266</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13455,7 +13450,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13498,7 +13493,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 48197-2024</t>
+          <t>A 19256-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13512,10 +13507,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45590</v>
+        <v>46132</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13528,7 +13523,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>3.1</v>
+        <v>0.7</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13571,7 +13566,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 55529-2024</t>
+          <t>A 37628-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13585,10 +13580,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45622</v>
+        <v>46276</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13600,8 +13595,13 @@
           <t>ÄNGELHOLM</t>
         </is>
       </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I157" t="n">
-        <v>2.2</v>
+        <v>4.5</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13644,7 +13644,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 32020-2025</t>
+          <t>A 26978-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13658,10 +13658,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45835</v>
+        <v>46185</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13674,7 +13674,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>0.7</v>
+        <v>7.7</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13717,7 +13717,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 13662-2025</t>
+          <t>A 26986-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13731,10 +13731,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45736</v>
+        <v>46185</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13747,7 +13747,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>6.4</v>
+        <v>3.5</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13807,7 +13807,7 @@
         <v>45582</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13880,7 +13880,7 @@
         <v>45582</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13953,7 +13953,7 @@
         <v>45582</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14026,7 +14026,7 @@
         <v>45582</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14099,7 +14099,7 @@
         <v>44519</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14172,7 +14172,7 @@
         <v>45239</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14245,7 +14245,7 @@
         <v>45168</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14318,7 +14318,7 @@
         <v>44861</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14391,7 +14391,7 @@
         <v>45582</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>

--- a/Översikt ÄNGELHOLM.xlsx
+++ b/Översikt ÄNGELHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45099</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         <v>45931</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
         <v>45931</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>46106</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>44802</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 74502-2021</t>
+          <t>A 32268-2022</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1204,10 +1204,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44560</v>
+        <v>44781</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1220,17 +1220,17 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>5.6</v>
+        <v>8.6</v>
       </c>
       <c r="J7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K7" t="n">
+        <v>5</v>
+      </c>
+      <c r="L7" t="n">
         <v>1</v>
       </c>
-      <c r="L7" t="n">
-        <v>3</v>
-      </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
@@ -1244,7 +1244,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1253,12 +1253,124 @@
         <v>8</v>
       </c>
       <c r="T7" t="n">
+        <v>14</v>
+      </c>
+      <c r="U7" t="n">
+        <v>14</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Bokvårtlav
+Blåmossa
+Dvärghäxört
+Skuggsprötmossa
+Trubbfjädermossa
+Västlig hakmossa
+Vanlig groda
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 32268-2022 artfynd.xlsx", "A 32268-2022")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 32268-2022 karta.png", "A 32268-2022")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 32268-2022 georefererad karta.tif", "A 32268-2022")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 32268-2022 FSC-klagomål.docx", "A 32268-2022")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 32268-2022 FSC-klagomål mail.docx", "A 32268-2022")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 32268-2022 tillsynsbegäran.docx", "A 32268-2022")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 32268-2022 tillsynsbegäran mail.docx", "A 32268-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 74502-2021</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>44560</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J8" t="n">
+        <v>6</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>3</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>8</v>
+      </c>
+      <c r="T8" t="n">
         <v>9</v>
       </c>
-      <c r="U7" t="n">
+      <c r="U8" t="n">
         <v>9</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Entita
 Grönsångare
@@ -1270,148 +1382,36 @@
 Skogsduva</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 74502-2021 artfynd.xlsx", "A 74502-2021")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 74502-2021 karta.png", "A 74502-2021")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 74502-2021 georefererad karta.tif", "A 74502-2021")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 74502-2021 FSC-klagomål.docx", "A 74502-2021")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 74502-2021 FSC-klagomål mail.docx", "A 74502-2021")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 74502-2021 tillsynsbegäran.docx", "A 74502-2021")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 74502-2021 tillsynsbegäran mail.docx", "A 74502-2021")</f>
         <v/>
       </c>
-      <c r="AE7">
+      <c r="AE8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 74502-2021 prioriterade fågelarter.docx", "A 74502-2021")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 32268-2022</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>44781</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="J8" t="n">
-        <v>2</v>
-      </c>
-      <c r="K8" t="n">
-        <v>5</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>8</v>
-      </c>
-      <c r="T8" t="n">
-        <v>14</v>
-      </c>
-      <c r="U8" t="n">
-        <v>14</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Bokvårtlav
-Blåmossa
-Dvärghäxört
-Skuggsprötmossa
-Trubbfjädermossa
-Västlig hakmossa
-Vanlig groda
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 32268-2022 artfynd.xlsx", "A 32268-2022")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 32268-2022 karta.png", "A 32268-2022")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 32268-2022 georefererad karta.tif", "A 32268-2022")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 32268-2022 FSC-klagomål.docx", "A 32268-2022")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 32268-2022 FSC-klagomål mail.docx", "A 32268-2022")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 32268-2022 tillsynsbegäran.docx", "A 32268-2022")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 32268-2022 tillsynsbegäran mail.docx", "A 32268-2022")</f>
         <v/>
       </c>
     </row>
@@ -1435,7 +1435,7 @@
         <v>45835</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 308-2023</t>
+          <t>A 5046-2022</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1547,10 +1547,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44929</v>
+        <v>44593</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1563,19 +1563,19 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.8</v>
+        <v>3</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K10" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1587,10 +1587,10 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" t="n">
         <v>1</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>6</v>
@@ -1599,9 +1599,123 @@
         <v>7</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Grönfink
+Gulsparv
+Kråka
+Kungsfågel
+Sävsparv
+Trädlärka</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 5046-2022 artfynd.xlsx", "A 5046-2022")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 5046-2022 karta.png", "A 5046-2022")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 5046-2022 georefererad karta.tif", "A 5046-2022")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 5046-2022 FSC-klagomål.docx", "A 5046-2022")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 5046-2022 FSC-klagomål mail.docx", "A 5046-2022")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 5046-2022 tillsynsbegäran.docx", "A 5046-2022")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 5046-2022 tillsynsbegäran mail.docx", "A 5046-2022")</f>
+        <v/>
+      </c>
+      <c r="AE10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 5046-2022 prioriterade fågelarter.docx", "A 5046-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 308-2023</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>44929</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>5</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>6</v>
+      </c>
+      <c r="T11" t="n">
+        <v>7</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Bokvårtlav
 Dvärghäxört
@@ -1611,146 +1725,32 @@
 Stor knopplav</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 308-2023 artfynd.xlsx", "A 308-2023")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 308-2023 karta.png", "A 308-2023")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 308-2023 georefererad karta.tif", "A 308-2023")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 308-2023 FSC-klagomål.docx", "A 308-2023")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 308-2023 FSC-klagomål mail.docx", "A 308-2023")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 308-2023 tillsynsbegäran.docx", "A 308-2023")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 308-2023 tillsynsbegäran mail.docx", "A 308-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 5046-2022</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>44593</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>3</v>
-      </c>
-      <c r="J11" t="n">
-        <v>6</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
-      <c r="S11" t="n">
-        <v>6</v>
-      </c>
-      <c r="T11" t="n">
-        <v>7</v>
-      </c>
-      <c r="U11" t="n">
-        <v>6</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Grönfink
-Gulsparv
-Kråka
-Kungsfågel
-Sävsparv
-Trädlärka</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 5046-2022 artfynd.xlsx", "A 5046-2022")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 5046-2022 karta.png", "A 5046-2022")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 5046-2022 georefererad karta.tif", "A 5046-2022")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 5046-2022 FSC-klagomål.docx", "A 5046-2022")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 5046-2022 FSC-klagomål mail.docx", "A 5046-2022")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 5046-2022 tillsynsbegäran.docx", "A 5046-2022")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 5046-2022 tillsynsbegäran mail.docx", "A 5046-2022")</f>
-        <v/>
-      </c>
-      <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 5046-2022 prioriterade fågelarter.docx", "A 5046-2022")</f>
         <v/>
       </c>
     </row>
@@ -1774,7 +1774,7 @@
         <v>45106</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>45245</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 35675-2026</t>
+          <t>A 2931-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1995,10 +1995,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46265</v>
+        <v>46038</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2011,13 +2011,13 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>8.9</v>
+        <v>3.5</v>
       </c>
       <c r="J14" t="n">
         <v>4</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>1</v>
@@ -2044,12 +2044,125 @@
         <v>5</v>
       </c>
       <c r="T14" t="n">
+        <v>6</v>
+      </c>
+      <c r="U14" t="n">
+        <v>5</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Småvänderot
+Entita
+Spillkråka
+Gröngöling
+Grönsiska</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 2931-2026 artfynd.xlsx", "A 2931-2026")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 2931-2026 karta.png", "A 2931-2026")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 2931-2026 georefererad karta.tif", "A 2931-2026")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 2931-2026 FSC-klagomål.docx", "A 2931-2026")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 2931-2026 FSC-klagomål mail.docx", "A 2931-2026")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 2931-2026 tillsynsbegäran.docx", "A 2931-2026")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 2931-2026 tillsynsbegäran mail.docx", "A 2931-2026")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 2931-2026 prioriterade fågelarter.docx", "A 2931-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 35675-2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="J15" t="n">
+        <v>4</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="n">
         <v>10</v>
       </c>
-      <c r="U14" t="n">
+      <c r="U15" t="n">
         <v>9</v>
       </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Lappuggla
 Entita
@@ -2058,111 +2171,111 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 35675-2026 artfynd.xlsx", "A 35675-2026")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 35675-2026 karta.png", "A 35675-2026")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 35675-2026 georefererad karta.tif", "A 35675-2026")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 35675-2026 FSC-klagomål.docx", "A 35675-2026")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 35675-2026 FSC-klagomål mail.docx", "A 35675-2026")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 35675-2026 tillsynsbegäran.docx", "A 35675-2026")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 35675-2026 tillsynsbegäran mail.docx", "A 35675-2026")</f>
         <v/>
       </c>
-      <c r="AE14">
+      <c r="AE15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 35675-2026 prioriterade fågelarter.docx", "A 35675-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>A 35680-2026</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
         <v>46265</v>
       </c>
-      <c r="E15" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
+      <c r="E16" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
         <v>2.9</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J16" t="n">
         <v>2</v>
       </c>
-      <c r="K15" t="n">
+      <c r="K16" t="n">
         <v>1</v>
       </c>
-      <c r="L15" t="n">
+      <c r="L16" t="n">
         <v>2</v>
       </c>
-      <c r="M15" t="n">
+      <c r="M16" t="n">
         <v>1</v>
       </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
         <v>3</v>
       </c>
-      <c r="R15" t="n">
+      <c r="R16" t="n">
         <v>1</v>
       </c>
-      <c r="S15" t="n">
+      <c r="S16" t="n">
         <v>5</v>
       </c>
-      <c r="T15" t="n">
+      <c r="T16" t="n">
         <v>7</v>
       </c>
-      <c r="U15" t="n">
+      <c r="U16" t="n">
         <v>7</v>
       </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Vedlavklubba
 Entita
@@ -2171,149 +2284,36 @@
 Spillkråka</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 35680-2026 artfynd.xlsx", "A 35680-2026")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 35680-2026 karta.png", "A 35680-2026")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 35680-2026 georefererad karta.tif", "A 35680-2026")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 35680-2026 FSC-klagomål.docx", "A 35680-2026")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 35680-2026 FSC-klagomål mail.docx", "A 35680-2026")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 35680-2026 tillsynsbegäran.docx", "A 35680-2026")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 35680-2026 tillsynsbegäran mail.docx", "A 35680-2026")</f>
         <v/>
       </c>
-      <c r="AE15">
+      <c r="AE16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 35680-2026 prioriterade fågelarter.docx", "A 35680-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 2931-2026</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>46038</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J16" t="n">
-        <v>4</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1</v>
-      </c>
-      <c r="S16" t="n">
-        <v>5</v>
-      </c>
-      <c r="T16" t="n">
-        <v>6</v>
-      </c>
-      <c r="U16" t="n">
-        <v>5</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Småvänderot
-Entita
-Spillkråka
-Gröngöling
-Grönsiska</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 2931-2026 artfynd.xlsx", "A 2931-2026")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 2931-2026 karta.png", "A 2931-2026")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 2931-2026 georefererad karta.tif", "A 2931-2026")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 2931-2026 FSC-klagomål.docx", "A 2931-2026")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 2931-2026 FSC-klagomål mail.docx", "A 2931-2026")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 2931-2026 tillsynsbegäran.docx", "A 2931-2026")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 2931-2026 tillsynsbegäran mail.docx", "A 2931-2026")</f>
-        <v/>
-      </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 2931-2026 prioriterade fågelarter.docx", "A 2931-2026")</f>
         <v/>
       </c>
     </row>
@@ -2337,7 +2337,7 @@
         <v>45664</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2449,7 +2449,7 @@
         <v>44864</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 28874-2023</t>
+          <t>A 905-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2554,10 +2554,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45104</v>
+        <v>45301</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2570,734 +2570,734 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>9</v>
+        <v>4.9</v>
       </c>
       <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
         <v>1</v>
       </c>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
         <v>2</v>
       </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S19" t="n">
         <v>3</v>
       </c>
       <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Igelkott
+Desmeknopp
+Myskmadra</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 905-2024 artfynd.xlsx", "A 905-2024")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 905-2024 karta.png", "A 905-2024")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 905-2024 georefererad karta.tif", "A 905-2024")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 905-2024 FSC-klagomål.docx", "A 905-2024")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 905-2024 FSC-klagomål mail.docx", "A 905-2024")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 905-2024 tillsynsbegäran.docx", "A 905-2024")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 905-2024 tillsynsbegäran mail.docx", "A 905-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 28874-2023</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>45104</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>9</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3</v>
+      </c>
+      <c r="T20" t="n">
         <v>5</v>
       </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>Blåmossa
 Stubbspretmossa
 Revlummer</t>
         </is>
       </c>
-      <c r="W19">
+      <c r="W20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 28874-2023 artfynd.xlsx", "A 28874-2023")</f>
         <v/>
       </c>
-      <c r="X19">
+      <c r="X20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 28874-2023 karta.png", "A 28874-2023")</f>
         <v/>
       </c>
-      <c r="Y19">
+      <c r="Y20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 28874-2023 georefererad karta.tif", "A 28874-2023")</f>
         <v/>
       </c>
-      <c r="AA19">
+      <c r="AA20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 28874-2023 FSC-klagomål.docx", "A 28874-2023")</f>
         <v/>
       </c>
-      <c r="AB19">
+      <c r="AB20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 28874-2023 FSC-klagomål mail.docx", "A 28874-2023")</f>
         <v/>
       </c>
-      <c r="AC19">
+      <c r="AC20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 28874-2023 tillsynsbegäran.docx", "A 28874-2023")</f>
         <v/>
       </c>
-      <c r="AD19">
+      <c r="AD20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 28874-2023 tillsynsbegäran mail.docx", "A 28874-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 8065-2025</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>45707</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Småvänderot
+Gullpudra
+Svinrot</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 8065-2025 artfynd.xlsx", "A 8065-2025")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 8065-2025 karta.png", "A 8065-2025")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 8065-2025 georefererad karta.tif", "A 8065-2025")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 8065-2025 FSC-klagomål.docx", "A 8065-2025")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 8065-2025 FSC-klagomål mail.docx", "A 8065-2025")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 8065-2025 tillsynsbegäran.docx", "A 8065-2025")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 8065-2025 tillsynsbegäran mail.docx", "A 8065-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 50684-2023</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>45210</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>1</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>Skogsalm
+Kopparödla
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 50684-2023 artfynd.xlsx", "A 50684-2023")</f>
+        <v/>
+      </c>
+      <c r="X22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 50684-2023 karta.png", "A 50684-2023")</f>
+        <v/>
+      </c>
+      <c r="Y22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 50684-2023 georefererad karta.tif", "A 50684-2023")</f>
+        <v/>
+      </c>
+      <c r="AA22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 50684-2023 FSC-klagomål.docx", "A 50684-2023")</f>
+        <v/>
+      </c>
+      <c r="AB22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 50684-2023 FSC-klagomål mail.docx", "A 50684-2023")</f>
+        <v/>
+      </c>
+      <c r="AC22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 50684-2023 tillsynsbegäran.docx", "A 50684-2023")</f>
+        <v/>
+      </c>
+      <c r="AD22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 50684-2023 tillsynsbegäran mail.docx", "A 50684-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>A 3317-2026</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>46041</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>2</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3</v>
+      </c>
+      <c r="T23" t="n">
+        <v>6</v>
+      </c>
+      <c r="U23" t="n">
+        <v>6</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>Entita
+Mindre hackspett
+Gröngöling</t>
+        </is>
+      </c>
+      <c r="W23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 3317-2026 artfynd.xlsx", "A 3317-2026")</f>
+        <v/>
+      </c>
+      <c r="X23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 3317-2026 karta.png", "A 3317-2026")</f>
+        <v/>
+      </c>
+      <c r="Y23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 3317-2026 georefererad karta.tif", "A 3317-2026")</f>
+        <v/>
+      </c>
+      <c r="AA23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 3317-2026 FSC-klagomål.docx", "A 3317-2026")</f>
+        <v/>
+      </c>
+      <c r="AB23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 3317-2026 FSC-klagomål mail.docx", "A 3317-2026")</f>
+        <v/>
+      </c>
+      <c r="AC23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 3317-2026 tillsynsbegäran.docx", "A 3317-2026")</f>
+        <v/>
+      </c>
+      <c r="AD23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 3317-2026 tillsynsbegäran mail.docx", "A 3317-2026")</f>
+        <v/>
+      </c>
+      <c r="AE23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 3317-2026 prioriterade fågelarter.docx", "A 3317-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" t="inlineStr">
         <is>
           <t>A 31907-2023</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="n">
         <v>45118</v>
       </c>
-      <c r="E20" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
+      <c r="E24" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
         <v>5.3</v>
       </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
         <v>2</v>
       </c>
-      <c r="L20" t="n">
+      <c r="L24" t="n">
         <v>1</v>
       </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
         <v>1</v>
       </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
         <v>3</v>
       </c>
-      <c r="T20" t="n">
+      <c r="T24" t="n">
         <v>3</v>
       </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
         <is>
           <t>Bokvårtlav
 Platt fjädermossa
 Stubbspretmossa</t>
         </is>
       </c>
-      <c r="W20">
+      <c r="W24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 31907-2023 artfynd.xlsx", "A 31907-2023")</f>
         <v/>
       </c>
-      <c r="X20">
+      <c r="X24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 31907-2023 karta.png", "A 31907-2023")</f>
         <v/>
       </c>
-      <c r="Y20">
+      <c r="Y24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 31907-2023 georefererad karta.tif", "A 31907-2023")</f>
         <v/>
       </c>
-      <c r="AA20">
+      <c r="AA24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 31907-2023 FSC-klagomål.docx", "A 31907-2023")</f>
         <v/>
       </c>
-      <c r="AB20">
+      <c r="AB24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 31907-2023 FSC-klagomål mail.docx", "A 31907-2023")</f>
         <v/>
       </c>
-      <c r="AC20">
+      <c r="AC24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 31907-2023 tillsynsbegäran.docx", "A 31907-2023")</f>
         <v/>
       </c>
-      <c r="AD20">
+      <c r="AD24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 31907-2023 tillsynsbegäran mail.docx", "A 31907-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 50684-2023</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>45210</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J21" t="n">
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>A 18559-2025</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="n">
+        <v>45763</v>
+      </c>
+      <c r="E25" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>3</v>
+      </c>
+      <c r="J25" t="n">
+        <v>3</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
         <v>2</v>
       </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>1</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1</v>
-      </c>
-      <c r="S21" t="n">
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
         <v>3</v>
       </c>
-      <c r="T21" t="n">
+      <c r="T25" t="n">
         <v>3</v>
       </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Skogsalm
-Kopparödla
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 50684-2023 artfynd.xlsx", "A 50684-2023")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 50684-2023 karta.png", "A 50684-2023")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 50684-2023 georefererad karta.tif", "A 50684-2023")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 50684-2023 FSC-klagomål.docx", "A 50684-2023")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 50684-2023 FSC-klagomål mail.docx", "A 50684-2023")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 50684-2023 tillsynsbegäran.docx", "A 50684-2023")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 50684-2023 tillsynsbegäran mail.docx", "A 50684-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 905-2024</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>45301</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>1</v>
-      </c>
-      <c r="L22" t="n">
-        <v>1</v>
-      </c>
-      <c r="M22" t="n">
-        <v>1</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>2</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1</v>
-      </c>
-      <c r="S22" t="n">
+      <c r="U25" t="n">
         <v>3</v>
       </c>
-      <c r="T22" t="n">
-        <v>3</v>
-      </c>
-      <c r="U22" t="n">
-        <v>2</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Igelkott
-Desmeknopp
-Myskmadra</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 905-2024 artfynd.xlsx", "A 905-2024")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 905-2024 karta.png", "A 905-2024")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 905-2024 georefererad karta.tif", "A 905-2024")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 905-2024 FSC-klagomål.docx", "A 905-2024")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 905-2024 FSC-klagomål mail.docx", "A 905-2024")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 905-2024 tillsynsbegäran.docx", "A 905-2024")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 905-2024 tillsynsbegäran mail.docx", "A 905-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>A 18559-2025</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>45763</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>3</v>
-      </c>
-      <c r="J23" t="n">
-        <v>3</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>2</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>2</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3</v>
-      </c>
-      <c r="T23" t="n">
-        <v>3</v>
-      </c>
-      <c r="U23" t="n">
-        <v>3</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>Grönsångare
 Gulsparv
 Gröngöling</t>
         </is>
       </c>
-      <c r="W23">
+      <c r="W25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 18559-2025 artfynd.xlsx", "A 18559-2025")</f>
         <v/>
       </c>
-      <c r="X23">
+      <c r="X25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 18559-2025 karta.png", "A 18559-2025")</f>
         <v/>
       </c>
-      <c r="Y23">
+      <c r="Y25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 18559-2025 georefererad karta.tif", "A 18559-2025")</f>
         <v/>
       </c>
-      <c r="AA23">
+      <c r="AA25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 18559-2025 FSC-klagomål.docx", "A 18559-2025")</f>
         <v/>
       </c>
-      <c r="AB23">
+      <c r="AB25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 18559-2025 FSC-klagomål mail.docx", "A 18559-2025")</f>
         <v/>
       </c>
-      <c r="AC23">
+      <c r="AC25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 18559-2025 tillsynsbegäran.docx", "A 18559-2025")</f>
         <v/>
       </c>
-      <c r="AD23">
+      <c r="AD25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 18559-2025 tillsynsbegäran mail.docx", "A 18559-2025")</f>
         <v/>
       </c>
-      <c r="AE23">
+      <c r="AE25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 18559-2025 prioriterade fågelarter.docx", "A 18559-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>A 8065-2025</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="n">
-        <v>45707</v>
-      </c>
-      <c r="E24" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>2</v>
-      </c>
-      <c r="M24" t="n">
-        <v>1</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>3</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3</v>
-      </c>
-      <c r="T24" t="n">
-        <v>3</v>
-      </c>
-      <c r="U24" t="n">
-        <v>2</v>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>Småvänderot
-Gullpudra
-Svinrot</t>
-        </is>
-      </c>
-      <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 8065-2025 artfynd.xlsx", "A 8065-2025")</f>
-        <v/>
-      </c>
-      <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 8065-2025 karta.png", "A 8065-2025")</f>
-        <v/>
-      </c>
-      <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 8065-2025 georefererad karta.tif", "A 8065-2025")</f>
-        <v/>
-      </c>
-      <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 8065-2025 FSC-klagomål.docx", "A 8065-2025")</f>
-        <v/>
-      </c>
-      <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 8065-2025 FSC-klagomål mail.docx", "A 8065-2025")</f>
-        <v/>
-      </c>
-      <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 8065-2025 tillsynsbegäran.docx", "A 8065-2025")</f>
-        <v/>
-      </c>
-      <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 8065-2025 tillsynsbegäran mail.docx", "A 8065-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>A 3317-2026</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="n">
-        <v>46041</v>
-      </c>
-      <c r="E25" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J25" t="n">
-        <v>3</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>2</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>2</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>3</v>
-      </c>
-      <c r="T25" t="n">
-        <v>6</v>
-      </c>
-      <c r="U25" t="n">
-        <v>6</v>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>Entita
-Mindre hackspett
-Gröngöling</t>
-        </is>
-      </c>
-      <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 3317-2026 artfynd.xlsx", "A 3317-2026")</f>
-        <v/>
-      </c>
-      <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 3317-2026 karta.png", "A 3317-2026")</f>
-        <v/>
-      </c>
-      <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 3317-2026 georefererad karta.tif", "A 3317-2026")</f>
-        <v/>
-      </c>
-      <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 3317-2026 FSC-klagomål.docx", "A 3317-2026")</f>
-        <v/>
-      </c>
-      <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 3317-2026 FSC-klagomål mail.docx", "A 3317-2026")</f>
-        <v/>
-      </c>
-      <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 3317-2026 tillsynsbegäran.docx", "A 3317-2026")</f>
-        <v/>
-      </c>
-      <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 3317-2026 tillsynsbegäran mail.docx", "A 3317-2026")</f>
-        <v/>
-      </c>
-      <c r="AE25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 3317-2026 prioriterade fågelarter.docx", "A 3317-2026")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 29157-2023</t>
+          <t>A 27544-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3311,10 +3311,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45105</v>
+        <v>45474</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3327,16 +3327,16 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>6.9</v>
+        <v>3.2</v>
       </c>
       <c r="J26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -3351,7 +3351,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -3363,264 +3363,264 @@
         <v>2</v>
       </c>
       <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 27544-2024 artfynd.xlsx", "A 27544-2024")</f>
+        <v/>
+      </c>
+      <c r="X26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 27544-2024 karta.png", "A 27544-2024")</f>
+        <v/>
+      </c>
+      <c r="Y26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 27544-2024 georefererad karta.tif", "A 27544-2024")</f>
+        <v/>
+      </c>
+      <c r="AA26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 27544-2024 FSC-klagomål.docx", "A 27544-2024")</f>
+        <v/>
+      </c>
+      <c r="AB26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 27544-2024 FSC-klagomål mail.docx", "A 27544-2024")</f>
+        <v/>
+      </c>
+      <c r="AC26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 27544-2024 tillsynsbegäran.docx", "A 27544-2024")</f>
+        <v/>
+      </c>
+      <c r="AD26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 27544-2024 tillsynsbegäran mail.docx", "A 27544-2024")</f>
+        <v/>
+      </c>
+      <c r="AE26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 27544-2024 prioriterade fågelarter.docx", "A 27544-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>A 33520-2025</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D27" s="1" t="n">
+        <v>45841</v>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
         <v>2</v>
       </c>
-      <c r="V26" s="2" t="inlineStr">
+      <c r="R27" t="n">
+        <v>1</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2</v>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>Småvänderot
+Entita</t>
+        </is>
+      </c>
+      <c r="W27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 33520-2025 artfynd.xlsx", "A 33520-2025")</f>
+        <v/>
+      </c>
+      <c r="X27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 33520-2025 karta.png", "A 33520-2025")</f>
+        <v/>
+      </c>
+      <c r="Y27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 33520-2025 georefererad karta.tif", "A 33520-2025")</f>
+        <v/>
+      </c>
+      <c r="AA27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 33520-2025 FSC-klagomål.docx", "A 33520-2025")</f>
+        <v/>
+      </c>
+      <c r="AB27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 33520-2025 FSC-klagomål mail.docx", "A 33520-2025")</f>
+        <v/>
+      </c>
+      <c r="AC27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 33520-2025 tillsynsbegäran.docx", "A 33520-2025")</f>
+        <v/>
+      </c>
+      <c r="AD27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 33520-2025 tillsynsbegäran mail.docx", "A 33520-2025")</f>
+        <v/>
+      </c>
+      <c r="AE27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 33520-2025 prioriterade fågelarter.docx", "A 33520-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>A 29157-2023</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D28" s="1" t="n">
+        <v>45105</v>
+      </c>
+      <c r="E28" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>2</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>2</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
         <is>
           <t>Entita
 Talltita</t>
         </is>
       </c>
-      <c r="W26">
+      <c r="W28">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 29157-2023 artfynd.xlsx", "A 29157-2023")</f>
         <v/>
       </c>
-      <c r="X26">
+      <c r="X28">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 29157-2023 karta.png", "A 29157-2023")</f>
         <v/>
       </c>
-      <c r="Y26">
+      <c r="Y28">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 29157-2023 georefererad karta.tif", "A 29157-2023")</f>
         <v/>
       </c>
-      <c r="AA26">
+      <c r="AA28">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 29157-2023 FSC-klagomål.docx", "A 29157-2023")</f>
         <v/>
       </c>
-      <c r="AB26">
+      <c r="AB28">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 29157-2023 FSC-klagomål mail.docx", "A 29157-2023")</f>
         <v/>
       </c>
-      <c r="AC26">
+      <c r="AC28">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 29157-2023 tillsynsbegäran.docx", "A 29157-2023")</f>
         <v/>
       </c>
-      <c r="AD26">
+      <c r="AD28">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 29157-2023 tillsynsbegäran mail.docx", "A 29157-2023")</f>
         <v/>
       </c>
-      <c r="AE26">
+      <c r="AE28">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 29157-2023 prioriterade fågelarter.docx", "A 29157-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>A 33520-2025</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="n">
-        <v>45841</v>
-      </c>
-      <c r="E27" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J27" t="n">
-        <v>1</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>1</v>
-      </c>
-      <c r="M27" t="n">
-        <v>1</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>2</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2</v>
-      </c>
-      <c r="U27" t="n">
-        <v>2</v>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>Småvänderot
-Entita</t>
-        </is>
-      </c>
-      <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 33520-2025 artfynd.xlsx", "A 33520-2025")</f>
-        <v/>
-      </c>
-      <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 33520-2025 karta.png", "A 33520-2025")</f>
-        <v/>
-      </c>
-      <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 33520-2025 georefererad karta.tif", "A 33520-2025")</f>
-        <v/>
-      </c>
-      <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 33520-2025 FSC-klagomål.docx", "A 33520-2025")</f>
-        <v/>
-      </c>
-      <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 33520-2025 FSC-klagomål mail.docx", "A 33520-2025")</f>
-        <v/>
-      </c>
-      <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 33520-2025 tillsynsbegäran.docx", "A 33520-2025")</f>
-        <v/>
-      </c>
-      <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 33520-2025 tillsynsbegäran mail.docx", "A 33520-2025")</f>
-        <v/>
-      </c>
-      <c r="AE27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 33520-2025 prioriterade fågelarter.docx", "A 33520-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="15" customHeight="1">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>A 27544-2024</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D28" s="1" t="n">
-        <v>45474</v>
-      </c>
-      <c r="E28" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I28" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J28" t="n">
-        <v>1</v>
-      </c>
-      <c r="K28" t="n">
-        <v>1</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2</v>
-      </c>
-      <c r="U28" t="n">
-        <v>0</v>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>Västlig hakmossa
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 27544-2024 artfynd.xlsx", "A 27544-2024")</f>
-        <v/>
-      </c>
-      <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 27544-2024 karta.png", "A 27544-2024")</f>
-        <v/>
-      </c>
-      <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 27544-2024 georefererad karta.tif", "A 27544-2024")</f>
-        <v/>
-      </c>
-      <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 27544-2024 FSC-klagomål.docx", "A 27544-2024")</f>
-        <v/>
-      </c>
-      <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 27544-2024 FSC-klagomål mail.docx", "A 27544-2024")</f>
-        <v/>
-      </c>
-      <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 27544-2024 tillsynsbegäran.docx", "A 27544-2024")</f>
-        <v/>
-      </c>
-      <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 27544-2024 tillsynsbegäran mail.docx", "A 27544-2024")</f>
-        <v/>
-      </c>
-      <c r="AE28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 27544-2024 prioriterade fågelarter.docx", "A 27544-2024")</f>
         <v/>
       </c>
     </row>
@@ -3644,7 +3644,7 @@
         <v>44553</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3754,7 +3754,7 @@
         <v>45359</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
         <v>45582</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>44839</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>44742</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4180,7 +4180,7 @@
         <v>44746</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 12150-2024</t>
+          <t>A 44062-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4286,10 +4286,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45377</v>
+        <v>44839</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4302,19 +4302,19 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -4326,10 +4326,10 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4342,42 +4342,42 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 12150-2024 artfynd.xlsx", "A 12150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 44062-2022 artfynd.xlsx", "A 44062-2022")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 12150-2024 karta.png", "A 12150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 44062-2022 karta.png", "A 44062-2022")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 12150-2024 georefererad karta.tif", "A 12150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 44062-2022 georefererad karta.tif", "A 44062-2022")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 12150-2024 FSC-klagomål.docx", "A 12150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 44062-2022 FSC-klagomål.docx", "A 44062-2022")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 12150-2024 FSC-klagomål mail.docx", "A 12150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 44062-2022 FSC-klagomål mail.docx", "A 44062-2022")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 12150-2024 tillsynsbegäran.docx", "A 12150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 44062-2022 tillsynsbegäran.docx", "A 44062-2022")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 12150-2024 tillsynsbegäran mail.docx", "A 12150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 44062-2022 tillsynsbegäran mail.docx", "A 44062-2022")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 25129-2024</t>
+          <t>A 4088-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4391,10 +4391,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45462</v>
+        <v>45323</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4407,7 +4407,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -4447,42 +4447,42 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Flikbålmossa</t>
         </is>
       </c>
       <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 25129-2024 artfynd.xlsx", "A 25129-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 4088-2024 artfynd.xlsx", "A 4088-2024")</f>
         <v/>
       </c>
       <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 25129-2024 karta.png", "A 25129-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 4088-2024 karta.png", "A 4088-2024")</f>
         <v/>
       </c>
       <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 25129-2024 georefererad karta.tif", "A 25129-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 4088-2024 georefererad karta.tif", "A 4088-2024")</f>
         <v/>
       </c>
       <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 25129-2024 FSC-klagomål.docx", "A 25129-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 4088-2024 FSC-klagomål.docx", "A 4088-2024")</f>
         <v/>
       </c>
       <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 25129-2024 FSC-klagomål mail.docx", "A 25129-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 4088-2024 FSC-klagomål mail.docx", "A 4088-2024")</f>
         <v/>
       </c>
       <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 25129-2024 tillsynsbegäran.docx", "A 25129-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 4088-2024 tillsynsbegäran.docx", "A 4088-2024")</f>
         <v/>
       </c>
       <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 25129-2024 tillsynsbegäran mail.docx", "A 25129-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 4088-2024 tillsynsbegäran mail.docx", "A 4088-2024")</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 61094-2021</t>
+          <t>A 25129-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4496,10 +4496,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44498</v>
+        <v>45462</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4512,17 +4512,17 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>6.4</v>
+        <v>4.6</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
         <v>1</v>
       </c>
-      <c r="L37" t="n">
-        <v>0</v>
-      </c>
       <c r="M37" t="n">
         <v>0</v>
       </c>
@@ -4536,7 +4536,7 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
@@ -4548,46 +4548,46 @@
         <v>1</v>
       </c>
       <c r="U37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 61094-2021 artfynd.xlsx", "A 61094-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 25129-2024 artfynd.xlsx", "A 25129-2024")</f>
         <v/>
       </c>
       <c r="X37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 61094-2021 karta.png", "A 61094-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 25129-2024 karta.png", "A 25129-2024")</f>
         <v/>
       </c>
       <c r="Y37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 61094-2021 georefererad karta.tif", "A 61094-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 25129-2024 georefererad karta.tif", "A 25129-2024")</f>
         <v/>
       </c>
       <c r="AA37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 61094-2021 FSC-klagomål.docx", "A 61094-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 25129-2024 FSC-klagomål.docx", "A 25129-2024")</f>
         <v/>
       </c>
       <c r="AB37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 61094-2021 FSC-klagomål mail.docx", "A 61094-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 25129-2024 FSC-klagomål mail.docx", "A 25129-2024")</f>
         <v/>
       </c>
       <c r="AC37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 61094-2021 tillsynsbegäran.docx", "A 61094-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 25129-2024 tillsynsbegäran.docx", "A 25129-2024")</f>
         <v/>
       </c>
       <c r="AD37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 61094-2021 tillsynsbegäran mail.docx", "A 61094-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 25129-2024 tillsynsbegäran mail.docx", "A 25129-2024")</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 4088-2024</t>
+          <t>A 12150-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4601,10 +4601,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45323</v>
+        <v>45377</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4617,7 +4617,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3.8</v>
+        <v>1.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4626,10 +4626,10 @@
         <v>0</v>
       </c>
       <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
         <v>1</v>
-      </c>
-      <c r="M38" t="n">
-        <v>0</v>
       </c>
       <c r="N38" t="n">
         <v>0</v>
@@ -4644,7 +4644,7 @@
         <v>1</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4653,46 +4653,46 @@
         <v>1</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>Flikbålmossa</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 4088-2024 artfynd.xlsx", "A 4088-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 12150-2024 artfynd.xlsx", "A 12150-2024")</f>
         <v/>
       </c>
       <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 4088-2024 karta.png", "A 4088-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 12150-2024 karta.png", "A 12150-2024")</f>
         <v/>
       </c>
       <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 4088-2024 georefererad karta.tif", "A 4088-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 12150-2024 georefererad karta.tif", "A 12150-2024")</f>
         <v/>
       </c>
       <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 4088-2024 FSC-klagomål.docx", "A 4088-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 12150-2024 FSC-klagomål.docx", "A 12150-2024")</f>
         <v/>
       </c>
       <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 4088-2024 FSC-klagomål mail.docx", "A 4088-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 12150-2024 FSC-klagomål mail.docx", "A 12150-2024")</f>
         <v/>
       </c>
       <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 4088-2024 tillsynsbegäran.docx", "A 4088-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 12150-2024 tillsynsbegäran.docx", "A 12150-2024")</f>
         <v/>
       </c>
       <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 4088-2024 tillsynsbegäran mail.docx", "A 4088-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 12150-2024 tillsynsbegäran mail.docx", "A 12150-2024")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 50642-2023</t>
+          <t>A 61094-2021</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4706,10 +4706,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45210</v>
+        <v>44498</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4722,13 +4722,13 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.8</v>
+        <v>6.4</v>
       </c>
       <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
         <v>1</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
@@ -4758,46 +4758,46 @@
         <v>1</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 50642-2023 artfynd.xlsx", "A 50642-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 61094-2021 artfynd.xlsx", "A 61094-2021")</f>
         <v/>
       </c>
       <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 50642-2023 karta.png", "A 50642-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 61094-2021 karta.png", "A 61094-2021")</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 50642-2023 georefererad karta.tif", "A 50642-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 61094-2021 georefererad karta.tif", "A 61094-2021")</f>
         <v/>
       </c>
       <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 50642-2023 FSC-klagomål.docx", "A 50642-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 61094-2021 FSC-klagomål.docx", "A 61094-2021")</f>
         <v/>
       </c>
       <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 50642-2023 FSC-klagomål mail.docx", "A 50642-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 61094-2021 FSC-klagomål mail.docx", "A 61094-2021")</f>
         <v/>
       </c>
       <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 50642-2023 tillsynsbegäran.docx", "A 50642-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 61094-2021 tillsynsbegäran.docx", "A 61094-2021")</f>
         <v/>
       </c>
       <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 50642-2023 tillsynsbegäran mail.docx", "A 50642-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 61094-2021 tillsynsbegäran mail.docx", "A 61094-2021")</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 46487-2024</t>
+          <t>A 27094-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4811,10 +4811,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45582</v>
+        <v>46188</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4827,13 +4827,13 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
         <v>1</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -4863,46 +4863,46 @@
         <v>1</v>
       </c>
       <c r="U40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="W40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 46487-2024 artfynd.xlsx", "A 46487-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 27094-2026 artfynd.xlsx", "A 27094-2026")</f>
         <v/>
       </c>
       <c r="X40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 46487-2024 karta.png", "A 46487-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 27094-2026 karta.png", "A 27094-2026")</f>
         <v/>
       </c>
       <c r="Y40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 46487-2024 georefererad karta.tif", "A 46487-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 27094-2026 georefererad karta.tif", "A 27094-2026")</f>
         <v/>
       </c>
       <c r="AA40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 46487-2024 FSC-klagomål.docx", "A 46487-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 27094-2026 FSC-klagomål.docx", "A 27094-2026")</f>
         <v/>
       </c>
       <c r="AB40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 46487-2024 FSC-klagomål mail.docx", "A 46487-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 27094-2026 FSC-klagomål mail.docx", "A 27094-2026")</f>
         <v/>
       </c>
       <c r="AC40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 46487-2024 tillsynsbegäran.docx", "A 46487-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 27094-2026 tillsynsbegäran.docx", "A 27094-2026")</f>
         <v/>
       </c>
       <c r="AD40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 46487-2024 tillsynsbegäran mail.docx", "A 46487-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 27094-2026 tillsynsbegäran mail.docx", "A 27094-2026")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 44062-2022</t>
+          <t>A 50642-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44839</v>
+        <v>45210</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4932,13 +4932,13 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -4968,39 +4968,39 @@
         <v>1</v>
       </c>
       <c r="U41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 44062-2022 artfynd.xlsx", "A 44062-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 50642-2023 artfynd.xlsx", "A 50642-2023")</f>
         <v/>
       </c>
       <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 44062-2022 karta.png", "A 44062-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 50642-2023 karta.png", "A 50642-2023")</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 44062-2022 georefererad karta.tif", "A 44062-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 50642-2023 georefererad karta.tif", "A 50642-2023")</f>
         <v/>
       </c>
       <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 44062-2022 FSC-klagomål.docx", "A 44062-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 50642-2023 FSC-klagomål.docx", "A 50642-2023")</f>
         <v/>
       </c>
       <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 44062-2022 FSC-klagomål mail.docx", "A 44062-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 50642-2023 FSC-klagomål mail.docx", "A 50642-2023")</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 44062-2022 tillsynsbegäran.docx", "A 44062-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 50642-2023 tillsynsbegäran.docx", "A 50642-2023")</f>
         <v/>
       </c>
       <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 44062-2022 tillsynsbegäran mail.docx", "A 44062-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 50642-2023 tillsynsbegäran mail.docx", "A 50642-2023")</f>
         <v/>
       </c>
     </row>
@@ -5024,7 +5024,7 @@
         <v>46265</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5133,7 +5133,7 @@
         <v>46224</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5221,7 +5221,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 27094-2026</t>
+          <t>A 46487-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5235,10 +5235,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46188</v>
+        <v>45582</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5251,13 +5251,13 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
@@ -5287,39 +5287,39 @@
         <v>1</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 27094-2026 artfynd.xlsx", "A 27094-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 46487-2024 artfynd.xlsx", "A 46487-2024")</f>
         <v/>
       </c>
       <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 27094-2026 karta.png", "A 27094-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 46487-2024 karta.png", "A 46487-2024")</f>
         <v/>
       </c>
       <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 27094-2026 georefererad karta.tif", "A 27094-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 46487-2024 georefererad karta.tif", "A 46487-2024")</f>
         <v/>
       </c>
       <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 27094-2026 FSC-klagomål.docx", "A 27094-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 46487-2024 FSC-klagomål.docx", "A 46487-2024")</f>
         <v/>
       </c>
       <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 27094-2026 FSC-klagomål mail.docx", "A 27094-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 46487-2024 FSC-klagomål mail.docx", "A 46487-2024")</f>
         <v/>
       </c>
       <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 27094-2026 tillsynsbegäran.docx", "A 27094-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 46487-2024 tillsynsbegäran.docx", "A 46487-2024")</f>
         <v/>
       </c>
       <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 27094-2026 tillsynsbegäran mail.docx", "A 27094-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 46487-2024 tillsynsbegäran mail.docx", "A 46487-2024")</f>
         <v/>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
         <v>45084</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5448,7 +5448,7 @@
         <v>44862</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5553,7 +5553,7 @@
         <v>44880</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5626,7 +5626,7 @@
         <v>44839</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5699,7 +5699,7 @@
         <v>44725</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5772,7 +5772,7 @@
         <v>44840</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5845,7 +5845,7 @@
         <v>44498</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5918,7 +5918,7 @@
         <v>44477</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5991,7 +5991,7 @@
         <v>44657</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
         <v>44634</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6137,7 +6137,7 @@
         <v>44802</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6210,7 +6210,7 @@
         <v>44802</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
         <v>44827</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 23328-2022</t>
+          <t>A 56569-2021</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6353,10 +6353,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44720</v>
+        <v>44480</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6369,7 +6369,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6429,7 +6429,7 @@
         <v>44634</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 32364-2023</t>
+          <t>A 40275-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6499,10 +6499,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45120</v>
+        <v>45169</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6558,7 +6558,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 56569-2021</t>
+          <t>A 6667-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6572,10 +6572,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44480</v>
+        <v>45700</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6588,7 +6588,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6631,7 +6631,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 8139-2025</t>
+          <t>A 46702-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6645,10 +6645,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45708</v>
+        <v>45583</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>3.5</v>
+        <v>1.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6704,7 +6704,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 23980-2024</t>
+          <t>A 31789-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6718,10 +6718,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45456</v>
+        <v>45118</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6777,7 +6777,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 55748-2024</t>
+          <t>A 1644-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6791,10 +6791,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45623</v>
+        <v>45670</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6850,7 +6850,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 29436-2024</t>
+          <t>A 55545-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6864,10 +6864,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45483</v>
+        <v>44887</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6923,7 +6923,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 40275-2023</t>
+          <t>A 64728-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6937,10 +6937,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45169</v>
+        <v>45281</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6953,7 +6953,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6996,7 +6996,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 12148-2024</t>
+          <t>A 25669-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -7010,10 +7010,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45377</v>
+        <v>45463</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7026,7 +7026,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.5</v>
+        <v>17.9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -7069,7 +7069,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 8882-2025</t>
+          <t>A 23676-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7083,10 +7083,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45713</v>
+        <v>45454</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7099,7 +7099,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -7142,7 +7142,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 1644-2025</t>
+          <t>A 8139-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7156,10 +7156,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45670</v>
+        <v>45708</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7172,7 +7172,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7215,7 +7215,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 9578-2025</t>
+          <t>A 44448-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7229,10 +7229,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45715</v>
+        <v>45189</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7245,7 +7245,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7288,7 +7288,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 53501-2022</t>
+          <t>A 31143-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7298,14 +7298,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44879</v>
+        <v>45502</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7318,7 +7318,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>7.2</v>
+        <v>0.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 24855-2024</t>
+          <t>A 23328-2022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7375,10 +7375,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45461</v>
+        <v>44720</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7391,7 +7391,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7434,7 +7434,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 27551-2023</t>
+          <t>A 15154-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7448,10 +7448,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45097</v>
+        <v>45016</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7464,7 +7464,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.6</v>
+        <v>3.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7507,7 +7507,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 48197-2024</t>
+          <t>A 46286-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7521,10 +7521,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45590</v>
+        <v>45581</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7537,7 +7537,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7580,7 +7580,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 7871-2025</t>
+          <t>A 55544-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7594,10 +7594,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45706</v>
+        <v>44887</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7653,7 +7653,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 13243-2025</t>
+          <t>A 19650-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7667,10 +7667,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45735</v>
+        <v>46134</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7683,7 +7683,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.5</v>
+        <v>8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7726,7 +7726,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 6667-2025</t>
+          <t>A 58134-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7740,10 +7740,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45700</v>
+        <v>44900</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7756,7 +7756,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7799,7 +7799,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 58137-2022</t>
+          <t>A 7337-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7813,10 +7813,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44900</v>
+        <v>45345</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7829,7 +7829,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.9</v>
+        <v>2.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7872,7 +7872,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 2575-2024</t>
+          <t>A 40287-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7886,10 +7886,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45313</v>
+        <v>45895</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7945,7 +7945,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 64728-2023</t>
+          <t>A 49610-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7959,10 +7959,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45281</v>
+        <v>45596</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7975,7 +7975,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.8</v>
+        <v>6.4</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -8018,7 +8018,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 31502-2023</t>
+          <t>A 13243-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -8032,10 +8032,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45115</v>
+        <v>45735</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -8091,7 +8091,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 40287-2025</t>
+          <t>A 42826-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -8105,10 +8105,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45895</v>
+        <v>45908</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8121,7 +8121,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8164,7 +8164,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 31720-2023</t>
+          <t>A 74214-2021</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8178,10 +8178,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45117</v>
+        <v>44553</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8194,7 +8194,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.5</v>
+        <v>19.8</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8237,7 +8237,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 46286-2024</t>
+          <t>A 7811-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8251,10 +8251,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45581</v>
+        <v>44973</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8267,7 +8267,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8310,7 +8310,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 25669-2024</t>
+          <t>A 58137-2022</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8324,10 +8324,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45463</v>
+        <v>44900</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8340,7 +8340,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>17.9</v>
+        <v>0.9</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8383,7 +8383,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 31143-2024</t>
+          <t>A 42105-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8393,14 +8393,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45502</v>
+        <v>44830</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8413,7 +8413,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8456,7 +8456,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 607-2024</t>
+          <t>A 50652-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8470,10 +8470,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45299</v>
+        <v>45210</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8486,7 +8486,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8529,7 +8529,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 42826-2025</t>
+          <t>A 24855-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8543,10 +8543,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45908</v>
+        <v>45461</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8559,7 +8559,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8602,7 +8602,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 54709-2023</t>
+          <t>A 4755-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8616,10 +8616,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45236</v>
+        <v>45328</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8632,7 +8632,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>3.6</v>
+        <v>0.9</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8675,7 +8675,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 7994-2023</t>
+          <t>A 14400-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8689,10 +8689,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44973</v>
+        <v>45012</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8748,7 +8748,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 55544-2022</t>
+          <t>A 52519-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8762,10 +8762,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44887</v>
+        <v>45954</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8778,7 +8778,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8821,7 +8821,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 23976-2024</t>
+          <t>A 23227-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8835,10 +8835,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45456</v>
+        <v>45075</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 27553-2023</t>
+          <t>A 9578-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8908,10 +8908,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45097</v>
+        <v>45715</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8924,7 +8924,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8967,7 +8967,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 8665-2022</t>
+          <t>A 55728-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8981,10 +8981,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44613</v>
+        <v>45972</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8997,7 +8997,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -9040,7 +9040,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 18571-2025</t>
+          <t>A 8882-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -9054,10 +9054,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45763</v>
+        <v>45713</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9070,7 +9070,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -9113,7 +9113,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 31709-2023</t>
+          <t>A 57725-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -9127,10 +9127,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45117</v>
+        <v>45981</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9143,7 +9143,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9186,7 +9186,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 28253-2023</t>
+          <t>A 18571-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9200,10 +9200,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45099</v>
+        <v>45763</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9216,7 +9216,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>2.7</v>
+        <v>0.9</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -9259,7 +9259,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 23227-2023</t>
+          <t>A 16419-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9273,10 +9273,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45075</v>
+        <v>45022</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9289,7 +9289,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.1</v>
+        <v>4.2</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9332,7 +9332,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 50652-2023</t>
+          <t>A 27551-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9346,10 +9346,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45210</v>
+        <v>45097</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9362,7 +9362,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2.4</v>
+        <v>0.6</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9405,7 +9405,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 16419-2023</t>
+          <t>A 2575-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9419,10 +9419,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45022</v>
+        <v>45313</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9435,7 +9435,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>4.2</v>
+        <v>1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9478,7 +9478,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 40278-2023</t>
+          <t>A 4089-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9492,10 +9492,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45169</v>
+        <v>45323</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9508,7 +9508,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9551,7 +9551,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 19503-2022</t>
+          <t>A 28496-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9565,10 +9565,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>44693</v>
+        <v>45103</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9581,7 +9581,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>5.1</v>
+        <v>1.8</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9624,7 +9624,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 55529-2024</t>
+          <t>A 1299-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9638,10 +9638,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45622</v>
+        <v>45303</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9654,7 +9654,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9697,7 +9697,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 46702-2024</t>
+          <t>A 32364-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9711,10 +9711,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45583</v>
+        <v>45120</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9727,7 +9727,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9770,7 +9770,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 52519-2025</t>
+          <t>A 9055-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9784,10 +9784,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45954</v>
+        <v>46069</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9843,7 +9843,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 49206-2024</t>
+          <t>A 31503-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9857,10 +9857,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45595</v>
+        <v>45115</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9873,7 +9873,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9916,7 +9916,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 31789-2023</t>
+          <t>A 39014-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9930,10 +9930,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45118</v>
+        <v>45163</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9946,7 +9946,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9989,7 +9989,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 55728-2025</t>
+          <t>A 43857-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -10003,10 +10003,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45972</v>
+        <v>45912</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10019,7 +10019,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -10062,7 +10062,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 31503-2023</t>
+          <t>A 31908-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10076,10 +10076,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45115</v>
+        <v>45118</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10092,7 +10092,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -10135,7 +10135,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 57725-2025</t>
+          <t>A 31502-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10149,10 +10149,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45981</v>
+        <v>45115</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10165,7 +10165,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>2.1</v>
+        <v>0.7</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -10208,7 +10208,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 39014-2023</t>
+          <t>A 60227-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10222,10 +10222,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45163</v>
+        <v>45994</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10238,7 +10238,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -10281,7 +10281,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 19500-2022</t>
+          <t>A 28253-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10295,10 +10295,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>44693</v>
+        <v>45099</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10311,7 +10311,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1.2</v>
+        <v>2.7</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10354,7 +10354,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 44448-2023</t>
+          <t>A 21488-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10368,10 +10368,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45189</v>
+        <v>45061</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10384,7 +10384,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10427,7 +10427,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 32020-2025</t>
+          <t>A 7994-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10441,10 +10441,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45835</v>
+        <v>44973</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10457,7 +10457,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10500,7 +10500,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 57923-2024</t>
+          <t>A 13278-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10514,10 +10514,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45631</v>
+        <v>46093</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10530,7 +10530,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>4.5</v>
+        <v>1.7</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10573,7 +10573,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 28264-2022</t>
+          <t>A 27097-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10587,10 +10587,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>44746</v>
+        <v>46188</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10603,7 +10603,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10646,7 +10646,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 55545-2022</t>
+          <t>A 27553-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10660,10 +10660,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>44887</v>
+        <v>45097</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10676,7 +10676,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>4.4</v>
+        <v>0.8</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10719,7 +10719,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 34514-2023</t>
+          <t>A 9803-2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10733,10 +10733,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45140</v>
+        <v>46072</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10749,7 +10749,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>3.1</v>
+        <v>5</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10792,7 +10792,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 35677-2026</t>
+          <t>A 53501-2022</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10806,10 +10806,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46265</v>
+        <v>44879</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10822,7 +10822,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>3.1</v>
+        <v>7.2</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10865,7 +10865,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 1299-2024</t>
+          <t>A 7707-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10879,10 +10879,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45303</v>
+        <v>45705</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10895,7 +10895,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10938,7 +10938,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 9055-2026</t>
+          <t>A 54709-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10952,10 +10952,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46069</v>
+        <v>45236</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10968,7 +10968,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>0.7</v>
+        <v>3.6</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -11011,7 +11011,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 19255-2026</t>
+          <t>A 12148-2024</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -11025,10 +11025,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46132</v>
+        <v>45377</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11041,7 +11041,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -11084,7 +11084,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 13662-2025</t>
+          <t>A 19500-2022</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -11098,10 +11098,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45736</v>
+        <v>44693</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11114,7 +11114,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>6.4</v>
+        <v>1.2</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -11157,7 +11157,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 42105-2022</t>
+          <t>A 4605-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -11171,10 +11171,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>44830</v>
+        <v>45687</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11187,7 +11187,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -11230,7 +11230,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 15154-2023</t>
+          <t>A 29369-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11244,10 +11244,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45016</v>
+        <v>46203</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11260,7 +11260,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>3.5</v>
+        <v>1.3</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -11303,7 +11303,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 7337-2024</t>
+          <t>A 31720-2023</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11317,10 +11317,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45345</v>
+        <v>45117</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11333,7 +11333,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>2.6</v>
+        <v>0.5</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11376,7 +11376,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 49610-2024</t>
+          <t>A 16314-2024</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11390,10 +11390,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45596</v>
+        <v>45407</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11406,7 +11406,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>6.4</v>
+        <v>1.1</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11449,7 +11449,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 9803-2026</t>
+          <t>A 34514-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46072</v>
+        <v>45140</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11479,7 +11479,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>5</v>
+        <v>3.1</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11522,7 +11522,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 14400-2023</t>
+          <t>A 46613-2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11536,10 +11536,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45012</v>
+        <v>45583</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11552,7 +11552,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.7</v>
+        <v>6.2</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11595,7 +11595,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 4089-2024</t>
+          <t>A 23976-2024</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11609,10 +11609,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45323</v>
+        <v>45456</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11625,7 +11625,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11668,7 +11668,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 19650-2026</t>
+          <t>A 40278-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11682,10 +11682,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46134</v>
+        <v>45169</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11698,7 +11698,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>8</v>
+        <v>1.1</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11741,7 +11741,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 23676-2024</t>
+          <t>A 7871-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11755,10 +11755,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45454</v>
+        <v>45706</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11771,7 +11771,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11814,7 +11814,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 60-2024</t>
+          <t>A 31576-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11828,10 +11828,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45293</v>
+        <v>46224</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11844,7 +11844,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11887,7 +11887,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 7707-2025</t>
+          <t>A 32430-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11901,10 +11901,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45705</v>
+        <v>45120</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11917,7 +11917,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11960,7 +11960,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 58150-2024</t>
+          <t>A 36001-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11974,10 +11974,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45632</v>
+        <v>46266</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11990,7 +11990,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -12033,7 +12033,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 4755-2024</t>
+          <t>A 35912-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -12047,10 +12047,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45328</v>
+        <v>46266</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12063,7 +12063,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -12106,7 +12106,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 58134-2022</t>
+          <t>A 29436-2024</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -12120,10 +12120,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>44900</v>
+        <v>45483</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12136,7 +12136,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1.2</v>
+        <v>4.2</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 32430-2023</t>
+          <t>A 58150-2024</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -12193,10 +12193,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45120</v>
+        <v>45632</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12209,7 +12209,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -12252,7 +12252,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 28496-2023</t>
+          <t>A 28264-2022</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12266,10 +12266,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45103</v>
+        <v>44746</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12282,7 +12282,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -12325,7 +12325,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 4605-2025</t>
+          <t>A 31709-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12339,10 +12339,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45687</v>
+        <v>45117</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12355,7 +12355,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -12398,7 +12398,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 21488-2023</t>
+          <t>A 19256-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12412,10 +12412,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45061</v>
+        <v>46132</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12428,7 +12428,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12471,7 +12471,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 74214-2021</t>
+          <t>A 8665-2022</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12485,10 +12485,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>44553</v>
+        <v>44613</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12501,7 +12501,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>19.8</v>
+        <v>0.6</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12544,7 +12544,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 31908-2023</t>
+          <t>A 60-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12558,10 +12558,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45118</v>
+        <v>45293</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12574,7 +12574,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12617,7 +12617,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 7811-2023</t>
+          <t>A 37628-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12631,10 +12631,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>44973</v>
+        <v>46276</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12646,8 +12646,13 @@
           <t>ÄNGELHOLM</t>
         </is>
       </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I144" t="n">
-        <v>0.9</v>
+        <v>4.5</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12690,7 +12695,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 16314-2024</t>
+          <t>A 607-2024</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12704,10 +12709,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45407</v>
+        <v>45299</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12720,7 +12725,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12763,7 +12768,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 46613-2024</t>
+          <t>A 26986-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12777,10 +12782,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45583</v>
+        <v>46185</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12793,7 +12798,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>6.2</v>
+        <v>3.5</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12836,7 +12841,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 20635-2024</t>
+          <t>A 49206-2024</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12850,10 +12855,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45436</v>
+        <v>45595</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12866,7 +12871,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>4.8</v>
+        <v>1.7</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12909,7 +12914,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 60227-2025</t>
+          <t>A 19503-2022</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12923,10 +12928,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45994</v>
+        <v>44693</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12939,7 +12944,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1.5</v>
+        <v>5.1</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12982,7 +12987,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 43857-2025</t>
+          <t>A 26978-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12996,10 +13001,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45912</v>
+        <v>46185</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13012,7 +13017,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1.1</v>
+        <v>7.7</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -13055,7 +13060,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 13278-2026</t>
+          <t>A 57923-2024</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -13069,10 +13074,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46093</v>
+        <v>45631</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13085,7 +13090,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.7</v>
+        <v>4.5</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -13128,7 +13133,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 27097-2026</t>
+          <t>A 35677-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -13142,10 +13147,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46188</v>
+        <v>46265</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13158,7 +13163,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -13201,7 +13206,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 29369-2026</t>
+          <t>A 20635-2024</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -13215,10 +13220,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46203</v>
+        <v>45436</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13231,7 +13236,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>1.3</v>
+        <v>4.8</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -13274,7 +13279,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 31576-2026</t>
+          <t>A 23980-2024</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -13288,10 +13293,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46224</v>
+        <v>45456</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13304,7 +13309,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -13347,7 +13352,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 36001-2026</t>
+          <t>A 55748-2024</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -13361,10 +13366,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46266</v>
+        <v>45623</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13377,7 +13382,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -13420,7 +13425,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 35912-2026</t>
+          <t>A 48197-2024</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13434,10 +13439,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46266</v>
+        <v>45590</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13450,7 +13455,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1.3</v>
+        <v>3.1</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13493,7 +13498,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 19256-2026</t>
+          <t>A 19255-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13510,7 +13515,7 @@
         <v>46132</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13523,7 +13528,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13566,7 +13571,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 37628-2026</t>
+          <t>A 55529-2024</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13580,10 +13585,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46276</v>
+        <v>45622</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13595,13 +13600,8 @@
           <t>ÄNGELHOLM</t>
         </is>
       </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I157" t="n">
-        <v>4.5</v>
+        <v>2.2</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13644,7 +13644,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 26978-2026</t>
+          <t>A 32020-2025</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13658,10 +13658,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46185</v>
+        <v>45835</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13674,7 +13674,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>7.7</v>
+        <v>0.7</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13717,7 +13717,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 26986-2026</t>
+          <t>A 13662-2025</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13731,10 +13731,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46185</v>
+        <v>45736</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13747,7 +13747,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>3.5</v>
+        <v>6.4</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13807,7 +13807,7 @@
         <v>45582</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13880,7 +13880,7 @@
         <v>45582</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13953,7 +13953,7 @@
         <v>45582</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14026,7 +14026,7 @@
         <v>45582</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14099,7 +14099,7 @@
         <v>44519</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14172,7 +14172,7 @@
         <v>45239</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14245,7 +14245,7 @@
         <v>45168</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14318,7 +14318,7 @@
         <v>44861</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14391,7 +14391,7 @@
         <v>45582</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>

--- a/Översikt ÄNGELHOLM.xlsx
+++ b/Översikt ÄNGELHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45099</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         <v>45931</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
         <v>45931</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>46106</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>44802</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 32268-2022</t>
+          <t>A 74502-2021</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1204,10 +1204,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44781</v>
+        <v>44560</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1220,16 +1220,16 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>8.6</v>
+        <v>5.6</v>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1244,7 +1244,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1253,12 +1253,128 @@
         <v>8</v>
       </c>
       <c r="T7" t="n">
+        <v>9</v>
+      </c>
+      <c r="U7" t="n">
+        <v>9</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Entita
+Grönsångare
+Sydlig sotticka
+Västlig hakmossa
+Spillkråka
+Gröngöling
+Kungsfågel
+Skogsduva</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 74502-2021 artfynd.xlsx", "A 74502-2021")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 74502-2021 karta.png", "A 74502-2021")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 74502-2021 georefererad karta.tif", "A 74502-2021")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 74502-2021 FSC-klagomål.docx", "A 74502-2021")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 74502-2021 FSC-klagomål mail.docx", "A 74502-2021")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 74502-2021 tillsynsbegäran.docx", "A 74502-2021")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 74502-2021 tillsynsbegäran mail.docx", "A 74502-2021")</f>
+        <v/>
+      </c>
+      <c r="AE7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 74502-2021 prioriterade fågelarter.docx", "A 74502-2021")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 32268-2022</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>44781</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>5</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>8</v>
+      </c>
+      <c r="T8" t="n">
         <v>14</v>
       </c>
-      <c r="U7" t="n">
+      <c r="U8" t="n">
         <v>14</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Bokvårtlav
 Blåmossa
@@ -1270,148 +1386,32 @@
 Vanlig padda</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 32268-2022 artfynd.xlsx", "A 32268-2022")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 32268-2022 karta.png", "A 32268-2022")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 32268-2022 georefererad karta.tif", "A 32268-2022")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 32268-2022 FSC-klagomål.docx", "A 32268-2022")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 32268-2022 FSC-klagomål mail.docx", "A 32268-2022")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 32268-2022 tillsynsbegäran.docx", "A 32268-2022")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 32268-2022 tillsynsbegäran mail.docx", "A 32268-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 74502-2021</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>44560</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="J8" t="n">
-        <v>6</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" t="n">
-        <v>3</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>3</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>8</v>
-      </c>
-      <c r="T8" t="n">
-        <v>9</v>
-      </c>
-      <c r="U8" t="n">
-        <v>9</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Entita
-Grönsångare
-Sydlig sotticka
-Västlig hakmossa
-Spillkråka
-Gröngöling
-Kungsfågel
-Skogsduva</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 74502-2021 artfynd.xlsx", "A 74502-2021")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 74502-2021 karta.png", "A 74502-2021")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 74502-2021 georefererad karta.tif", "A 74502-2021")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 74502-2021 FSC-klagomål.docx", "A 74502-2021")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 74502-2021 FSC-klagomål mail.docx", "A 74502-2021")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 74502-2021 tillsynsbegäran.docx", "A 74502-2021")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 74502-2021 tillsynsbegäran mail.docx", "A 74502-2021")</f>
-        <v/>
-      </c>
-      <c r="AE8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 74502-2021 prioriterade fågelarter.docx", "A 74502-2021")</f>
         <v/>
       </c>
     </row>
@@ -1435,7 +1435,7 @@
         <v>45835</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 5046-2022</t>
+          <t>A 308-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1547,10 +1547,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44593</v>
+        <v>44929</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1563,34 +1563,34 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>3</v>
+        <v>0.8</v>
       </c>
       <c r="J10" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L10" t="n">
         <v>1</v>
       </c>
       <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
         <v>1</v>
       </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2</v>
-      </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>6</v>
@@ -1599,9 +1599,119 @@
         <v>7</v>
       </c>
       <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Bokvårtlav
+Dvärghäxört
+Havstulpanlav
+Klippfrullania
+Platt fjädermossa
+Stor knopplav</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 308-2023 artfynd.xlsx", "A 308-2023")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 308-2023 karta.png", "A 308-2023")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 308-2023 georefererad karta.tif", "A 308-2023")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 308-2023 FSC-klagomål.docx", "A 308-2023")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 308-2023 FSC-klagomål mail.docx", "A 308-2023")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 308-2023 tillsynsbegäran.docx", "A 308-2023")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 308-2023 tillsynsbegäran mail.docx", "A 308-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 5046-2022</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>44593</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>3</v>
+      </c>
+      <c r="J11" t="n">
         <v>6</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>6</v>
+      </c>
+      <c r="T11" t="n">
+        <v>7</v>
+      </c>
+      <c r="U11" t="n">
+        <v>6</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Grönfink
 Gulsparv
@@ -1611,111 +1721,225 @@
 Trädlärka</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 5046-2022 artfynd.xlsx", "A 5046-2022")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 5046-2022 karta.png", "A 5046-2022")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 5046-2022 georefererad karta.tif", "A 5046-2022")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 5046-2022 FSC-klagomål.docx", "A 5046-2022")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 5046-2022 FSC-klagomål mail.docx", "A 5046-2022")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 5046-2022 tillsynsbegäran.docx", "A 5046-2022")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 5046-2022 tillsynsbegäran mail.docx", "A 5046-2022")</f>
         <v/>
       </c>
-      <c r="AE10">
+      <c r="AE11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 5046-2022 prioriterade fågelarter.docx", "A 5046-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 308-2023</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>44929</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>S 2334-2023</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Askåterföring</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>45106</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>6</v>
+      </c>
+      <c r="T12" t="n">
+        <v>6</v>
+      </c>
+      <c r="U12" t="n">
+        <v>6</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Småvänderot
+Vitfläckig guldvinge
+Kambräken
+Spillkråka
+Törnskata
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/S 2334-2023 artfynd.xlsx", "S 2334-2023")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/S 2334-2023 karta.png", "S 2334-2023")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/S 2334-2023 georefererad karta.tif", "S 2334-2023")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/S 2334-2023 FSC-klagomål.docx", "S 2334-2023")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/S 2334-2023 FSC-klagomål mail.docx", "S 2334-2023")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/S 2334-2023 tillsynsbegäran.docx", "S 2334-2023")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/S 2334-2023 tillsynsbegäran mail.docx", "S 2334-2023")</f>
+        <v/>
+      </c>
+      <c r="AE12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/S 2334-2023 prioriterade fågelarter.docx", "S 2334-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>S 4107-2023</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45245</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
         <v>5</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L13" t="n">
         <v>1</v>
       </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
         <v>1</v>
       </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
         <v>6</v>
       </c>
-      <c r="T11" t="n">
+      <c r="T13" t="n">
         <v>7</v>
       </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Bokvårtlav
 Dvärghäxört
@@ -1725,230 +1949,6 @@
 Stor knopplav</t>
         </is>
       </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 308-2023 artfynd.xlsx", "A 308-2023")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 308-2023 karta.png", "A 308-2023")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 308-2023 georefererad karta.tif", "A 308-2023")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 308-2023 FSC-klagomål.docx", "A 308-2023")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 308-2023 FSC-klagomål mail.docx", "A 308-2023")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 308-2023 tillsynsbegäran.docx", "A 308-2023")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 308-2023 tillsynsbegäran mail.docx", "A 308-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>S 2334-2023</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Askåterföring</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>45106</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>47.6</v>
-      </c>
-      <c r="J12" t="n">
-        <v>3</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1</v>
-      </c>
-      <c r="S12" t="n">
-        <v>6</v>
-      </c>
-      <c r="T12" t="n">
-        <v>6</v>
-      </c>
-      <c r="U12" t="n">
-        <v>6</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Småvänderot
-Vitfläckig guldvinge
-Kambräken
-Spillkråka
-Törnskata
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/S 2334-2023 artfynd.xlsx", "S 2334-2023")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/S 2334-2023 karta.png", "S 2334-2023")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/S 2334-2023 georefererad karta.tif", "S 2334-2023")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/S 2334-2023 FSC-klagomål.docx", "S 2334-2023")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/S 2334-2023 FSC-klagomål mail.docx", "S 2334-2023")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/S 2334-2023 tillsynsbegäran.docx", "S 2334-2023")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/S 2334-2023 tillsynsbegäran mail.docx", "S 2334-2023")</f>
-        <v/>
-      </c>
-      <c r="AE12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/S 2334-2023 prioriterade fågelarter.docx", "S 2334-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>S 4107-2023</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45245</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>5</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>6</v>
-      </c>
-      <c r="T13" t="n">
-        <v>7</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Bokvårtlav
-Dvärghäxört
-Havstulpanlav
-Klippfrullania
-Platt fjädermossa
-Stor knopplav</t>
-        </is>
-      </c>
       <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/S 4107-2023 artfynd.xlsx", "S 4107-2023")</f>
         <v/>
@@ -1998,7 +1998,7 @@
         <v>46038</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>46265</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>46265</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2337,7 +2337,7 @@
         <v>45664</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2449,7 +2449,7 @@
         <v>44864</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 905-2024</t>
+          <t>A 28874-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2554,10 +2554,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45301</v>
+        <v>45104</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2570,19 +2570,19 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>4.9</v>
+        <v>9</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -2594,592 +2594,592 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>3</v>
       </c>
       <c r="T19" t="n">
+        <v>5</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Blåmossa
+Stubbspretmossa
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 28874-2023 artfynd.xlsx", "A 28874-2023")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 28874-2023 karta.png", "A 28874-2023")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 28874-2023 georefererad karta.tif", "A 28874-2023")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 28874-2023 FSC-klagomål.docx", "A 28874-2023")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 28874-2023 FSC-klagomål mail.docx", "A 28874-2023")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 28874-2023 tillsynsbegäran.docx", "A 28874-2023")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 28874-2023 tillsynsbegäran mail.docx", "A 28874-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 31907-2023</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>45118</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
         <v>3</v>
       </c>
-      <c r="U19" t="n">
+      <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Bokvårtlav
+Platt fjädermossa
+Stubbspretmossa</t>
+        </is>
+      </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 31907-2023 artfynd.xlsx", "A 31907-2023")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 31907-2023 karta.png", "A 31907-2023")</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 31907-2023 georefererad karta.tif", "A 31907-2023")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 31907-2023 FSC-klagomål.docx", "A 31907-2023")</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 31907-2023 FSC-klagomål mail.docx", "A 31907-2023")</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 31907-2023 tillsynsbegäran.docx", "A 31907-2023")</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 31907-2023 tillsynsbegäran mail.docx", "A 31907-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 8065-2025</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>45707</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
         <v>2</v>
       </c>
-      <c r="V19" s="2" t="inlineStr">
+      <c r="M21" t="n">
+        <v>1</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Småvänderot
+Gullpudra
+Svinrot</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 8065-2025 artfynd.xlsx", "A 8065-2025")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 8065-2025 karta.png", "A 8065-2025")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 8065-2025 georefererad karta.tif", "A 8065-2025")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 8065-2025 FSC-klagomål.docx", "A 8065-2025")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 8065-2025 FSC-klagomål mail.docx", "A 8065-2025")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 8065-2025 tillsynsbegäran.docx", "A 8065-2025")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 8065-2025 tillsynsbegäran mail.docx", "A 8065-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 3317-2026</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>46041</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>2</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3</v>
+      </c>
+      <c r="T22" t="n">
+        <v>6</v>
+      </c>
+      <c r="U22" t="n">
+        <v>6</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>Entita
+Mindre hackspett
+Gröngöling</t>
+        </is>
+      </c>
+      <c r="W22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 3317-2026 artfynd.xlsx", "A 3317-2026")</f>
+        <v/>
+      </c>
+      <c r="X22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 3317-2026 karta.png", "A 3317-2026")</f>
+        <v/>
+      </c>
+      <c r="Y22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 3317-2026 georefererad karta.tif", "A 3317-2026")</f>
+        <v/>
+      </c>
+      <c r="AA22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 3317-2026 FSC-klagomål.docx", "A 3317-2026")</f>
+        <v/>
+      </c>
+      <c r="AB22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 3317-2026 FSC-klagomål mail.docx", "A 3317-2026")</f>
+        <v/>
+      </c>
+      <c r="AC22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 3317-2026 tillsynsbegäran.docx", "A 3317-2026")</f>
+        <v/>
+      </c>
+      <c r="AD22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 3317-2026 tillsynsbegäran mail.docx", "A 3317-2026")</f>
+        <v/>
+      </c>
+      <c r="AE22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 3317-2026 prioriterade fågelarter.docx", "A 3317-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>A 50684-2023</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>45210</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>1</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>Skogsalm
+Kopparödla
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 50684-2023 artfynd.xlsx", "A 50684-2023")</f>
+        <v/>
+      </c>
+      <c r="X23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 50684-2023 karta.png", "A 50684-2023")</f>
+        <v/>
+      </c>
+      <c r="Y23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 50684-2023 georefererad karta.tif", "A 50684-2023")</f>
+        <v/>
+      </c>
+      <c r="AA23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 50684-2023 FSC-klagomål.docx", "A 50684-2023")</f>
+        <v/>
+      </c>
+      <c r="AB23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 50684-2023 FSC-klagomål mail.docx", "A 50684-2023")</f>
+        <v/>
+      </c>
+      <c r="AC23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 50684-2023 tillsynsbegäran.docx", "A 50684-2023")</f>
+        <v/>
+      </c>
+      <c r="AD23">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 50684-2023 tillsynsbegäran mail.docx", "A 50684-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>A 905-2024</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="n">
+        <v>45301</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
         <is>
           <t>Igelkott
 Desmeknopp
 Myskmadra</t>
         </is>
       </c>
-      <c r="W19">
+      <c r="W24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 905-2024 artfynd.xlsx", "A 905-2024")</f>
         <v/>
       </c>
-      <c r="X19">
+      <c r="X24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 905-2024 karta.png", "A 905-2024")</f>
         <v/>
       </c>
-      <c r="Y19">
+      <c r="Y24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 905-2024 georefererad karta.tif", "A 905-2024")</f>
         <v/>
       </c>
-      <c r="AA19">
+      <c r="AA24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 905-2024 FSC-klagomål.docx", "A 905-2024")</f>
         <v/>
       </c>
-      <c r="AB19">
+      <c r="AB24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 905-2024 FSC-klagomål mail.docx", "A 905-2024")</f>
         <v/>
       </c>
-      <c r="AC19">
+      <c r="AC24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 905-2024 tillsynsbegäran.docx", "A 905-2024")</f>
         <v/>
       </c>
-      <c r="AD19">
+      <c r="AD24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 905-2024 tillsynsbegäran mail.docx", "A 905-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 28874-2023</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>45104</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>9</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1</v>
-      </c>
-      <c r="K20" t="n">
-        <v>2</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3</v>
-      </c>
-      <c r="T20" t="n">
-        <v>5</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Blåmossa
-Stubbspretmossa
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 28874-2023 artfynd.xlsx", "A 28874-2023")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 28874-2023 karta.png", "A 28874-2023")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 28874-2023 georefererad karta.tif", "A 28874-2023")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 28874-2023 FSC-klagomål.docx", "A 28874-2023")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 28874-2023 FSC-klagomål mail.docx", "A 28874-2023")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 28874-2023 tillsynsbegäran.docx", "A 28874-2023")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 28874-2023 tillsynsbegäran mail.docx", "A 28874-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 8065-2025</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>45707</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>2</v>
-      </c>
-      <c r="M21" t="n">
-        <v>1</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>3</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3</v>
-      </c>
-      <c r="T21" t="n">
-        <v>3</v>
-      </c>
-      <c r="U21" t="n">
-        <v>2</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Småvänderot
-Gullpudra
-Svinrot</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 8065-2025 artfynd.xlsx", "A 8065-2025")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 8065-2025 karta.png", "A 8065-2025")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 8065-2025 georefererad karta.tif", "A 8065-2025")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 8065-2025 FSC-klagomål.docx", "A 8065-2025")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 8065-2025 FSC-klagomål mail.docx", "A 8065-2025")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 8065-2025 tillsynsbegäran.docx", "A 8065-2025")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 8065-2025 tillsynsbegäran mail.docx", "A 8065-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 50684-2023</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>45210</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J22" t="n">
-        <v>2</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>1</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3</v>
-      </c>
-      <c r="T22" t="n">
-        <v>3</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Skogsalm
-Kopparödla
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 50684-2023 artfynd.xlsx", "A 50684-2023")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 50684-2023 karta.png", "A 50684-2023")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 50684-2023 georefererad karta.tif", "A 50684-2023")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 50684-2023 FSC-klagomål.docx", "A 50684-2023")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 50684-2023 FSC-klagomål mail.docx", "A 50684-2023")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 50684-2023 tillsynsbegäran.docx", "A 50684-2023")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 50684-2023 tillsynsbegäran mail.docx", "A 50684-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>A 3317-2026</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>46041</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J23" t="n">
-        <v>3</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>2</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>2</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3</v>
-      </c>
-      <c r="T23" t="n">
-        <v>6</v>
-      </c>
-      <c r="U23" t="n">
-        <v>6</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>Entita
-Mindre hackspett
-Gröngöling</t>
-        </is>
-      </c>
-      <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 3317-2026 artfynd.xlsx", "A 3317-2026")</f>
-        <v/>
-      </c>
-      <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 3317-2026 karta.png", "A 3317-2026")</f>
-        <v/>
-      </c>
-      <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 3317-2026 georefererad karta.tif", "A 3317-2026")</f>
-        <v/>
-      </c>
-      <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 3317-2026 FSC-klagomål.docx", "A 3317-2026")</f>
-        <v/>
-      </c>
-      <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 3317-2026 FSC-klagomål mail.docx", "A 3317-2026")</f>
-        <v/>
-      </c>
-      <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 3317-2026 tillsynsbegäran.docx", "A 3317-2026")</f>
-        <v/>
-      </c>
-      <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 3317-2026 tillsynsbegäran mail.docx", "A 3317-2026")</f>
-        <v/>
-      </c>
-      <c r="AE23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 3317-2026 prioriterade fågelarter.docx", "A 3317-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>A 31907-2023</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="n">
-        <v>45118</v>
-      </c>
-      <c r="E24" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>2</v>
-      </c>
-      <c r="L24" t="n">
-        <v>1</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3</v>
-      </c>
-      <c r="T24" t="n">
-        <v>3</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>Bokvårtlav
-Platt fjädermossa
-Stubbspretmossa</t>
-        </is>
-      </c>
-      <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 31907-2023 artfynd.xlsx", "A 31907-2023")</f>
-        <v/>
-      </c>
-      <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 31907-2023 karta.png", "A 31907-2023")</f>
-        <v/>
-      </c>
-      <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 31907-2023 georefererad karta.tif", "A 31907-2023")</f>
-        <v/>
-      </c>
-      <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 31907-2023 FSC-klagomål.docx", "A 31907-2023")</f>
-        <v/>
-      </c>
-      <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 31907-2023 FSC-klagomål mail.docx", "A 31907-2023")</f>
-        <v/>
-      </c>
-      <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 31907-2023 tillsynsbegäran.docx", "A 31907-2023")</f>
-        <v/>
-      </c>
-      <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 31907-2023 tillsynsbegäran mail.docx", "A 31907-2023")</f>
         <v/>
       </c>
     </row>
@@ -3203,7 +3203,7 @@
         <v>45763</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3314,7 +3314,7 @@
         <v>45474</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3424,7 +3424,7 @@
         <v>45841</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
         <v>45105</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
         <v>44553</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3754,7 +3754,7 @@
         <v>45359</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
         <v>45582</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>44839</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>44742</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4180,7 +4180,7 @@
         <v>44746</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 44062-2022</t>
+          <t>A 12150-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4286,10 +4286,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44839</v>
+        <v>45377</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4302,20 +4302,20 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
         <v>1</v>
       </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
       <c r="N35" t="n">
         <v>0</v>
       </c>
@@ -4326,10 +4326,10 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4342,35 +4342,35 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 44062-2022 artfynd.xlsx", "A 44062-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 12150-2024 artfynd.xlsx", "A 12150-2024")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 44062-2022 karta.png", "A 44062-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 12150-2024 karta.png", "A 12150-2024")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 44062-2022 georefererad karta.tif", "A 44062-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 12150-2024 georefererad karta.tif", "A 12150-2024")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 44062-2022 FSC-klagomål.docx", "A 44062-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 12150-2024 FSC-klagomål.docx", "A 12150-2024")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 44062-2022 FSC-klagomål mail.docx", "A 44062-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 12150-2024 FSC-klagomål mail.docx", "A 12150-2024")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 44062-2022 tillsynsbegäran.docx", "A 44062-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 12150-2024 tillsynsbegäran.docx", "A 12150-2024")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 44062-2022 tillsynsbegäran mail.docx", "A 44062-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 12150-2024 tillsynsbegäran mail.docx", "A 12150-2024")</f>
         <v/>
       </c>
     </row>
@@ -4394,7 +4394,7 @@
         <v>45323</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4482,7 +4482,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 25129-2024</t>
+          <t>A 50642-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4496,10 +4496,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45462</v>
+        <v>45210</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4512,16 +4512,16 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>4.6</v>
+        <v>0.8</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
@@ -4536,7 +4536,7 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
@@ -4552,42 +4552,42 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="W37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 25129-2024 artfynd.xlsx", "A 25129-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 50642-2023 artfynd.xlsx", "A 50642-2023")</f>
         <v/>
       </c>
       <c r="X37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 25129-2024 karta.png", "A 25129-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 50642-2023 karta.png", "A 50642-2023")</f>
         <v/>
       </c>
       <c r="Y37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 25129-2024 georefererad karta.tif", "A 25129-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 50642-2023 georefererad karta.tif", "A 50642-2023")</f>
         <v/>
       </c>
       <c r="AA37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 25129-2024 FSC-klagomål.docx", "A 25129-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 50642-2023 FSC-klagomål.docx", "A 50642-2023")</f>
         <v/>
       </c>
       <c r="AB37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 25129-2024 FSC-klagomål mail.docx", "A 25129-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 50642-2023 FSC-klagomål mail.docx", "A 50642-2023")</f>
         <v/>
       </c>
       <c r="AC37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 25129-2024 tillsynsbegäran.docx", "A 25129-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 50642-2023 tillsynsbegäran.docx", "A 50642-2023")</f>
         <v/>
       </c>
       <c r="AD37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 25129-2024 tillsynsbegäran mail.docx", "A 25129-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 50642-2023 tillsynsbegäran mail.docx", "A 50642-2023")</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 12150-2024</t>
+          <t>A 46487-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4601,10 +4601,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45377</v>
+        <v>45582</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.4</v>
+        <v>5.8</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -4629,7 +4629,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
         <v>0</v>
@@ -4641,10 +4641,10 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -4657,42 +4657,42 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 12150-2024 artfynd.xlsx", "A 12150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 46487-2024 artfynd.xlsx", "A 46487-2024")</f>
         <v/>
       </c>
       <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 12150-2024 karta.png", "A 12150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 46487-2024 karta.png", "A 46487-2024")</f>
         <v/>
       </c>
       <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 12150-2024 georefererad karta.tif", "A 12150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 46487-2024 georefererad karta.tif", "A 46487-2024")</f>
         <v/>
       </c>
       <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 12150-2024 FSC-klagomål.docx", "A 12150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 46487-2024 FSC-klagomål.docx", "A 46487-2024")</f>
         <v/>
       </c>
       <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 12150-2024 FSC-klagomål mail.docx", "A 12150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 46487-2024 FSC-klagomål mail.docx", "A 46487-2024")</f>
         <v/>
       </c>
       <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 12150-2024 tillsynsbegäran.docx", "A 12150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 46487-2024 tillsynsbegäran.docx", "A 46487-2024")</f>
         <v/>
       </c>
       <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 12150-2024 tillsynsbegäran mail.docx", "A 12150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 46487-2024 tillsynsbegäran mail.docx", "A 46487-2024")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 61094-2021</t>
+          <t>A 25129-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4706,10 +4706,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44498</v>
+        <v>45462</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4722,17 +4722,17 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>6.4</v>
+        <v>4.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
         <v>1</v>
       </c>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
       <c r="M39" t="n">
         <v>0</v>
       </c>
@@ -4746,7 +4746,7 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -4758,46 +4758,46 @@
         <v>1</v>
       </c>
       <c r="U39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 61094-2021 artfynd.xlsx", "A 61094-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 25129-2024 artfynd.xlsx", "A 25129-2024")</f>
         <v/>
       </c>
       <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 61094-2021 karta.png", "A 61094-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 25129-2024 karta.png", "A 25129-2024")</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 61094-2021 georefererad karta.tif", "A 61094-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 25129-2024 georefererad karta.tif", "A 25129-2024")</f>
         <v/>
       </c>
       <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 61094-2021 FSC-klagomål.docx", "A 61094-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 25129-2024 FSC-klagomål.docx", "A 25129-2024")</f>
         <v/>
       </c>
       <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 61094-2021 FSC-klagomål mail.docx", "A 61094-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 25129-2024 FSC-klagomål mail.docx", "A 25129-2024")</f>
         <v/>
       </c>
       <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 61094-2021 tillsynsbegäran.docx", "A 61094-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 25129-2024 tillsynsbegäran.docx", "A 25129-2024")</f>
         <v/>
       </c>
       <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 61094-2021 tillsynsbegäran mail.docx", "A 61094-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 25129-2024 tillsynsbegäran mail.docx", "A 25129-2024")</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 27094-2026</t>
+          <t>A 61094-2021</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4811,10 +4811,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46188</v>
+        <v>44498</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4863,46 +4863,46 @@
         <v>1</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="W40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 27094-2026 artfynd.xlsx", "A 27094-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 61094-2021 artfynd.xlsx", "A 61094-2021")</f>
         <v/>
       </c>
       <c r="X40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 27094-2026 karta.png", "A 27094-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 61094-2021 karta.png", "A 61094-2021")</f>
         <v/>
       </c>
       <c r="Y40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 27094-2026 georefererad karta.tif", "A 27094-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 61094-2021 georefererad karta.tif", "A 61094-2021")</f>
         <v/>
       </c>
       <c r="AA40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 27094-2026 FSC-klagomål.docx", "A 27094-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 61094-2021 FSC-klagomål.docx", "A 61094-2021")</f>
         <v/>
       </c>
       <c r="AB40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 27094-2026 FSC-klagomål mail.docx", "A 27094-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 61094-2021 FSC-klagomål mail.docx", "A 61094-2021")</f>
         <v/>
       </c>
       <c r="AC40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 27094-2026 tillsynsbegäran.docx", "A 27094-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 61094-2021 tillsynsbegäran.docx", "A 61094-2021")</f>
         <v/>
       </c>
       <c r="AD40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 27094-2026 tillsynsbegäran mail.docx", "A 27094-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 61094-2021 tillsynsbegäran mail.docx", "A 61094-2021")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 50642-2023</t>
+          <t>A 27094-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45210</v>
+        <v>46188</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4932,13 +4932,13 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.8</v>
+        <v>6.2</v>
       </c>
       <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
         <v>1</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -4972,42 +4972,42 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 50642-2023 artfynd.xlsx", "A 50642-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 27094-2026 artfynd.xlsx", "A 27094-2026")</f>
         <v/>
       </c>
       <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 50642-2023 karta.png", "A 50642-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 27094-2026 karta.png", "A 27094-2026")</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 50642-2023 georefererad karta.tif", "A 50642-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 27094-2026 georefererad karta.tif", "A 27094-2026")</f>
         <v/>
       </c>
       <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 50642-2023 FSC-klagomål.docx", "A 50642-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 27094-2026 FSC-klagomål.docx", "A 27094-2026")</f>
         <v/>
       </c>
       <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 50642-2023 FSC-klagomål mail.docx", "A 50642-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 27094-2026 FSC-klagomål mail.docx", "A 27094-2026")</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 50642-2023 tillsynsbegäran.docx", "A 50642-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 27094-2026 tillsynsbegäran.docx", "A 27094-2026")</f>
         <v/>
       </c>
       <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 50642-2023 tillsynsbegäran mail.docx", "A 50642-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 27094-2026 tillsynsbegäran mail.docx", "A 27094-2026")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 35684-2026</t>
+          <t>A 44062-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5021,10 +5021,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46265</v>
+        <v>44839</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5037,16 +5037,16 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3.9</v>
+        <v>1.2</v>
       </c>
       <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
         <v>1</v>
       </c>
-      <c r="K42" t="n">
-        <v>0</v>
-      </c>
       <c r="L42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
@@ -5061,7 +5061,7 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -5077,46 +5077,42 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 35684-2026 artfynd.xlsx", "A 35684-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 44062-2022 artfynd.xlsx", "A 44062-2022")</f>
         <v/>
       </c>
       <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 35684-2026 karta.png", "A 35684-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 44062-2022 karta.png", "A 44062-2022")</f>
         <v/>
       </c>
       <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 35684-2026 georefererad karta.tif", "A 35684-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 44062-2022 georefererad karta.tif", "A 44062-2022")</f>
         <v/>
       </c>
       <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 35684-2026 FSC-klagomål.docx", "A 35684-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 44062-2022 FSC-klagomål.docx", "A 44062-2022")</f>
         <v/>
       </c>
       <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 35684-2026 FSC-klagomål mail.docx", "A 35684-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 44062-2022 FSC-klagomål mail.docx", "A 44062-2022")</f>
         <v/>
       </c>
       <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 35684-2026 tillsynsbegäran.docx", "A 35684-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 44062-2022 tillsynsbegäran.docx", "A 44062-2022")</f>
         <v/>
       </c>
       <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 35684-2026 tillsynsbegäran mail.docx", "A 35684-2026")</f>
-        <v/>
-      </c>
-      <c r="AE42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 35684-2026 prioriterade fågelarter.docx", "A 35684-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 44062-2022 tillsynsbegäran mail.docx", "A 44062-2022")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 31599-2026</t>
+          <t>A 35684-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5130,10 +5126,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46224</v>
+        <v>46265</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5146,17 +5142,17 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.7</v>
+        <v>3.9</v>
       </c>
       <c r="J43" t="n">
         <v>1</v>
       </c>
       <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
         <v>1</v>
       </c>
-      <c r="L43" t="n">
-        <v>0</v>
-      </c>
       <c r="M43" t="n">
         <v>0</v>
       </c>
@@ -5170,7 +5166,7 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
@@ -5179,49 +5175,53 @@
         <v>1</v>
       </c>
       <c r="T43" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>Ekoxe</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="W43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 31599-2026 artfynd.xlsx", "A 31599-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 35684-2026 artfynd.xlsx", "A 35684-2026")</f>
         <v/>
       </c>
       <c r="X43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 31599-2026 karta.png", "A 31599-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 35684-2026 karta.png", "A 35684-2026")</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 31599-2026 georefererad karta.tif", "A 31599-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 35684-2026 georefererad karta.tif", "A 35684-2026")</f>
         <v/>
       </c>
       <c r="AA43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 31599-2026 FSC-klagomål.docx", "A 31599-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 35684-2026 FSC-klagomål.docx", "A 35684-2026")</f>
         <v/>
       </c>
       <c r="AB43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 31599-2026 FSC-klagomål mail.docx", "A 31599-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 35684-2026 FSC-klagomål mail.docx", "A 35684-2026")</f>
         <v/>
       </c>
       <c r="AC43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 31599-2026 tillsynsbegäran.docx", "A 31599-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 35684-2026 tillsynsbegäran.docx", "A 35684-2026")</f>
         <v/>
       </c>
       <c r="AD43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 31599-2026 tillsynsbegäran mail.docx", "A 31599-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 35684-2026 tillsynsbegäran mail.docx", "A 35684-2026")</f>
+        <v/>
+      </c>
+      <c r="AE43">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 35684-2026 prioriterade fågelarter.docx", "A 35684-2026")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 46487-2024</t>
+          <t>A 31599-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5235,10 +5235,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45582</v>
+        <v>46224</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5251,13 +5251,13 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>5.8</v>
+        <v>1.7</v>
       </c>
       <c r="J44" t="n">
         <v>1</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
@@ -5284,42 +5284,42 @@
         <v>1</v>
       </c>
       <c r="T44" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 46487-2024 artfynd.xlsx", "A 46487-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 31599-2026 artfynd.xlsx", "A 31599-2026")</f>
         <v/>
       </c>
       <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 46487-2024 karta.png", "A 46487-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 31599-2026 karta.png", "A 31599-2026")</f>
         <v/>
       </c>
       <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 46487-2024 georefererad karta.tif", "A 46487-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 31599-2026 georefererad karta.tif", "A 31599-2026")</f>
         <v/>
       </c>
       <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 46487-2024 FSC-klagomål.docx", "A 46487-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 31599-2026 FSC-klagomål.docx", "A 31599-2026")</f>
         <v/>
       </c>
       <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 46487-2024 FSC-klagomål mail.docx", "A 46487-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 31599-2026 FSC-klagomål mail.docx", "A 31599-2026")</f>
         <v/>
       </c>
       <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 46487-2024 tillsynsbegäran.docx", "A 46487-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 31599-2026 tillsynsbegäran.docx", "A 31599-2026")</f>
         <v/>
       </c>
       <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 46487-2024 tillsynsbegäran mail.docx", "A 46487-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 31599-2026 tillsynsbegäran mail.docx", "A 31599-2026")</f>
         <v/>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
         <v>45084</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5448,7 +5448,7 @@
         <v>44862</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5553,7 +5553,7 @@
         <v>44880</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5626,7 +5626,7 @@
         <v>44839</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5699,7 +5699,7 @@
         <v>44725</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5772,7 +5772,7 @@
         <v>44840</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5845,7 +5845,7 @@
         <v>44498</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5918,7 +5918,7 @@
         <v>44477</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5991,7 +5991,7 @@
         <v>44657</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
         <v>44634</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6137,7 +6137,7 @@
         <v>44802</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6210,7 +6210,7 @@
         <v>44802</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
         <v>44827</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6356,7 +6356,7 @@
         <v>44480</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6429,7 +6429,7 @@
         <v>44634</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 40275-2023</t>
+          <t>A 29436-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6499,10 +6499,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45169</v>
+        <v>45483</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6515,7 +6515,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.6</v>
+        <v>4.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6558,7 +6558,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 6667-2025</t>
+          <t>A 8882-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6572,10 +6572,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45700</v>
+        <v>45713</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6588,7 +6588,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6631,7 +6631,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 46702-2024</t>
+          <t>A 12148-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6645,10 +6645,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45583</v>
+        <v>45377</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6704,7 +6704,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 31789-2023</t>
+          <t>A 9578-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6718,10 +6718,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45118</v>
+        <v>45715</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6777,7 +6777,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 1644-2025</t>
+          <t>A 53501-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6791,10 +6791,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45670</v>
+        <v>44879</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1</v>
+        <v>7.2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6850,7 +6850,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 55545-2022</t>
+          <t>A 27551-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6864,10 +6864,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44887</v>
+        <v>45097</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>4.4</v>
+        <v>0.6</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6940,7 +6940,7 @@
         <v>45281</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6996,7 +6996,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 25669-2024</t>
+          <t>A 31720-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -7010,10 +7010,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45463</v>
+        <v>45117</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7026,7 +7026,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>17.9</v>
+        <v>0.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -7069,7 +7069,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 23676-2024</t>
+          <t>A 25669-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7083,10 +7083,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45454</v>
+        <v>45463</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7099,7 +7099,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.9</v>
+        <v>17.9</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -7142,7 +7142,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 8139-2025</t>
+          <t>A 31143-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7152,14 +7152,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45708</v>
+        <v>45502</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7172,7 +7172,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>3.5</v>
+        <v>0.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7215,7 +7215,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 44448-2023</t>
+          <t>A 607-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7229,10 +7229,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45189</v>
+        <v>45299</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7288,7 +7288,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 31143-2024</t>
+          <t>A 54709-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7298,14 +7298,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45502</v>
+        <v>45236</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7318,7 +7318,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.6</v>
+        <v>3.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 23328-2022</t>
+          <t>A 40287-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7375,10 +7375,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44720</v>
+        <v>45895</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7391,7 +7391,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7434,7 +7434,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 15154-2023</t>
+          <t>A 55544-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7448,10 +7448,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45016</v>
+        <v>44887</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7464,7 +7464,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>3.5</v>
+        <v>1.1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7507,7 +7507,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 46286-2024</t>
+          <t>A 23976-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7521,10 +7521,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45581</v>
+        <v>45456</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7537,7 +7537,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7580,7 +7580,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 55544-2022</t>
+          <t>A 42826-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7594,10 +7594,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44887</v>
+        <v>45908</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7610,7 +7610,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7653,7 +7653,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 19650-2026</t>
+          <t>A 27553-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7667,10 +7667,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46134</v>
+        <v>45097</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7683,7 +7683,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>8</v>
+        <v>0.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7726,7 +7726,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 58134-2022</t>
+          <t>A 9055-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7740,10 +7740,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44900</v>
+        <v>46069</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7756,7 +7756,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7799,7 +7799,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 7337-2024</t>
+          <t>A 28253-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7813,10 +7813,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45345</v>
+        <v>45099</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7829,7 +7829,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7872,7 +7872,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 40287-2025</t>
+          <t>A 16419-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7886,10 +7886,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45895</v>
+        <v>45022</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.5</v>
+        <v>4.2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7945,7 +7945,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 49610-2024</t>
+          <t>A 19503-2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7959,10 +7959,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45596</v>
+        <v>44693</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7975,7 +7975,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>6.4</v>
+        <v>5.1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -8018,7 +8018,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 13243-2025</t>
+          <t>A 46702-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -8032,10 +8032,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45735</v>
+        <v>45583</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -8091,7 +8091,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 42826-2025</t>
+          <t>A 49206-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -8105,10 +8105,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45908</v>
+        <v>45595</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8121,7 +8121,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8164,7 +8164,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 74214-2021</t>
+          <t>A 52519-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8178,10 +8178,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44553</v>
+        <v>45954</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8194,7 +8194,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>19.8</v>
+        <v>0.7</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8237,7 +8237,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 7811-2023</t>
+          <t>A 31503-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8251,10 +8251,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44973</v>
+        <v>45115</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8267,7 +8267,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8310,7 +8310,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 58137-2022</t>
+          <t>A 9803-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8324,10 +8324,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44900</v>
+        <v>46072</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8340,7 +8340,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.9</v>
+        <v>5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8383,7 +8383,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 42105-2022</t>
+          <t>A 55728-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8397,10 +8397,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44830</v>
+        <v>45972</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8456,7 +8456,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 50652-2023</t>
+          <t>A 19650-2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8470,10 +8470,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45210</v>
+        <v>46134</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8486,7 +8486,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2.4</v>
+        <v>8</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8529,7 +8529,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 24855-2024</t>
+          <t>A 57725-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8543,10 +8543,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45461</v>
+        <v>45981</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8559,7 +8559,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8602,7 +8602,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 4755-2024</t>
+          <t>A 55529-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8616,10 +8616,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45328</v>
+        <v>45622</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8632,7 +8632,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.9</v>
+        <v>2.2</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8675,7 +8675,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 14400-2023</t>
+          <t>A 23328-2022</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8689,10 +8689,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45012</v>
+        <v>44720</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8748,7 +8748,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 52519-2025</t>
+          <t>A 7707-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8762,10 +8762,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45954</v>
+        <v>45705</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8778,7 +8778,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8821,7 +8821,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 23227-2023</t>
+          <t>A 32364-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8835,10 +8835,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45075</v>
+        <v>45120</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 9578-2025</t>
+          <t>A 58134-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8908,10 +8908,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45715</v>
+        <v>44900</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8924,7 +8924,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8967,7 +8967,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 55728-2025</t>
+          <t>A 8139-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8981,10 +8981,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45972</v>
+        <v>45708</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8997,7 +8997,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -9040,7 +9040,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 8882-2025</t>
+          <t>A 40275-2023</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -9054,10 +9054,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45713</v>
+        <v>45169</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9070,7 +9070,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -9113,7 +9113,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 57725-2025</t>
+          <t>A 74214-2021</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -9127,10 +9127,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45981</v>
+        <v>44553</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9143,7 +9143,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.1</v>
+        <v>19.8</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9186,7 +9186,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 18571-2025</t>
+          <t>A 1644-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9200,10 +9200,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45763</v>
+        <v>45670</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9216,7 +9216,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -9259,7 +9259,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 16419-2023</t>
+          <t>A 24855-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9273,10 +9273,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45022</v>
+        <v>45461</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9289,7 +9289,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>4.2</v>
+        <v>2.4</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9332,7 +9332,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 27551-2023</t>
+          <t>A 7871-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9346,10 +9346,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45097</v>
+        <v>45706</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9362,7 +9362,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9405,7 +9405,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 2575-2024</t>
+          <t>A 13243-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9419,10 +9419,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45313</v>
+        <v>45735</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9435,7 +9435,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9478,7 +9478,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 4089-2024</t>
+          <t>A 6667-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9492,10 +9492,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45323</v>
+        <v>45700</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9508,7 +9508,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9551,7 +9551,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 28496-2023</t>
+          <t>A 32020-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9565,10 +9565,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45103</v>
+        <v>45835</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9581,7 +9581,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9624,7 +9624,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 1299-2024</t>
+          <t>A 58137-2022</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9638,10 +9638,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45303</v>
+        <v>44900</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9654,7 +9654,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9697,7 +9697,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 32364-2023</t>
+          <t>A 2575-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9711,10 +9711,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45120</v>
+        <v>45313</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9727,7 +9727,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9770,7 +9770,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 9055-2026</t>
+          <t>A 31502-2023</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9784,10 +9784,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46069</v>
+        <v>45115</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9843,7 +9843,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 31503-2023</t>
+          <t>A 13662-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9857,10 +9857,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45115</v>
+        <v>45736</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9873,7 +9873,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.9</v>
+        <v>6.4</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9916,7 +9916,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 39014-2023</t>
+          <t>A 46286-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9930,10 +9930,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45163</v>
+        <v>45581</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9946,7 +9946,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9989,7 +9989,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 43857-2025</t>
+          <t>A 60227-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -10003,10 +10003,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45912</v>
+        <v>45994</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10019,7 +10019,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -10062,7 +10062,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 31908-2023</t>
+          <t>A 43857-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10076,10 +10076,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45118</v>
+        <v>45912</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10092,7 +10092,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -10135,7 +10135,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 31502-2023</t>
+          <t>A 7994-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10149,10 +10149,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45115</v>
+        <v>44973</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10165,7 +10165,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -10208,7 +10208,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 60227-2025</t>
+          <t>A 13278-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10222,10 +10222,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45994</v>
+        <v>46093</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10238,7 +10238,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -10281,7 +10281,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 28253-2023</t>
+          <t>A 8665-2022</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10295,10 +10295,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45099</v>
+        <v>44613</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10311,7 +10311,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>2.7</v>
+        <v>0.6</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10354,7 +10354,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 21488-2023</t>
+          <t>A 27097-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10368,10 +10368,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45061</v>
+        <v>46188</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10384,7 +10384,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1.1</v>
+        <v>4</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10427,7 +10427,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 7994-2023</t>
+          <t>A 18571-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10441,10 +10441,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44973</v>
+        <v>45763</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10457,7 +10457,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10500,7 +10500,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 13278-2026</t>
+          <t>A 31709-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10514,10 +10514,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46093</v>
+        <v>45117</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10530,7 +10530,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10573,7 +10573,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 27097-2026</t>
+          <t>A 23227-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10587,10 +10587,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46188</v>
+        <v>45075</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10603,7 +10603,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>4</v>
+        <v>1.1</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10646,7 +10646,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 27553-2023</t>
+          <t>A 50652-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10660,10 +10660,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45097</v>
+        <v>45210</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10676,7 +10676,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10719,7 +10719,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 9803-2026</t>
+          <t>A 40278-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10733,10 +10733,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46072</v>
+        <v>45169</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10749,7 +10749,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>5</v>
+        <v>1.1</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10792,7 +10792,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 53501-2022</t>
+          <t>A 29369-2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10806,10 +10806,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>44879</v>
+        <v>46203</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10822,7 +10822,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>7.2</v>
+        <v>1.3</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10865,7 +10865,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 7707-2025</t>
+          <t>A 31789-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10879,10 +10879,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45705</v>
+        <v>45118</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10895,7 +10895,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10938,7 +10938,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 54709-2023</t>
+          <t>A 39014-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10952,10 +10952,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45236</v>
+        <v>45163</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10968,7 +10968,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>3.6</v>
+        <v>1.9</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -11011,7 +11011,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 12148-2024</t>
+          <t>A 19500-2022</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -11025,10 +11025,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45377</v>
+        <v>44693</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11041,7 +11041,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -11084,7 +11084,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 19500-2022</t>
+          <t>A 44448-2023</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -11098,10 +11098,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>44693</v>
+        <v>45189</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11114,7 +11114,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -11157,7 +11157,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 4605-2025</t>
+          <t>A 57923-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -11171,10 +11171,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45687</v>
+        <v>45631</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11187,7 +11187,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.8</v>
+        <v>4.5</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -11230,7 +11230,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 29369-2026</t>
+          <t>A 31576-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11244,10 +11244,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46203</v>
+        <v>46224</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11260,7 +11260,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -11303,7 +11303,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 31720-2023</t>
+          <t>A 28264-2022</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11317,10 +11317,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45117</v>
+        <v>44746</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11333,7 +11333,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11376,7 +11376,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 16314-2024</t>
+          <t>A 36001-2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11390,10 +11390,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45407</v>
+        <v>46266</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11406,7 +11406,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11449,7 +11449,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 34514-2023</t>
+          <t>A 35912-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45140</v>
+        <v>46266</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11479,7 +11479,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>3.1</v>
+        <v>1.3</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11522,7 +11522,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 46613-2024</t>
+          <t>A 55545-2022</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11536,10 +11536,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45583</v>
+        <v>44887</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11552,7 +11552,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>6.2</v>
+        <v>4.4</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11595,7 +11595,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 23976-2024</t>
+          <t>A 37628-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11609,10 +11609,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45456</v>
+        <v>46276</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11624,8 +11624,13 @@
           <t>ÄNGELHOLM</t>
         </is>
       </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I130" t="n">
-        <v>0.6</v>
+        <v>4.5</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11668,7 +11673,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 40278-2023</t>
+          <t>A 34514-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11682,10 +11687,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45169</v>
+        <v>45140</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11698,7 +11703,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.1</v>
+        <v>3.1</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11741,7 +11746,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 7871-2025</t>
+          <t>A 26978-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11755,10 +11760,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45706</v>
+        <v>46185</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11771,7 +11776,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.1</v>
+        <v>7.7</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11814,7 +11819,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 31576-2026</t>
+          <t>A 26986-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11828,10 +11833,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46224</v>
+        <v>46185</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11844,7 +11849,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>0.6</v>
+        <v>3.5</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11887,7 +11892,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 32430-2023</t>
+          <t>A 1299-2024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11901,10 +11906,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45120</v>
+        <v>45303</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11917,7 +11922,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11960,7 +11965,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 36001-2026</t>
+          <t>A 35677-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11974,10 +11979,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46266</v>
+        <v>46265</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11990,7 +11995,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>0.8</v>
+        <v>3.1</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -12033,7 +12038,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 35912-2026</t>
+          <t>A 42105-2022</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -12047,10 +12052,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46266</v>
+        <v>44830</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12063,7 +12068,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -12106,7 +12111,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 29436-2024</t>
+          <t>A 15154-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -12120,10 +12125,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45483</v>
+        <v>45016</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12136,7 +12141,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -12179,7 +12184,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 58150-2024</t>
+          <t>A 19255-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -12193,10 +12198,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45632</v>
+        <v>46132</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12209,7 +12214,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -12252,7 +12257,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 28264-2022</t>
+          <t>A 19256-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12266,10 +12271,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>44746</v>
+        <v>46132</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12282,7 +12287,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -12325,7 +12330,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 31709-2023</t>
+          <t>A 7337-2024</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12339,10 +12344,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45117</v>
+        <v>45345</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12355,7 +12360,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -12398,7 +12403,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 19256-2026</t>
+          <t>A 49610-2024</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12412,10 +12417,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46132</v>
+        <v>45596</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12428,7 +12433,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>0.7</v>
+        <v>6.4</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12471,7 +12476,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 8665-2022</t>
+          <t>A 14400-2023</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12485,10 +12490,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>44613</v>
+        <v>45012</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12501,7 +12506,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12544,7 +12549,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 60-2024</t>
+          <t>A 4089-2024</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12558,10 +12563,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45293</v>
+        <v>45323</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12574,7 +12579,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12617,7 +12622,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 37628-2026</t>
+          <t>A 23676-2024</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12631,10 +12636,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46276</v>
+        <v>45454</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12646,13 +12651,8 @@
           <t>ÄNGELHOLM</t>
         </is>
       </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I144" t="n">
-        <v>4.5</v>
+        <v>0.9</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12695,7 +12695,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 607-2024</t>
+          <t>A 60-2024</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12709,10 +12709,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45299</v>
+        <v>45293</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12725,7 +12725,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12768,7 +12768,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 26986-2026</t>
+          <t>A 58150-2024</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12782,10 +12782,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46185</v>
+        <v>45632</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12798,7 +12798,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>3.5</v>
+        <v>0.5</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12841,7 +12841,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 49206-2024</t>
+          <t>A 4755-2024</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12855,10 +12855,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45595</v>
+        <v>45328</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12871,7 +12871,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12914,7 +12914,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 19503-2022</t>
+          <t>A 32430-2023</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12928,10 +12928,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>44693</v>
+        <v>45120</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12944,7 +12944,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>5.1</v>
+        <v>0.9</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12987,7 +12987,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 26978-2026</t>
+          <t>A 28496-2023</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -13001,10 +13001,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46185</v>
+        <v>45103</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13017,7 +13017,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>7.7</v>
+        <v>1.8</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -13060,7 +13060,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 57923-2024</t>
+          <t>A 4605-2025</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -13074,10 +13074,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45631</v>
+        <v>45687</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13090,7 +13090,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>4.5</v>
+        <v>0.8</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -13133,7 +13133,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 35677-2026</t>
+          <t>A 21488-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -13147,10 +13147,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46265</v>
+        <v>45061</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13163,7 +13163,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>3.1</v>
+        <v>1.1</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -13206,7 +13206,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 20635-2024</t>
+          <t>A 31908-2023</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -13220,10 +13220,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45436</v>
+        <v>45118</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13236,7 +13236,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>4.8</v>
+        <v>1.5</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -13279,7 +13279,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 23980-2024</t>
+          <t>A 7811-2023</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -13293,10 +13293,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45456</v>
+        <v>44973</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13309,7 +13309,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -13352,7 +13352,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 55748-2024</t>
+          <t>A 16314-2024</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -13366,10 +13366,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45623</v>
+        <v>45407</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13382,7 +13382,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -13425,7 +13425,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 48197-2024</t>
+          <t>A 46613-2024</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13439,10 +13439,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45590</v>
+        <v>45583</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13455,7 +13455,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>3.1</v>
+        <v>6.2</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13498,7 +13498,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 19255-2026</t>
+          <t>A 20635-2024</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13512,10 +13512,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46132</v>
+        <v>45436</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13528,7 +13528,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>1</v>
+        <v>4.8</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13571,7 +13571,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 55529-2024</t>
+          <t>A 23980-2024</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13585,10 +13585,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45622</v>
+        <v>45456</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13601,7 +13601,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13644,7 +13644,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 32020-2025</t>
+          <t>A 55748-2024</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13658,10 +13658,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45835</v>
+        <v>45623</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13674,7 +13674,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13717,7 +13717,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 13662-2025</t>
+          <t>A 48197-2024</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13731,10 +13731,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45736</v>
+        <v>45590</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13747,7 +13747,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>6.4</v>
+        <v>3.1</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13807,7 +13807,7 @@
         <v>45582</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13880,7 +13880,7 @@
         <v>45582</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13953,7 +13953,7 @@
         <v>45582</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14026,7 +14026,7 @@
         <v>45582</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14099,7 +14099,7 @@
         <v>44519</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14172,7 +14172,7 @@
         <v>45239</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14245,7 +14245,7 @@
         <v>45168</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14318,7 +14318,7 @@
         <v>44861</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14391,7 +14391,7 @@
         <v>45582</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>

--- a/Översikt ÄNGELHOLM.xlsx
+++ b/Översikt ÄNGELHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45099</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         <v>45931</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
         <v>45931</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>46106</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>44802</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>44560</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>44781</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
         <v>45835</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>44929</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         <v>44593</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>45106</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>45245</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>46038</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>46265</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>46265</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2337,7 +2337,7 @@
         <v>45664</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2449,7 +2449,7 @@
         <v>44864</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
         <v>45104</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>45118</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         <v>45707</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2878,7 +2878,7 @@
         <v>46041</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         <v>45210</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>45301</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>45763</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3314,7 +3314,7 @@
         <v>45474</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3424,7 +3424,7 @@
         <v>45841</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
         <v>45105</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
         <v>44553</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3754,7 +3754,7 @@
         <v>45359</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
         <v>45582</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>44839</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>44742</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4180,7 +4180,7 @@
         <v>44746</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4289,7 +4289,7 @@
         <v>45377</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4394,7 +4394,7 @@
         <v>45323</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4499,7 +4499,7 @@
         <v>45210</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
         <v>45582</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         <v>45462</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4814,7 +4814,7 @@
         <v>44498</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4919,7 +4919,7 @@
         <v>46188</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5024,7 +5024,7 @@
         <v>44839</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5129,7 +5129,7 @@
         <v>46265</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5238,7 +5238,7 @@
         <v>46224</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         <v>45084</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5448,7 +5448,7 @@
         <v>44862</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5553,7 +5553,7 @@
         <v>44880</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5626,7 +5626,7 @@
         <v>44839</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5699,7 +5699,7 @@
         <v>44725</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5772,7 +5772,7 @@
         <v>44840</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5845,7 +5845,7 @@
         <v>44498</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5918,7 +5918,7 @@
         <v>44477</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5991,7 +5991,7 @@
         <v>44657</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
         <v>44634</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6137,7 +6137,7 @@
         <v>44802</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6210,7 +6210,7 @@
         <v>44802</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
         <v>44827</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6356,7 +6356,7 @@
         <v>44480</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6429,7 +6429,7 @@
         <v>44634</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         <v>45483</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6575,7 +6575,7 @@
         <v>45713</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6648,7 +6648,7 @@
         <v>45377</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6721,7 +6721,7 @@
         <v>45715</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6794,7 +6794,7 @@
         <v>44879</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6867,7 +6867,7 @@
         <v>45097</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6940,7 +6940,7 @@
         <v>45281</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7013,7 +7013,7 @@
         <v>45117</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7086,7 +7086,7 @@
         <v>45463</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7159,7 +7159,7 @@
         <v>45502</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7232,7 +7232,7 @@
         <v>45299</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         <v>45236</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7378,7 +7378,7 @@
         <v>45895</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7451,7 +7451,7 @@
         <v>44887</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7524,7 +7524,7 @@
         <v>45456</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7597,7 +7597,7 @@
         <v>45908</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7670,7 +7670,7 @@
         <v>45097</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7743,7 +7743,7 @@
         <v>46069</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7816,7 +7816,7 @@
         <v>45099</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7889,7 +7889,7 @@
         <v>45022</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7962,7 +7962,7 @@
         <v>44693</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8035,7 +8035,7 @@
         <v>45583</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8108,7 +8108,7 @@
         <v>45595</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8181,7 +8181,7 @@
         <v>45954</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8254,7 +8254,7 @@
         <v>45115</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8327,7 +8327,7 @@
         <v>46072</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8400,7 +8400,7 @@
         <v>45972</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8473,7 +8473,7 @@
         <v>46134</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8546,7 +8546,7 @@
         <v>45981</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8619,7 +8619,7 @@
         <v>45622</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8692,7 +8692,7 @@
         <v>44720</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8765,7 +8765,7 @@
         <v>45705</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8838,7 +8838,7 @@
         <v>45120</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8911,7 +8911,7 @@
         <v>44900</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8984,7 +8984,7 @@
         <v>45708</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9057,7 +9057,7 @@
         <v>45169</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9130,7 +9130,7 @@
         <v>44553</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         <v>45670</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9276,7 +9276,7 @@
         <v>45461</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         <v>45706</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9422,7 +9422,7 @@
         <v>45735</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9495,7 +9495,7 @@
         <v>45700</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         <v>45835</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9641,7 +9641,7 @@
         <v>44900</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9714,7 +9714,7 @@
         <v>45313</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9787,7 +9787,7 @@
         <v>45115</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9860,7 +9860,7 @@
         <v>45736</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9933,7 +9933,7 @@
         <v>45581</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10006,7 +10006,7 @@
         <v>45994</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10079,7 +10079,7 @@
         <v>45912</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10152,7 +10152,7 @@
         <v>44973</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10225,7 +10225,7 @@
         <v>46093</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10298,7 +10298,7 @@
         <v>44613</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10371,7 +10371,7 @@
         <v>46188</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10444,7 +10444,7 @@
         <v>45763</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10517,7 +10517,7 @@
         <v>45117</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10590,7 +10590,7 @@
         <v>45075</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10663,7 +10663,7 @@
         <v>45210</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10736,7 +10736,7 @@
         <v>45169</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10809,7 +10809,7 @@
         <v>46203</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10882,7 +10882,7 @@
         <v>45118</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10955,7 +10955,7 @@
         <v>45163</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11028,7 +11028,7 @@
         <v>44693</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11101,7 +11101,7 @@
         <v>45189</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11174,7 +11174,7 @@
         <v>45631</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11247,7 +11247,7 @@
         <v>46224</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11320,7 +11320,7 @@
         <v>44746</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11393,7 +11393,7 @@
         <v>46266</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11466,7 +11466,7 @@
         <v>46266</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11539,7 +11539,7 @@
         <v>44887</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11612,7 +11612,7 @@
         <v>46276</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11690,7 +11690,7 @@
         <v>45140</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11763,7 +11763,7 @@
         <v>46185</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11836,7 +11836,7 @@
         <v>46185</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11909,7 +11909,7 @@
         <v>45303</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11982,7 +11982,7 @@
         <v>46265</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12055,7 +12055,7 @@
         <v>44830</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12128,7 +12128,7 @@
         <v>45016</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12201,7 +12201,7 @@
         <v>46132</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12274,7 +12274,7 @@
         <v>46132</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12347,7 +12347,7 @@
         <v>45345</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12420,7 +12420,7 @@
         <v>45596</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12493,7 +12493,7 @@
         <v>45012</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12566,7 +12566,7 @@
         <v>45323</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12639,7 +12639,7 @@
         <v>45454</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12712,7 +12712,7 @@
         <v>45293</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12785,7 +12785,7 @@
         <v>45632</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12858,7 +12858,7 @@
         <v>45328</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12931,7 +12931,7 @@
         <v>45120</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13004,7 +13004,7 @@
         <v>45103</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13077,7 +13077,7 @@
         <v>45687</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13150,7 +13150,7 @@
         <v>45061</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13223,7 +13223,7 @@
         <v>45118</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13296,7 +13296,7 @@
         <v>44973</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13369,7 +13369,7 @@
         <v>45407</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13442,7 +13442,7 @@
         <v>45583</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13515,7 +13515,7 @@
         <v>45436</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13588,7 +13588,7 @@
         <v>45456</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13661,7 +13661,7 @@
         <v>45623</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13734,7 +13734,7 @@
         <v>45590</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13807,7 +13807,7 @@
         <v>45582</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13880,7 +13880,7 @@
         <v>45582</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13953,7 +13953,7 @@
         <v>45582</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14026,7 +14026,7 @@
         <v>45582</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14099,7 +14099,7 @@
         <v>44519</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14172,7 +14172,7 @@
         <v>45239</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14245,7 +14245,7 @@
         <v>45168</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14318,7 +14318,7 @@
         <v>44861</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14391,7 +14391,7 @@
         <v>45582</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>

--- a/Översikt ÄNGELHOLM.xlsx
+++ b/Översikt ÄNGELHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45099</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         <v>45931</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
         <v>45931</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>46106</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>44802</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>44560</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>44781</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
         <v>45835</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>44929</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         <v>44593</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>45106</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>45245</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>46038</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>46265</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>46265</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2337,7 +2337,7 @@
         <v>45664</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2449,7 +2449,7 @@
         <v>44864</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2557,7 +2557,7 @@
         <v>45104</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>45118</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
         <v>45707</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2878,7 +2878,7 @@
         <v>46041</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         <v>45210</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>45301</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>45763</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3314,7 +3314,7 @@
         <v>45474</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3424,7 +3424,7 @@
         <v>45841</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
         <v>45105</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
         <v>44553</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3754,7 +3754,7 @@
         <v>45359</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
         <v>45582</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>44839</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>44742</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4180,7 +4180,7 @@
         <v>44746</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4289,7 +4289,7 @@
         <v>45377</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4394,7 +4394,7 @@
         <v>45323</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4499,7 +4499,7 @@
         <v>45210</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4604,7 +4604,7 @@
         <v>45582</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         <v>45462</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4814,7 +4814,7 @@
         <v>44498</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4919,7 +4919,7 @@
         <v>46188</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5024,7 +5024,7 @@
         <v>44839</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5129,7 +5129,7 @@
         <v>46265</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5238,7 +5238,7 @@
         <v>46224</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         <v>45084</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5448,7 +5448,7 @@
         <v>44862</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5553,7 +5553,7 @@
         <v>44880</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5626,7 +5626,7 @@
         <v>44839</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5699,7 +5699,7 @@
         <v>44725</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5772,7 +5772,7 @@
         <v>44840</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5845,7 +5845,7 @@
         <v>44498</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5918,7 +5918,7 @@
         <v>44477</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5991,7 +5991,7 @@
         <v>44657</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
         <v>44634</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6137,7 +6137,7 @@
         <v>44802</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6210,7 +6210,7 @@
         <v>44802</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
         <v>44827</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6356,7 +6356,7 @@
         <v>44480</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6429,7 +6429,7 @@
         <v>44634</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         <v>45483</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6575,7 +6575,7 @@
         <v>45713</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6648,7 +6648,7 @@
         <v>45377</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6721,7 +6721,7 @@
         <v>45715</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6794,7 +6794,7 @@
         <v>44879</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6867,7 +6867,7 @@
         <v>45097</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6940,7 +6940,7 @@
         <v>45281</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7013,7 +7013,7 @@
         <v>45117</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7086,7 +7086,7 @@
         <v>45463</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7159,7 +7159,7 @@
         <v>45502</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7232,7 +7232,7 @@
         <v>45299</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         <v>45236</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7378,7 +7378,7 @@
         <v>45895</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7451,7 +7451,7 @@
         <v>44887</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7524,7 +7524,7 @@
         <v>45456</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7597,7 +7597,7 @@
         <v>45908</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7670,7 +7670,7 @@
         <v>45097</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7743,7 +7743,7 @@
         <v>46069</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7816,7 +7816,7 @@
         <v>45099</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7889,7 +7889,7 @@
         <v>45022</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7962,7 +7962,7 @@
         <v>44693</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8035,7 +8035,7 @@
         <v>45583</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8108,7 +8108,7 @@
         <v>45595</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8181,7 +8181,7 @@
         <v>45954</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8254,7 +8254,7 @@
         <v>45115</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8327,7 +8327,7 @@
         <v>46072</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8400,7 +8400,7 @@
         <v>45972</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8473,7 +8473,7 @@
         <v>46134</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8546,7 +8546,7 @@
         <v>45981</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8619,7 +8619,7 @@
         <v>45622</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8692,7 +8692,7 @@
         <v>44720</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8765,7 +8765,7 @@
         <v>45705</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8838,7 +8838,7 @@
         <v>45120</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8911,7 +8911,7 @@
         <v>44900</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8984,7 +8984,7 @@
         <v>45708</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9057,7 +9057,7 @@
         <v>45169</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9130,7 +9130,7 @@
         <v>44553</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         <v>45670</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9276,7 +9276,7 @@
         <v>45461</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         <v>45706</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9422,7 +9422,7 @@
         <v>45735</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9495,7 +9495,7 @@
         <v>45700</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         <v>45835</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9641,7 +9641,7 @@
         <v>44900</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9714,7 +9714,7 @@
         <v>45313</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9787,7 +9787,7 @@
         <v>45115</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9860,7 +9860,7 @@
         <v>45736</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9933,7 +9933,7 @@
         <v>45581</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10006,7 +10006,7 @@
         <v>45994</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10079,7 +10079,7 @@
         <v>45912</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10152,7 +10152,7 @@
         <v>44973</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10225,7 +10225,7 @@
         <v>46093</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10298,7 +10298,7 @@
         <v>44613</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10371,7 +10371,7 @@
         <v>46188</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10444,7 +10444,7 @@
         <v>45763</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10517,7 +10517,7 @@
         <v>45117</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10590,7 +10590,7 @@
         <v>45075</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10663,7 +10663,7 @@
         <v>45210</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10736,7 +10736,7 @@
         <v>45169</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10809,7 +10809,7 @@
         <v>46203</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10882,7 +10882,7 @@
         <v>45118</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10955,7 +10955,7 @@
         <v>45163</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11028,7 +11028,7 @@
         <v>44693</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11101,7 +11101,7 @@
         <v>45189</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11174,7 +11174,7 @@
         <v>45631</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11247,7 +11247,7 @@
         <v>46224</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11320,7 +11320,7 @@
         <v>44746</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11393,7 +11393,7 @@
         <v>46266</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11466,7 +11466,7 @@
         <v>46266</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11539,7 +11539,7 @@
         <v>44887</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11612,7 +11612,7 @@
         <v>46276</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11690,7 +11690,7 @@
         <v>45140</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11763,7 +11763,7 @@
         <v>46185</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11836,7 +11836,7 @@
         <v>46185</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11909,7 +11909,7 @@
         <v>45303</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11982,7 +11982,7 @@
         <v>46265</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12055,7 +12055,7 @@
         <v>44830</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12128,7 +12128,7 @@
         <v>45016</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12201,7 +12201,7 @@
         <v>46132</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12274,7 +12274,7 @@
         <v>46132</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12347,7 +12347,7 @@
         <v>45345</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12420,7 +12420,7 @@
         <v>45596</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12493,7 +12493,7 @@
         <v>45012</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12566,7 +12566,7 @@
         <v>45323</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12639,7 +12639,7 @@
         <v>45454</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12712,7 +12712,7 @@
         <v>45293</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12785,7 +12785,7 @@
         <v>45632</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12858,7 +12858,7 @@
         <v>45328</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12931,7 +12931,7 @@
         <v>45120</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13004,7 +13004,7 @@
         <v>45103</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13077,7 +13077,7 @@
         <v>45687</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13150,7 +13150,7 @@
         <v>45061</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13223,7 +13223,7 @@
         <v>45118</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13296,7 +13296,7 @@
         <v>44973</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13369,7 +13369,7 @@
         <v>45407</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13442,7 +13442,7 @@
         <v>45583</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13515,7 +13515,7 @@
         <v>45436</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13588,7 +13588,7 @@
         <v>45456</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13661,7 +13661,7 @@
         <v>45623</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13734,7 +13734,7 @@
         <v>45590</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13807,7 +13807,7 @@
         <v>45582</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13880,7 +13880,7 @@
         <v>45582</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13953,7 +13953,7 @@
         <v>45582</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14026,7 +14026,7 @@
         <v>45582</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14099,7 +14099,7 @@
         <v>44519</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14172,7 +14172,7 @@
         <v>45239</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14245,7 +14245,7 @@
         <v>45168</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14318,7 +14318,7 @@
         <v>44861</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14391,7 +14391,7 @@
         <v>45582</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>

--- a/Översikt ÄNGELHOLM.xlsx
+++ b/Översikt ÄNGELHOLM.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE168"/>
+  <dimension ref="A1:AE169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45099</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         <v>45931</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
         <v>45931</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>46106</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>44802</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 74502-2021</t>
+          <t>A 32268-2022</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1204,10 +1204,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44560</v>
+        <v>44781</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1220,17 +1220,17 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>5.6</v>
+        <v>8.6</v>
       </c>
       <c r="J7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K7" t="n">
+        <v>5</v>
+      </c>
+      <c r="L7" t="n">
         <v>1</v>
       </c>
-      <c r="L7" t="n">
-        <v>3</v>
-      </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
@@ -1244,7 +1244,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1253,12 +1253,124 @@
         <v>8</v>
       </c>
       <c r="T7" t="n">
+        <v>14</v>
+      </c>
+      <c r="U7" t="n">
+        <v>14</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Bokvårtlav
+Blåmossa
+Dvärghäxört
+Skuggsprötmossa
+Trubbfjädermossa
+Västlig hakmossa
+Vanlig groda
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 32268-2022 artfynd.xlsx", "A 32268-2022")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 32268-2022 karta.png", "A 32268-2022")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 32268-2022 georefererad karta.tif", "A 32268-2022")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 32268-2022 FSC-klagomål.docx", "A 32268-2022")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 32268-2022 FSC-klagomål mail.docx", "A 32268-2022")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 32268-2022 tillsynsbegäran.docx", "A 32268-2022")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 32268-2022 tillsynsbegäran mail.docx", "A 32268-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 74502-2021</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>44560</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J8" t="n">
+        <v>6</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>3</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>8</v>
+      </c>
+      <c r="T8" t="n">
         <v>9</v>
       </c>
-      <c r="U7" t="n">
+      <c r="U8" t="n">
         <v>9</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Entita
 Grönsångare
@@ -1270,148 +1382,36 @@
 Skogsduva</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 74502-2021 artfynd.xlsx", "A 74502-2021")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 74502-2021 karta.png", "A 74502-2021")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 74502-2021 georefererad karta.tif", "A 74502-2021")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 74502-2021 FSC-klagomål.docx", "A 74502-2021")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 74502-2021 FSC-klagomål mail.docx", "A 74502-2021")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 74502-2021 tillsynsbegäran.docx", "A 74502-2021")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 74502-2021 tillsynsbegäran mail.docx", "A 74502-2021")</f>
         <v/>
       </c>
-      <c r="AE7">
+      <c r="AE8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 74502-2021 prioriterade fågelarter.docx", "A 74502-2021")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 32268-2022</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>44781</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="J8" t="n">
-        <v>2</v>
-      </c>
-      <c r="K8" t="n">
-        <v>5</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>8</v>
-      </c>
-      <c r="T8" t="n">
-        <v>14</v>
-      </c>
-      <c r="U8" t="n">
-        <v>14</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Bokvårtlav
-Blåmossa
-Dvärghäxört
-Skuggsprötmossa
-Trubbfjädermossa
-Västlig hakmossa
-Vanlig groda
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 32268-2022 artfynd.xlsx", "A 32268-2022")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 32268-2022 karta.png", "A 32268-2022")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 32268-2022 georefererad karta.tif", "A 32268-2022")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 32268-2022 FSC-klagomål.docx", "A 32268-2022")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 32268-2022 FSC-klagomål mail.docx", "A 32268-2022")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 32268-2022 tillsynsbegäran.docx", "A 32268-2022")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 32268-2022 tillsynsbegäran mail.docx", "A 32268-2022")</f>
         <v/>
       </c>
     </row>
@@ -1435,7 +1435,7 @@
         <v>45835</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 308-2023</t>
+          <t>A 5046-2022</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1547,10 +1547,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44929</v>
+        <v>44593</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1563,19 +1563,19 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.8</v>
+        <v>3</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K10" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -1587,10 +1587,10 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" t="n">
         <v>1</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>6</v>
@@ -1599,9 +1599,123 @@
         <v>7</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Grönfink
+Gulsparv
+Kråka
+Kungsfågel
+Sävsparv
+Trädlärka</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 5046-2022 artfynd.xlsx", "A 5046-2022")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 5046-2022 karta.png", "A 5046-2022")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 5046-2022 georefererad karta.tif", "A 5046-2022")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 5046-2022 FSC-klagomål.docx", "A 5046-2022")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 5046-2022 FSC-klagomål mail.docx", "A 5046-2022")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 5046-2022 tillsynsbegäran.docx", "A 5046-2022")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 5046-2022 tillsynsbegäran mail.docx", "A 5046-2022")</f>
+        <v/>
+      </c>
+      <c r="AE10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 5046-2022 prioriterade fågelarter.docx", "A 5046-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 308-2023</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>44929</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>5</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>6</v>
+      </c>
+      <c r="T11" t="n">
+        <v>7</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Bokvårtlav
 Dvärghäxört
@@ -1611,146 +1725,32 @@
 Stor knopplav</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 308-2023 artfynd.xlsx", "A 308-2023")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 308-2023 karta.png", "A 308-2023")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 308-2023 georefererad karta.tif", "A 308-2023")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 308-2023 FSC-klagomål.docx", "A 308-2023")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 308-2023 FSC-klagomål mail.docx", "A 308-2023")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 308-2023 tillsynsbegäran.docx", "A 308-2023")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 308-2023 tillsynsbegäran mail.docx", "A 308-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 5046-2022</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>44593</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>3</v>
-      </c>
-      <c r="J11" t="n">
-        <v>6</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
-      <c r="S11" t="n">
-        <v>6</v>
-      </c>
-      <c r="T11" t="n">
-        <v>7</v>
-      </c>
-      <c r="U11" t="n">
-        <v>6</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Grönfink
-Gulsparv
-Kråka
-Kungsfågel
-Sävsparv
-Trädlärka</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 5046-2022 artfynd.xlsx", "A 5046-2022")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 5046-2022 karta.png", "A 5046-2022")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 5046-2022 georefererad karta.tif", "A 5046-2022")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 5046-2022 FSC-klagomål.docx", "A 5046-2022")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 5046-2022 FSC-klagomål mail.docx", "A 5046-2022")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 5046-2022 tillsynsbegäran.docx", "A 5046-2022")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 5046-2022 tillsynsbegäran mail.docx", "A 5046-2022")</f>
-        <v/>
-      </c>
-      <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 5046-2022 prioriterade fågelarter.docx", "A 5046-2022")</f>
         <v/>
       </c>
     </row>
@@ -1774,7 +1774,7 @@
         <v>45106</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>45245</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>46038</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 35675-2026</t>
+          <t>A 35680-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2111,7 +2111,7 @@
         <v>46265</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2124,16 +2124,16 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>8.9</v>
+        <v>2.9</v>
       </c>
       <c r="J15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M15" t="n">
         <v>1</v>
@@ -2148,7 +2148,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R15" t="n">
         <v>1</v>
@@ -2157,12 +2157,125 @@
         <v>5</v>
       </c>
       <c r="T15" t="n">
+        <v>7</v>
+      </c>
+      <c r="U15" t="n">
+        <v>7</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Vedlavklubba
+Entita
+Kandelabersvamp
+Blåmossa
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 35680-2026 artfynd.xlsx", "A 35680-2026")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 35680-2026 karta.png", "A 35680-2026")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 35680-2026 georefererad karta.tif", "A 35680-2026")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 35680-2026 FSC-klagomål.docx", "A 35680-2026")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 35680-2026 FSC-klagomål mail.docx", "A 35680-2026")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 35680-2026 tillsynsbegäran.docx", "A 35680-2026")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 35680-2026 tillsynsbegäran mail.docx", "A 35680-2026")</f>
+        <v/>
+      </c>
+      <c r="AE15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 35680-2026 prioriterade fågelarter.docx", "A 35680-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 35675-2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="J16" t="n">
+        <v>4</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="n">
         <v>10</v>
       </c>
-      <c r="U15" t="n">
+      <c r="U16" t="n">
         <v>9</v>
       </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Lappuggla
 Entita
@@ -2171,149 +2284,36 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 35675-2026 artfynd.xlsx", "A 35675-2026")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 35675-2026 karta.png", "A 35675-2026")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 35675-2026 georefererad karta.tif", "A 35675-2026")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 35675-2026 FSC-klagomål.docx", "A 35675-2026")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 35675-2026 FSC-klagomål mail.docx", "A 35675-2026")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 35675-2026 tillsynsbegäran.docx", "A 35675-2026")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 35675-2026 tillsynsbegäran mail.docx", "A 35675-2026")</f>
         <v/>
       </c>
-      <c r="AE15">
+      <c r="AE16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 35675-2026 prioriterade fågelarter.docx", "A 35675-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 35680-2026</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J16" t="n">
-        <v>2</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" t="n">
-        <v>2</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>3</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1</v>
-      </c>
-      <c r="S16" t="n">
-        <v>5</v>
-      </c>
-      <c r="T16" t="n">
-        <v>7</v>
-      </c>
-      <c r="U16" t="n">
-        <v>7</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Vedlavklubba
-Entita
-Kandelabersvamp
-Blåmossa
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 35680-2026 artfynd.xlsx", "A 35680-2026")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 35680-2026 karta.png", "A 35680-2026")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 35680-2026 georefererad karta.tif", "A 35680-2026")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 35680-2026 FSC-klagomål.docx", "A 35680-2026")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 35680-2026 FSC-klagomål mail.docx", "A 35680-2026")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 35680-2026 tillsynsbegäran.docx", "A 35680-2026")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 35680-2026 tillsynsbegäran mail.docx", "A 35680-2026")</f>
-        <v/>
-      </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 35680-2026 prioriterade fågelarter.docx", "A 35680-2026")</f>
         <v/>
       </c>
     </row>
@@ -2337,7 +2337,7 @@
         <v>45664</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2449,7 +2449,7 @@
         <v>44864</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 28874-2023</t>
+          <t>A 905-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2554,10 +2554,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45104</v>
+        <v>45301</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2570,616 +2570,616 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>9</v>
+        <v>4.9</v>
       </c>
       <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
         <v>1</v>
       </c>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
         <v>2</v>
       </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S19" t="n">
         <v>3</v>
       </c>
       <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Igelkott
+Desmeknopp
+Myskmadra</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 905-2024 artfynd.xlsx", "A 905-2024")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 905-2024 karta.png", "A 905-2024")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 905-2024 georefererad karta.tif", "A 905-2024")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 905-2024 FSC-klagomål.docx", "A 905-2024")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 905-2024 FSC-klagomål mail.docx", "A 905-2024")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 905-2024 tillsynsbegäran.docx", "A 905-2024")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 905-2024 tillsynsbegäran mail.docx", "A 905-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 28874-2023</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>45104</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>9</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3</v>
+      </c>
+      <c r="T20" t="n">
         <v>5</v>
       </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>Blåmossa
 Stubbspretmossa
 Revlummer</t>
         </is>
       </c>
-      <c r="W19">
+      <c r="W20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 28874-2023 artfynd.xlsx", "A 28874-2023")</f>
         <v/>
       </c>
-      <c r="X19">
+      <c r="X20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 28874-2023 karta.png", "A 28874-2023")</f>
         <v/>
       </c>
-      <c r="Y19">
+      <c r="Y20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 28874-2023 georefererad karta.tif", "A 28874-2023")</f>
         <v/>
       </c>
-      <c r="AA19">
+      <c r="AA20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 28874-2023 FSC-klagomål.docx", "A 28874-2023")</f>
         <v/>
       </c>
-      <c r="AB19">
+      <c r="AB20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 28874-2023 FSC-klagomål mail.docx", "A 28874-2023")</f>
         <v/>
       </c>
-      <c r="AC19">
+      <c r="AC20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 28874-2023 tillsynsbegäran.docx", "A 28874-2023")</f>
         <v/>
       </c>
-      <c r="AD19">
+      <c r="AD20">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 28874-2023 tillsynsbegäran mail.docx", "A 28874-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 8065-2025</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>45707</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Småvänderot
+Gullpudra
+Svinrot</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 8065-2025 artfynd.xlsx", "A 8065-2025")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 8065-2025 karta.png", "A 8065-2025")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 8065-2025 georefererad karta.tif", "A 8065-2025")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 8065-2025 FSC-klagomål.docx", "A 8065-2025")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 8065-2025 FSC-klagomål mail.docx", "A 8065-2025")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 8065-2025 tillsynsbegäran.docx", "A 8065-2025")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 8065-2025 tillsynsbegäran mail.docx", "A 8065-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 50684-2023</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>45210</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>1</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>Skogsalm
+Kopparödla
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 50684-2023 artfynd.xlsx", "A 50684-2023")</f>
+        <v/>
+      </c>
+      <c r="X22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 50684-2023 karta.png", "A 50684-2023")</f>
+        <v/>
+      </c>
+      <c r="Y22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 50684-2023 georefererad karta.tif", "A 50684-2023")</f>
+        <v/>
+      </c>
+      <c r="AA22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 50684-2023 FSC-klagomål.docx", "A 50684-2023")</f>
+        <v/>
+      </c>
+      <c r="AB22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 50684-2023 FSC-klagomål mail.docx", "A 50684-2023")</f>
+        <v/>
+      </c>
+      <c r="AC22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 50684-2023 tillsynsbegäran.docx", "A 50684-2023")</f>
+        <v/>
+      </c>
+      <c r="AD22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 50684-2023 tillsynsbegäran mail.docx", "A 50684-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
         <is>
           <t>A 31907-2023</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
         <v>45118</v>
       </c>
-      <c r="E20" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
+      <c r="E23" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
         <v>5.3</v>
       </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
         <v>2</v>
       </c>
-      <c r="L20" t="n">
+      <c r="L23" t="n">
         <v>1</v>
       </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
         <v>1</v>
       </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
         <v>3</v>
       </c>
-      <c r="T20" t="n">
+      <c r="T23" t="n">
         <v>3</v>
       </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>Bokvårtlav
 Platt fjädermossa
 Stubbspretmossa</t>
         </is>
       </c>
-      <c r="W20">
+      <c r="W23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 31907-2023 artfynd.xlsx", "A 31907-2023")</f>
         <v/>
       </c>
-      <c r="X20">
+      <c r="X23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 31907-2023 karta.png", "A 31907-2023")</f>
         <v/>
       </c>
-      <c r="Y20">
+      <c r="Y23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 31907-2023 georefererad karta.tif", "A 31907-2023")</f>
         <v/>
       </c>
-      <c r="AA20">
+      <c r="AA23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 31907-2023 FSC-klagomål.docx", "A 31907-2023")</f>
         <v/>
       </c>
-      <c r="AB20">
+      <c r="AB23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 31907-2023 FSC-klagomål mail.docx", "A 31907-2023")</f>
         <v/>
       </c>
-      <c r="AC20">
+      <c r="AC23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 31907-2023 tillsynsbegäran.docx", "A 31907-2023")</f>
         <v/>
       </c>
-      <c r="AD20">
+      <c r="AD23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 31907-2023 tillsynsbegäran mail.docx", "A 31907-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 8065-2025</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>45707</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>A 3317-2026</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="n">
+        <v>46041</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
         <v>2</v>
       </c>
-      <c r="M21" t="n">
-        <v>1</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
         <v>3</v>
       </c>
-      <c r="R21" t="n">
-        <v>1</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3</v>
-      </c>
-      <c r="T21" t="n">
-        <v>3</v>
-      </c>
-      <c r="U21" t="n">
-        <v>2</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Småvänderot
-Gullpudra
-Svinrot</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 8065-2025 artfynd.xlsx", "A 8065-2025")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 8065-2025 karta.png", "A 8065-2025")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 8065-2025 georefererad karta.tif", "A 8065-2025")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 8065-2025 FSC-klagomål.docx", "A 8065-2025")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 8065-2025 FSC-klagomål mail.docx", "A 8065-2025")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 8065-2025 tillsynsbegäran.docx", "A 8065-2025")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 8065-2025 tillsynsbegäran mail.docx", "A 8065-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 3317-2026</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>46041</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J22" t="n">
-        <v>3</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>2</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>2</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3</v>
-      </c>
-      <c r="T22" t="n">
+      <c r="T24" t="n">
         <v>6</v>
       </c>
-      <c r="U22" t="n">
+      <c r="U24" t="n">
         <v>6</v>
       </c>
-      <c r="V22" s="2" t="inlineStr">
+      <c r="V24" s="2" t="inlineStr">
         <is>
           <t>Entita
 Mindre hackspett
 Gröngöling</t>
         </is>
       </c>
-      <c r="W22">
+      <c r="W24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 3317-2026 artfynd.xlsx", "A 3317-2026")</f>
         <v/>
       </c>
-      <c r="X22">
+      <c r="X24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 3317-2026 karta.png", "A 3317-2026")</f>
         <v/>
       </c>
-      <c r="Y22">
+      <c r="Y24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 3317-2026 georefererad karta.tif", "A 3317-2026")</f>
         <v/>
       </c>
-      <c r="AA22">
+      <c r="AA24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 3317-2026 FSC-klagomål.docx", "A 3317-2026")</f>
         <v/>
       </c>
-      <c r="AB22">
+      <c r="AB24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 3317-2026 FSC-klagomål mail.docx", "A 3317-2026")</f>
         <v/>
       </c>
-      <c r="AC22">
+      <c r="AC24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 3317-2026 tillsynsbegäran.docx", "A 3317-2026")</f>
         <v/>
       </c>
-      <c r="AD22">
+      <c r="AD24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 3317-2026 tillsynsbegäran mail.docx", "A 3317-2026")</f>
         <v/>
       </c>
-      <c r="AE22">
+      <c r="AE24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 3317-2026 prioriterade fågelarter.docx", "A 3317-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>A 50684-2023</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>45210</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J23" t="n">
-        <v>2</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>1</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3</v>
-      </c>
-      <c r="T23" t="n">
-        <v>3</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>Skogsalm
-Kopparödla
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 50684-2023 artfynd.xlsx", "A 50684-2023")</f>
-        <v/>
-      </c>
-      <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 50684-2023 karta.png", "A 50684-2023")</f>
-        <v/>
-      </c>
-      <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 50684-2023 georefererad karta.tif", "A 50684-2023")</f>
-        <v/>
-      </c>
-      <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 50684-2023 FSC-klagomål.docx", "A 50684-2023")</f>
-        <v/>
-      </c>
-      <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 50684-2023 FSC-klagomål mail.docx", "A 50684-2023")</f>
-        <v/>
-      </c>
-      <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 50684-2023 tillsynsbegäran.docx", "A 50684-2023")</f>
-        <v/>
-      </c>
-      <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 50684-2023 tillsynsbegäran mail.docx", "A 50684-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>A 905-2024</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="n">
-        <v>45301</v>
-      </c>
-      <c r="E24" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>1</v>
-      </c>
-      <c r="L24" t="n">
-        <v>1</v>
-      </c>
-      <c r="M24" t="n">
-        <v>1</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>2</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3</v>
-      </c>
-      <c r="T24" t="n">
-        <v>3</v>
-      </c>
-      <c r="U24" t="n">
-        <v>2</v>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>Igelkott
-Desmeknopp
-Myskmadra</t>
-        </is>
-      </c>
-      <c r="W24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 905-2024 artfynd.xlsx", "A 905-2024")</f>
-        <v/>
-      </c>
-      <c r="X24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 905-2024 karta.png", "A 905-2024")</f>
-        <v/>
-      </c>
-      <c r="Y24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 905-2024 georefererad karta.tif", "A 905-2024")</f>
-        <v/>
-      </c>
-      <c r="AA24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 905-2024 FSC-klagomål.docx", "A 905-2024")</f>
-        <v/>
-      </c>
-      <c r="AB24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 905-2024 FSC-klagomål mail.docx", "A 905-2024")</f>
-        <v/>
-      </c>
-      <c r="AC24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 905-2024 tillsynsbegäran.docx", "A 905-2024")</f>
-        <v/>
-      </c>
-      <c r="AD24">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 905-2024 tillsynsbegäran mail.docx", "A 905-2024")</f>
         <v/>
       </c>
     </row>
@@ -3203,7 +3203,7 @@
         <v>45763</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3314,7 +3314,7 @@
         <v>45474</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3424,7 +3424,7 @@
         <v>45841</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
         <v>45105</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
         <v>44553</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3754,7 +3754,7 @@
         <v>45359</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
         <v>45582</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>44839</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>44742</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4180,7 +4180,7 @@
         <v>44746</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 12150-2024</t>
+          <t>A 44062-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4286,10 +4286,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45377</v>
+        <v>44839</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4302,19 +4302,19 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -4326,10 +4326,10 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4342,42 +4342,42 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 12150-2024 artfynd.xlsx", "A 12150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 44062-2022 artfynd.xlsx", "A 44062-2022")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 12150-2024 karta.png", "A 12150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 44062-2022 karta.png", "A 44062-2022")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 12150-2024 georefererad karta.tif", "A 12150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 44062-2022 georefererad karta.tif", "A 44062-2022")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 12150-2024 FSC-klagomål.docx", "A 12150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 44062-2022 FSC-klagomål.docx", "A 44062-2022")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 12150-2024 FSC-klagomål mail.docx", "A 12150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 44062-2022 FSC-klagomål mail.docx", "A 44062-2022")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 12150-2024 tillsynsbegäran.docx", "A 12150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 44062-2022 tillsynsbegäran.docx", "A 44062-2022")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 12150-2024 tillsynsbegäran mail.docx", "A 12150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 44062-2022 tillsynsbegäran mail.docx", "A 44062-2022")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 4088-2024</t>
+          <t>A 46487-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4391,10 +4391,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45323</v>
+        <v>45582</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4407,16 +4407,16 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>3.8</v>
+        <v>5.8</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -4443,46 +4443,46 @@
         <v>1</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>Flikbålmossa</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 4088-2024 artfynd.xlsx", "A 4088-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 46487-2024 artfynd.xlsx", "A 46487-2024")</f>
         <v/>
       </c>
       <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 4088-2024 karta.png", "A 4088-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 46487-2024 karta.png", "A 46487-2024")</f>
         <v/>
       </c>
       <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 4088-2024 georefererad karta.tif", "A 4088-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 46487-2024 georefererad karta.tif", "A 46487-2024")</f>
         <v/>
       </c>
       <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 4088-2024 FSC-klagomål.docx", "A 4088-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 46487-2024 FSC-klagomål.docx", "A 46487-2024")</f>
         <v/>
       </c>
       <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 4088-2024 FSC-klagomål mail.docx", "A 4088-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 46487-2024 FSC-klagomål mail.docx", "A 46487-2024")</f>
         <v/>
       </c>
       <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 4088-2024 tillsynsbegäran.docx", "A 4088-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 46487-2024 tillsynsbegäran.docx", "A 46487-2024")</f>
         <v/>
       </c>
       <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 4088-2024 tillsynsbegäran mail.docx", "A 4088-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 46487-2024 tillsynsbegäran mail.docx", "A 46487-2024")</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 50642-2023</t>
+          <t>A 4088-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4496,10 +4496,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45210</v>
+        <v>45323</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4512,17 +4512,17 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.8</v>
+        <v>3.8</v>
       </c>
       <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
         <v>1</v>
       </c>
-      <c r="K37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" t="n">
-        <v>0</v>
-      </c>
       <c r="M37" t="n">
         <v>0</v>
       </c>
@@ -4536,7 +4536,7 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
@@ -4552,42 +4552,42 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Flikbålmossa</t>
         </is>
       </c>
       <c r="W37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 50642-2023 artfynd.xlsx", "A 50642-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 4088-2024 artfynd.xlsx", "A 4088-2024")</f>
         <v/>
       </c>
       <c r="X37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 50642-2023 karta.png", "A 50642-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 4088-2024 karta.png", "A 4088-2024")</f>
         <v/>
       </c>
       <c r="Y37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 50642-2023 georefererad karta.tif", "A 50642-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 4088-2024 georefererad karta.tif", "A 4088-2024")</f>
         <v/>
       </c>
       <c r="AA37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 50642-2023 FSC-klagomål.docx", "A 50642-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 4088-2024 FSC-klagomål.docx", "A 4088-2024")</f>
         <v/>
       </c>
       <c r="AB37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 50642-2023 FSC-klagomål mail.docx", "A 50642-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 4088-2024 FSC-klagomål mail.docx", "A 4088-2024")</f>
         <v/>
       </c>
       <c r="AC37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 50642-2023 tillsynsbegäran.docx", "A 50642-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 4088-2024 tillsynsbegäran.docx", "A 4088-2024")</f>
         <v/>
       </c>
       <c r="AD37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 50642-2023 tillsynsbegäran mail.docx", "A 50642-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 4088-2024 tillsynsbegäran mail.docx", "A 4088-2024")</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 46487-2024</t>
+          <t>A 25129-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4601,10 +4601,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45582</v>
+        <v>45462</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4617,17 +4617,17 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>5.8</v>
+        <v>4.6</v>
       </c>
       <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
         <v>1</v>
       </c>
-      <c r="K38" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" t="n">
-        <v>0</v>
-      </c>
       <c r="M38" t="n">
         <v>0</v>
       </c>
@@ -4641,7 +4641,7 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -4653,46 +4653,46 @@
         <v>1</v>
       </c>
       <c r="U38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 46487-2024 artfynd.xlsx", "A 46487-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 25129-2024 artfynd.xlsx", "A 25129-2024")</f>
         <v/>
       </c>
       <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 46487-2024 karta.png", "A 46487-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 25129-2024 karta.png", "A 25129-2024")</f>
         <v/>
       </c>
       <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 46487-2024 georefererad karta.tif", "A 46487-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 25129-2024 georefererad karta.tif", "A 25129-2024")</f>
         <v/>
       </c>
       <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 46487-2024 FSC-klagomål.docx", "A 46487-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 25129-2024 FSC-klagomål.docx", "A 25129-2024")</f>
         <v/>
       </c>
       <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 46487-2024 FSC-klagomål mail.docx", "A 46487-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 25129-2024 FSC-klagomål mail.docx", "A 25129-2024")</f>
         <v/>
       </c>
       <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 46487-2024 tillsynsbegäran.docx", "A 46487-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 25129-2024 tillsynsbegäran.docx", "A 25129-2024")</f>
         <v/>
       </c>
       <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 46487-2024 tillsynsbegäran mail.docx", "A 46487-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 25129-2024 tillsynsbegäran mail.docx", "A 25129-2024")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 25129-2024</t>
+          <t>A 12150-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4706,10 +4706,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45462</v>
+        <v>45377</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4722,7 +4722,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>4.6</v>
+        <v>1.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4731,10 +4731,10 @@
         <v>0</v>
       </c>
       <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
         <v>1</v>
-      </c>
-      <c r="M39" t="n">
-        <v>0</v>
       </c>
       <c r="N39" t="n">
         <v>0</v>
@@ -4749,7 +4749,7 @@
         <v>1</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -4758,39 +4758,39 @@
         <v>1</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 25129-2024 artfynd.xlsx", "A 25129-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 12150-2024 artfynd.xlsx", "A 12150-2024")</f>
         <v/>
       </c>
       <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 25129-2024 karta.png", "A 25129-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 12150-2024 karta.png", "A 12150-2024")</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 25129-2024 georefererad karta.tif", "A 25129-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 12150-2024 georefererad karta.tif", "A 12150-2024")</f>
         <v/>
       </c>
       <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 25129-2024 FSC-klagomål.docx", "A 25129-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 12150-2024 FSC-klagomål.docx", "A 12150-2024")</f>
         <v/>
       </c>
       <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 25129-2024 FSC-klagomål mail.docx", "A 25129-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 12150-2024 FSC-klagomål mail.docx", "A 12150-2024")</f>
         <v/>
       </c>
       <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 25129-2024 tillsynsbegäran.docx", "A 25129-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 12150-2024 tillsynsbegäran.docx", "A 12150-2024")</f>
         <v/>
       </c>
       <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 25129-2024 tillsynsbegäran mail.docx", "A 25129-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 12150-2024 tillsynsbegäran mail.docx", "A 12150-2024")</f>
         <v/>
       </c>
     </row>
@@ -4814,7 +4814,7 @@
         <v>44498</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 27094-2026</t>
+          <t>A 50642-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46188</v>
+        <v>45210</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4932,13 +4932,13 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>6.2</v>
+        <v>0.8</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -4972,42 +4972,42 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 27094-2026 artfynd.xlsx", "A 27094-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 50642-2023 artfynd.xlsx", "A 50642-2023")</f>
         <v/>
       </c>
       <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 27094-2026 karta.png", "A 27094-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 50642-2023 karta.png", "A 50642-2023")</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 27094-2026 georefererad karta.tif", "A 27094-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 50642-2023 georefererad karta.tif", "A 50642-2023")</f>
         <v/>
       </c>
       <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 27094-2026 FSC-klagomål.docx", "A 27094-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 50642-2023 FSC-klagomål.docx", "A 50642-2023")</f>
         <v/>
       </c>
       <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 27094-2026 FSC-klagomål mail.docx", "A 27094-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 50642-2023 FSC-klagomål mail.docx", "A 50642-2023")</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 27094-2026 tillsynsbegäran.docx", "A 27094-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 50642-2023 tillsynsbegäran.docx", "A 50642-2023")</f>
         <v/>
       </c>
       <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 27094-2026 tillsynsbegäran mail.docx", "A 27094-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 50642-2023 tillsynsbegäran mail.docx", "A 50642-2023")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 44062-2022</t>
+          <t>A 27094-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5021,10 +5021,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44839</v>
+        <v>46188</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5037,7 +5037,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.2</v>
+        <v>6.2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -5073,39 +5073,39 @@
         <v>1</v>
       </c>
       <c r="U42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 44062-2022 artfynd.xlsx", "A 44062-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 27094-2026 artfynd.xlsx", "A 27094-2026")</f>
         <v/>
       </c>
       <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 44062-2022 karta.png", "A 44062-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 27094-2026 karta.png", "A 27094-2026")</f>
         <v/>
       </c>
       <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 44062-2022 georefererad karta.tif", "A 44062-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 27094-2026 georefererad karta.tif", "A 27094-2026")</f>
         <v/>
       </c>
       <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 44062-2022 FSC-klagomål.docx", "A 44062-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 27094-2026 FSC-klagomål.docx", "A 27094-2026")</f>
         <v/>
       </c>
       <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 44062-2022 FSC-klagomål mail.docx", "A 44062-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 27094-2026 FSC-klagomål mail.docx", "A 27094-2026")</f>
         <v/>
       </c>
       <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 44062-2022 tillsynsbegäran.docx", "A 44062-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 27094-2026 tillsynsbegäran.docx", "A 27094-2026")</f>
         <v/>
       </c>
       <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 44062-2022 tillsynsbegäran mail.docx", "A 44062-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 27094-2026 tillsynsbegäran mail.docx", "A 27094-2026")</f>
         <v/>
       </c>
     </row>
@@ -5129,7 +5129,7 @@
         <v>46265</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5238,7 +5238,7 @@
         <v>46224</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         <v>45084</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5448,7 +5448,7 @@
         <v>44862</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5553,7 +5553,7 @@
         <v>44880</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5626,7 +5626,7 @@
         <v>44839</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5699,7 +5699,7 @@
         <v>44725</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5772,7 +5772,7 @@
         <v>44840</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5845,7 +5845,7 @@
         <v>44498</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5918,7 +5918,7 @@
         <v>44477</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5991,7 +5991,7 @@
         <v>44657</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
         <v>44634</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6137,7 +6137,7 @@
         <v>44802</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6210,7 +6210,7 @@
         <v>44802</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
         <v>44827</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6356,7 +6356,7 @@
         <v>44480</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6429,7 +6429,7 @@
         <v>44634</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 29436-2024</t>
+          <t>A 40275-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6499,10 +6499,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45483</v>
+        <v>45169</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6515,7 +6515,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>4.2</v>
+        <v>0.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6558,7 +6558,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 8882-2025</t>
+          <t>A 6667-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6572,10 +6572,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45713</v>
+        <v>45700</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6588,7 +6588,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6631,7 +6631,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 12148-2024</t>
+          <t>A 23980-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6645,10 +6645,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45377</v>
+        <v>45456</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6704,7 +6704,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 9578-2025</t>
+          <t>A 55748-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6718,10 +6718,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45715</v>
+        <v>45623</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6777,7 +6777,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 53501-2022</t>
+          <t>A 48197-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6791,10 +6791,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44879</v>
+        <v>45590</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>7.2</v>
+        <v>3.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6850,7 +6850,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 27551-2023</t>
+          <t>A 46702-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6864,10 +6864,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45097</v>
+        <v>45583</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6923,7 +6923,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 64728-2023</t>
+          <t>A 40287-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6937,10 +6937,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45281</v>
+        <v>45895</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6953,7 +6953,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6996,7 +6996,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 31720-2023</t>
+          <t>A 31789-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -7010,10 +7010,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45117</v>
+        <v>45118</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7026,7 +7026,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -7069,7 +7069,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 25669-2024</t>
+          <t>A 1644-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7083,10 +7083,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45463</v>
+        <v>45670</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7099,7 +7099,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>17.9</v>
+        <v>1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -7142,7 +7142,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 31143-2024</t>
+          <t>A 42826-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7152,14 +7152,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45502</v>
+        <v>45908</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7172,7 +7172,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7215,7 +7215,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 607-2024</t>
+          <t>A 55545-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7229,10 +7229,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45299</v>
+        <v>44887</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7245,7 +7245,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.6</v>
+        <v>4.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7288,7 +7288,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 54709-2023</t>
+          <t>A 55529-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7302,10 +7302,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45236</v>
+        <v>45622</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7318,7 +7318,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>3.6</v>
+        <v>2.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 40287-2025</t>
+          <t>A 32020-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7375,10 +7375,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45895</v>
+        <v>45835</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7391,7 +7391,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7434,7 +7434,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 55544-2022</t>
+          <t>A 64728-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7448,10 +7448,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44887</v>
+        <v>45281</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7464,7 +7464,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7507,7 +7507,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 23976-2024</t>
+          <t>A 25669-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7521,10 +7521,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45456</v>
+        <v>45463</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7537,7 +7537,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.6</v>
+        <v>17.9</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7580,7 +7580,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 42826-2025</t>
+          <t>A 23676-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7594,10 +7594,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45908</v>
+        <v>45454</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7610,7 +7610,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7653,7 +7653,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 27553-2023</t>
+          <t>A 13662-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7667,10 +7667,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45097</v>
+        <v>45736</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7683,7 +7683,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.8</v>
+        <v>6.4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7726,7 +7726,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 9055-2026</t>
+          <t>A 52519-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7740,10 +7740,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46069</v>
+        <v>45954</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7799,7 +7799,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 28253-2023</t>
+          <t>A 8139-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7813,10 +7813,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45099</v>
+        <v>45708</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7829,7 +7829,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7872,7 +7872,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 16419-2023</t>
+          <t>A 44448-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7886,10 +7886,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45022</v>
+        <v>45189</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>4.2</v>
+        <v>0.6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7945,7 +7945,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 19503-2022</t>
+          <t>A 31143-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7955,14 +7955,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44693</v>
+        <v>45502</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7975,7 +7975,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>5.1</v>
+        <v>0.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -8018,7 +8018,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 46702-2024</t>
+          <t>A 55728-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -8032,10 +8032,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45583</v>
+        <v>45972</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -8091,7 +8091,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 49206-2024</t>
+          <t>A 23328-2022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -8105,10 +8105,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45595</v>
+        <v>44720</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8121,7 +8121,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8164,7 +8164,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 52519-2025</t>
+          <t>A 15154-2023</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8178,10 +8178,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45954</v>
+        <v>45016</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8194,7 +8194,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0.7</v>
+        <v>3.5</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8237,7 +8237,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 31503-2023</t>
+          <t>A 57725-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8251,10 +8251,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45115</v>
+        <v>45981</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8267,7 +8267,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8310,7 +8310,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 9803-2026</t>
+          <t>A 46286-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8324,10 +8324,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>46072</v>
+        <v>45581</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8340,7 +8340,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8383,7 +8383,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 55728-2025</t>
+          <t>A 55544-2022</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8397,10 +8397,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45972</v>
+        <v>44887</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8413,7 +8413,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8456,7 +8456,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 19650-2026</t>
+          <t>A 7337-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8470,10 +8470,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46134</v>
+        <v>45345</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8486,7 +8486,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>8</v>
+        <v>2.6</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8529,7 +8529,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 57725-2025</t>
+          <t>A 49610-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8543,10 +8543,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45981</v>
+        <v>45596</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8559,7 +8559,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.1</v>
+        <v>6.4</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8602,7 +8602,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 55529-2024</t>
+          <t>A 13243-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8616,10 +8616,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45622</v>
+        <v>45735</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8632,7 +8632,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8675,7 +8675,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 23328-2022</t>
+          <t>A 9055-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8689,10 +8689,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44720</v>
+        <v>46069</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8748,7 +8748,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 7707-2025</t>
+          <t>A 7811-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8762,10 +8762,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45705</v>
+        <v>44973</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8778,7 +8778,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8821,7 +8821,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 32364-2023</t>
+          <t>A 58137-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8835,10 +8835,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45120</v>
+        <v>44900</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 58134-2022</t>
+          <t>A 42105-2022</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8908,10 +8908,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44900</v>
+        <v>44830</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8924,7 +8924,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8967,7 +8967,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 8139-2025</t>
+          <t>A 50652-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8981,10 +8981,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45708</v>
+        <v>45210</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8997,7 +8997,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -9040,7 +9040,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 40275-2023</t>
+          <t>A 24855-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -9054,10 +9054,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45169</v>
+        <v>45461</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9070,7 +9070,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -9113,7 +9113,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 74214-2021</t>
+          <t>A 4755-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -9127,10 +9127,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>44553</v>
+        <v>45328</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9143,7 +9143,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>19.8</v>
+        <v>0.9</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9186,7 +9186,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 1644-2025</t>
+          <t>A 14400-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9200,10 +9200,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45670</v>
+        <v>45012</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9216,7 +9216,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -9259,7 +9259,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 24855-2024</t>
+          <t>A 23227-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9273,10 +9273,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45461</v>
+        <v>45075</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9289,7 +9289,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9332,7 +9332,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 7871-2025</t>
+          <t>A 9578-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9346,10 +9346,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45706</v>
+        <v>45715</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9362,7 +9362,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9405,7 +9405,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 13243-2025</t>
+          <t>A 9803-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9419,10 +9419,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45735</v>
+        <v>46072</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9435,7 +9435,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9478,7 +9478,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 6667-2025</t>
+          <t>A 8882-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9492,10 +9492,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45700</v>
+        <v>45713</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9508,7 +9508,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9551,7 +9551,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 32020-2025</t>
+          <t>A 7707-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9565,10 +9565,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45835</v>
+        <v>45705</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9581,7 +9581,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9624,7 +9624,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 58137-2022</t>
+          <t>A 19650-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9638,10 +9638,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44900</v>
+        <v>46134</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9654,7 +9654,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.9</v>
+        <v>8</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9697,7 +9697,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 2575-2024</t>
+          <t>A 58134-2022</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9711,10 +9711,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45313</v>
+        <v>44900</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9727,7 +9727,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9770,7 +9770,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 31502-2023</t>
+          <t>A 74214-2021</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9784,10 +9784,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45115</v>
+        <v>44553</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9800,7 +9800,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.7</v>
+        <v>19.8</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9843,7 +9843,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 13662-2025</t>
+          <t>A 18571-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9857,10 +9857,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45736</v>
+        <v>45763</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9873,7 +9873,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>6.4</v>
+        <v>0.9</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9916,7 +9916,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 46286-2024</t>
+          <t>A 16419-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9930,10 +9930,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45581</v>
+        <v>45022</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9946,7 +9946,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2</v>
+        <v>4.2</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9989,7 +9989,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 60227-2025</t>
+          <t>A 27551-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -10003,10 +10003,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45994</v>
+        <v>45097</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10019,7 +10019,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -10062,7 +10062,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 43857-2025</t>
+          <t>A 2575-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10076,10 +10076,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45912</v>
+        <v>45313</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10092,7 +10092,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -10135,7 +10135,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 7994-2023</t>
+          <t>A 4089-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10149,10 +10149,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44973</v>
+        <v>45323</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10165,7 +10165,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -10208,7 +10208,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 13278-2026</t>
+          <t>A 28496-2023</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10222,10 +10222,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46093</v>
+        <v>45103</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10238,7 +10238,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -10281,7 +10281,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 8665-2022</t>
+          <t>A 1299-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10295,10 +10295,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>44613</v>
+        <v>45303</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10311,7 +10311,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10354,7 +10354,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 27097-2026</t>
+          <t>A 32364-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10368,10 +10368,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46188</v>
+        <v>45120</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10384,7 +10384,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>4</v>
+        <v>0.6</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10427,7 +10427,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 18571-2025</t>
+          <t>A 31503-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10441,10 +10441,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45763</v>
+        <v>45115</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10457,7 +10457,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10500,7 +10500,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 31709-2023</t>
+          <t>A 39014-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10514,10 +10514,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45117</v>
+        <v>45163</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10530,7 +10530,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10573,7 +10573,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 23227-2023</t>
+          <t>A 31908-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10587,10 +10587,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45075</v>
+        <v>45118</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10603,7 +10603,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10646,7 +10646,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 50652-2023</t>
+          <t>A 31502-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10660,10 +10660,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45210</v>
+        <v>45115</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10676,7 +10676,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10719,7 +10719,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 40278-2023</t>
+          <t>A 28253-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10733,10 +10733,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45169</v>
+        <v>45099</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10749,7 +10749,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.1</v>
+        <v>2.7</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10792,7 +10792,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 29369-2026</t>
+          <t>A 21488-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10806,10 +10806,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46203</v>
+        <v>45061</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10822,7 +10822,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10865,7 +10865,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 31789-2023</t>
+          <t>A 7994-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10879,10 +10879,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45118</v>
+        <v>44973</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10895,7 +10895,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10938,7 +10938,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 39014-2023</t>
+          <t>A 43857-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10952,10 +10952,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45163</v>
+        <v>45912</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10968,7 +10968,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -11011,7 +11011,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 19500-2022</t>
+          <t>A 27553-2023</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -11025,10 +11025,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>44693</v>
+        <v>45097</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11041,7 +11041,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -11084,7 +11084,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 44448-2023</t>
+          <t>A 60227-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -11098,10 +11098,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45189</v>
+        <v>45994</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11114,7 +11114,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -11157,7 +11157,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 57923-2024</t>
+          <t>A 13278-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -11171,10 +11171,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45631</v>
+        <v>46093</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11187,7 +11187,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>4.5</v>
+        <v>1.7</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -11230,7 +11230,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 31576-2026</t>
+          <t>A 53501-2022</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11244,10 +11244,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46224</v>
+        <v>44879</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11260,7 +11260,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.6</v>
+        <v>7.2</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -11303,7 +11303,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 28264-2022</t>
+          <t>A 27097-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11317,10 +11317,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>44746</v>
+        <v>46188</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11333,7 +11333,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11376,7 +11376,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 36001-2026</t>
+          <t>A 54709-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11390,10 +11390,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46266</v>
+        <v>45236</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11406,7 +11406,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>0.8</v>
+        <v>3.6</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11449,7 +11449,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 35912-2026</t>
+          <t>A 12148-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>46266</v>
+        <v>45377</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11479,7 +11479,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11522,7 +11522,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 55545-2022</t>
+          <t>A 19500-2022</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11536,10 +11536,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>44887</v>
+        <v>44693</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11552,7 +11552,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>4.4</v>
+        <v>1.2</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11595,7 +11595,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 37628-2026</t>
+          <t>A 4605-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11609,10 +11609,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>46276</v>
+        <v>45687</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11624,13 +11624,8 @@
           <t>ÄNGELHOLM</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I130" t="n">
-        <v>4.5</v>
+        <v>0.8</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11673,7 +11668,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 34514-2023</t>
+          <t>A 31720-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11687,10 +11682,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45140</v>
+        <v>45117</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11703,7 +11698,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>3.1</v>
+        <v>0.5</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11746,7 +11741,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 26978-2026</t>
+          <t>A 16314-2024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11760,10 +11755,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46185</v>
+        <v>45407</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11776,7 +11771,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>7.7</v>
+        <v>1.1</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11819,7 +11814,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 26986-2026</t>
+          <t>A 29369-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11833,10 +11828,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46185</v>
+        <v>46203</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11849,7 +11844,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>3.5</v>
+        <v>1.3</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11892,7 +11887,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 1299-2024</t>
+          <t>A 34514-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11906,10 +11901,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45303</v>
+        <v>45140</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11922,7 +11917,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>0.5</v>
+        <v>3.1</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11965,7 +11960,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 35677-2026</t>
+          <t>A 46613-2024</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11979,10 +11974,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46265</v>
+        <v>45583</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11995,7 +11990,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>3.1</v>
+        <v>6.2</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -12038,7 +12033,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 42105-2022</t>
+          <t>A 23976-2024</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -12052,10 +12047,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>44830</v>
+        <v>45456</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12068,7 +12063,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -12111,7 +12106,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 15154-2023</t>
+          <t>A 40278-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -12125,10 +12120,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45016</v>
+        <v>45169</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12141,7 +12136,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>3.5</v>
+        <v>1.1</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -12184,7 +12179,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 19255-2026</t>
+          <t>A 7871-2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -12198,10 +12193,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46132</v>
+        <v>45706</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12214,7 +12209,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -12257,7 +12252,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 19256-2026</t>
+          <t>A 32430-2023</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12271,10 +12266,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46132</v>
+        <v>45120</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12287,7 +12282,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -12330,7 +12325,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 7337-2024</t>
+          <t>A 29436-2024</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12344,10 +12339,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45345</v>
+        <v>45483</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12360,7 +12355,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>2.6</v>
+        <v>4.2</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -12403,7 +12398,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 49610-2024</t>
+          <t>A 31576-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12417,10 +12412,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45596</v>
+        <v>46224</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12433,7 +12428,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>6.4</v>
+        <v>0.6</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12476,7 +12471,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 14400-2023</t>
+          <t>A 36001-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12490,10 +12485,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45012</v>
+        <v>46266</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12506,7 +12501,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12549,7 +12544,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 4089-2024</t>
+          <t>A 35912-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12563,10 +12558,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45323</v>
+        <v>46266</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12579,7 +12574,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12622,7 +12617,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 23676-2024</t>
+          <t>A 58150-2024</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12636,10 +12631,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45454</v>
+        <v>45632</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12652,7 +12647,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12695,7 +12690,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 60-2024</t>
+          <t>A 28264-2022</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12709,10 +12704,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45293</v>
+        <v>44746</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12725,7 +12720,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12768,7 +12763,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 58150-2024</t>
+          <t>A 31709-2023</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12782,10 +12777,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45632</v>
+        <v>45117</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12798,7 +12793,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12841,7 +12836,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 4755-2024</t>
+          <t>A 8665-2022</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12855,10 +12850,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45328</v>
+        <v>44613</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12871,7 +12866,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12914,7 +12909,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 32430-2023</t>
+          <t>A 60-2024</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12928,10 +12923,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45120</v>
+        <v>45293</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12944,7 +12939,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12987,7 +12982,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 28496-2023</t>
+          <t>A 607-2024</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -13001,10 +12996,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45103</v>
+        <v>45299</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13017,7 +13012,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -13060,7 +13055,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 4605-2025</t>
+          <t>A 49206-2024</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -13074,10 +13069,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45687</v>
+        <v>45595</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13090,7 +13085,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -13133,7 +13128,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 21488-2023</t>
+          <t>A 19503-2022</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -13147,10 +13142,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45061</v>
+        <v>44693</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13163,7 +13158,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.1</v>
+        <v>5.1</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -13206,7 +13201,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 31908-2023</t>
+          <t>A 37628-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -13220,10 +13215,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45118</v>
+        <v>46276</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13235,8 +13230,13 @@
           <t>ÄNGELHOLM</t>
         </is>
       </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I152" t="n">
-        <v>1.5</v>
+        <v>4.5</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -13279,7 +13279,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 7811-2023</t>
+          <t>A 57923-2024</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -13293,10 +13293,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>44973</v>
+        <v>45631</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13309,7 +13309,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>0.9</v>
+        <v>4.5</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -13352,7 +13352,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 16314-2024</t>
+          <t>A 26986-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -13366,10 +13366,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45407</v>
+        <v>46185</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13382,7 +13382,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1.1</v>
+        <v>3.5</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -13425,7 +13425,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 46613-2024</t>
+          <t>A 26978-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13439,10 +13439,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45583</v>
+        <v>46185</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13455,7 +13455,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>6.2</v>
+        <v>7.7</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13515,7 +13515,7 @@
         <v>45436</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13571,7 +13571,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 23980-2024</t>
+          <t>A 39993-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13585,10 +13585,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45456</v>
+        <v>46293</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13601,7 +13601,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1.3</v>
+        <v>6.3</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13644,7 +13644,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 55748-2024</t>
+          <t>A 19255-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13658,10 +13658,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45623</v>
+        <v>46132</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13674,7 +13674,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13717,7 +13717,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 48197-2024</t>
+          <t>A 19256-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13731,10 +13731,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45590</v>
+        <v>46132</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13747,7 +13747,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>3.1</v>
+        <v>0.7</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13790,24 +13790,24 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>S 4250-2024</t>
+          <t>A 35677-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45582</v>
+        <v>46265</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13820,7 +13820,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>23.3</v>
+        <v>3.1</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13863,7 +13863,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>S 4255-2024</t>
+          <t>S 4250-2024</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13880,7 +13880,7 @@
         <v>45582</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13893,7 +13893,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>5.9</v>
+        <v>23.3</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13936,7 +13936,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>S 4256-2024</t>
+          <t>S 4255-2024</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13953,7 +13953,7 @@
         <v>45582</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13966,7 +13966,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -14009,7 +14009,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>S 4258-2024</t>
+          <t>S 4256-2024</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -14026,7 +14026,7 @@
         <v>45582</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14039,7 +14039,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>8.800000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -14082,7 +14082,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>S 9359-2021</t>
+          <t>S 4258-2024</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -14092,14 +14092,14 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>44519</v>
+        <v>45582</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14112,7 +14112,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>0.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -14155,7 +14155,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>S 3993-2023</t>
+          <t>S 9359-2021</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -14165,14 +14165,14 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45239</v>
+        <v>44519</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14185,7 +14185,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>11.8</v>
+        <v>0.5</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -14228,7 +14228,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>S 2862-2023</t>
+          <t>S 3993-2023</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -14242,10 +14242,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45168</v>
+        <v>45239</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14258,7 +14258,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>13.7</v>
+        <v>11.8</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -14301,148 +14301,221 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
+          <t>S 2862-2023</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Askåterföring</t>
+        </is>
+      </c>
+      <c r="D167" s="1" t="n">
+        <v>45168</v>
+      </c>
+      <c r="E167" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I167" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="J167" t="n">
+        <v>0</v>
+      </c>
+      <c r="K167" t="n">
+        <v>0</v>
+      </c>
+      <c r="L167" t="n">
+        <v>0</v>
+      </c>
+      <c r="M167" t="n">
+        <v>0</v>
+      </c>
+      <c r="N167" t="n">
+        <v>0</v>
+      </c>
+      <c r="O167" t="n">
+        <v>0</v>
+      </c>
+      <c r="P167" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q167" t="n">
+        <v>0</v>
+      </c>
+      <c r="R167" t="n">
+        <v>0</v>
+      </c>
+      <c r="S167" t="n">
+        <v>0</v>
+      </c>
+      <c r="T167" t="n">
+        <v>0</v>
+      </c>
+      <c r="U167" t="n">
+        <v>0</v>
+      </c>
+      <c r="V167" s="2" t="inlineStr"/>
+    </row>
+    <row r="168" ht="15" customHeight="1">
+      <c r="A168" t="inlineStr">
+        <is>
           <t>S 6022-2022</t>
         </is>
       </c>
-      <c r="B167" t="inlineStr">
+      <c r="B168" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C167" t="inlineStr">
+      <c r="C168" t="inlineStr">
         <is>
           <t>Askåterföring</t>
         </is>
       </c>
-      <c r="D167" s="1" t="n">
+      <c r="D168" s="1" t="n">
         <v>44861</v>
       </c>
-      <c r="E167" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I167" t="n">
+      <c r="E168" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I168" t="n">
         <v>21.4</v>
       </c>
-      <c r="J167" t="n">
-        <v>0</v>
-      </c>
-      <c r="K167" t="n">
-        <v>0</v>
-      </c>
-      <c r="L167" t="n">
-        <v>0</v>
-      </c>
-      <c r="M167" t="n">
-        <v>0</v>
-      </c>
-      <c r="N167" t="n">
-        <v>0</v>
-      </c>
-      <c r="O167" t="n">
-        <v>0</v>
-      </c>
-      <c r="P167" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q167" t="n">
-        <v>0</v>
-      </c>
-      <c r="R167" t="n">
-        <v>0</v>
-      </c>
-      <c r="S167" t="n">
-        <v>0</v>
-      </c>
-      <c r="T167" t="n">
-        <v>0</v>
-      </c>
-      <c r="U167" t="n">
-        <v>0</v>
-      </c>
-      <c r="V167" s="2" t="inlineStr"/>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
+      <c r="J168" t="n">
+        <v>0</v>
+      </c>
+      <c r="K168" t="n">
+        <v>0</v>
+      </c>
+      <c r="L168" t="n">
+        <v>0</v>
+      </c>
+      <c r="M168" t="n">
+        <v>0</v>
+      </c>
+      <c r="N168" t="n">
+        <v>0</v>
+      </c>
+      <c r="O168" t="n">
+        <v>0</v>
+      </c>
+      <c r="P168" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q168" t="n">
+        <v>0</v>
+      </c>
+      <c r="R168" t="n">
+        <v>0</v>
+      </c>
+      <c r="S168" t="n">
+        <v>0</v>
+      </c>
+      <c r="T168" t="n">
+        <v>0</v>
+      </c>
+      <c r="U168" t="n">
+        <v>0</v>
+      </c>
+      <c r="V168" s="2" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
         <is>
           <t>S 4254-2024</t>
         </is>
       </c>
-      <c r="B168" t="inlineStr">
+      <c r="B169" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C168" t="inlineStr">
+      <c r="C169" t="inlineStr">
         <is>
           <t>Askåterföring</t>
         </is>
       </c>
-      <c r="D168" s="1" t="n">
+      <c r="D169" s="1" t="n">
         <v>45582</v>
       </c>
-      <c r="E168" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I168" t="n">
+      <c r="E169" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I169" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="J168" t="n">
-        <v>0</v>
-      </c>
-      <c r="K168" t="n">
-        <v>0</v>
-      </c>
-      <c r="L168" t="n">
-        <v>0</v>
-      </c>
-      <c r="M168" t="n">
-        <v>0</v>
-      </c>
-      <c r="N168" t="n">
-        <v>0</v>
-      </c>
-      <c r="O168" t="n">
-        <v>0</v>
-      </c>
-      <c r="P168" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
-      <c r="R168" t="n">
-        <v>0</v>
-      </c>
-      <c r="S168" t="n">
-        <v>0</v>
-      </c>
-      <c r="T168" t="n">
-        <v>0</v>
-      </c>
-      <c r="U168" t="n">
-        <v>0</v>
-      </c>
-      <c r="V168" s="2" t="inlineStr"/>
+      <c r="J169" t="n">
+        <v>0</v>
+      </c>
+      <c r="K169" t="n">
+        <v>0</v>
+      </c>
+      <c r="L169" t="n">
+        <v>0</v>
+      </c>
+      <c r="M169" t="n">
+        <v>0</v>
+      </c>
+      <c r="N169" t="n">
+        <v>0</v>
+      </c>
+      <c r="O169" t="n">
+        <v>0</v>
+      </c>
+      <c r="P169" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q169" t="n">
+        <v>0</v>
+      </c>
+      <c r="R169" t="n">
+        <v>0</v>
+      </c>
+      <c r="S169" t="n">
+        <v>0</v>
+      </c>
+      <c r="T169" t="n">
+        <v>0</v>
+      </c>
+      <c r="U169" t="n">
+        <v>0</v>
+      </c>
+      <c r="V169" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt ÄNGELHOLM.xlsx
+++ b/Översikt ÄNGELHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45099</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         <v>45931</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
         <v>45931</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>46106</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>44802</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 32268-2022</t>
+          <t>A 74502-2021</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1204,10 +1204,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44781</v>
+        <v>44560</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1220,16 +1220,16 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>8.6</v>
+        <v>5.6</v>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1244,7 +1244,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1253,12 +1253,128 @@
         <v>8</v>
       </c>
       <c r="T7" t="n">
+        <v>9</v>
+      </c>
+      <c r="U7" t="n">
+        <v>9</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Entita
+Grönsångare
+Sydlig sotticka
+Västlig hakmossa
+Spillkråka
+Gröngöling
+Kungsfågel
+Skogsduva</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 74502-2021 artfynd.xlsx", "A 74502-2021")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 74502-2021 karta.png", "A 74502-2021")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 74502-2021 georefererad karta.tif", "A 74502-2021")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 74502-2021 FSC-klagomål.docx", "A 74502-2021")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 74502-2021 FSC-klagomål mail.docx", "A 74502-2021")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 74502-2021 tillsynsbegäran.docx", "A 74502-2021")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 74502-2021 tillsynsbegäran mail.docx", "A 74502-2021")</f>
+        <v/>
+      </c>
+      <c r="AE7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 74502-2021 prioriterade fågelarter.docx", "A 74502-2021")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 32268-2022</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>44781</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>5</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>8</v>
+      </c>
+      <c r="T8" t="n">
         <v>14</v>
       </c>
-      <c r="U7" t="n">
+      <c r="U8" t="n">
         <v>14</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Bokvårtlav
 Blåmossa
@@ -1270,148 +1386,32 @@
 Vanlig padda</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 32268-2022 artfynd.xlsx", "A 32268-2022")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 32268-2022 karta.png", "A 32268-2022")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 32268-2022 georefererad karta.tif", "A 32268-2022")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 32268-2022 FSC-klagomål.docx", "A 32268-2022")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 32268-2022 FSC-klagomål mail.docx", "A 32268-2022")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 32268-2022 tillsynsbegäran.docx", "A 32268-2022")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 32268-2022 tillsynsbegäran mail.docx", "A 32268-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 74502-2021</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>44560</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="J8" t="n">
-        <v>6</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" t="n">
-        <v>3</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>3</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>8</v>
-      </c>
-      <c r="T8" t="n">
-        <v>9</v>
-      </c>
-      <c r="U8" t="n">
-        <v>9</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Entita
-Grönsångare
-Sydlig sotticka
-Västlig hakmossa
-Spillkråka
-Gröngöling
-Kungsfågel
-Skogsduva</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 74502-2021 artfynd.xlsx", "A 74502-2021")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 74502-2021 karta.png", "A 74502-2021")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 74502-2021 georefererad karta.tif", "A 74502-2021")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 74502-2021 FSC-klagomål.docx", "A 74502-2021")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 74502-2021 FSC-klagomål mail.docx", "A 74502-2021")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 74502-2021 tillsynsbegäran.docx", "A 74502-2021")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 74502-2021 tillsynsbegäran mail.docx", "A 74502-2021")</f>
-        <v/>
-      </c>
-      <c r="AE8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 74502-2021 prioriterade fågelarter.docx", "A 74502-2021")</f>
         <v/>
       </c>
     </row>
@@ -1435,7 +1435,7 @@
         <v>45835</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 5046-2022</t>
+          <t>A 308-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1547,10 +1547,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44593</v>
+        <v>44929</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1563,34 +1563,34 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>3</v>
+        <v>0.8</v>
       </c>
       <c r="J10" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L10" t="n">
         <v>1</v>
       </c>
       <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
         <v>1</v>
       </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2</v>
-      </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>6</v>
@@ -1599,9 +1599,119 @@
         <v>7</v>
       </c>
       <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Bokvårtlav
+Dvärghäxört
+Havstulpanlav
+Klippfrullania
+Platt fjädermossa
+Stor knopplav</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 308-2023 artfynd.xlsx", "A 308-2023")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 308-2023 karta.png", "A 308-2023")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 308-2023 georefererad karta.tif", "A 308-2023")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 308-2023 FSC-klagomål.docx", "A 308-2023")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 308-2023 FSC-klagomål mail.docx", "A 308-2023")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 308-2023 tillsynsbegäran.docx", "A 308-2023")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 308-2023 tillsynsbegäran mail.docx", "A 308-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 5046-2022</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>44593</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>3</v>
+      </c>
+      <c r="J11" t="n">
         <v>6</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>6</v>
+      </c>
+      <c r="T11" t="n">
+        <v>7</v>
+      </c>
+      <c r="U11" t="n">
+        <v>6</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Grönfink
 Gulsparv
@@ -1611,111 +1721,225 @@
 Trädlärka</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 5046-2022 artfynd.xlsx", "A 5046-2022")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 5046-2022 karta.png", "A 5046-2022")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 5046-2022 georefererad karta.tif", "A 5046-2022")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 5046-2022 FSC-klagomål.docx", "A 5046-2022")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 5046-2022 FSC-klagomål mail.docx", "A 5046-2022")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 5046-2022 tillsynsbegäran.docx", "A 5046-2022")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 5046-2022 tillsynsbegäran mail.docx", "A 5046-2022")</f>
         <v/>
       </c>
-      <c r="AE10">
+      <c r="AE11">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 5046-2022 prioriterade fågelarter.docx", "A 5046-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 308-2023</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>44929</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>S 2334-2023</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Askåterföring</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>45106</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>6</v>
+      </c>
+      <c r="T12" t="n">
+        <v>6</v>
+      </c>
+      <c r="U12" t="n">
+        <v>6</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Småvänderot
+Vitfläckig guldvinge
+Kambräken
+Spillkråka
+Törnskata
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/S 2334-2023 artfynd.xlsx", "S 2334-2023")</f>
+        <v/>
+      </c>
+      <c r="X12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/S 2334-2023 karta.png", "S 2334-2023")</f>
+        <v/>
+      </c>
+      <c r="Y12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/S 2334-2023 georefererad karta.tif", "S 2334-2023")</f>
+        <v/>
+      </c>
+      <c r="AA12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/S 2334-2023 FSC-klagomål.docx", "S 2334-2023")</f>
+        <v/>
+      </c>
+      <c r="AB12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/S 2334-2023 FSC-klagomål mail.docx", "S 2334-2023")</f>
+        <v/>
+      </c>
+      <c r="AC12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/S 2334-2023 tillsynsbegäran.docx", "S 2334-2023")</f>
+        <v/>
+      </c>
+      <c r="AD12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/S 2334-2023 tillsynsbegäran mail.docx", "S 2334-2023")</f>
+        <v/>
+      </c>
+      <c r="AE12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/S 2334-2023 prioriterade fågelarter.docx", "S 2334-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>S 4107-2023</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>45245</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
         <v>5</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L13" t="n">
         <v>1</v>
       </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
         <v>1</v>
       </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
         <v>6</v>
       </c>
-      <c r="T11" t="n">
+      <c r="T13" t="n">
         <v>7</v>
       </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>Bokvårtlav
 Dvärghäxört
@@ -1725,230 +1949,6 @@
 Stor knopplav</t>
         </is>
       </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 308-2023 artfynd.xlsx", "A 308-2023")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 308-2023 karta.png", "A 308-2023")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 308-2023 georefererad karta.tif", "A 308-2023")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 308-2023 FSC-klagomål.docx", "A 308-2023")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 308-2023 FSC-klagomål mail.docx", "A 308-2023")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 308-2023 tillsynsbegäran.docx", "A 308-2023")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 308-2023 tillsynsbegäran mail.docx", "A 308-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>S 2334-2023</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Askåterföring</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>45106</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>47.6</v>
-      </c>
-      <c r="J12" t="n">
-        <v>3</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1</v>
-      </c>
-      <c r="S12" t="n">
-        <v>6</v>
-      </c>
-      <c r="T12" t="n">
-        <v>6</v>
-      </c>
-      <c r="U12" t="n">
-        <v>6</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Småvänderot
-Vitfläckig guldvinge
-Kambräken
-Spillkråka
-Törnskata
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/S 2334-2023 artfynd.xlsx", "S 2334-2023")</f>
-        <v/>
-      </c>
-      <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/S 2334-2023 karta.png", "S 2334-2023")</f>
-        <v/>
-      </c>
-      <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/S 2334-2023 georefererad karta.tif", "S 2334-2023")</f>
-        <v/>
-      </c>
-      <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/S 2334-2023 FSC-klagomål.docx", "S 2334-2023")</f>
-        <v/>
-      </c>
-      <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/S 2334-2023 FSC-klagomål mail.docx", "S 2334-2023")</f>
-        <v/>
-      </c>
-      <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/S 2334-2023 tillsynsbegäran.docx", "S 2334-2023")</f>
-        <v/>
-      </c>
-      <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/S 2334-2023 tillsynsbegäran mail.docx", "S 2334-2023")</f>
-        <v/>
-      </c>
-      <c r="AE12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/S 2334-2023 prioriterade fågelarter.docx", "S 2334-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>S 4107-2023</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>45245</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>5</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>6</v>
-      </c>
-      <c r="T13" t="n">
-        <v>7</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Bokvårtlav
-Dvärghäxört
-Havstulpanlav
-Klippfrullania
-Platt fjädermossa
-Stor knopplav</t>
-        </is>
-      </c>
       <c r="W13">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/S 4107-2023 artfynd.xlsx", "S 4107-2023")</f>
         <v/>
@@ -1998,7 +1998,7 @@
         <v>46038</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 35680-2026</t>
+          <t>A 35675-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2111,7 +2111,7 @@
         <v>46265</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2124,16 +2124,16 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.9</v>
+        <v>8.9</v>
       </c>
       <c r="J15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M15" t="n">
         <v>1</v>
@@ -2148,7 +2148,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R15" t="n">
         <v>1</v>
@@ -2157,12 +2157,125 @@
         <v>5</v>
       </c>
       <c r="T15" t="n">
+        <v>10</v>
+      </c>
+      <c r="U15" t="n">
+        <v>9</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Lappuggla
+Entita
+Blåmossa
+Skogsödla
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 35675-2026 artfynd.xlsx", "A 35675-2026")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 35675-2026 karta.png", "A 35675-2026")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 35675-2026 georefererad karta.tif", "A 35675-2026")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 35675-2026 FSC-klagomål.docx", "A 35675-2026")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 35675-2026 FSC-klagomål mail.docx", "A 35675-2026")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 35675-2026 tillsynsbegäran.docx", "A 35675-2026")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 35675-2026 tillsynsbegäran mail.docx", "A 35675-2026")</f>
+        <v/>
+      </c>
+      <c r="AE15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 35675-2026 prioriterade fågelarter.docx", "A 35675-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 35680-2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>2</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="n">
         <v>7</v>
       </c>
-      <c r="U15" t="n">
+      <c r="U16" t="n">
         <v>7</v>
       </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Vedlavklubba
 Entita
@@ -2171,149 +2284,36 @@
 Spillkråka</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 35680-2026 artfynd.xlsx", "A 35680-2026")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 35680-2026 karta.png", "A 35680-2026")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 35680-2026 georefererad karta.tif", "A 35680-2026")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 35680-2026 FSC-klagomål.docx", "A 35680-2026")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 35680-2026 FSC-klagomål mail.docx", "A 35680-2026")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 35680-2026 tillsynsbegäran.docx", "A 35680-2026")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 35680-2026 tillsynsbegäran mail.docx", "A 35680-2026")</f>
         <v/>
       </c>
-      <c r="AE15">
+      <c r="AE16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 35680-2026 prioriterade fågelarter.docx", "A 35680-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 35675-2026</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="J16" t="n">
-        <v>4</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1</v>
-      </c>
-      <c r="S16" t="n">
-        <v>5</v>
-      </c>
-      <c r="T16" t="n">
-        <v>10</v>
-      </c>
-      <c r="U16" t="n">
-        <v>9</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Lappuggla
-Entita
-Blåmossa
-Skogsödla
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 35675-2026 artfynd.xlsx", "A 35675-2026")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 35675-2026 karta.png", "A 35675-2026")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 35675-2026 georefererad karta.tif", "A 35675-2026")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 35675-2026 FSC-klagomål.docx", "A 35675-2026")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 35675-2026 FSC-klagomål mail.docx", "A 35675-2026")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 35675-2026 tillsynsbegäran.docx", "A 35675-2026")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 35675-2026 tillsynsbegäran mail.docx", "A 35675-2026")</f>
-        <v/>
-      </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 35675-2026 prioriterade fågelarter.docx", "A 35675-2026")</f>
         <v/>
       </c>
     </row>
@@ -2337,7 +2337,7 @@
         <v>45664</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2449,7 +2449,7 @@
         <v>44864</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 905-2024</t>
+          <t>A 28874-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2554,10 +2554,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45301</v>
+        <v>45104</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2570,19 +2570,19 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>4.9</v>
+        <v>9</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -2594,481 +2594,481 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>3</v>
       </c>
       <c r="T19" t="n">
+        <v>5</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Blåmossa
+Stubbspretmossa
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 28874-2023 artfynd.xlsx", "A 28874-2023")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 28874-2023 karta.png", "A 28874-2023")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 28874-2023 georefererad karta.tif", "A 28874-2023")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 28874-2023 FSC-klagomål.docx", "A 28874-2023")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 28874-2023 FSC-klagomål mail.docx", "A 28874-2023")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 28874-2023 tillsynsbegäran.docx", "A 28874-2023")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 28874-2023 tillsynsbegäran mail.docx", "A 28874-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 31907-2023</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>45118</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
         <v>3</v>
       </c>
-      <c r="U19" t="n">
+      <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Bokvårtlav
+Platt fjädermossa
+Stubbspretmossa</t>
+        </is>
+      </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 31907-2023 artfynd.xlsx", "A 31907-2023")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 31907-2023 karta.png", "A 31907-2023")</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 31907-2023 georefererad karta.tif", "A 31907-2023")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 31907-2023 FSC-klagomål.docx", "A 31907-2023")</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 31907-2023 FSC-klagomål mail.docx", "A 31907-2023")</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 31907-2023 tillsynsbegäran.docx", "A 31907-2023")</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 31907-2023 tillsynsbegäran mail.docx", "A 31907-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 50684-2023</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>45210</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J21" t="n">
         <v>2</v>
       </c>
-      <c r="V19" s="2" t="inlineStr">
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Skogsalm
+Kopparödla
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 50684-2023 artfynd.xlsx", "A 50684-2023")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 50684-2023 karta.png", "A 50684-2023")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 50684-2023 georefererad karta.tif", "A 50684-2023")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 50684-2023 FSC-klagomål.docx", "A 50684-2023")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 50684-2023 FSC-klagomål mail.docx", "A 50684-2023")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 50684-2023 tillsynsbegäran.docx", "A 50684-2023")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 50684-2023 tillsynsbegäran mail.docx", "A 50684-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 8065-2025</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>45707</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>2</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>3</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>Småvänderot
+Gullpudra
+Svinrot</t>
+        </is>
+      </c>
+      <c r="W22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 8065-2025 artfynd.xlsx", "A 8065-2025")</f>
+        <v/>
+      </c>
+      <c r="X22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 8065-2025 karta.png", "A 8065-2025")</f>
+        <v/>
+      </c>
+      <c r="Y22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 8065-2025 georefererad karta.tif", "A 8065-2025")</f>
+        <v/>
+      </c>
+      <c r="AA22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 8065-2025 FSC-klagomål.docx", "A 8065-2025")</f>
+        <v/>
+      </c>
+      <c r="AB22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 8065-2025 FSC-klagomål mail.docx", "A 8065-2025")</f>
+        <v/>
+      </c>
+      <c r="AC22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 8065-2025 tillsynsbegäran.docx", "A 8065-2025")</f>
+        <v/>
+      </c>
+      <c r="AD22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 8065-2025 tillsynsbegäran mail.docx", "A 8065-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>A 905-2024</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>45301</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>Igelkott
 Desmeknopp
 Myskmadra</t>
         </is>
       </c>
-      <c r="W19">
+      <c r="W23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 905-2024 artfynd.xlsx", "A 905-2024")</f>
         <v/>
       </c>
-      <c r="X19">
+      <c r="X23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 905-2024 karta.png", "A 905-2024")</f>
         <v/>
       </c>
-      <c r="Y19">
+      <c r="Y23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 905-2024 georefererad karta.tif", "A 905-2024")</f>
         <v/>
       </c>
-      <c r="AA19">
+      <c r="AA23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 905-2024 FSC-klagomål.docx", "A 905-2024")</f>
         <v/>
       </c>
-      <c r="AB19">
+      <c r="AB23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 905-2024 FSC-klagomål mail.docx", "A 905-2024")</f>
         <v/>
       </c>
-      <c r="AC19">
+      <c r="AC23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 905-2024 tillsynsbegäran.docx", "A 905-2024")</f>
         <v/>
       </c>
-      <c r="AD19">
+      <c r="AD23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 905-2024 tillsynsbegäran mail.docx", "A 905-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 28874-2023</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>45104</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>9</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1</v>
-      </c>
-      <c r="K20" t="n">
-        <v>2</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3</v>
-      </c>
-      <c r="T20" t="n">
-        <v>5</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Blåmossa
-Stubbspretmossa
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 28874-2023 artfynd.xlsx", "A 28874-2023")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 28874-2023 karta.png", "A 28874-2023")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 28874-2023 georefererad karta.tif", "A 28874-2023")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 28874-2023 FSC-klagomål.docx", "A 28874-2023")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 28874-2023 FSC-klagomål mail.docx", "A 28874-2023")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 28874-2023 tillsynsbegäran.docx", "A 28874-2023")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 28874-2023 tillsynsbegäran mail.docx", "A 28874-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 8065-2025</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>45707</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>2</v>
-      </c>
-      <c r="M21" t="n">
-        <v>1</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>3</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3</v>
-      </c>
-      <c r="T21" t="n">
-        <v>3</v>
-      </c>
-      <c r="U21" t="n">
-        <v>2</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Småvänderot
-Gullpudra
-Svinrot</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 8065-2025 artfynd.xlsx", "A 8065-2025")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 8065-2025 karta.png", "A 8065-2025")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 8065-2025 georefererad karta.tif", "A 8065-2025")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 8065-2025 FSC-klagomål.docx", "A 8065-2025")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 8065-2025 FSC-klagomål mail.docx", "A 8065-2025")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 8065-2025 tillsynsbegäran.docx", "A 8065-2025")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 8065-2025 tillsynsbegäran mail.docx", "A 8065-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 50684-2023</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>45210</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J22" t="n">
-        <v>2</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>1</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3</v>
-      </c>
-      <c r="T22" t="n">
-        <v>3</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Skogsalm
-Kopparödla
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 50684-2023 artfynd.xlsx", "A 50684-2023")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 50684-2023 karta.png", "A 50684-2023")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 50684-2023 georefererad karta.tif", "A 50684-2023")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 50684-2023 FSC-klagomål.docx", "A 50684-2023")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 50684-2023 FSC-klagomål mail.docx", "A 50684-2023")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 50684-2023 tillsynsbegäran.docx", "A 50684-2023")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 50684-2023 tillsynsbegäran mail.docx", "A 50684-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>A 31907-2023</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>45118</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>2</v>
-      </c>
-      <c r="L23" t="n">
-        <v>1</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3</v>
-      </c>
-      <c r="T23" t="n">
-        <v>3</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>Bokvårtlav
-Platt fjädermossa
-Stubbspretmossa</t>
-        </is>
-      </c>
-      <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 31907-2023 artfynd.xlsx", "A 31907-2023")</f>
-        <v/>
-      </c>
-      <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 31907-2023 karta.png", "A 31907-2023")</f>
-        <v/>
-      </c>
-      <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 31907-2023 georefererad karta.tif", "A 31907-2023")</f>
-        <v/>
-      </c>
-      <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 31907-2023 FSC-klagomål.docx", "A 31907-2023")</f>
-        <v/>
-      </c>
-      <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 31907-2023 FSC-klagomål mail.docx", "A 31907-2023")</f>
-        <v/>
-      </c>
-      <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 31907-2023 tillsynsbegäran.docx", "A 31907-2023")</f>
-        <v/>
-      </c>
-      <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 31907-2023 tillsynsbegäran mail.docx", "A 31907-2023")</f>
         <v/>
       </c>
     </row>
@@ -3092,7 +3092,7 @@
         <v>46041</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>45763</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3314,7 +3314,7 @@
         <v>45474</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3424,7 +3424,7 @@
         <v>45841</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
         <v>45105</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
         <v>44553</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3754,7 +3754,7 @@
         <v>45359</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
         <v>45582</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>44839</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>44742</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4180,7 +4180,7 @@
         <v>44746</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 44062-2022</t>
+          <t>A 12150-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4286,10 +4286,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44839</v>
+        <v>45377</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4302,20 +4302,20 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
         <v>1</v>
       </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
       <c r="N35" t="n">
         <v>0</v>
       </c>
@@ -4326,10 +4326,10 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4342,42 +4342,42 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 44062-2022 artfynd.xlsx", "A 44062-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 12150-2024 artfynd.xlsx", "A 12150-2024")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 44062-2022 karta.png", "A 44062-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 12150-2024 karta.png", "A 12150-2024")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 44062-2022 georefererad karta.tif", "A 44062-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 12150-2024 georefererad karta.tif", "A 12150-2024")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 44062-2022 FSC-klagomål.docx", "A 44062-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 12150-2024 FSC-klagomål.docx", "A 12150-2024")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 44062-2022 FSC-klagomål mail.docx", "A 44062-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 12150-2024 FSC-klagomål mail.docx", "A 12150-2024")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 44062-2022 tillsynsbegäran.docx", "A 44062-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 12150-2024 tillsynsbegäran.docx", "A 12150-2024")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 44062-2022 tillsynsbegäran mail.docx", "A 44062-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 12150-2024 tillsynsbegäran mail.docx", "A 12150-2024")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 46487-2024</t>
+          <t>A 4088-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4391,10 +4391,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45582</v>
+        <v>45323</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4407,17 +4407,17 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>5.8</v>
+        <v>3.8</v>
       </c>
       <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
         <v>1</v>
       </c>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
       <c r="M36" t="n">
         <v>0</v>
       </c>
@@ -4431,7 +4431,7 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -4443,46 +4443,46 @@
         <v>1</v>
       </c>
       <c r="U36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Flikbålmossa</t>
         </is>
       </c>
       <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 46487-2024 artfynd.xlsx", "A 46487-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 4088-2024 artfynd.xlsx", "A 4088-2024")</f>
         <v/>
       </c>
       <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 46487-2024 karta.png", "A 46487-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 4088-2024 karta.png", "A 4088-2024")</f>
         <v/>
       </c>
       <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 46487-2024 georefererad karta.tif", "A 46487-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 4088-2024 georefererad karta.tif", "A 4088-2024")</f>
         <v/>
       </c>
       <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 46487-2024 FSC-klagomål.docx", "A 46487-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 4088-2024 FSC-klagomål.docx", "A 4088-2024")</f>
         <v/>
       </c>
       <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 46487-2024 FSC-klagomål mail.docx", "A 46487-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 4088-2024 FSC-klagomål mail.docx", "A 4088-2024")</f>
         <v/>
       </c>
       <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 46487-2024 tillsynsbegäran.docx", "A 46487-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 4088-2024 tillsynsbegäran.docx", "A 4088-2024")</f>
         <v/>
       </c>
       <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 46487-2024 tillsynsbegäran mail.docx", "A 46487-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 4088-2024 tillsynsbegäran mail.docx", "A 4088-2024")</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 4088-2024</t>
+          <t>A 46487-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4496,10 +4496,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45323</v>
+        <v>45582</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4512,16 +4512,16 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.8</v>
+        <v>5.8</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
@@ -4536,7 +4536,7 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
@@ -4548,46 +4548,46 @@
         <v>1</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>Flikbålmossa</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="W37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 4088-2024 artfynd.xlsx", "A 4088-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 46487-2024 artfynd.xlsx", "A 46487-2024")</f>
         <v/>
       </c>
       <c r="X37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 4088-2024 karta.png", "A 4088-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 46487-2024 karta.png", "A 46487-2024")</f>
         <v/>
       </c>
       <c r="Y37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 4088-2024 georefererad karta.tif", "A 4088-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 46487-2024 georefererad karta.tif", "A 46487-2024")</f>
         <v/>
       </c>
       <c r="AA37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 4088-2024 FSC-klagomål.docx", "A 4088-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 46487-2024 FSC-klagomål.docx", "A 46487-2024")</f>
         <v/>
       </c>
       <c r="AB37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 4088-2024 FSC-klagomål mail.docx", "A 4088-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 46487-2024 FSC-klagomål mail.docx", "A 46487-2024")</f>
         <v/>
       </c>
       <c r="AC37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 4088-2024 tillsynsbegäran.docx", "A 4088-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 46487-2024 tillsynsbegäran.docx", "A 46487-2024")</f>
         <v/>
       </c>
       <c r="AD37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 4088-2024 tillsynsbegäran mail.docx", "A 4088-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 46487-2024 tillsynsbegäran mail.docx", "A 46487-2024")</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 25129-2024</t>
+          <t>A 50642-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4601,10 +4601,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45462</v>
+        <v>45210</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4617,16 +4617,16 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>4.6</v>
+        <v>0.8</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
@@ -4641,7 +4641,7 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -4657,42 +4657,42 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>Gullpudra</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 25129-2024 artfynd.xlsx", "A 25129-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 50642-2023 artfynd.xlsx", "A 50642-2023")</f>
         <v/>
       </c>
       <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 25129-2024 karta.png", "A 25129-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 50642-2023 karta.png", "A 50642-2023")</f>
         <v/>
       </c>
       <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 25129-2024 georefererad karta.tif", "A 25129-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 50642-2023 georefererad karta.tif", "A 50642-2023")</f>
         <v/>
       </c>
       <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 25129-2024 FSC-klagomål.docx", "A 25129-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 50642-2023 FSC-klagomål.docx", "A 50642-2023")</f>
         <v/>
       </c>
       <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 25129-2024 FSC-klagomål mail.docx", "A 25129-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 50642-2023 FSC-klagomål mail.docx", "A 50642-2023")</f>
         <v/>
       </c>
       <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 25129-2024 tillsynsbegäran.docx", "A 25129-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 50642-2023 tillsynsbegäran.docx", "A 50642-2023")</f>
         <v/>
       </c>
       <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 25129-2024 tillsynsbegäran mail.docx", "A 25129-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 50642-2023 tillsynsbegäran mail.docx", "A 50642-2023")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 12150-2024</t>
+          <t>A 25129-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4706,10 +4706,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45377</v>
+        <v>45462</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4722,7 +4722,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.4</v>
+        <v>4.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4731,10 +4731,10 @@
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
         <v>0</v>
@@ -4749,7 +4749,7 @@
         <v>1</v>
       </c>
       <c r="R39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
@@ -4758,39 +4758,39 @@
         <v>1</v>
       </c>
       <c r="U39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 12150-2024 artfynd.xlsx", "A 12150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 25129-2024 artfynd.xlsx", "A 25129-2024")</f>
         <v/>
       </c>
       <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 12150-2024 karta.png", "A 12150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 25129-2024 karta.png", "A 25129-2024")</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 12150-2024 georefererad karta.tif", "A 12150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 25129-2024 georefererad karta.tif", "A 25129-2024")</f>
         <v/>
       </c>
       <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 12150-2024 FSC-klagomål.docx", "A 12150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 25129-2024 FSC-klagomål.docx", "A 25129-2024")</f>
         <v/>
       </c>
       <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 12150-2024 FSC-klagomål mail.docx", "A 12150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 25129-2024 FSC-klagomål mail.docx", "A 25129-2024")</f>
         <v/>
       </c>
       <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 12150-2024 tillsynsbegäran.docx", "A 12150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 25129-2024 tillsynsbegäran.docx", "A 25129-2024")</f>
         <v/>
       </c>
       <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 12150-2024 tillsynsbegäran mail.docx", "A 12150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 25129-2024 tillsynsbegäran mail.docx", "A 25129-2024")</f>
         <v/>
       </c>
     </row>
@@ -4814,7 +4814,7 @@
         <v>44498</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 50642-2023</t>
+          <t>A 44062-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45210</v>
+        <v>44839</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4932,13 +4932,13 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
         <v>1</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -4968,39 +4968,39 @@
         <v>1</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 50642-2023 artfynd.xlsx", "A 50642-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 44062-2022 artfynd.xlsx", "A 44062-2022")</f>
         <v/>
       </c>
       <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 50642-2023 karta.png", "A 50642-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 44062-2022 karta.png", "A 44062-2022")</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 50642-2023 georefererad karta.tif", "A 50642-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 44062-2022 georefererad karta.tif", "A 44062-2022")</f>
         <v/>
       </c>
       <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 50642-2023 FSC-klagomål.docx", "A 50642-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 44062-2022 FSC-klagomål.docx", "A 44062-2022")</f>
         <v/>
       </c>
       <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 50642-2023 FSC-klagomål mail.docx", "A 50642-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 44062-2022 FSC-klagomål mail.docx", "A 44062-2022")</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 50642-2023 tillsynsbegäran.docx", "A 50642-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 44062-2022 tillsynsbegäran.docx", "A 44062-2022")</f>
         <v/>
       </c>
       <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 50642-2023 tillsynsbegäran mail.docx", "A 50642-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 44062-2022 tillsynsbegäran mail.docx", "A 44062-2022")</f>
         <v/>
       </c>
     </row>
@@ -5024,7 +5024,7 @@
         <v>46188</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5129,7 +5129,7 @@
         <v>46265</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5238,7 +5238,7 @@
         <v>46224</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         <v>45084</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5448,7 +5448,7 @@
         <v>44862</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5553,7 +5553,7 @@
         <v>44880</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5626,7 +5626,7 @@
         <v>44839</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5699,7 +5699,7 @@
         <v>44725</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5772,7 +5772,7 @@
         <v>44840</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5845,7 +5845,7 @@
         <v>44498</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5918,7 +5918,7 @@
         <v>44477</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5991,7 +5991,7 @@
         <v>44657</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6064,7 +6064,7 @@
         <v>44634</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6137,7 +6137,7 @@
         <v>44802</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6210,7 +6210,7 @@
         <v>44802</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6283,7 +6283,7 @@
         <v>44827</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6356,7 +6356,7 @@
         <v>44480</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6429,7 +6429,7 @@
         <v>44634</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 40275-2023</t>
+          <t>A 29436-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6499,10 +6499,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45169</v>
+        <v>45483</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6515,7 +6515,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.6</v>
+        <v>4.2</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6558,7 +6558,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 6667-2025</t>
+          <t>A 8882-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6572,10 +6572,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45700</v>
+        <v>45713</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6588,7 +6588,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6631,7 +6631,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 23980-2024</t>
+          <t>A 12148-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6645,10 +6645,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45456</v>
+        <v>45377</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -6704,7 +6704,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 55748-2024</t>
+          <t>A 9578-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6718,10 +6718,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45623</v>
+        <v>45715</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -6777,7 +6777,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 48197-2024</t>
+          <t>A 53501-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6791,10 +6791,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45590</v>
+        <v>44879</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>3.1</v>
+        <v>7.2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6850,7 +6850,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 46702-2024</t>
+          <t>A 27551-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6864,10 +6864,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45583</v>
+        <v>45097</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6923,7 +6923,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 40287-2025</t>
+          <t>A 64728-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6937,10 +6937,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45895</v>
+        <v>45281</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6953,7 +6953,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6996,7 +6996,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 31789-2023</t>
+          <t>A 48197-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -7010,10 +7010,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45118</v>
+        <v>45590</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7026,7 +7026,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1.1</v>
+        <v>3.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -7069,7 +7069,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 1644-2025</t>
+          <t>A 31720-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7083,10 +7083,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45670</v>
+        <v>45117</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7099,7 +7099,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -7142,7 +7142,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 42826-2025</t>
+          <t>A 25669-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7156,10 +7156,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45908</v>
+        <v>45463</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7172,7 +7172,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.1</v>
+        <v>17.9</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7215,7 +7215,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 55545-2022</t>
+          <t>A 31143-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7225,14 +7225,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44887</v>
+        <v>45502</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7245,7 +7245,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>4.4</v>
+        <v>0.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7288,7 +7288,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 55529-2024</t>
+          <t>A 607-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7302,10 +7302,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45622</v>
+        <v>45299</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7318,7 +7318,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 32020-2025</t>
+          <t>A 54709-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7375,10 +7375,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45835</v>
+        <v>45236</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7391,7 +7391,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.7</v>
+        <v>3.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7434,7 +7434,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 64728-2023</t>
+          <t>A 40287-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7448,10 +7448,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45281</v>
+        <v>45895</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7464,7 +7464,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7507,7 +7507,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 25669-2024</t>
+          <t>A 55544-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7521,10 +7521,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45463</v>
+        <v>44887</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7537,7 +7537,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>17.9</v>
+        <v>1.1</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -7580,7 +7580,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 23676-2024</t>
+          <t>A 42826-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7594,10 +7594,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45454</v>
+        <v>45908</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7610,7 +7610,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7653,7 +7653,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 13662-2025</t>
+          <t>A 23976-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7667,10 +7667,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45736</v>
+        <v>45456</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7683,7 +7683,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>6.4</v>
+        <v>0.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7726,7 +7726,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 52519-2025</t>
+          <t>A 27553-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7740,10 +7740,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45954</v>
+        <v>45097</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7756,7 +7756,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7799,7 +7799,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 8139-2025</t>
+          <t>A 55529-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7813,10 +7813,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45708</v>
+        <v>45622</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7829,7 +7829,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3.5</v>
+        <v>2.2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7872,7 +7872,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 44448-2023</t>
+          <t>A 28253-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7886,10 +7886,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45189</v>
+        <v>45099</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7902,7 +7902,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.6</v>
+        <v>2.7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7945,7 +7945,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 31143-2024</t>
+          <t>A 16419-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7955,14 +7955,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45502</v>
+        <v>45022</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7975,7 +7975,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.6</v>
+        <v>4.2</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -8018,7 +8018,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 55728-2025</t>
+          <t>A 32020-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -8032,10 +8032,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45972</v>
+        <v>45835</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -8091,7 +8091,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 23328-2022</t>
+          <t>A 19503-2022</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -8105,10 +8105,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44720</v>
+        <v>44693</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8121,7 +8121,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1.1</v>
+        <v>5.1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8164,7 +8164,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 15154-2023</t>
+          <t>A 13662-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8178,10 +8178,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45016</v>
+        <v>45736</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8194,7 +8194,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>3.5</v>
+        <v>6.4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8237,7 +8237,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 57725-2025</t>
+          <t>A 46702-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8251,10 +8251,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45981</v>
+        <v>45583</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8267,7 +8267,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8310,7 +8310,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 46286-2024</t>
+          <t>A 49206-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8324,10 +8324,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45581</v>
+        <v>45595</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8340,7 +8340,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8383,7 +8383,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 55544-2022</t>
+          <t>A 52519-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8397,10 +8397,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>44887</v>
+        <v>45954</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8413,7 +8413,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8456,7 +8456,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 7337-2024</t>
+          <t>A 31503-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8470,10 +8470,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45345</v>
+        <v>45115</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8486,7 +8486,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -8529,7 +8529,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 49610-2024</t>
+          <t>A 55728-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8543,10 +8543,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45596</v>
+        <v>45972</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8559,7 +8559,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>6.4</v>
+        <v>1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -8602,7 +8602,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 13243-2025</t>
+          <t>A 9055-2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8616,10 +8616,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45735</v>
+        <v>46069</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8632,7 +8632,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -8675,7 +8675,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 9055-2026</t>
+          <t>A 57725-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8689,10 +8689,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>46069</v>
+        <v>45981</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -8748,7 +8748,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 7811-2023</t>
+          <t>A 23328-2022</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8762,10 +8762,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44973</v>
+        <v>44720</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8778,7 +8778,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -8821,7 +8821,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 58137-2022</t>
+          <t>A 32364-2023</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8835,10 +8835,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>44900</v>
+        <v>45120</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 42105-2022</t>
+          <t>A 8139-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8908,10 +8908,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>44830</v>
+        <v>45708</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8924,7 +8924,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -8967,7 +8967,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 50652-2023</t>
+          <t>A 40275-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8981,10 +8981,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45210</v>
+        <v>45169</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8997,7 +8997,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.4</v>
+        <v>0.6</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -9040,7 +9040,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 24855-2024</t>
+          <t>A 1644-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -9054,10 +9054,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45461</v>
+        <v>45670</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9070,7 +9070,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2.4</v>
+        <v>1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -9113,7 +9113,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 4755-2024</t>
+          <t>A 24855-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -9127,10 +9127,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45328</v>
+        <v>45461</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9143,7 +9143,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9186,7 +9186,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 14400-2023</t>
+          <t>A 9803-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9200,10 +9200,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45012</v>
+        <v>46072</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9216,7 +9216,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.7</v>
+        <v>5</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -9259,7 +9259,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 23227-2023</t>
+          <t>A 7871-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9273,10 +9273,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45075</v>
+        <v>45706</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9332,7 +9332,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 9578-2025</t>
+          <t>A 13243-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9346,10 +9346,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45715</v>
+        <v>45735</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9405,7 +9405,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 9803-2026</t>
+          <t>A 6667-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9419,10 +9419,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>46072</v>
+        <v>45700</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9435,7 +9435,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9478,7 +9478,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 8882-2025</t>
+          <t>A 58137-2022</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9492,10 +9492,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45713</v>
+        <v>44900</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9508,7 +9508,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9551,7 +9551,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 7707-2025</t>
+          <t>A 19650-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9565,10 +9565,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45705</v>
+        <v>46134</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9581,7 +9581,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.2</v>
+        <v>8</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -9624,7 +9624,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 19650-2026</t>
+          <t>A 2575-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9638,10 +9638,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46134</v>
+        <v>45313</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9654,7 +9654,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -9697,7 +9697,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 58134-2022</t>
+          <t>A 31502-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9711,10 +9711,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44900</v>
+        <v>45115</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9727,7 +9727,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -9770,7 +9770,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 74214-2021</t>
+          <t>A 7707-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9784,10 +9784,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44553</v>
+        <v>45705</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9800,7 +9800,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>19.8</v>
+        <v>1.2</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9843,7 +9843,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 18571-2025</t>
+          <t>A 46286-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9857,10 +9857,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45763</v>
+        <v>45581</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9873,7 +9873,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9916,7 +9916,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 16419-2023</t>
+          <t>A 58134-2022</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9930,10 +9930,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45022</v>
+        <v>44900</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9946,7 +9946,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>4.2</v>
+        <v>1.2</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9989,7 +9989,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 27551-2023</t>
+          <t>A 74214-2021</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -10003,10 +10003,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45097</v>
+        <v>44553</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10019,7 +10019,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.6</v>
+        <v>19.8</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -10062,7 +10062,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 2575-2024</t>
+          <t>A 7994-2023</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10076,10 +10076,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45313</v>
+        <v>44973</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10092,7 +10092,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -10135,7 +10135,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 4089-2024</t>
+          <t>A 8665-2022</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10149,10 +10149,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45323</v>
+        <v>44613</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10165,7 +10165,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -10208,7 +10208,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 28496-2023</t>
+          <t>A 18571-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10222,10 +10222,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45103</v>
+        <v>45763</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10238,7 +10238,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -10281,7 +10281,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 1299-2024</t>
+          <t>A 31709-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10295,10 +10295,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45303</v>
+        <v>45117</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10311,7 +10311,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10354,7 +10354,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 32364-2023</t>
+          <t>A 23227-2023</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10368,10 +10368,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45120</v>
+        <v>45075</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10384,7 +10384,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10427,7 +10427,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 31503-2023</t>
+          <t>A 50652-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10441,10 +10441,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45115</v>
+        <v>45210</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10457,7 +10457,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10500,7 +10500,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 39014-2023</t>
+          <t>A 40278-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10514,10 +10514,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45163</v>
+        <v>45169</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10530,7 +10530,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10573,7 +10573,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 31908-2023</t>
+          <t>A 31789-2023</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10590,7 +10590,7 @@
         <v>45118</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10603,7 +10603,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10646,7 +10646,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 31502-2023</t>
+          <t>A 60227-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10660,10 +10660,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45115</v>
+        <v>45994</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10676,7 +10676,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10719,7 +10719,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 28253-2023</t>
+          <t>A 43857-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10733,10 +10733,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45099</v>
+        <v>45912</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10749,7 +10749,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10792,7 +10792,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 21488-2023</t>
+          <t>A 39014-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10806,10 +10806,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45061</v>
+        <v>45163</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10822,7 +10822,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10865,7 +10865,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 7994-2023</t>
+          <t>A 19500-2022</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10879,10 +10879,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>44973</v>
+        <v>44693</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10895,7 +10895,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10938,7 +10938,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 43857-2025</t>
+          <t>A 44448-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10952,10 +10952,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45912</v>
+        <v>45189</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10968,7 +10968,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -11011,7 +11011,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 27553-2023</t>
+          <t>A 13278-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -11025,10 +11025,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45097</v>
+        <v>46093</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11041,7 +11041,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -11084,7 +11084,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 60227-2025</t>
+          <t>A 57923-2024</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -11098,10 +11098,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45994</v>
+        <v>45631</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11114,7 +11114,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.5</v>
+        <v>4.5</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -11157,7 +11157,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 13278-2026</t>
+          <t>A 28264-2022</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -11171,10 +11171,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46093</v>
+        <v>44746</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11187,7 +11187,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -11230,7 +11230,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 53501-2022</t>
+          <t>A 27097-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11244,10 +11244,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>44879</v>
+        <v>46188</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11260,7 +11260,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>7.2</v>
+        <v>4</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -11303,7 +11303,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 27097-2026</t>
+          <t>A 55545-2022</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11317,10 +11317,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46188</v>
+        <v>44887</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11333,7 +11333,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11376,7 +11376,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 54709-2023</t>
+          <t>A 34514-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11390,10 +11390,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45236</v>
+        <v>45140</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11406,7 +11406,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11449,7 +11449,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 12148-2024</t>
+          <t>A 1299-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45377</v>
+        <v>45303</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11479,7 +11479,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11522,7 +11522,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 19500-2022</t>
+          <t>A 29369-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11536,10 +11536,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>44693</v>
+        <v>46203</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11552,7 +11552,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11595,7 +11595,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 4605-2025</t>
+          <t>A 42105-2022</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11609,10 +11609,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45687</v>
+        <v>44830</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11625,7 +11625,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11668,7 +11668,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 31720-2023</t>
+          <t>A 15154-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11682,10 +11682,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45117</v>
+        <v>45016</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11698,7 +11698,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11741,7 +11741,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 16314-2024</t>
+          <t>A 7337-2024</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11755,10 +11755,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45407</v>
+        <v>45345</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11771,7 +11771,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11814,7 +11814,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 29369-2026</t>
+          <t>A 49610-2024</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11828,10 +11828,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46203</v>
+        <v>45596</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11844,7 +11844,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>1.3</v>
+        <v>6.4</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11887,7 +11887,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 34514-2023</t>
+          <t>A 14400-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11901,10 +11901,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45140</v>
+        <v>45012</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11917,7 +11917,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>3.1</v>
+        <v>1.7</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11960,7 +11960,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 46613-2024</t>
+          <t>A 4089-2024</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11974,10 +11974,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45583</v>
+        <v>45323</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11990,7 +11990,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>6.2</v>
+        <v>0.7</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -12033,7 +12033,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 23976-2024</t>
+          <t>A 31576-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -12047,10 +12047,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45456</v>
+        <v>46224</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12106,7 +12106,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 40278-2023</t>
+          <t>A 36001-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -12120,10 +12120,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45169</v>
+        <v>46266</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12136,7 +12136,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 7871-2025</t>
+          <t>A 23676-2024</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -12193,10 +12193,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45706</v>
+        <v>45454</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12209,7 +12209,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -12252,7 +12252,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 32430-2023</t>
+          <t>A 35912-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12266,10 +12266,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45120</v>
+        <v>46266</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12282,7 +12282,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -12325,7 +12325,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 29436-2024</t>
+          <t>A 60-2024</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12339,10 +12339,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45483</v>
+        <v>45293</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12355,7 +12355,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>4.2</v>
+        <v>1.2</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -12398,7 +12398,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 31576-2026</t>
+          <t>A 58150-2024</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12412,10 +12412,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46224</v>
+        <v>45632</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12428,7 +12428,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12471,7 +12471,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 36001-2026</t>
+          <t>A 4755-2024</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12485,10 +12485,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46266</v>
+        <v>45328</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12501,7 +12501,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12544,7 +12544,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 35912-2026</t>
+          <t>A 37628-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12558,10 +12558,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46266</v>
+        <v>46276</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12573,8 +12573,13 @@
           <t>ÄNGELHOLM</t>
         </is>
       </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I143" t="n">
-        <v>1.3</v>
+        <v>4.5</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12617,7 +12622,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 58150-2024</t>
+          <t>A 26978-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12631,10 +12636,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45632</v>
+        <v>46185</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12647,7 +12652,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>0.5</v>
+        <v>7.7</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12690,7 +12695,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 28264-2022</t>
+          <t>A 26986-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12704,10 +12709,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>44746</v>
+        <v>46185</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12720,7 +12725,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12763,7 +12768,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 31709-2023</t>
+          <t>A 32430-2023</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12777,10 +12782,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45117</v>
+        <v>45120</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12793,7 +12798,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12836,7 +12841,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 8665-2022</t>
+          <t>A 28496-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12850,10 +12855,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>44613</v>
+        <v>45103</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12866,7 +12871,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12909,7 +12914,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 60-2024</t>
+          <t>A 4605-2025</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12923,10 +12928,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45293</v>
+        <v>45687</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12939,7 +12944,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12982,7 +12987,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 607-2024</t>
+          <t>A 21488-2023</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12996,10 +13001,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45299</v>
+        <v>45061</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13012,7 +13017,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -13055,7 +13060,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 49206-2024</t>
+          <t>A 31908-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -13069,10 +13074,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45595</v>
+        <v>45118</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13085,7 +13090,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -13128,7 +13133,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 19503-2022</t>
+          <t>A 7811-2023</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -13142,10 +13147,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>44693</v>
+        <v>44973</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13158,7 +13163,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>5.1</v>
+        <v>0.9</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -13201,7 +13206,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 37628-2026</t>
+          <t>A 16314-2024</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -13215,10 +13220,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46276</v>
+        <v>45407</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13230,13 +13235,8 @@
           <t>ÄNGELHOLM</t>
         </is>
       </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I152" t="n">
-        <v>4.5</v>
+        <v>1.1</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -13279,7 +13279,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 57923-2024</t>
+          <t>A 46613-2024</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -13293,10 +13293,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45631</v>
+        <v>45583</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13309,7 +13309,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>4.5</v>
+        <v>6.2</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -13352,7 +13352,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 26986-2026</t>
+          <t>A 35677-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -13366,10 +13366,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46185</v>
+        <v>46265</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13382,7 +13382,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -13425,7 +13425,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 26978-2026</t>
+          <t>A 20635-2024</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13439,10 +13439,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46185</v>
+        <v>45436</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13455,7 +13455,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>7.7</v>
+        <v>4.8</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13498,7 +13498,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 20635-2024</t>
+          <t>A 23980-2024</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13512,10 +13512,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45436</v>
+        <v>45456</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13528,7 +13528,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>4.8</v>
+        <v>1.3</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13571,7 +13571,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 39993-2026</t>
+          <t>A 55748-2024</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13585,10 +13585,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46293</v>
+        <v>45623</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13601,7 +13601,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>6.3</v>
+        <v>0.9</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13644,7 +13644,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 19255-2026</t>
+          <t>A 39993-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13658,10 +13658,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46132</v>
+        <v>46293</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13674,7 +13674,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>1</v>
+        <v>6.3</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13717,7 +13717,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 19256-2026</t>
+          <t>A 19255-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13734,7 +13734,7 @@
         <v>46132</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13747,7 +13747,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13790,7 +13790,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 35677-2026</t>
+          <t>A 19256-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13804,10 +13804,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46265</v>
+        <v>46132</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13820,7 +13820,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>3.1</v>
+        <v>0.7</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13880,7 +13880,7 @@
         <v>45582</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13953,7 +13953,7 @@
         <v>45582</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14026,7 +14026,7 @@
         <v>45582</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14099,7 +14099,7 @@
         <v>45582</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14172,7 +14172,7 @@
         <v>44519</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14245,7 +14245,7 @@
         <v>45239</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14318,7 +14318,7 @@
         <v>45168</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14391,7 +14391,7 @@
         <v>44861</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14464,7 +14464,7 @@
         <v>45582</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>

--- a/Översikt ÄNGELHOLM.xlsx
+++ b/Översikt ÄNGELHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45099</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         <v>45931</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
         <v>45931</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>46106</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>44802</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 74502-2021</t>
+          <t>A 32268-2022</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1204,10 +1204,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44560</v>
+        <v>44781</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1220,17 +1220,17 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>5.6</v>
+        <v>8.6</v>
       </c>
       <c r="J7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K7" t="n">
+        <v>5</v>
+      </c>
+      <c r="L7" t="n">
         <v>1</v>
       </c>
-      <c r="L7" t="n">
-        <v>3</v>
-      </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
@@ -1244,7 +1244,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1253,12 +1253,124 @@
         <v>8</v>
       </c>
       <c r="T7" t="n">
+        <v>14</v>
+      </c>
+      <c r="U7" t="n">
+        <v>14</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Bokvårtlav
+Blåmossa
+Dvärghäxört
+Skuggsprötmossa
+Trubbfjädermossa
+Västlig hakmossa
+Vanlig groda
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 32268-2022 artfynd.xlsx", "A 32268-2022")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 32268-2022 karta.png", "A 32268-2022")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 32268-2022 georefererad karta.tif", "A 32268-2022")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 32268-2022 FSC-klagomål.docx", "A 32268-2022")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 32268-2022 FSC-klagomål mail.docx", "A 32268-2022")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 32268-2022 tillsynsbegäran.docx", "A 32268-2022")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 32268-2022 tillsynsbegäran mail.docx", "A 32268-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 74502-2021</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>44560</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J8" t="n">
+        <v>6</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>3</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>8</v>
+      </c>
+      <c r="T8" t="n">
         <v>9</v>
       </c>
-      <c r="U7" t="n">
+      <c r="U8" t="n">
         <v>9</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Entita
 Grönsångare
@@ -1270,148 +1382,36 @@
 Skogsduva</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 74502-2021 artfynd.xlsx", "A 74502-2021")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 74502-2021 karta.png", "A 74502-2021")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 74502-2021 georefererad karta.tif", "A 74502-2021")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 74502-2021 FSC-klagomål.docx", "A 74502-2021")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 74502-2021 FSC-klagomål mail.docx", "A 74502-2021")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 74502-2021 tillsynsbegäran.docx", "A 74502-2021")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 74502-2021 tillsynsbegäran mail.docx", "A 74502-2021")</f>
         <v/>
       </c>
-      <c r="AE7">
+      <c r="AE8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 74502-2021 prioriterade fågelarter.docx", "A 74502-2021")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 32268-2022</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>44781</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="J8" t="n">
-        <v>2</v>
-      </c>
-      <c r="K8" t="n">
-        <v>5</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>8</v>
-      </c>
-      <c r="T8" t="n">
-        <v>14</v>
-      </c>
-      <c r="U8" t="n">
-        <v>14</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Bokvårtlav
-Blåmossa
-Dvärghäxört
-Skuggsprötmossa
-Trubbfjädermossa
-Västlig hakmossa
-Vanlig groda
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 32268-2022 artfynd.xlsx", "A 32268-2022")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 32268-2022 karta.png", "A 32268-2022")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 32268-2022 georefererad karta.tif", "A 32268-2022")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 32268-2022 FSC-klagomål.docx", "A 32268-2022")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 32268-2022 FSC-klagomål mail.docx", "A 32268-2022")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 32268-2022 tillsynsbegäran.docx", "A 32268-2022")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 32268-2022 tillsynsbegäran mail.docx", "A 32268-2022")</f>
         <v/>
       </c>
     </row>
@@ -1435,7 +1435,7 @@
         <v>45835</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>44929</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         <v>44593</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>45106</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>45245</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1998,7 +1998,7 @@
         <v>46038</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 35675-2026</t>
+          <t>A 35680-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2111,7 +2111,7 @@
         <v>46265</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2124,16 +2124,16 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>8.9</v>
+        <v>2.9</v>
       </c>
       <c r="J15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M15" t="n">
         <v>1</v>
@@ -2148,7 +2148,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R15" t="n">
         <v>1</v>
@@ -2157,12 +2157,125 @@
         <v>5</v>
       </c>
       <c r="T15" t="n">
+        <v>7</v>
+      </c>
+      <c r="U15" t="n">
+        <v>7</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Vedlavklubba
+Entita
+Kandelabersvamp
+Blåmossa
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 35680-2026 artfynd.xlsx", "A 35680-2026")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 35680-2026 karta.png", "A 35680-2026")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 35680-2026 georefererad karta.tif", "A 35680-2026")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 35680-2026 FSC-klagomål.docx", "A 35680-2026")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 35680-2026 FSC-klagomål mail.docx", "A 35680-2026")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 35680-2026 tillsynsbegäran.docx", "A 35680-2026")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 35680-2026 tillsynsbegäran mail.docx", "A 35680-2026")</f>
+        <v/>
+      </c>
+      <c r="AE15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 35680-2026 prioriterade fågelarter.docx", "A 35680-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 35675-2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="J16" t="n">
+        <v>4</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="n">
         <v>10</v>
       </c>
-      <c r="U15" t="n">
+      <c r="U16" t="n">
         <v>9</v>
       </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Lappuggla
 Entita
@@ -2171,149 +2284,36 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 35675-2026 artfynd.xlsx", "A 35675-2026")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 35675-2026 karta.png", "A 35675-2026")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 35675-2026 georefererad karta.tif", "A 35675-2026")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 35675-2026 FSC-klagomål.docx", "A 35675-2026")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 35675-2026 FSC-klagomål mail.docx", "A 35675-2026")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 35675-2026 tillsynsbegäran.docx", "A 35675-2026")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 35675-2026 tillsynsbegäran mail.docx", "A 35675-2026")</f>
         <v/>
       </c>
-      <c r="AE15">
+      <c r="AE16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 35675-2026 prioriterade fågelarter.docx", "A 35675-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 35680-2026</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J16" t="n">
-        <v>2</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" t="n">
-        <v>2</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>3</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1</v>
-      </c>
-      <c r="S16" t="n">
-        <v>5</v>
-      </c>
-      <c r="T16" t="n">
-        <v>7</v>
-      </c>
-      <c r="U16" t="n">
-        <v>7</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Vedlavklubba
-Entita
-Kandelabersvamp
-Blåmossa
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 35680-2026 artfynd.xlsx", "A 35680-2026")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 35680-2026 karta.png", "A 35680-2026")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 35680-2026 georefererad karta.tif", "A 35680-2026")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 35680-2026 FSC-klagomål.docx", "A 35680-2026")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 35680-2026 FSC-klagomål mail.docx", "A 35680-2026")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 35680-2026 tillsynsbegäran.docx", "A 35680-2026")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 35680-2026 tillsynsbegäran mail.docx", "A 35680-2026")</f>
-        <v/>
-      </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 35680-2026 prioriterade fågelarter.docx", "A 35680-2026")</f>
         <v/>
       </c>
     </row>
@@ -2337,7 +2337,7 @@
         <v>45664</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2449,7 +2449,7 @@
         <v>44864</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 28874-2023</t>
+          <t>A 50684-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2554,10 +2554,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45104</v>
+        <v>45210</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2570,23 +2570,23 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>9</v>
+        <v>1.6</v>
       </c>
       <c r="J19" t="n">
+        <v>2</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
         <v>1</v>
       </c>
-      <c r="K19" t="n">
-        <v>2</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
       <c r="O19" t="n">
         <v>0</v>
       </c>
@@ -2594,710 +2594,710 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S19" t="n">
         <v>3</v>
       </c>
       <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Skogsalm
+Kopparödla
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 50684-2023 artfynd.xlsx", "A 50684-2023")</f>
+        <v/>
+      </c>
+      <c r="X19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 50684-2023 karta.png", "A 50684-2023")</f>
+        <v/>
+      </c>
+      <c r="Y19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 50684-2023 georefererad karta.tif", "A 50684-2023")</f>
+        <v/>
+      </c>
+      <c r="AA19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 50684-2023 FSC-klagomål.docx", "A 50684-2023")</f>
+        <v/>
+      </c>
+      <c r="AB19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 50684-2023 FSC-klagomål mail.docx", "A 50684-2023")</f>
+        <v/>
+      </c>
+      <c r="AC19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 50684-2023 tillsynsbegäran.docx", "A 50684-2023")</f>
+        <v/>
+      </c>
+      <c r="AD19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 50684-2023 tillsynsbegäran mail.docx", "A 50684-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A 905-2024</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>45301</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Igelkott
+Desmeknopp
+Myskmadra</t>
+        </is>
+      </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 905-2024 artfynd.xlsx", "A 905-2024")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 905-2024 karta.png", "A 905-2024")</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 905-2024 georefererad karta.tif", "A 905-2024")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 905-2024 FSC-klagomål.docx", "A 905-2024")</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 905-2024 FSC-klagomål mail.docx", "A 905-2024")</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 905-2024 tillsynsbegäran.docx", "A 905-2024")</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 905-2024 tillsynsbegäran mail.docx", "A 905-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 18559-2025</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>45763</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>3</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>3</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Grönsångare
+Gulsparv
+Gröngöling</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 18559-2025 artfynd.xlsx", "A 18559-2025")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 18559-2025 karta.png", "A 18559-2025")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 18559-2025 georefererad karta.tif", "A 18559-2025")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 18559-2025 FSC-klagomål.docx", "A 18559-2025")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 18559-2025 FSC-klagomål mail.docx", "A 18559-2025")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 18559-2025 tillsynsbegäran.docx", "A 18559-2025")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 18559-2025 tillsynsbegäran mail.docx", "A 18559-2025")</f>
+        <v/>
+      </c>
+      <c r="AE21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 18559-2025 prioriterade fågelarter.docx", "A 18559-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 28874-2023</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>45104</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>9</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3</v>
+      </c>
+      <c r="T22" t="n">
         <v>5</v>
       </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>Blåmossa
 Stubbspretmossa
 Revlummer</t>
         </is>
       </c>
-      <c r="W19">
+      <c r="W22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 28874-2023 artfynd.xlsx", "A 28874-2023")</f>
         <v/>
       </c>
-      <c r="X19">
+      <c r="X22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 28874-2023 karta.png", "A 28874-2023")</f>
         <v/>
       </c>
-      <c r="Y19">
+      <c r="Y22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 28874-2023 georefererad karta.tif", "A 28874-2023")</f>
         <v/>
       </c>
-      <c r="AA19">
+      <c r="AA22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 28874-2023 FSC-klagomål.docx", "A 28874-2023")</f>
         <v/>
       </c>
-      <c r="AB19">
+      <c r="AB22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 28874-2023 FSC-klagomål mail.docx", "A 28874-2023")</f>
         <v/>
       </c>
-      <c r="AC19">
+      <c r="AC22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 28874-2023 tillsynsbegäran.docx", "A 28874-2023")</f>
         <v/>
       </c>
-      <c r="AD19">
+      <c r="AD22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 28874-2023 tillsynsbegäran mail.docx", "A 28874-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
         <is>
           <t>A 31907-2023</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
         <v>45118</v>
       </c>
-      <c r="E20" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
+      <c r="E23" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
         <v>5.3</v>
       </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
         <v>2</v>
       </c>
-      <c r="L20" t="n">
+      <c r="L23" t="n">
         <v>1</v>
       </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
         <v>1</v>
       </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
         <v>3</v>
       </c>
-      <c r="T20" t="n">
+      <c r="T23" t="n">
         <v>3</v>
       </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>Bokvårtlav
 Platt fjädermossa
 Stubbspretmossa</t>
         </is>
       </c>
-      <c r="W20">
+      <c r="W23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 31907-2023 artfynd.xlsx", "A 31907-2023")</f>
         <v/>
       </c>
-      <c r="X20">
+      <c r="X23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 31907-2023 karta.png", "A 31907-2023")</f>
         <v/>
       </c>
-      <c r="Y20">
+      <c r="Y23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 31907-2023 georefererad karta.tif", "A 31907-2023")</f>
         <v/>
       </c>
-      <c r="AA20">
+      <c r="AA23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 31907-2023 FSC-klagomål.docx", "A 31907-2023")</f>
         <v/>
       </c>
-      <c r="AB20">
+      <c r="AB23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 31907-2023 FSC-klagomål mail.docx", "A 31907-2023")</f>
         <v/>
       </c>
-      <c r="AC20">
+      <c r="AC23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 31907-2023 tillsynsbegäran.docx", "A 31907-2023")</f>
         <v/>
       </c>
-      <c r="AD20">
+      <c r="AD23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 31907-2023 tillsynsbegäran mail.docx", "A 31907-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A 50684-2023</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>45210</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J21" t="n">
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>A 8065-2025</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="n">
+        <v>45707</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
         <v>2</v>
       </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
+      <c r="M24" t="n">
         <v>1</v>
       </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>3</v>
+      </c>
+      <c r="R24" t="n">
         <v>1</v>
       </c>
-      <c r="R21" t="n">
-        <v>1</v>
-      </c>
-      <c r="S21" t="n">
+      <c r="S24" t="n">
         <v>3</v>
       </c>
-      <c r="T21" t="n">
+      <c r="T24" t="n">
         <v>3</v>
       </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>Skogsalm
-Kopparödla
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 50684-2023 artfynd.xlsx", "A 50684-2023")</f>
-        <v/>
-      </c>
-      <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 50684-2023 karta.png", "A 50684-2023")</f>
-        <v/>
-      </c>
-      <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 50684-2023 georefererad karta.tif", "A 50684-2023")</f>
-        <v/>
-      </c>
-      <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 50684-2023 FSC-klagomål.docx", "A 50684-2023")</f>
-        <v/>
-      </c>
-      <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 50684-2023 FSC-klagomål mail.docx", "A 50684-2023")</f>
-        <v/>
-      </c>
-      <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 50684-2023 tillsynsbegäran.docx", "A 50684-2023")</f>
-        <v/>
-      </c>
-      <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 50684-2023 tillsynsbegäran mail.docx", "A 50684-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 8065-2025</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>45707</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
+      <c r="U24" t="n">
         <v>2</v>
       </c>
-      <c r="M22" t="n">
-        <v>1</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>3</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3</v>
-      </c>
-      <c r="T22" t="n">
-        <v>3</v>
-      </c>
-      <c r="U22" t="n">
-        <v>2</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
+      <c r="V24" s="2" t="inlineStr">
         <is>
           <t>Småvänderot
 Gullpudra
 Svinrot</t>
         </is>
       </c>
-      <c r="W22">
+      <c r="W24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 8065-2025 artfynd.xlsx", "A 8065-2025")</f>
         <v/>
       </c>
-      <c r="X22">
+      <c r="X24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 8065-2025 karta.png", "A 8065-2025")</f>
         <v/>
       </c>
-      <c r="Y22">
+      <c r="Y24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 8065-2025 georefererad karta.tif", "A 8065-2025")</f>
         <v/>
       </c>
-      <c r="AA22">
+      <c r="AA24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 8065-2025 FSC-klagomål.docx", "A 8065-2025")</f>
         <v/>
       </c>
-      <c r="AB22">
+      <c r="AB24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 8065-2025 FSC-klagomål mail.docx", "A 8065-2025")</f>
         <v/>
       </c>
-      <c r="AC22">
+      <c r="AC24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 8065-2025 tillsynsbegäran.docx", "A 8065-2025")</f>
         <v/>
       </c>
-      <c r="AD22">
+      <c r="AD24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 8065-2025 tillsynsbegäran mail.docx", "A 8065-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>A 905-2024</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>45301</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>1</v>
-      </c>
-      <c r="L23" t="n">
-        <v>1</v>
-      </c>
-      <c r="M23" t="n">
-        <v>1</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>A 3317-2026</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="n">
+        <v>46041</v>
+      </c>
+      <c r="E25" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J25" t="n">
+        <v>3</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
         <v>2</v>
       </c>
-      <c r="R23" t="n">
-        <v>1</v>
-      </c>
-      <c r="S23" t="n">
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
         <v>3</v>
       </c>
-      <c r="T23" t="n">
-        <v>3</v>
-      </c>
-      <c r="U23" t="n">
-        <v>2</v>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>Igelkott
-Desmeknopp
-Myskmadra</t>
-        </is>
-      </c>
-      <c r="W23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 905-2024 artfynd.xlsx", "A 905-2024")</f>
-        <v/>
-      </c>
-      <c r="X23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 905-2024 karta.png", "A 905-2024")</f>
-        <v/>
-      </c>
-      <c r="Y23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 905-2024 georefererad karta.tif", "A 905-2024")</f>
-        <v/>
-      </c>
-      <c r="AA23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 905-2024 FSC-klagomål.docx", "A 905-2024")</f>
-        <v/>
-      </c>
-      <c r="AB23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 905-2024 FSC-klagomål mail.docx", "A 905-2024")</f>
-        <v/>
-      </c>
-      <c r="AC23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 905-2024 tillsynsbegäran.docx", "A 905-2024")</f>
-        <v/>
-      </c>
-      <c r="AD23">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 905-2024 tillsynsbegäran mail.docx", "A 905-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>A 3317-2026</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="n">
-        <v>46041</v>
-      </c>
-      <c r="E24" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J24" t="n">
-        <v>3</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>2</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>2</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3</v>
-      </c>
-      <c r="T24" t="n">
+      <c r="T25" t="n">
         <v>6</v>
       </c>
-      <c r="U24" t="n">
+      <c r="U25" t="n">
         <v>6</v>
       </c>
-      <c r="V24" s="2" t="inlineStr">
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>Entita
 Mindre hackspett
 Gröngöling</t>
         </is>
       </c>
-      <c r="W24">
+      <c r="W25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 3317-2026 artfynd.xlsx", "A 3317-2026")</f>
         <v/>
       </c>
-      <c r="X24">
+      <c r="X25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 3317-2026 karta.png", "A 3317-2026")</f>
         <v/>
       </c>
-      <c r="Y24">
+      <c r="Y25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 3317-2026 georefererad karta.tif", "A 3317-2026")</f>
         <v/>
       </c>
-      <c r="AA24">
+      <c r="AA25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 3317-2026 FSC-klagomål.docx", "A 3317-2026")</f>
         <v/>
       </c>
-      <c r="AB24">
+      <c r="AB25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 3317-2026 FSC-klagomål mail.docx", "A 3317-2026")</f>
         <v/>
       </c>
-      <c r="AC24">
+      <c r="AC25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 3317-2026 tillsynsbegäran.docx", "A 3317-2026")</f>
         <v/>
       </c>
-      <c r="AD24">
+      <c r="AD25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 3317-2026 tillsynsbegäran mail.docx", "A 3317-2026")</f>
         <v/>
       </c>
-      <c r="AE24">
+      <c r="AE25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 3317-2026 prioriterade fågelarter.docx", "A 3317-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>A 18559-2025</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="n">
-        <v>45763</v>
-      </c>
-      <c r="E25" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>3</v>
-      </c>
-      <c r="J25" t="n">
-        <v>3</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>2</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>2</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>3</v>
-      </c>
-      <c r="T25" t="n">
-        <v>3</v>
-      </c>
-      <c r="U25" t="n">
-        <v>3</v>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>Grönsångare
-Gulsparv
-Gröngöling</t>
-        </is>
-      </c>
-      <c r="W25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 18559-2025 artfynd.xlsx", "A 18559-2025")</f>
-        <v/>
-      </c>
-      <c r="X25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 18559-2025 karta.png", "A 18559-2025")</f>
-        <v/>
-      </c>
-      <c r="Y25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 18559-2025 georefererad karta.tif", "A 18559-2025")</f>
-        <v/>
-      </c>
-      <c r="AA25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 18559-2025 FSC-klagomål.docx", "A 18559-2025")</f>
-        <v/>
-      </c>
-      <c r="AB25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 18559-2025 FSC-klagomål mail.docx", "A 18559-2025")</f>
-        <v/>
-      </c>
-      <c r="AC25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 18559-2025 tillsynsbegäran.docx", "A 18559-2025")</f>
-        <v/>
-      </c>
-      <c r="AD25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 18559-2025 tillsynsbegäran mail.docx", "A 18559-2025")</f>
-        <v/>
-      </c>
-      <c r="AE25">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 18559-2025 prioriterade fågelarter.docx", "A 18559-2025")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 27544-2024</t>
+          <t>A 74272-2021</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3311,10 +3311,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45474</v>
+        <v>44553</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3327,31 +3327,31 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="J26" t="n">
+        <v>2</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
         <v>1</v>
       </c>
-      <c r="K26" t="n">
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
         <v>1</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -3363,560 +3363,560 @@
         <v>2</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>Entita
+Grönsiska</t>
+        </is>
+      </c>
+      <c r="W26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 74272-2021 artfynd.xlsx", "A 74272-2021")</f>
+        <v/>
+      </c>
+      <c r="X26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 74272-2021 karta.png", "A 74272-2021")</f>
+        <v/>
+      </c>
+      <c r="Y26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 74272-2021 georefererad karta.tif", "A 74272-2021")</f>
+        <v/>
+      </c>
+      <c r="AA26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 74272-2021 FSC-klagomål.docx", "A 74272-2021")</f>
+        <v/>
+      </c>
+      <c r="AB26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 74272-2021 FSC-klagomål mail.docx", "A 74272-2021")</f>
+        <v/>
+      </c>
+      <c r="AC26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 74272-2021 tillsynsbegäran.docx", "A 74272-2021")</f>
+        <v/>
+      </c>
+      <c r="AD26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 74272-2021 tillsynsbegäran mail.docx", "A 74272-2021")</f>
+        <v/>
+      </c>
+      <c r="AE26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 74272-2021 prioriterade fågelarter.docx", "A 74272-2021")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>A 27544-2024</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D27" s="1" t="n">
+        <v>45474</v>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
         <is>
           <t>Västlig hakmossa
 Spillkråka</t>
         </is>
       </c>
-      <c r="W26">
+      <c r="W27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 27544-2024 artfynd.xlsx", "A 27544-2024")</f>
         <v/>
       </c>
-      <c r="X26">
+      <c r="X27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 27544-2024 karta.png", "A 27544-2024")</f>
         <v/>
       </c>
-      <c r="Y26">
+      <c r="Y27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 27544-2024 georefererad karta.tif", "A 27544-2024")</f>
         <v/>
       </c>
-      <c r="AA26">
+      <c r="AA27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 27544-2024 FSC-klagomål.docx", "A 27544-2024")</f>
         <v/>
       </c>
-      <c r="AB26">
+      <c r="AB27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 27544-2024 FSC-klagomål mail.docx", "A 27544-2024")</f>
         <v/>
       </c>
-      <c r="AC26">
+      <c r="AC27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 27544-2024 tillsynsbegäran.docx", "A 27544-2024")</f>
         <v/>
       </c>
-      <c r="AD26">
+      <c r="AD27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 27544-2024 tillsynsbegäran mail.docx", "A 27544-2024")</f>
         <v/>
       </c>
-      <c r="AE26">
+      <c r="AE27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 27544-2024 prioriterade fågelarter.docx", "A 27544-2024")</f>
         <v/>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" t="inlineStr">
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>A 29157-2023</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D28" s="1" t="n">
+        <v>45105</v>
+      </c>
+      <c r="E28" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>2</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>2</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>Entita
+Talltita</t>
+        </is>
+      </c>
+      <c r="W28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 29157-2023 artfynd.xlsx", "A 29157-2023")</f>
+        <v/>
+      </c>
+      <c r="X28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 29157-2023 karta.png", "A 29157-2023")</f>
+        <v/>
+      </c>
+      <c r="Y28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 29157-2023 georefererad karta.tif", "A 29157-2023")</f>
+        <v/>
+      </c>
+      <c r="AA28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 29157-2023 FSC-klagomål.docx", "A 29157-2023")</f>
+        <v/>
+      </c>
+      <c r="AB28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 29157-2023 FSC-klagomål mail.docx", "A 29157-2023")</f>
+        <v/>
+      </c>
+      <c r="AC28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 29157-2023 tillsynsbegäran.docx", "A 29157-2023")</f>
+        <v/>
+      </c>
+      <c r="AD28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 29157-2023 tillsynsbegäran mail.docx", "A 29157-2023")</f>
+        <v/>
+      </c>
+      <c r="AE28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 29157-2023 prioriterade fågelarter.docx", "A 29157-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" t="inlineStr">
         <is>
           <t>A 33520-2025</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="n">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D29" s="1" t="n">
         <v>45841</v>
       </c>
-      <c r="E27" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
+      <c r="E29" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
         <v>2.4</v>
       </c>
-      <c r="J27" t="n">
+      <c r="J29" t="n">
         <v>1</v>
       </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
         <v>1</v>
       </c>
-      <c r="M27" t="n">
+      <c r="M29" t="n">
         <v>1</v>
       </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
         <v>2</v>
       </c>
-      <c r="R27" t="n">
+      <c r="R29" t="n">
         <v>1</v>
       </c>
-      <c r="S27" t="n">
+      <c r="S29" t="n">
         <v>2</v>
       </c>
-      <c r="T27" t="n">
+      <c r="T29" t="n">
         <v>2</v>
       </c>
-      <c r="U27" t="n">
+      <c r="U29" t="n">
         <v>2</v>
       </c>
-      <c r="V27" s="2" t="inlineStr">
+      <c r="V29" s="2" t="inlineStr">
         <is>
           <t>Småvänderot
 Entita</t>
         </is>
       </c>
-      <c r="W27">
+      <c r="W29">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 33520-2025 artfynd.xlsx", "A 33520-2025")</f>
         <v/>
       </c>
-      <c r="X27">
+      <c r="X29">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 33520-2025 karta.png", "A 33520-2025")</f>
         <v/>
       </c>
-      <c r="Y27">
+      <c r="Y29">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 33520-2025 georefererad karta.tif", "A 33520-2025")</f>
         <v/>
       </c>
-      <c r="AA27">
+      <c r="AA29">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 33520-2025 FSC-klagomål.docx", "A 33520-2025")</f>
         <v/>
       </c>
-      <c r="AB27">
+      <c r="AB29">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 33520-2025 FSC-klagomål mail.docx", "A 33520-2025")</f>
         <v/>
       </c>
-      <c r="AC27">
+      <c r="AC29">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 33520-2025 tillsynsbegäran.docx", "A 33520-2025")</f>
         <v/>
       </c>
-      <c r="AD27">
+      <c r="AD29">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 33520-2025 tillsynsbegäran mail.docx", "A 33520-2025")</f>
         <v/>
       </c>
-      <c r="AE27">
+      <c r="AE29">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 33520-2025 prioriterade fågelarter.docx", "A 33520-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>A 29157-2023</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D28" s="1" t="n">
-        <v>45105</v>
-      </c>
-      <c r="E28" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I28" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="J28" t="n">
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>S 687-2024</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Askåterföring</t>
+        </is>
+      </c>
+      <c r="D30" s="1" t="n">
+        <v>45359</v>
+      </c>
+      <c r="E30" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>37.1</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
         <v>2</v>
       </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
         <v>2</v>
       </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
+      <c r="T30" t="n">
+        <v>4</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>Skuggmossa
+Stubbspretmossa</t>
+        </is>
+      </c>
+      <c r="W30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/S 687-2024 artfynd.xlsx", "S 687-2024")</f>
+        <v/>
+      </c>
+      <c r="X30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/S 687-2024 karta.png", "S 687-2024")</f>
+        <v/>
+      </c>
+      <c r="Y30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/S 687-2024 georefererad karta.tif", "S 687-2024")</f>
+        <v/>
+      </c>
+      <c r="AA30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/S 687-2024 FSC-klagomål.docx", "S 687-2024")</f>
+        <v/>
+      </c>
+      <c r="AB30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/S 687-2024 FSC-klagomål mail.docx", "S 687-2024")</f>
+        <v/>
+      </c>
+      <c r="AC30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/S 687-2024 tillsynsbegäran.docx", "S 687-2024")</f>
+        <v/>
+      </c>
+      <c r="AD30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/S 687-2024 tillsynsbegäran mail.docx", "S 687-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>S 4248-2024</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Askåterföring</t>
+        </is>
+      </c>
+      <c r="D31" s="1" t="n">
+        <v>45582</v>
+      </c>
+      <c r="E31" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>SKÅNE LÄN</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>ÄNGELHOLM</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="J31" t="n">
         <v>2</v>
       </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="n">
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
         <v>2</v>
       </c>
-      <c r="T28" t="n">
+      <c r="T31" t="n">
         <v>2</v>
       </c>
-      <c r="U28" t="n">
-        <v>2</v>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>Entita
-Talltita</t>
-        </is>
-      </c>
-      <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 29157-2023 artfynd.xlsx", "A 29157-2023")</f>
-        <v/>
-      </c>
-      <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 29157-2023 karta.png", "A 29157-2023")</f>
-        <v/>
-      </c>
-      <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 29157-2023 georefererad karta.tif", "A 29157-2023")</f>
-        <v/>
-      </c>
-      <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 29157-2023 FSC-klagomål.docx", "A 29157-2023")</f>
-        <v/>
-      </c>
-      <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 29157-2023 FSC-klagomål mail.docx", "A 29157-2023")</f>
-        <v/>
-      </c>
-      <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 29157-2023 tillsynsbegäran.docx", "A 29157-2023")</f>
-        <v/>
-      </c>
-      <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 29157-2023 tillsynsbegäran mail.docx", "A 29157-2023")</f>
-        <v/>
-      </c>
-      <c r="AE28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 29157-2023 prioriterade fågelarter.docx", "A 29157-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" ht="15" customHeight="1">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>A 74272-2021</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D29" s="1" t="n">
-        <v>44553</v>
-      </c>
-      <c r="E29" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I29" t="n">
-        <v>5</v>
-      </c>
-      <c r="J29" t="n">
-        <v>2</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>1</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>1</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2</v>
-      </c>
-      <c r="U29" t="n">
-        <v>2</v>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
         <is>
           <t>Entita
 Grönsiska</t>
         </is>
       </c>
-      <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 74272-2021 artfynd.xlsx", "A 74272-2021")</f>
-        <v/>
-      </c>
-      <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 74272-2021 karta.png", "A 74272-2021")</f>
-        <v/>
-      </c>
-      <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 74272-2021 georefererad karta.tif", "A 74272-2021")</f>
-        <v/>
-      </c>
-      <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 74272-2021 FSC-klagomål.docx", "A 74272-2021")</f>
-        <v/>
-      </c>
-      <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 74272-2021 FSC-klagomål mail.docx", "A 74272-2021")</f>
-        <v/>
-      </c>
-      <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 74272-2021 tillsynsbegäran.docx", "A 74272-2021")</f>
-        <v/>
-      </c>
-      <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 74272-2021 tillsynsbegäran mail.docx", "A 74272-2021")</f>
-        <v/>
-      </c>
-      <c r="AE29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/fåglar/A 74272-2021 prioriterade fågelarter.docx", "A 74272-2021")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" ht="15" customHeight="1">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>S 687-2024</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Askåterföring</t>
-        </is>
-      </c>
-      <c r="D30" s="1" t="n">
-        <v>45359</v>
-      </c>
-      <c r="E30" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I30" t="n">
-        <v>37.1</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" t="n">
-        <v>2</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
-        <v>2</v>
-      </c>
-      <c r="T30" t="n">
-        <v>4</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>Skuggmossa
-Stubbspretmossa</t>
-        </is>
-      </c>
-      <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/S 687-2024 artfynd.xlsx", "S 687-2024")</f>
-        <v/>
-      </c>
-      <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/S 687-2024 karta.png", "S 687-2024")</f>
-        <v/>
-      </c>
-      <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/S 687-2024 georefererad karta.tif", "S 687-2024")</f>
-        <v/>
-      </c>
-      <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/S 687-2024 FSC-klagomål.docx", "S 687-2024")</f>
-        <v/>
-      </c>
-      <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/S 687-2024 FSC-klagomål mail.docx", "S 687-2024")</f>
-        <v/>
-      </c>
-      <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/S 687-2024 tillsynsbegäran.docx", "S 687-2024")</f>
-        <v/>
-      </c>
-      <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/S 687-2024 tillsynsbegäran mail.docx", "S 687-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" ht="15" customHeight="1">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>S 4248-2024</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Askåterföring</t>
-        </is>
-      </c>
-      <c r="D31" s="1" t="n">
-        <v>45582</v>
-      </c>
-      <c r="E31" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>ÄNGELHOLM</t>
-        </is>
-      </c>
-      <c r="I31" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="J31" t="n">
-        <v>2</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
-        <v>1</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>1</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" s="2" t="inlineStr">
-        <is>
-          <t>Entita
-Grönsiska</t>
-        </is>
-      </c>
       <c r="W31">
         <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/S 4248-2024 artfynd.xlsx", "S 4248-2024")</f>
         <v/>
@@ -3970,7 +3970,7 @@
         <v>44839</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>44742</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4180,7 +4180,7 @@
         <v>44746</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 12150-2024</t>
+          <t>A 44062-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4286,10 +4286,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45377</v>
+        <v>44839</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4302,19 +4302,19 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -4326,10 +4326,10 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4342,35 +4342,35 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 12150-2024 artfynd.xlsx", "A 12150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 44062-2022 artfynd.xlsx", "A 44062-2022")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 12150-2024 karta.png", "A 12150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 44062-2022 karta.png", "A 44062-2022")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 12150-2024 georefererad karta.tif", "A 12150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 44062-2022 georefererad karta.tif", "A 44062-2022")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 12150-2024 FSC-klagomål.docx", "A 12150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 44062-2022 FSC-klagomål.docx", "A 44062-2022")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 12150-2024 FSC-klagomål mail.docx", "A 12150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 44062-2022 FSC-klagomål mail.docx", "A 44062-2022")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 12150-2024 tillsynsbegäran.docx", "A 12150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 44062-2022 tillsynsbegäran.docx", "A 44062-2022")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 12150-2024 tillsynsbegäran mail.docx", "A 12150-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 44062-2022 tillsynsbegäran mail.docx", "A 44062-2022")</f>
         <v/>
       </c>
     </row>
@@ -4394,7 +4394,7 @@
         <v>45323</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4482,7 +4482,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 46487-2024</t>
+          <t>A 61094-2021</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4496,10 +4496,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45582</v>
+        <v>44498</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4512,13 +4512,13 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
         <v>1</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -4552,35 +4552,35 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="W37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 46487-2024 artfynd.xlsx", "A 46487-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 61094-2021 artfynd.xlsx", "A 61094-2021")</f>
         <v/>
       </c>
       <c r="X37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 46487-2024 karta.png", "A 46487-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 61094-2021 karta.png", "A 61094-2021")</f>
         <v/>
       </c>
       <c r="Y37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 46487-2024 georefererad karta.tif", "A 46487-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 61094-2021 georefererad karta.tif", "A 61094-2021")</f>
         <v/>
       </c>
       <c r="AA37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 46487-2024 FSC-klagomål.docx", "A 46487-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 61094-2021 FSC-klagomål.docx", "A 61094-2021")</f>
         <v/>
       </c>
       <c r="AB37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 46487-2024 FSC-klagomål mail.docx", "A 46487-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 61094-2021 FSC-klagomål mail.docx", "A 61094-2021")</f>
         <v/>
       </c>
       <c r="AC37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 46487-2024 tillsynsbegäran.docx", "A 46487-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 61094-2021 tillsynsbegäran.docx", "A 61094-2021")</f>
         <v/>
       </c>
       <c r="AD37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 46487-2024 tillsynsbegäran mail.docx", "A 46487-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 61094-2021 tillsynsbegäran mail.docx", "A 61094-2021")</f>
         <v/>
       </c>
     </row>
@@ -4604,7 +4604,7 @@
         <v>45210</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4709,7 +4709,7 @@
         <v>45462</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4797,7 +4797,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 61094-2021</t>
+          <t>A 46487-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4811,10 +4811,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44498</v>
+        <v>45582</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4827,13 +4827,13 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -4867,42 +4867,42 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="W40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 61094-2021 artfynd.xlsx", "A 61094-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 46487-2024 artfynd.xlsx", "A 46487-2024")</f>
         <v/>
       </c>
       <c r="X40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 61094-2021 karta.png", "A 61094-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 46487-2024 karta.png", "A 46487-2024")</f>
         <v/>
       </c>
       <c r="Y40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 61094-2021 georefererad karta.tif", "A 61094-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 46487-2024 georefererad karta.tif", "A 46487-2024")</f>
         <v/>
       </c>
       <c r="AA40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 61094-2021 FSC-klagomål.docx", "A 61094-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 46487-2024 FSC-klagomål.docx", "A 46487-2024")</f>
         <v/>
       </c>
       <c r="AB40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 61094-2021 FSC-klagomål mail.docx", "A 61094-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 46487-2024 FSC-klagomål mail.docx", "A 46487-2024")</f>
         <v/>
       </c>
       <c r="AC40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 61094-2021 tillsynsbegäran.docx", "A 61094-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 46487-2024 tillsynsbegäran.docx", "A 46487-2024")</f>
         <v/>
       </c>
       <c r="AD40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 61094-2021 tillsynsbegäran mail.docx", "A 61094-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 46487-2024 tillsynsbegäran mail.docx", "A 46487-2024")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 44062-2022</t>
+          <t>A 12150-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44839</v>
+        <v>45377</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4932,20 +4932,20 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
         <v>1</v>
       </c>
-      <c r="L41" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" t="n">
-        <v>0</v>
-      </c>
       <c r="N41" t="n">
         <v>0</v>
       </c>
@@ -4956,10 +4956,10 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -4972,35 +4972,35 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 44062-2022 artfynd.xlsx", "A 44062-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/artfynd/A 12150-2024 artfynd.xlsx", "A 12150-2024")</f>
         <v/>
       </c>
       <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 44062-2022 karta.png", "A 44062-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor/A 12150-2024 karta.png", "A 12150-2024")</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 44062-2022 georefererad karta.tif", "A 44062-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/kartor_geotiff/A 12150-2024 georefererad karta.tif", "A 12150-2024")</f>
         <v/>
       </c>
       <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 44062-2022 FSC-klagomål.docx", "A 44062-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomål/A 12150-2024 FSC-klagomål.docx", "A 12150-2024")</f>
         <v/>
       </c>
       <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 44062-2022 FSC-klagomål mail.docx", "A 44062-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/klagomålsmail/A 12150-2024 FSC-klagomål mail.docx", "A 12150-2024")</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 44062-2022 tillsynsbegäran.docx", "A 44062-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsyn/A 12150-2024 tillsynsbegäran.docx", "A 12150-2024")</f>
         <v/>
       </c>
       <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 44062-2022 tillsynsbegäran mail.docx", "A 44062-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1292/tillsynsmail/A 12150-2024 tillsynsbegäran mail.docx", "A 12150-2024")</f>
         <v/>
       </c>
     </row>
@@ -5024,7 +5024,7 @@
         <v>46188</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5129,7 +5129,7 @@
         <v>46265</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5238,7 +5238,7 @@
         <v>46224</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         <v>45084</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5448,7 +5448,7 @@
         <v>44862</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5553,7 +5553,7 @@
         <v>44880</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5626,7 +5626,7 @@
         <v>44839</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5699,7 +5699,7 @@
         <v>44725</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5772,7 +5772,7 @@
         <v>44840</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5828,7 +5828,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 61263-2021</t>
+          <t>A 15046-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5842,10 +5842,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44498</v>
+        <v>44657</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5858,7 +5858,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5901,7 +5901,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 56094-2021</t>
+          <t>A 61263-2021</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5915,10 +5915,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44477</v>
+        <v>44498</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5931,7 +5931,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5974,7 +5974,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 15046-2022</t>
+          <t>A 11775-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5988,10 +5988,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44657</v>
+        <v>44634</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6004,7 +6004,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -6047,7 +6047,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 11775-2022</t>
+          <t>A 36036-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6061,10 +6061,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44634</v>
+        <v>44802</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6120,7 +6120,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 36036-2022</t>
+          <t>A 36041-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6137,7 +6137,7 @@
         <v>44802</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6150,7 +6150,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -6193,7 +6193,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 36041-2022</t>
+          <t>A 56094-2021</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6207,10 +6207,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44802</v>
+        <v>44477</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6223,7 +6223,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -6266,7 +6266,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 41725-2022</t>
+          <t>A 56569-2021</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6280,10 +6280,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44827</v>
+        <v>44480</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6296,7 +6296,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.2</v>
+        <v>2.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6339,7 +6339,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 56569-2021</t>
+          <t>A 41725-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6353,10 +6353,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44480</v>
+        <v>44827</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6369,7 +6369,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2.4</v>
+        <v>0.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6429,7 +6429,7 @@
         <v>44634</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 29436-2024</t>
+          <t>A 44448-2023</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6499,10 +6499,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45483</v>
+        <v>45189</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6515,7 +6515,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>4.2</v>
+        <v>0.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6558,7 +6558,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 8882-2025</t>
+          <t>A 28496-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6572,10 +6572,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45713</v>
+        <v>45103</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6588,7 +6588,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -6631,7 +6631,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 12148-2024</t>
+          <t>A 1299-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6645,10 +6645,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45377</v>
+        <v>45303</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
